--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10584,6 +10584,1926 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>12001</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>선의의 점유자라도 본권에 관한 소에서 패소한 때에는 그 소가 제기된 때부터 악의의 점유자로 보며, '소가 제기된 때'란 소장 부본이 피고에게 송달된 때를 말한다.</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>민법 제197조 제2항의 효과이고, 판례는 '소가 제기된 때'를 소송계속 시점인 소장 부본 송달 시로 본다.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>민법 제197조② · 대판 2016.12.29. 2016다242273</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>제197조</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>12002</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>점유물이 점유자의 책임 있는 사유로 멸실된 경우, 소유의 의사가 없는 점유자는 선의라면 이익이 현존하는 한도에서만 배상하면 된다.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>주체혼동</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>제202조는 선의 점유자의 현존이익 배상을 자주점유자에 한정하고, 소유의 의사가 없는 점유자(타주점유자)는 선의라도 손해 전부를 배상하도록 정한다.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>민법 제202조</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>제202조</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>12003</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>과실을 취득한 선의의 점유자는 회복자에 대하여 통상의 필요비의 상환을 청구하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>상환제한</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>민법 제203조 제1항 단서의 명문 규정이다. 과실수취권과 통상필요비 상환은 양립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>민법 제203조① 단서</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>제203조</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>12004</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>점유자의 필요비·유익비 상환청구권은 회복자로부터 점유물의 반환을 청구받은 때에 비로소 행사할 수 있는 상태가 되어 이행기가 도래한다.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>행사시기</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>제203조가 '점유물을 반환할 때' 상환을 청구할 수 있다고 정하므로, 판례는 반환청구를 받은 때 비로소 행사 가능하고 이행기가 도래한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>대판 2011.12.13. 2009다5162</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>제203조</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>12005</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>악의의 점유자는 수취한 과실을 반환하여야 하며, 과실을 소비한 경우에는 그 과실의 대가를 보상하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>반환범위</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>민법 제201조 제2항의 명문 규정으로, 폭력 또는 은비에 의한 점유자에게도 준용된다.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>민법 제201조②③</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>제201조</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>12006</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>피성년후견인인 양부모는 성년후견인의 동의를 받아 파양을 협의할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>능력보충</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>민법 제902조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>민법 제902조</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>제902조</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>12007</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>조부모는 이미 손자녀와 혈족관계에 있으므로 손자녀를 입양할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>반대결론</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>판례(전합)는 민법이 존속 외 혈족의 입양을 금지하지 않으므로(제877조 참조) 입양 요건을 갖추고 자녀의 복리에 부합하면 조부모의 손자녀 입양을 허가할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>대결 2021.12.23. 2018스5 전합</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>제877조</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>12008</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>성년자가 양자가 되려는 경우 부모의 동의를 받아야 하고, 부모가 정당한 이유 없이 동의를 거부하면 가정법원이 동의를 갈음하는 심판을 할 수 있으며 이 경우 부모를 심문하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>절차요건</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>민법 제871조 제1항·제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>민법 제871조</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>제871조</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>12009</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>13세 이상의 미성년 양자에게 재판상 파양 사유가 발생한 경우, 입양에 동의하였던 부모가 소재불명이어도 그 동의 없이는 파양을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>예외누락</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>제906조 제2항 단서는 부모가 사망하거나 그 밖의 사유로 동의할 수 없는 경우 동의 없이 파양을 청구할 수 있다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>민법 제906조②</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>제906조</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>12010</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>부부가 공동으로 입양한 후 양부가 사망한 때에는, 양모는 단독으로 양자와 협의상 또는 재판상 파양을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>공동원칙예외</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>판례는 부부공동입양 원칙에도 불구하고 양친 일방이 사망한 때에는 공동파양 원칙이 적용될 여지가 없어 양모의 단독 파양이 가능하다고 한다(다만 사망한 양부와의 양친자관계에는 영향이 없다).</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>판례 · 민법 제874조</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>제874조</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>12011</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>주위토지통행권의 범위는 현재 토지의 용법에 따른 이용 범위에서 인정될 뿐, 장래의 이용상황까지 미리 대비하여 정할 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>범위기준</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>판례는 건축 관련 법령상 도로 폭 규정만으로 그에 일치하는 통행권이 당연히 생기지 않고, 통행권 범위는 현재의 용법 기준으로 정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>대판 2006.10.26. 2005다30993</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>제219조</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>12012</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>공로에 통할 수 있는 자기의 공유토지가 있는 경우, 그 공로에 접하는 부분을 구분소유적 공유관계의 다른 공유자가 배타적으로 사용·수익하고 있다면 타인의 토지에 대한 주위토지통행권이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>요건누락</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>판례는 공로에 통할 수 있는 자기의 공유토지가 있으면 타인 토지 통행은 허용될 수 없고, 구분소유적 공유관계에서 다른 공유자가 배타적으로 사용 중이어도 마찬가지라고 한다.</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>대판 2021.9.30. 2021다245443</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>제219조</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>12013</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>토지의 분할로 인하여 공로에 통하지 못하는 토지가 생긴 때에는, 그 토지소유자는 다른 분할자의 토지를 보상 없이 통행할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>무상통행</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>민법 제220조 제1항의 명문 규정으로, 일부 양도의 경우에도 준용된다.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>민법 제220조</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>제220조</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>12014</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>주위토지통행권의 통행로는 통행지역권과 마찬가지로 항상 특정한 장소로 고정된다.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>개념혼동</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>판례는 주위토지통행권의 통행로는 고정되지 않으며, 주위토지 소유자가 토지 사용방법을 바꾸면 손해가 더 적은 다른 장소로 옮겨 통행해야 할 수도 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>대판 2009.6.11. 2008다75300</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>제219조</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>12015</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>포위된 토지가 사정변경으로 공로에 접하게 되거나 그 소유자가 주위 토지를 취득한 경우, 주위토지통행권은 당연히 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>소멸사유</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>판례는 주위토지통행권이 법정 요건 충족 시 당연히 성립하고 요건이 없어지면 당연히 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>대판 2014.12.24. 2013다11669</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>제219조</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>12016</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>불법행위로 영업용 물건이 멸실된 경우, 대체물을 마련하는 데 필요한 합리적인 기간 동안의 휴업손해는 증명이 가능한 한 통상손해로서 교환가치와 별도로 배상하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>손해분류</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>판례(전합)는 영업용 물건 멸실 시 휴업손해를 특별손해가 아닌 통상손해로 보아 교환가치와 별도 배상을 인정하며, 일부 손괴 시 수리기간 휴업손해도 같다.</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>대판 2004.3.18. 2001다82507 전합</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>12017</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>수급인이 신축한 건물에 하자가 있어 도급인이 정신적 고통을 입은 경우, 하자보수나 손해배상으로 회복될 수 없는 정신적 고통은 특별손해로서 수급인이 그 사정을 알았거나 알 수 있었을 때에 한하여 위자료가 인정된다.</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>손해분류</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>판례는 도급인의 정신적 고통은 원칙적으로 하자보수·손해배상으로 회복되고, 그것으로 회복되지 않는 고통은 특별손해로서 예견가능성이 있어야 배상된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>대판 1996.6.11. 95다12798</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>제393조</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>12018</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>불법행위로 건물이 훼손된 경우 수리가 가능하면 수리비가 통상손해이지만, 수리비가 건물의 교환가치를 초과하는 때에는 손해액은 교환가치 범위 내로 제한된다.</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>배상한도</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>판례는 형평의 원칙상 교환가치 초과 수리비는 교환가치 범위로 제한하고, 수리로 교환가치가 증가하면 증가분을 공제한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>대판 1998.9.8. 98다22048</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>12019</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>매매계약의 이행불능 당시 목적물의 시가가 계약 당시보다 현저하게 앙등되어 있었다면, 그 앙등된 시가 상당액은 특별한 사정으로 인한 손해이다.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>시점혼동</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>판례는 이행불능 당시의 시가 상당액이 통상손해이고, 불능 이후의 시가 등귀만 예견가능성을 요건으로 한 특별손해라고 한다. 계약 당시 대비 앙등 여부는 무관하다.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>대판 1993.5.27. 92다20163</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>제393조</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>12020</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>임대차보증금반환채권이 양도되고 임대인에게 양도통지가 도달한 후에도, 임차인이 목적물을 인도할 때까지 생긴 연체차임 등 임차인의 채무는 보증금에서 당연히 공제된다.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>당연공제</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>보증금반환의무는 목적물 반환 시까지 생긴 임차인의 모든 채무를 공제한 잔액에 관해서만 이행기에 도달하므로, 양도통지 후 발생 채무도 공제된다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>대판 2012.9.27. 2012다49490</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>12021</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>확정일자 있는 채권양도 통지와 채권가압류결정 정본 사이의 우열은 확정일자의 선후가 아니라 채무자(제3채무자)에 대한 도달의 선후에 의하여 결정한다.</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>기준혼동</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>판례(전합)는 채무자의 인식 가능 시점인 도달(승낙) 시를 기준으로 우열을 정하며, 양수인과 가압류채권자 사이에도 같다고 한다.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223 전합</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>12022</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>채권양도 통지와 압류명령이 제3채무자에게 동시에 송달되어 상호 우열이 없는 경우, 제3채무자는 그중 누구에게라도 채무 전액을 변제하면 다른 채권자에 대한 관계에서도 유효하게 면책된다.</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>동시도달</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>판례는 동시도달 시 각 채권자가 모두 완전한 대항력을 갖추므로 전액 이행청구가 가능하고, 채무자는 누구에게든 전액 변제로 면책된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223 전합</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>12023</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>채권에 대한 가압류가 있는 경우, 가압류채무자는 제3채무자를 상대로 그 이행을 구하는 소를 제기할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>효력범위</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>가압류는 채무자가 현실로 급부를 추심하는 것만 금지할 뿐이므로, 가압류채무자는 제3채무자를 상대로 이행의 소를 제기할 수 있다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>판례(채권가압류의 효력)</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>12024</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>채권양도금지특약으로는 선의의 제3자에게 대항할 수 없으나, 양수인이 특약을 알았거나 중대한 과실로 알지 못한 때에는 특약으로 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>주관요건</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>제449조 제2항 단서와 판례는 악의·중과실 양수인에 대한 금지특약의 대항을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>민법 제449조② · 판례</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>12025</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>공동상속인이 다른 공동상속인에게 무상으로 자신의 상속분을 양도한 경우, 특별한 사정이 없는 한 그 상속분은 양도인의 사망으로 인한 상속에서 유류분 산정을 위한 기초재산에 산입된다.</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>실질판단</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>판례는 무상의 상속분 양도가 제1008조의 증여에 해당한다고 보아 유류분 기초재산 산입을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>대판 2021.7.15. 2016다210498</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>제1118조</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>12026</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>유류분 산정의 기초재산에 산입되는 증여에 해당하는지는 재산처분행위의 법적 성질을 형식적·추상적으로 파악할 것이 아니라, 실질적인 관점에서 피상속인의 재산을 감소시키는 무상처분인지에 따라 판단하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>판단기준</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>판례가 무상 상속분 양도의 증여성을 인정하며 제시한 기준이다.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>대판 2021.7.15. 2016다210498</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>제1113조</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>12027</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>피상속인의 생전 증여에 상속인의 특별한 부양 내지 기여에 대한 대가의 의미가 포함되어 있는 경우, 그 증여는 특별수익에서 제외될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>형평고려</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>판례는 생전 증여를 상속분 선급으로 취급하면 오히려 공동상속인 간 실질적 형평을 해치는 경우(특별한 부양·기여의 대가 등) 특별수익에서 제외할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>판례(특별수익의 판단)</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>제1008조</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>12028</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>유류분 부족액을 산정할 때 유류분액에서 공제하는 순상속분액은, 법정상속분이 아니라 특별수익을 고려한 구체적인 상속분에서 유류분권리자가 부담하는 상속채무를 공제하여 산정한다.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>산정기준</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>판례는 유류분 부족액 = 유류분액 − 특별수익액 − 순상속분액이고, 순상속분액은 구체적 상속분 기준으로 상속채무를 공제해 산정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>대판 2022.8.11. 2020다247428</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>제1113조</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>12029</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>유류분권리자의 구체적 상속분보다 그가 부담하는 상속채무가 더 많은 경우 그 초과분을 유류분액에 가산하지만, 유류분권리자가 한정승인을 하였다면 초과분을 가산하지 않고 순상속분액을 0으로 보아 부족액을 산정한다.</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>한정승인</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>한정승인 시 책임이 상속재산으로 한정되므로 초과분 가산은 과잉반환이 된다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>대판 2022.8.11. 2020다247428</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>제1113조</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>12030</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>점유를 침탈당한 자가 본권인 유치권의 소멸에 따른 손해배상청구권을 행사하는 경우에도, 민법 제204조 제3항의 1년 제척기간이 적용된다.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>판례는 제204조 제3항은 점유보호청구권에 적용될 뿐 본권 침해로 인한 손해배상청구에는 적용되지 않으므로 1년 내 행사를 요하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>대판 2021.8.19. 2021다213866</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>제204조</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>12031</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>제3자가 특정인에 대하여만 공로의 통행을 방해하여 일상생활에 지장을 주는 경우, 이는 불법행위에 해당하고 침해받은 자는 통행방해 행위의 금지를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>구제수단</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>판례는 일반 공중의 통행에 공용된 도로에 대한 통행의 자유 침해를 불법행위로 보고 방해배제·예방으로서 금지청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>대판 2021.10.14. 2021다242154</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>12032</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>아내가 혼인 중 제3자의 정자를 제공받아 인공수정으로 임신·출산한 자녀에 대하여도 남편의 자녀라는 친생추정이 미친다.</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>추정범위</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>판례(전합)는 친생추정이 혈연 개연성뿐 아니라 실질적 가족관계 형성 개연성을 전제로 한다는 점 등을 들어 인공수정 자녀에 대한 친생추정을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>대판 2019.10.23. 2016므2510 전합</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>제844조</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>12033</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>혼인 중 아내가 임신하여 출산한 자녀가 남편과 혈연관계가 없다는 점이 밝혀졌다면, 그 자녀에게는 친생추정이 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>반대결론</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>판례(전합)는 혈연관계 부존재가 밝혀졌더라도 친생추정이 미치지 않는다고 볼 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>대판 2019.10.23. 2016므2510 전합</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>제844조</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>12034</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>혼인 중 출생한 인공수정 자녀에 대해서는 다른 명확한 사정의 증명이 없는 한 남편의 동의가 있었던 것으로 볼 수 있고, 그 친자관계를 다투려면 친생자관계부존재확인의 소가 아니라 친생부인의 소에 의하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>판례(전합)는 정상적 혼인생활 중 출생한 인공수정 자녀에 대한 남편의 동의를 사실상 추정하고, 친생추정이 미치는 이상 친생부인의 소에 의하도록 한다.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>대판 2019.10.23. 2016므2510 전합</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>제846조</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>12035</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>계약을 둘러싼 법률관계에서 당사자는 원칙적으로 상대방에게 손실이 발생하지 않도록 상대방의 이익을 보호하거나 배려할 일반적인 의무를 부담하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>자기책임</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>판례(전합)는 자기책임의 원칙상 계약 당사자는 자신의 선택과 결정에 따른 이익·손실을 스스로 감수할 뿐 상대방 이익 보호의 일반적 의무는 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>대판 2014.8.21. 2010다92438 전합</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>12036</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>카지노사업자가 공익상 포괄적인 영업 규제를 받고 있다는 사정이 있으면, 그것만으로 카지노이용자의 이익을 위한 보호의무 내지 배려의무가 인정된다.</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>근거부족</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>판례(전합)는 포괄적 영업 규제를 근거로 함부로 보호의무를 인정할 수 없고, 도박 중독 인식 + 가족의 요청 묵살 + 영업제한 위반 등 특별한 사정이 있는 경우에만 예외적으로 책임을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>대판 2014.8.21. 2010다92438 전합</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>12037</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>병원은 입원환자의 휴대품 도난을 방지하기 위하여 출입자 통제 또는 시정장치 있는 사물함 제공 등 적절한 조치를 강구할 신의칙상 보호의무가 있고, 이를 소홀히 하여 도난이 발생하면 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>부수의무</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>판례는 입원계약상 병원이 숙식·간호·보호 등 포괄적 채무를 지므로 휴대품 도난 방지의 신의칙상 보호의무를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>대판 2003.4.11. 2002다63275</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>12038</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>숙박업자는 일시사용을 위한 임대차계약인 숙박계약의 성질상 투숙객의 안전을 배려할 신의칙상 보호의무를 부담한다.</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>부수의무</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>판례는 숙박업자에게 고객의 안전을 배려할 보호의무를 인정하고, 위반 시 불완전이행으로 인한 채무불이행책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>판례(숙박계약의 안전배려의무)</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>12039</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>이자제한법의 최고이자율 제한 규정은 금전대차에 관한 계약상의 이자에 적용될 뿐, 계약 위반을 제재하기 위한 위약벌에는 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>판례는 위약벌은 이자가 아니므로 이자제한법의 적용 대상이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>대판 2017.11.29. 2016다259769</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>12040</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>채권자가 고의 또는 과실로 최고이자율을 초과하는 이자를 받은 경우, 초과 지급액에 대하여 부당이득반환청구권이 인정되는 이상 별도로 불법행위는 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>청구권경합</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>판례는 원본 충당 후 남는 초과 지급액은 이자제한법 위반으로 인한 손해로서 불법행위가 성립하고, 부당이득반환청구권의 존재가 불법행위 성립을 방해하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>대판 2021.2.25. 2020다230239</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>12041</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>이자제한법을 위반하여 제한초과이자를 받은 채권자와 공동으로 위반행위를 하였거나 이에 가담한 자는 민법 제760조에 따라 연대하여 손해를 배상할 책임이 있다.</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>공동불법행위</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>판례는 이자제한법 위반에 공동·가담한 자의 공동불법행위책임을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>대판 2021.2.25. 2020다230239</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>12042</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>선이자를 사전에 공제한 경우 제한이자율 초과 여부는 채무자가 실제로 받은 금액을 원본으로 하여 판단하고, 초과 부분이 있으면 약정된 공제 전 대부원금에 충당된다.</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>산정기준</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>판례는 실수령액 기준으로 제한이율 초과 여부를 판단하고 초과분은 원금에 충당되어 충당 후 잔액이 변제기에 갚을 원금이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>대판 2014.11.13. 2014다24785</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>제379조</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>12043</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>복리약정은 이자제한법상 최고이자율을 초과하는 부분에 한하여 무효이다.</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>일부무효</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>판례는 복리약정 전체가 아니라 최고이율 초과 부분만 무효로 본다.</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>대판 2008.10.23. 2008다37742</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>제379조</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>12044</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>민법상 사단법인·재단법인의 정관 변경은 주무관청의 허가를 얻지 아니하면 그 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>효력요건</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>민법 제42조 제2항(재단법인은 제45조 제3항에서 준용)의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>민법 제42조②·제45조③</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>제42조</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>12045</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>민법상 사단법인은 정관에 다른 규정이 없는 한 총사원 4분의 3 이상의 동의가 없으면 해산을 결의하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>정족수</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>민법 제78조의 명문 규정이다(정관 우선).</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>민법 제78조</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>제78조</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>12046</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>법인이 채무를 완제하지 못하게 된 때에는 이사는 지체 없이 파산신청을 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>이사의무</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>민법 제79조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>민법 제79조</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>제79조</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>12047</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>이사가 없거나 결원이 있는 경우에 이로 인하여 손해가 생길 염려가 있는 때에는, 법원은 이해관계인이나 검사의 청구에 의하여 임시이사를 선임하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>선임요건</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>민법 제63조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>민법 제63조</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>제63조</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>12048</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>변시12</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>민법상 법인에서 이사는 임의기관이므로 정관으로 정하면 이사를 두지 않을 수 있다.</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>필수기관</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>민법 제57조는 '법인은 이사를 두어야 한다'고 정하므로 이사는 필수기관이다.</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>민법 제57조</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>제57조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12504,6 +12504,5046 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>신축건물의 도급인이 민법 제666조에 따른 수급인의 저당권설정청구권 행사에 따라 공사대금채무 담보로 그 건물에 저당권을 설정하는 행위는 특별한 사정이 없는 한 사해행위에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>사해성판단</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>판례는 제666조의 취지상 수급인의 지위가 유치권자보다 강화되는 것이 아니어서 일반채권자에게 부당하게 불리하지 않다는 이유로 사해행위성을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>대판 2008.3.27. 2007다78616</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>제666조</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>공사도급계약이 해제·해지된 경우, 도급인의 별도 상계 의사표시가 없으면 기성고에 해당하는 미지급 공사대금은 선급금으로 충당되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>당연충당</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>판례는 선급금은 전체 공사 관련 공사대금의 일부이므로 해제·해지 시 별도 상계 의사표시 없이 미지급 공사대금에 당연 충당된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>대판 2017.1.12. 2014다11574</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>제664조</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>임차인의 건물매수청구권 행사 시 건물에 근저당권이 설정되어 있으면, 그 매수가격은 시가에서 피담보채무액을 공제한 금액으로 정한다.</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>공제여부</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>판례는 매수가격은 현존 상태의 시가 상당액이고 채권최고액·피담보채무액을 공제하지 않으며, 다만 토지소유자는 근저당권 말소 시까지 채권최고액 상당 대금 지급을 거절할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>대판 2008.5.29. 2007다4356</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>건물 소유 목적 토지임차인이 신축한 건물을 제3자에게 매각한 경우에도, 임차인은 임대인에 대하여 지상물매수청구권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>행사주체</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>판례는 제643조의 지상물매수청구권은 지상물의 소유자에 한하여 행사할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>대판 1993.7.27. 93다6386</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>비법인사단의 대표자가 타인에게 업무를 포괄적으로 위임한 경우, 그 수임인의 대행행위는 비법인사단에 효력이 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>복임제한</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>제62조의 유추적용상 대표자는 특정한 행위만 대리하게 할 수 있을 뿐 포괄적 위임은 허용되지 않는다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>대판 1996.9.6. 94다18522</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>제62조</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>비법인사단의 채권자가 비법인사단의 총유재산에 관한 권리를 대위행사하는 경우에는 사원총회의 결의 등 내부 의사결정절차를 거칠 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>절차요부</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위권 행사에는 비법인사단의 내부절차가 요구되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>대판 2014.9.25. 2014다211336</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>비법인사단 대표자의 행위가 개인의 이익을 도모하기 위한 것이거나 법령에 위반된 것이라도, 외관상·객관적으로 직무에 관한 행위로 인정되면 제35조 제1항의 '직무에 관하여'에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>외형이론</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>판례는 비법인사단에 제35조 제1항을 유추적용하며 직무관련성을 외형상 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>대판 2003.7.25. 2002다27088</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>비법인사단이 총유물 매매계약으로 부담하는 채무의 존재를 인식하고 있다는 뜻을 표시하는 소멸시효 중단사유로서의 승인도 총유물의 관리·처분행위이므로 사원총회의 결의를 거쳐야 한다.</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>개념혼동</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>판례는 시효중단 사유인 승인은 총유물 자체의 관리·처분이 따르는 행위가 아니므로 총유물의 관리·처분행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>대판 2009.11.26. 2009다64383</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>비법인사단인 재건축조합의 조합장이 조합규약상 임원회의나 총회 결의를 거치지 않고 채무보증계약을 체결하였다면, 그 보증계약은 그것만으로 무효이다.</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>효력판단</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>판례는 내부 결의 흠결만으로 바로 보증계약이 무효라고 할 수 없다고 한다(총유물 처분이 아닌 채무부담행위).</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>대판 2007.4.19. 2004다60072</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>의사능력의 유무는 일률적으로 정할 것이 아니라 구체적인 법률행위와 관련하여 개별적으로 판단하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>판단기준</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>판례는 의사능력을 자기 행위의 의미·결과를 합리적으로 판단할 정신적 능력으로 보고 행위별 개별 판단을 요구한다.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>대판 2002.10.11. 2001다10113</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>제9조</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>제한능력자 제도는 거래의 안전을 희생시키더라도 제한능력자를 보호하고자 함에 근본적인 입법 취지가 있다.</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>제도취지</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>판례는 행위무능력자 제도의 입법취지를 거래안전의 희생 위에서의 무능력자 보호로 명시한다.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>대판 2007.11.16. 2005다71659</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>제5조</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>피성년후견인의 법률행위는 취소할 수 있으나, 일용품의 구입 등 일상생활에 필요하고 그 대가가 과도하지 아니한 법률행위는 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>취소제한</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>민법 제10조 제1항·제4항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>민법 제10조</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>제10조</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>임의후견인의 대리권 소멸은 등기하지 아니하면 선의의 제3자에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>민법 제959조의19의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>민법 제959조의19</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>제959조의19</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>미성년후견인은 한 명으로 하여야 하지만, 성년후견인은 여러 명을 둘 수 있고 법인도 성년후견인이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>수와자격</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>민법 제930조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>민법 제930조</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>제930조</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>사해행위취소의 소에서 보전하고자 하는 채권을 추가하거나 교환하는 것은 소의 변경이 아니라 공격방법의 변경에 불과하므로, 그로 인해 제척기간 준수 여부가 달라지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>소송물</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>판례는 피보전채권의 추가·교환은 소송물 변경이 아니므로 '안 날로부터 1년' 제척기간을 도과한 것으로 볼 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>대판 2003.5.27. 2001다13532</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>근저당권설정계약이 사해행위로 취소되었으나 이미 경매로 타인이 소유권을 취득하고 등기가 말소되었으며 배당까지 종료된 경우, 배당금을 수령한 수익자에게 그 배당금의 반환을 명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>원상회복방법</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>원물반환이 불가능하므로 가액배상으로서 수익자의 배당금 반환을 명한다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>대판 2004.1.27. 2003다6200</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>사해행위취소소송의 상대방인 수익자는 취소채권자의 채권에 대한 소멸시효 완성을 원용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>원용권자</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>판례는 수익자가 채권 소멸로 직접 이익을 받는 자에 해당하므로 시효원용권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>대판 2007.11.29. 2007다54849</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>채무자의 사해의사가 인정되려면 특정 채권자를 해한다는 인식이 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>요건추가</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>판례는 사해의사는 공동담보 부족 위험에 대한 단순한 인식으로 충분하고 일반 채권자에 대한 관계에서 있으면 족하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>대판 2009.3.26. 2007다63102</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>처분행위 당시에는 채권자를 해하는 것이었더라도, 사실심 변론종결 시까지 채무자가 자력을 회복하였다면 채권자취소권은 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>판단시점</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>판례는 사해성 요건이 행위 당시와 취소권 행사 당시(사실심 변론종결시) 모두 갖춰져야 하므로 자력 회복 시 취소권이 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>대판 2009.3.26. 2007다63102</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>강제경매절차의 기초가 된 채무자 명의의 소유권이전등기가 원인무효여서 경락인이 소유권을 취득하지 못한 경우, 경락인은 제578조에 따라 경매 채무자나 채권자에게 담보책임을 물을 수 있다.</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>구제수단</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>판례는 이 경우 경매 자체가 무효이므로 담보책임은 인정될 여지가 없고, 배당받은 채권자에 대한 일반 부당이득반환청구만 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>대판 2004.6.24. 2003다59259</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>제578조</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>건축을 목적으로 매매된 토지에 건축허가를 받을 수 없는 법률적 제한이 있는 경우 이는 매매목적물의 하자에 해당하고, 그 하자의 존부는 매매계약 성립 시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>판례는 법률적 제한·장애도 물건의 하자로 보며 하자 판단 기준시를 계약 성립 시로 본다.</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>대판 2000.1.18. 98다18506</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>제580조</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>매도인의 담보책임에 기한 손해배상채권의 제척기간이 지난 후에는, 제척기간 경과 전에 상대방 채권과 상계할 수 있었던 경우에도 이를 자동채권으로 상계할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>유추적용</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>판례는 민법 제495조를 유추적용하여 제척기간 경과 전 상계적상에 있었던 담보책임 손해배상채권에 의한 상계를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>대판 2019.3.14. 2018다255648</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>제495조</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>매도인이 폐기물을 은밀히 매립한 토지를 정상 토지인 것처럼 매도한 경우, 불완전이행으로 인한 채무불이행책임과 제580조의 하자담보책임이 경합하여 인정될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>책임경합</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>판례는 채무불이행책임과 하자담보책임의 경합을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>대판 2004.7.22. 2002다51586</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>제580조</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>하자담보책임에 기한 매수인의 손해배상청구권에는 제582조의 제척기간 외에 소멸시효 규정도 적용되며, 그 소멸시효는 매수인이 매매 목적물을 인도받은 때부터 진행한다.</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>기간경합</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>판례는 제척기간 규정이 소멸시효 적용을 배제하지 않으며 시효 기산점을 목적물 인도 시로 본다.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>대판 2011.10.13. 2011다10266</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>제582조</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>민법 제135조에 따른 무권대리인의 상대방에 대한 책임은 대리권 흠결에 관하여 무권대리인에게 과실 등 귀책사유가 있어야 인정된다.</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>책임성질</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>판례는 제135조 책임을 무과실책임으로 보아, 무권대리가 제3자의 기망·문서위조로 야기되었어도 책임이 부정되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>대판 2014.2.27. 2013다213038</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>제135조</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>상대방이 무권대리인에게 계약 이행을 선택하였는데 무권대리인이 이행하지 않는 경우, 계약에 손해배상액 예정 조항이 있으면 무권대리인은 그 조항에 따라 산정한 손해액을 지급하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>배상범위</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>판례는 무권대리인이 계약상 채무불이행 책임을 지며 손해배상액 예정 조항(제398조)도 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>대판 2018.6.28. 2018다210775</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>제135조</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>무권대리행위의 추인은 묵시적인 방법으로도 할 수 있고, 무권대리인이나 상대방뿐 아니라 무권대리행위로 인한 법률관계의 승계인에 대하여도 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>추인방식</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>판례는 추인에 특별한 방식이 요구되지 않고 상대방 범위도 넓게 인정한다.</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>대판 1981.4.14. 80다2314</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>제130조</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>무권대리 계약의 상대방이 유효하게 철회권을 행사한 후에는 본인은 더 이상 무권대리행위를 추인할 수 없고, 상대방이 대리권 없음을 알았다는 점의 증명책임은 철회의 효과를 다투는 본인에게 있다.</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>판례는 유효한 철회로 무권대리행위가 확정적 무효가 되고, 상대방의 악의는 본인이 증명해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>대판 2017.6.29. 2017다213838</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>제134조</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>주채무자의 재산에 대한 압류로 소멸시효가 중단된 경우, 그 압류 사실이 보증인에게 통지되지 않았다면 보증인에 대한 시효중단의 효력은 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>통지요부</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>제440조는 제169조의 예외로서 주채무자에 대한 시효중단 시 별도 조치 없이 보증인에게도 효력이 생기며, 압류 등의 경우에도 통지를 요하지 않는다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>대판 2005.10.27. 2005다35554,35561 · 민법 제440조</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>제440조</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>이행인수인이 채권자에 대하여 채무자의 채무를 승인하더라도, 특별한 사정이 없는 한 소멸시효 중단사유인 채무승인의 효력은 발생하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>승인주체</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>승인은 시효이익을 받을 당사자나 대리인만 할 수 있는데 이행인수인은 채권자에게 직접 의무를 부담하지 않기 때문이라는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>대판 2016.10.27. 2015다239744</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>현존하지 아니하는 장래의 채권에 대하여 미리 승인을 하면 소멸시효 중단의 효력이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>시기제한</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>판례는 승인은 시효 진행 개시 이후에만 가능하고, 장래 채권의 사전 승인은 권리 존재의 인식이 없어 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>대판 2001.11.9. 2001다52568</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 임차권등기명령에 따른 임차권등기에는 압류·가압류·가처분에 준하는 소멸시효 중단의 효력이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>성질혼동</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>판례는 임차권등기는 대항력·우선변제권의 취득·유지를 위한 담보적 기능을 주목적으로 하므로 제168조 제2호의 중단사유에 준하는 효력이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>대판 2019.5.16. 2017다226629</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>토지의 담보가치 저감을 막을 목적으로 근저당권과 함께 채권자 앞으로 설정된 지상권은, 피담보채권이 변제 또는 시효로 소멸하면 그에 부종하여 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>판례는 이른바 담보지상권의 피담보채권 소멸 시 지상권도 부종하여 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>대판 2011.4.14. 2011다6342</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>제279조</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>피담보채권과 함께 근저당권을 양수하여 이전의 부기등기를 마친 자는 채권양도의 대항요건을 갖추지 못하였더라도 경매신청을 할 수 있고, 후순위 근저당권자는 그 대항요건 흠결을 주장할 수 있는 제3자에 포함되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>판례는 대항요건 흠결을 주장할 수 있는 제3자를 양수인과 양립할 수 없는 법률상 지위 취득자로 한정하여 후순위 근저당권자를 제외한다.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>대판 2005.6.23. 2004다29279</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>도박자금 대여로 인한 채권을 담보하기 위하여 근저당권설정등기가 마쳐진 경우, 불법원인급여이므로 등기설정자는 그 말소를 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>종국성</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>판례는 근저당권설정은 수령자가 경매신청 등 별도 조치를 해야 이익을 얻는 것이어서 종국적 급여가 아니므로 설정자의 말소청구를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>대판 1995.8.11. 94다54108</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>매매계약이 해제되어 원상회복으로 이미 지급한 매매대금의 반환을 구하는 경우에도 과실상계가 적용될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>판례는 과실상계는 채무불이행·불법행위 손해배상에 인정되는 것이고 원상회복의무의 이행에는 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>대판 2014.3.13. 2013다34143</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>매매계약 해제 시 매도인의 대금반환의무와 매수인의 말소등기의무가 동시이행관계에 있다면, 매도인은 이행지체가 없는 한 받은 날부터의 법정이자를 가산할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>이자성질</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>제548조 제2항의 이자는 원상회복의 범위에 속하는 부당이득반환의 성질로서 지체책임이 아니므로, 동시이행관계 여부와 무관하게 받은 날부터 가산해야 한다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>대판 2000.6.9. 2000다9123</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>매수인과 매매예약을 체결한 후 그에 기한 소유권이전청구권 보전을 위한 가등기를 마친 사람은 해제의 소급효로부터 보호되는 제548조 제1항 단서의 제3자에 포함된다.</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>판례는 가등기를 마친 매매예약 권리자도 등기로 권리를 취득한 제3자에 해당한다고 본다.</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>대판 2014.12.11. 2013다14569</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>유치권의 행사는 피담보채권의 소멸시효 진행에 영향을 미치지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>민법 제326조의 명문 규정이다. 유치권을 행사 중이어도 채권의 시효는 별도로 진행한다.</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>민법 제326조</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>제326조</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>유치권에 의한 경매는 목적부동산 위의 부담을 매수인이 인수하는 인수주의를 원칙으로 진행된다.</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>매각조건</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>판례는 유치권에 의한 경매도 강제경매·담보권실행경매처럼 부담 소멸주의를 법정매각조건으로 하고, 유치권자는 일반채권자와 동순위로 배당받는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>대결 2011.6.15. 2010마1059</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>제322조</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>채무자 소유의 부동산에 선행저당권이 설정된 후에 상사유치권이 성립한 경우, 상사유치권자는 선행저당권에 기한 경매절차의 매수인에게 유치권으로 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>민상구별</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>판례는 상사유치권이 성립 당시 채무자가 보유한 제한된 담보가치만을 대상으로 하므로 선행저당권자·그 경매 매수인에게 대항할 수 없다고 한다(민사유치권과 구별).</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>대판 2013.2.28. 2010다57350</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>근로계약이 의사표시의 하자를 이유로 취소된 경우에도, 이미 제공된 노무를 기초로 형성된 법률관계는 효력을 잃지 않고 취소 이후 장래에 관하여만 근로계약의 효력이 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>소급제한</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>판례는 계속적 계약인 근로계약의 특성상 취소의 소급효를 제한한다.</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>대판 2017.12.22. 2013다25194,25200</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>제141조</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>매매대금의 과다로 불공정한 법률행위에 해당하여 무효인 매매계약에는 무효행위의 전환에 관한 제138조가 적용될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>전환가부</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>판례는 쌍방이 무효를 알았더라면 다른 대금액으로 합의하였을 것으로 인정되는 경우 그 대금액으로 매매계약이 유효하게 성립한다고 보아 제138조의 적용을 긍정한다.</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>대판 2010.7.15. 2009다50308</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>제138조</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>법률행위의 취소를 당연한 전제로 한 소송상의 이행청구나 이를 전제로 한 이행거절에는 취소의 의사표시가 포함되어 있다고 볼 수 있다.</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>취소방식</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>판례는 취소의 의사표시에 특정한 방식이 요구되지 않으며 상대방이 인식할 수 있으면 족하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>대판 1993.9.14. 93다13162</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>제143조</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>취소할 수 있는 법률행위가 일단 취소된 후에도, 취소할 수 있는 법률행위의 추인에 의하여 이를 다시 확정적으로 유효하게 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>추인시기</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>판례는 취소로 처음부터 무효로 간주된 법률행위는 더 이상 취소할 수 있는 법률행위의 추인 대상이 될 수 없다고 한다(무효행위 추인의 요건을 갖추면 새로운 법률행위로 볼 수 있을 뿐).</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>대판 1997.12.12. 95다38240</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>제143조</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>통정허위표시에서 선의의 제3자로부터 권리를 전득한 자는 자신이 허위표시에 관하여 악의이면 보호받지 못한다.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>엄폐물법칙</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>제3자가 선의이면 허위표시의 흠은 치유되므로 그로부터의 전득자는 선의·악의를 불문하고 보호된다(판례·통설).</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>대판 2013.2.15. 2012다49292</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>점유취득시효 완성으로 등기를 마친 자는 원시취득자이므로, 시효기간 진행 중 마쳐진 가등기로 보전된 매매예약상 매수인의 지위는 소멸하지만, 점유자가 아직 등기를 마치지 않았다면 그러한 부담은 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>등기요건</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>판례는 시효취득의 반사적 효과로 가등기상 지위가 소멸하되 이는 점유자 명의의 등기를 전제로 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>대판 2004.9.24. 2004다31463</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>점유취득시효 완성 당시의 소유권보존등기나 이전등기가 무효인 경우, 시효취득자는 그 등기명의인을 상대로 직접 시효완성을 원인으로 한 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>상대방확정</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>판례는 이전등기청구의 상대방은 시효완성 당시의 진정한 소유자이므로, 무효등기 명의인을 상대로는 청구할 수 없고 소유자를 대위해 말소를 구한 후 소유자에게 청구해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>대판 2005.5.26. 2002다43417</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>부동산 소유자가 시효취득자의 이전등기 청구소송 소장 부본을 송달받는 등으로 시효완성 사실을 알 수 있었던 상태에서 부동산을 제3자에게 처분하여 이전등기의무가 이행불능이 되었다면, 소유자는 시효취득자에게 불법행위로 인한 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>인식요건</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>판례는 시효완성 사실에 대한 인식가능성이 인정되는 처분행위를 등기의무 면탈을 위한 위법행위로 본다.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>대판 1999.9.3. 99다20926</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>취득시효 완성 후 점유자가 등기하기 전에 제3자 명의로 마쳐진 소유권이전등기가 원인무효인 경우, 점유자는 시효완성 당시의 소유자를 대위하여 그 등기의 말소를 구함과 아울러 소유자에게 시효완성을 원인으로 한 이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>대위구성</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>판례는 제3자 명의 등기가 무효인 때에는 시효취득자의 대위말소청구와 이전등기청구를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>대판 2002.3.15. 2001다77352</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>간접점유자도 점유보호청구권을 행사할 수 있고, 직접점유자가 물건의 반환을 받을 수 없거나 원하지 아니하는 때에는 자기에게 반환할 것을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>행사주체</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>민법 제207조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>민법 제207조</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>제207조</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>권원 없이 타인 소유물을 점유한 악의의 수익자는 받은 이익에 이자를 붙여 반환하여야 하지만, 그 이자의 이행지체로 인한 지연손해금까지 지급할 의무는 없다.</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>범위누락</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>판례는 악의 수익자의 반환범위가 제748조 제2항에 따라 정해지므로 이자는 물론 그 이자의 지연손해금도 지급해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>대판 2003.11.14. 2001다61869</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>제748조</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>지상권을 설정해 준 토지소유자는 그 토지의 불법점유자에 대하여 물권적 청구권을 행사할 수 있으나, 특별한 사정이 없는 한 임료 상당의 손해배상은 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>권리분화</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>판례는 지상권 존속 중 토지소유자는 사용·수익할 수 없어 임료 상당 손해가 없다고 보되, 소유권에 기한 방해배제는 인정한다.</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>대판 1974.11.12. 74다1150</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>제213조</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>선대의 점유가 타주점유인 경우, 상속으로 점유를 승계한 상속인이 새로운 권원 없이 소유의 의사를 표시하지 않는 한 그 점유는 자주점유로 전환되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>점유승계</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>판례는 상속인은 새로운 권원 없이는 피상속인의 점유와 분리된 자기만의 점유를 주장할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>대판 1997.5.30. 97다2344</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>제193조</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>점유물반환청구권의 1년 행사기간은 제척기간으로서 그 기간 내에 소를 제기하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>기간성질</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>판례는 제204조 제3항의 1년을 출소기간인 제척기간으로 본다.</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>대판 2021.8.19. 2021다213866</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>제204조</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>점유자가 물건에 대한 사실상의 지배를 상실하면 점유권이 소멸하지만, 점유물반환청구권에 의하여 점유를 회수한 때에는 점유가 계속된 것으로 된다.</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>소멸예외</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>민법 제192조 제2항 단서의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>민법 제192조②</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>제192조</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>양도인이 소유자로부터 보관을 위탁받아 제3자에게 보관시킨 동산을 양도하면서 그 제3자에 대한 반환청구권을 양도하고 지명채권양도의 대항요건을 갖추었다면, 선의취득에 필요한 점유취득 요건을 충족한다.</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>인도방법</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>판례는 목적물반환청구권의 양도에 의한 선의취득을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>대판 1999.1.26. 97다48906</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>제249조</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>토지 또는 지상 건물이 강제경매로 매수인에게 이전되는 경우, 관습법상 법정지상권의 성립요건인 '토지와 건물의 동일인 소유'는 매수인이 매각대금을 완납한 때를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>판례(전합)는 압류의 효력 발생 시(선행 가압류가 있으면 가압류 시, 그보다 앞선 저당권이 있으면 저당권 설정 시)를 기준으로 동일인 소유 여부를 판단한다.</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>대판 2012.10.18. 2010다52140 전합</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>건물에 대한 저당권 실행으로 경락인이 건물의 소유권을 취득한 경우, 경락인은 등기 없이도 그 건물의 소유를 위한 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>등기요부</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>법정지상권은 법률 규정에 의한 물권취득(제187조)이므로 등기 없이 취득한다.</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>민법 제187조 · 판례</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>건물공유자 중 1인이 그 건물의 부지인 토지를 단독으로 소유하면서 토지에 저당권을 설정하였다가 경매로 토지 소유자가 달라진 경우, 건물공유자들을 위한 법정지상권이 성립한다.</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>공유관계</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>판례는 건물공유의 경우 토지소유자가 건물공유자 전원을 위하여 토지 이용을 인정한 것으로 보아 법정지상권 성립을 긍정한다(토지공유의 경우와 구별).</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>판례(건물공유와 법정지상권)</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>미등기건물을 그 대지와 함께 매도하였으나 매수인 앞으로 대지에 관해서만 소유권이전등기가 마쳐진 경우, 형식상 대지와 건물의 소유 명의자가 달라졌으므로 매도인에게 관습법상 법정지상권이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>의사해석</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>판례(전합)는 건물 처분권까지 함께 이전된 이 경우 토지 계속 사용에 관한 당사자 의사를 인정할 수 없어 매도인의 관습상 법정지상권을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>대판 2002.6.20. 2002다9660 전합</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>토지공유자 중 1인이 다른 공유자 지분 과반수의 동의를 얻어 건물을 건축한 후 토지와 건물의 소유자가 달라진 경우, 그 토지에 관습법상 법정지상권이 성립한다.</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>처분효과</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>판례는 이를 인정하면 1인의 공유자가 다른 공유자 지분에까지 지상권 설정의 처분행위를 하는 셈이 되어 부당하다고 하며, 이 법리는 제366조 법정지상권에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>대판 2014.9.4. 2011다73038,73045</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에서 특정 부분을 소유하는 자는 그 부분에 관하여 지분등기를 가진 자를 상대로 공유물분할청구를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>청구방식</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>판례는 특정 부분 소유를 주장하는 자는 명의신탁 해지를 원인으로 한 지분이전등기를 구해야 하고 공유물분할청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>대판 1996.2.23. 95다8430</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>제268조</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>공유자 간의 공유물 사용·수익·관리에 관한 특약은 특정승계인에게 당연히 승계되지만, 지분권자의 사용수익권을 사실상 포기하는 등 본질적 부분에 관한 특약은 특정승계인이 이를 알고 지분을 취득한 경우가 아닌 한 당연히 승계되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>승계범위</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>판례는 통상의 관리특약의 승계를 인정하되 본질적 제약은 악의의 특정승계인에게만 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>판례(공유물 특약의 승계)</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>제263조</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>토지의 과반수 지분 공유자로부터 특정부분의 사용·수익을 허락받아 점유하는 제3자는 소수지분권자에 대하여 그 점유로 인한 부당이득반환의무를 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>관리행위</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>과반수 지분권자의 사용·수익 허락은 공유물의 관리행위로서 적법하므로 제3자의 점유에 법률상 원인이 있다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>판례(과반수 지분의 관리행위)</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>부동산을 채권담보 목적으로 양도한 경우 특별한 사정이 없는 한 사용수익권은 양도담보설정자에게 있으므로, 양도담보권자는 사용수익 권한 있는 채무자나 그 승계인에게 임료 상당의 손해배상이나 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>권능귀속</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>판례는 양도담보의 담보적 성격상 사용수익권이 설정자에게 유보된다고 본다.</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>대판 2008.2.28. 2007다37394,37400</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>채무자가 동산을 양도담보로 제공한 후 다른 채권자와 다시 양도담보설정계약을 체결하고 점유개정의 방법으로 인도한 경우, 뒤의 채권자는 선의라면 양도담보권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>인도방법</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>판례는 점유개정에 의한 선의취득을 부정하므로, 무권리자인 채무자로부터 점유개정으로 인도받은 뒤의 채권자는 양도담보권을 취득할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>대판 2005.2.18. 2004다37430</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>제249조</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>양도담보의 목적인 주된 동산에 다른 동산이 부합되어 권리를 상실한 자는, 그 부합으로 인한 실질적 이익의 귀속 주체인 양도담보권자를 상대로 민법 제261조의 보상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>이익귀속</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>판례는 담보가치 증가에 따른 실질적 이익은 양도담보권설정자에게 귀속되므로 설정자를 상대로만 보상청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>대판 2016.4.28. 2012다19659</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>제261조</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>부당이득 수익자의 '악의'는 부당이득반환의무의 발생요건에 해당하는 사실이 있음을 인식하는 것으로 충분하다.</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>개념정의</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>판례는 악의란 자신의 이익 보유가 법률상 원인 없는 것임을 인식하는 것을 말하고 요건사실의 인식만으로는 부족하다고 하며, 악의의 증명책임은 이를 주장하는 측에 있다.</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>대판 2018.10.25. 2016다42800</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>제749조</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>채무자가 횡령한 금전을 자신의 채권자에 대한 채무변제에 사용한 경우, 채권자가 그 금전이 횡령된 것임에 대하여 악의 또는 중대한 과실이 없는 한 채권자의 금전취득은 피해자에 대한 관계에서 법률상 원인이 있다.</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>원인판단</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>판례는 이 법리를 횡령금의 증여에도 동일하게 적용한다.</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>대판 2012.1.12. 2011다74246</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>쌍무계약에서 당사자 쌍방의 책임 없는 사유로 채무가 이행불능이 된 경우, 채무자는 급부의무를 면하지만 상대방에게 반대급부를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>위험부담</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>제537조의 채무자위험부담주의상 반대급부도 청구하지 못하며, 이미 이행된 급부는 부당이득으로 반환된다.</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>민법 제537조 · 대판 2009.5.28. 2008다98655</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>제537조</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>계약상 급부가 계약 상대방뿐 아니라 제3자에게도 이익이 된 경우, 급부를 한 계약당사자는 그 제3자에 대하여 직접 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>전용물소권</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>판례는 전용물소권을 부정한다. 계약 위험의 제3자 전가, 일반채권자에 대한 우대, 제3자의 항변권 침해가 근거이며 사무관리의 경우도 같다.</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>대판 2002.8.23. 99다66564</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>전세금의 지급은 전세권 성립의 요소이므로 반드시 현실적으로 수수되어야 하고, 기존의 채권으로 전세금 지급에 갈음할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>현실수수</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>판례는 전세금 지급이 성립요소이지만 기존 채권으로 갈음할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>대판 1995.2.10. 94다18508</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>전세권 존속 중에는 전세권을 존속시키면서 전세금반환채권만을 분리하여 확정적으로 양도할 수 없고, 전세권 소멸 시 전세금반환채권이 발생하는 것을 조건으로 하는 장래 조건부 채권의 양도만 허용된다.</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>분리양도</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>전세금은 전세권과 분리될 수 없는 요소이므로 존속 중 확정적 분리양도는 허용되지 않는다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>판례(전세금반환채권의 분리양도)</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>전세권 성립 후 전세목적물의 소유권이 이전된 경우, 신 소유자가 전세권설정자의 지위를 승계하여 전세권 소멸 시 전세금반환의무를 부담한다.</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>지위승계</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>판례는 전세권 법률관계의 당사자를 신 소유자로 보아 구 소유자의 반환의무가 신 소유자에게 승계된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>대판 2006.5.11. 2006다6072</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>저당목적물의 변형물인 금전에 대하여 제3자가 이미 압류하여 특정된 경우에도, 저당권자는 스스로 압류하지 않으면 물상대위권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>압류주체</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>판례는 제3자의 압류로 특정성이 유지되면 저당권자 스스로 압류하지 않아도 물상대위권을 행사(배당요구 등)할 수 있다고 한다. 다만 행사에 나아가지 않으면 우선변제권을 상실하고 부당이득반환청구도 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>대판 2010.10.28. 2010다46756</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>제342조</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>건물 일부에 전세권이 설정된 경우, 전세권자는 건물 전부에 대하여 우선변제권이 있을 뿐 아니라 전세권의 목적물이 아닌 나머지 부분에 대하여도 경매를 신청할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>권능구별</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>판례는 일부 전세권자의 우선변제권은 건물 전부의 매각대금에 미치지만, 경매신청권은 전세권의 목적물 부분에 한정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>판례(건물 일부 전세권의 경매신청권)</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>채권자대위소송이 제기된 사실을 채무자가 알았다면 그 판결의 기판력이 채무자에게 미치지만, 피보전채권의 부존재를 이유로 한 소각하 판결의 기판력은 채권자가 채무자를 상대로 피보전채권의 이행을 구하는 소송에는 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>기판력범위</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>판례는 기판력이 미치는 것은 소송물인 피대위채권의 존부에 관한 것이고, 소송요건인 피보전채권 존부에 관한 판단에는 미치지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>대판 2014.1.23. 2011다108095</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사의 통지를 받은 후 채무자의 채무불이행을 이유로 제3채무자가 매매계약을 해제한 경우, 제3채무자는 그 해제로써 대위채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>판례(전합)는 채무불이행에 따른 법정해제는 제405조 제2항의 '처분'이 아니라고 한다. 다만 실질이 합의해제이거나 외관만 갖춘 때에는 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2011다87235 전합</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>사해행위인 매매예약에 기한 가등기가 전득자 앞으로 부기등기로 이전되고 본등기까지 마쳐진 경우에도, 채권자는 수익자를 상대로 매매예약의 취소를 청구할 수 있고, 가등기말소의무의 이행이 불가능하게 되었더라도 수익자는 가액배상의무를 진다.</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>피고적격</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>판례(전합)는 부기등기로 수익자 지위가 소멸하지 않으며 원물반환 불능 시 가액배상을 명할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>대판 2015.5.21. 2012다952 전합</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>채무자가 근저당권이 설정된 부동산을 처분하면서 그 매매대금으로 근저당권자의 피담보채권 일부를 변제하고 근저당권을 말소한 경우, 특별한 사정이 없는 한 그 처분행위는 사해행위로 볼 수 없다.</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>공동담보</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>우선변제권 있는 근저당권자에 대한 변제는 일반채권자의 공동담보를 해하지 않는다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>대판 2018.4.24. 2017다287891</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>채무자의 수익자에 대한 채권양도가 사해행위로 취소되고 제3채무자에게 취소 통지가 이루어지면, 채무자가 직접 채권을 취득하므로 채권자는 채무자를 대위하여 제3채무자에게 지급을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>판례는 취소의 상대적 효력상 채권이 채권자·수익자 관계에서 책임재산으로 취급될 뿐 채무자가 권리자로 되는 것이 아니므로 대위 지급청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>대판 2015.11.17. 2012다2743</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>채권자가 전득자를 상대로 사해행위취소를 구하는 경우, 전득자의 악의는 전득행위 당시 채무자와 수익자 사이 법률행위의 사해성에 대한 인식을 의미하며, 수익자의 악의 여부는 문제되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>악의대상</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>판례는 전득자 상대 취소에서 전득자 자신의 사해성 인식만 문제된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>판례(전득자의 악의 판단)</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>이행기의 정함이 없는 채권을 양수한 자가 이행청구의 소를 제기하고 소송 계속 중 채무자에 대한 채권양도통지가 이루어진 경우, 채무자는 소장 부본 송달 다음 날부터 이행지체책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>판례는 대항요건을 갖추기 전에는 양수인이 채무자에게 대항할 수 없으므로 양도통지가 도달한 다음 날부터 지체책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>대판 2014.4.10. 2012다29557</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>불법행위에서 위법행위 시점과 손해발생 시점 사이에 시간적 간격이 있는 경우, 손해배상청구권의 지연손해금은 위법행위 시점부터 발생한다.</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>판례는 이 경우 지연손해금은 손해발생 시점을 기산일로 하여 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>대판 2012.2.23. 2010다97426</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>금전채무에 관하여 이행지체에 대비한 지연손해금 비율을 따로 약정한 경우, 이는 손해배상액의 예정으로서 법원의 직권 감액 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>성질결정</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>판례는 지연손해금 비율 약정을 제398조의 손해배상액 예정으로 보아 부당히 과다하면 감액할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>대판 2017.7.11. 2016다52265</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>승소판결 확정 후 소송촉진법상 지연손해금 이율이 변경된 경우, 시효중단을 위한 후소에서 법원은 변경된 이율을 적용하여 선행판결과 다른 금액을 인정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>차단효</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>판례는 법률·판례의 변경은 변론종결 후 새로 발생한 사유가 아니므로 후소 법원이 선행 확정판결과 달리 판단할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>대판 2019.8.29. 2019다215272</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>제165조</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>사립학교 교사가 법령상 금지된 영리업무로 얻고 있던 유흥업소 출연 급료는 위법소득이므로 불법행위로 인한 일실수익 산정의 기초로 삼을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>위법소득</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>판례는 사립학교법·국가공무원법상 영리업무 금지에 위반한 소득을 일실수익 기초에서 제외한다.</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>대판 1992.10.27. 92다34582</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>1189</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>등기서류 위조로 원인무효의 소유권이전등기가 순차로 마쳐진 후 진정한 소유자가 최종 매수인을 상대로 한 말소등기소송에서 승소 확정된 경우, 최종 매수인이 입은 손해는 그 토지 소유권 상실 상당액이다.</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>손해개념</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>판례(전합)는 최종 매수인은 처음부터 소유권을 취득하지 못했으므로 소유권 상실이 손해가 아니라, 유효한 등기로 믿고 출연한 매매대금이 적극적 손해라고 한다.</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>대판 1992.6.23. 91다33070 전합</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인이 자기 부담부분 이상을 변제하여 공동 면책을 얻게 한 경우, 다른 공동불법행위자들에게 부담부분 비율에 따라 구상할 수 있고, 구상의무자가 여럿인 때 그 구상채무는 특별한 사정이 없는 한 분할채무이다.</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>채무형태</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>판례는 내부 구상관계에서 분할채무 원칙을 취하되, 구상권자에게 과실이 없어 부담부분이 전혀 없는 경우 등에는 부진정연대로 본다.</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>판례(공동불법행위자 간 구상관계)</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>1191</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>매도인이 매수인의 채무불이행을 이유로 매매계약을 적법하게 해제한 후에는, 매수인은 더 이상 착오를 이유로 그 매매계약을 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>경합관계</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>판례는 해제 후라도 매수인이 손해배상책임 등 해제의 불이익을 면하기 위하여 착오 취소권을 행사하여 계약 전체를 무효로 돌릴 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>대판 1991.8.27. 91다11308</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>1192</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>매매계약 내용의 중요부분에 착오가 있는 경우, 매수인은 매도인의 하자담보책임이 성립하는지와 상관없이 착오를 이유로 매매계약을 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>제도경합</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>판례는 착오 취소와 하자담보책임은 취지·요건·효과가 다른 별개 제도로서 경합을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>대판 2018.9.13. 2015다78703</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>토지매매에서 매수인이 측량이나 지적도 대조 등으로 매매목적물이 지적도상의 것과 일치하는지 미리 확인하지 않았다면, 그 자체로 착오에 관한 중대한 과실이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>주의의무</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>판례는 특별한 사정이 없는 한 매수인에게 그러한 확인 의무가 있다고 볼 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>대판 2020.3.26. 2019다288232</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>부동산 매매에서 쌍방이 갑 토지를 목적물로 삼았으나 지번에 착오를 일으켜 계약서에 을 토지로 표시한 경우, 매매계약은 계약서 문언대로 을 토지에 관하여 성립한다.</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>오표시무해</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>판례는 쌍방의 의사합치가 있는 갑 토지에 관하여 계약이 성립하고(자연적 해석), 을 토지에 마쳐진 이전등기는 원인 없는 무효 등기라고 한다.</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>대판 1996.8.20. 96다19581</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>제105조</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>어느 연대채무자에 대한 법률행위의 무효나 취소의 원인은 다른 연대채무자의 채무에 영향을 미치지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>독립성</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>민법 제415조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>민법 제415조</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>제415조</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>상계할 채권이 있는 연대채무자가 상계하지 아니한 때에는, 그 채무자의 부담부분에 한하여 다른 연대채무자가 상계할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>상계원용</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>민법 제418조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>민법 제418조②</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>연대채무자는 자기의 부담부분을 초과하여 출재한 경우에만 다른 연대채무자에게 구상권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>보증혼동</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>제425조 제1항상 연대채무자는 출재로 공동면책이 되면 부담부분 초과 여부와 관계없이 다른 채무자의 부담부분에 대해 구상할 수 있다. 부담부분 초과 출재는 공동보증 등에서 요구된다.</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>민법 제425조①</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>제425조</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>1198</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>양도금지특약이 있는 채권을 악의의 양수인으로부터 다시 선의로 양수한 전득자는 제449조 제2항 단서의 선의의 제3자에 해당하고, 그 선의 양수인으로부터 다시 양수한 자는 선의·악의를 불문하고 채권을 유효하게 취득한다.</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>전득보호</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>판례는 '선의의 제3자'를 직접 양수인에 한정하지 않고, 선의자 개입 후의 전득자는 악의여도 보호한다.</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>대판 2015.4.9. 2012다118020</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>1199</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>대항력을 갖춘 임차인이 있는 임대주택이 양도되면 양수인이 임대인의 지위를 승계하여 보증금반환채무를 면책적으로 인수하고 양도인은 임대차관계에서 탈퇴하며, 이는 보증금반환채권에 질권이 설정되고 임대인이 이를 승낙한 경우에도 마찬가지이다.</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>면책승계</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>판례는 주임법 제3조 제4항의 법정 지위승계에 따라 질권 설정 승낙이 있어도 양도인이 보증금반환채무를 면한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>대판 2018.6.19. 2018다201610</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>병존적 채무인수에서 인수인이 채무자의 부탁 없이 채권자와의 계약으로 채무를 인수하여 주관적 공동관계가 없는 경우, 채무자와 인수인은 부진정연대관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>관계형태</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>판례는 부탁 있는 통상의 경우 연대채무, 부탁 없는 경우 부진정연대관계로 본다.</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>대판 2014.8.26. 2013다49428,49435</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>제453조</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>11001</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>채무자와 인수인의 합의에 의한 중첩적 채무인수에서 채권자의 수익의 의사표시는 계약의 성립요건이자 효력발생요건이다.</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>요건구별</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>판례는 중첩적 채무인수를 제3자를 위한 계약으로 보아, 수익의 의사표시는 성립·효력발생요건이 아니라 채권자가 인수인에 대한 채권을 취득하기 위한 요건이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>대판 2013.9.13. 2011다56033</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>11002</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>양도금지특약이 있는 채권도 전부명령에 의하여 전부될 수 있고, 그 전부채권자로부터 채권을 양수한 자가 특약에 대해 악의이거나 중과실이 있더라도 채무자는 특약을 근거로 양도의 무효를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>집행우선</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>판례는 전부명령의 효력은 집행채권자의 선악과 무관하고, 유효한 전부 후의 양도에는 특약을 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>대판 2003.12.11. 2001다3771</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>11003</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>제1양수인이 확정일자 있는 증서로 대항요건을 갖춘 후 양도인이 동일한 채권을 제2양수인에게 다시 양도한 경우, 그 후 제1차 양도계약이 합의해지되면 제2양수인은 당연히 채권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>무권처분</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>판례는 처분권한 없는 양도인의 제2차 양도는 무효이고, 사후에 제1차 양도가 합의해지되어도 유효로 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>대판 2016.7.14. 2015다46119</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>11004</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>채권양도가 다른 채무의 담보 목적으로 이루어진 경우, 그 피담보채무가 변제로 소멸하였다면 양도채권의 채무자는 이를 이유로 양수인의 양수금 청구를 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>내부관계</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>판례는 피담보채무 소멸은 양도인·양수인 간의 문제일 뿐이므로 채무자는 이를 이유로 지급을 거절할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>대판 1999.11.26. 99다23093</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>11005</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>채권양수인이 채권양도의 대항요건을 갖추지 못한 상태에서 채무자를 상대로 재판상 청구를 하더라도 소멸시효 중단사유인 재판상 청구에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>중단효력</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>판례는 대항요건 미비 양수인의 재판상 청구도 시효중단 사유인 재판상 청구에 해당한다고 한다(채권의 동일성 유지).</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>판례(대항요건 미비 양수인의 재판상 청구)</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>11006</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>상계의 요건인 '채무의 이행기가 도래한 때'는 채무자가 이행지체에 빠진 때를 의미하며, 상계의 효력은 상계 의사표시 시점을 기준으로 발생한다.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>개념혼동</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>판례는 이행기 도래란 이행을 청구할 수 있는 시기의 도래를 의미하고 지체를 요하지 않으며, 상계 시 양 채무는 상계적상 시에 소급하여 소멸하므로 충당 계산도 상계적상 시점 기준이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>대판 2021.5.7. 2018다25946</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>11007</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>민법 제496조의 상계금지는 고의의 채무불이행으로 인한 손해배상채권에는 적용되지 않지만, 고의의 행위가 불법행위와 채무불이행을 동시에 구성하여 두 손해배상채권이 경합하는 경우에는 유추적용된다.</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>유추적용</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>판례는 경합 시 채무불이행 손배채권을 수동채권으로 한 상계를 허용하면 제496조의 취지가 몰각되므로 유추적용한다.</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>대판 2017.2.15. 2014다19776,19783</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>11008</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인이 자신의 반대채권으로 상계하거나 채권자와 상계계약을 체결한 경우, 그 채무소멸의 효력은 다른 부진정연대채무자에게는 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>절대효</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>판례는 상계는 변제와 같이 현실적 만족을 주므로 소멸한 채무 전액에 관하여 다른 부진정연대채무자에게도 효력이 미친다고 한다(상계계약도 같다).</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>판례(부진정연대채무와 상계의 절대효)</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>11009</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>소송상 상계항변에 대하여 상대방이 다시 소송상 상계의 재항변을 하는 것은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>소송상상계</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>판례는 소송상 상계의 재항변은 법원의 판단 구조상 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>판례(소송상 상계의 재항변)</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>11010</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>유책배우자의 이혼청구는 원칙적으로 허용되지 않으나, 상대방도 혼인 계속의 의사가 없는 등 유책성이 이혼청구를 배척해야 할 정도로 남아 있지 아니한 특별한 사정이 있는 경우에는 예외적으로 허용된다.</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>원칙예외</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>판례(전합)는 유책주의를 유지하면서 축출이혼 염려가 없는 경우, 보호·배려가 이루어진 경우, 세월 경과로 유책성·고통이 약화된 경우 등 예외를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>대판 2015.9.15. 2013므568 전합</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>제840조</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>11011</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>이혼으로 인한 재산분할청구권은 협의 또는 심판에 의하여 구체적 내용이 형성되기 전이라도 채무자의 책임재산에 속하므로, 이를 포기하는 행위는 채권자취소권의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>권리구체화</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권은 범위·내용이 불확정하여 책임재산이 아니므로 그 포기는 사해행위취소의 대상이 될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>대판 2013.10.11. 2013다7936</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>11012</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>이혼 후 자녀에 대한 양육권을 부모 중 일방에게, 친권을 다른 일방에게 또는 부모 공동으로 귀속시키는 것은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>분리귀속</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>판례는 친권과 양육권이 항상 같은 사람에게 귀속되어야 하는 것은 아니며 일정한 기준을 충족하면 분리 귀속도 허용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>판례(친권·양육권의 분리 귀속)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>제909조</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>11013</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>자필증서 유언에서 문자의 삽입·삭제·변경에는 유언자의 자서와 날인이 필요하지만, 증서의 기재 자체로 보아 명백한 오기를 정정한 것에 불과하면 그 정정 부분에 날인이 없어도 유언의 효력에 영향이 없다.</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>방식완화</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>판례는 명백한 오기 정정에는 제1066조 제2항의 방식 위반이 문제되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>대판 1998.5.29. 97다38503</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>제1066조</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>11014</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>자필증서 유언의 주소는 유언 전문과 동일한 지편에 기재해야 하는 것은 아니어서 일체성이 인정되면 봉투에 기재해도 되고, 날인은 무인(拇印)으로도 유효하다.</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>방식해석</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>판례는 봉투 주소 기재와 무인 날인의 유효성을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>대판 1998.5.29. 97다38503</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>제1066조</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>11015</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>자필증서에 의한 유언에서 유언자가 주소를 자서하지 않았더라도 유언자의 특정에 지장이 없다면 그 유언은 유효하다.</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>요식엄격</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>판례는 법정 방식에 어긋난 유언은 진의에 합치해도 무효이므로 주소 자서가 없으면 특정에 지장이 없어도 효력이 부정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>대판 2014.9.26. 2012다71688</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>제1066조</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>11016</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>우리 민법상 유언으로 상속인을 지정하거나 법정상속분을 직접 변경할 수는 없지만, 포괄적 유증을 통하여 실질적으로 그와 같은 결과를 달성할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>제도구별</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>민법은 유언상속을 인정하지 않고 유증만 인정하므로, 포괄유증(제1078조)으로 상속분 변경과 유사한 효과를 얻을 수 있을 뿐이다(유류분 침해 시 반환청구 가능).</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>민법 제1078조 · 통설</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>제1078조</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>11017</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>자필증서에 의한 유언에는 증인의 서명 또는 기명날인이 있어야 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>요건추가</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>제1066조 제1항의 요건은 전문·연월일·주소·성명의 자서와 날인이며 증인은 요건이 아니다.</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>민법 제1066조①</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>제1066조</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>11018</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>피상속인의 배우자와 자녀 중 자녀 전부가 상속을 포기한 경우, 배우자와 피상속인의 손자녀 또는 직계존속이 공동상속인이 된다.</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>판례변경</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>대법원 전원합의체는 2023년 이 경우 배우자가 단독상속인이 된다고 하여 종래 판례(배우자·손자녀 공동상속)를 변경하였다.</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>대결 2023.3.23. 2020그42 전합</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>제1043조</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>11019</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>금전채무와 같이 급부의 내용이 가분인 채무가 공동상속된 경우, 상속 개시와 동시에 법정상속분에 따라 공동상속인에게 분할되어 귀속되므로 상속재산분할의 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>당연분할</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>판례는 가분채무의 당연분할 귀속을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>대판 1997.6.24. 97다8809</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>제1006조</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>11020</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>법정변제충당에서는 이행기가 도래한 채무에 먼저 충당하고, 채무 전부의 이행기가 도래하였거나 도래하지 아니한 때에는 채무자에게 변제이익이 많은 채무에 먼저 충당한다.</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>충당순서</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>민법 제477조 제1호·제2호의 명문 규정이다. 변제이익은 통상 고이율 채무가 크다.</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>민법 제477조</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>11021</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>비용·이자·원본의 법정 충당순서(제479조)는 변제자의 일방적 지정에 의해서도 배제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>지정한계</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>판례는 제479조의 순서를 일방적 지정충당으로는 바꿀 수 없고 당사자의 합의충당으로만 달리 정할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>민법 제479조 · 판례</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>제479조</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>11022</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>상행위에 해당하는 부동산 매매계약이 무효가 되어 이미 지급한 매매대금의 반환을 구하는 부당이득반환청구권은 언제나 상법 제64조의 5년 소멸시효에 걸린다.</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>시효구별</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>판례는 상거래 관계와 같은 정도로 신속하게 해결할 필요성이 없는 경우에는 상법 제64조가 적용되지 않고 10년의 민사시효(제162조 제1항)가 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>대판 2003.4.8. 2002다64957</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>11023</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>은행 대출 시 근저당권설정비용을 부담시킨 약관조항이 무효라며 그 비용 상당액의 반환을 구하는 부당이득반환채권에는 상법 제64조가 적용되어 5년의 소멸시효에 걸린다.</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>시효구별</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>판례는 상행위에 기초하고 정형적·집단적 거래로 신속 해결 필요성이 있는 부당이득반환채권에 5년의 상사시효를 적용한다(가맹본부의 부당 수취금도 같다).</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>대판 2014.7.24. 2013다214871</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>11024</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>배당가능이익이 없음에도 이루어진 위법배당에 따른 회사의 주주에 대한 부당이득반환청구권은 상행위에 기초한 채권이므로 5년의 상사 소멸시효에 걸린다.</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>시효구별</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>판례는 이익배당은 회사 내부의 이익 분배행위로서 상행위가 아니므로 위법배당 부당이득반환청구권에는 10년의 민사시효가 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>판례(위법배당과 소멸시효)</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>11025</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>부부 사이 및 부모와 미성년 자녀 사이의 부양은 1차적 부양의무이고, 그 밖의 친족 사이의 부양은 부양권리자가 자력·근로로 생활을 유지할 수 없고 부양의무자에게 여력이 있는 경우에 인정되는 2차적 부양의무이다.</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>의무층위</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>판례는 공동생활에 기초한 1차적 부양의무와 사회보장 대체물인 2차적 부양의무를 구별한다(제975조 참조).</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>민법 제975조 · 판례</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>제974조</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>11026</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>변시11</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>직계혈족인 배우자가 사망한 후에도, 그 직계혈족의 부모(직계인척)에 대한 생존배우자의 부양의무는 생계를 같이 하는지와 관계없이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>관계소멸</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>직계혈족 사망으로 배우자관계가 소멸하므로 제974조 제1호가 아니라 제3호가 적용되어, 생계를 같이 하는 경우에 한하여 부양의무가 인정된다.</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>민법 제974조 · 서울가법 2007브28</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>제974조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17544,6 +17544,4646 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>보증의 효력 발생 요건인 '보증인의 기명날인'은 타인이 대행하는 방법으로 하여도 무방하다.</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>방식해석</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>판례는 제428조의2 제1항의 '서명'은 보증인이 직접 써야 하지만 '기명날인'은 타인 대행이 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>대판 2019.3.14. 2018다282473</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>제428조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>지급보증서에 보증금액의 한도액을 정한 경우, 보증채무 자체의 이행지체로 인한 지연손해금은 그 한도액에 포함되어 별도로 부담하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>범위구별</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>판례는 한도액에는 주채무의 원금·이자·지연손해금이 포함되지만, 보증채무 자체의 이행지체로 인한 지연손해금은 한도액과 별도로 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>대판 1998.2.27. 97다1433</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>제429조</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>보증계약 체결 후 채권자가 보증인의 승낙 없이 주채무자에 대하여 변제기를 연장하여 준 경우, 그 효력은 원칙적으로 보증채무에도 미친다.</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>판례는 변제기 연장이 반드시 보증인의 책임을 가중하는 것은 아니므로 원칙적으로 보증채무에도 효력이 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>대판 1996.2.23. 95다49141</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>제428조</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>주채무의 소멸시효가 완성되어 보증채무가 소멸된 상태에서 보증인이 보증채무를 이행하거나 승인하였더라도, 부종성을 부정할 특별한 사정이 없는 한 보증인은 여전히 주채무의 시효소멸을 이유로 보증채무의 소멸을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>시효원용</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>판례는 보증인의 행위로 주채무의 시효이익 포기 효과가 생기지 않으므로 보증인이 주채무 시효소멸을 원용할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>대판 2012.7.12. 2010다51192</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>제433조</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>확정판결로 주채무의 소멸시효기간이 10년으로 연장된 경우, 보증채무의 소멸시효기간도 당연히 10년으로 연장된다.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>독립성</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>판례는 주채무가 판결로 시효가 연장되어도 연대보증채무의 소멸시효기간은 여전히 종전의 시효기간에 따른다고 한다.</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>대판 2006.8.24. 2004다26287</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>제165조</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>당사자가 불확정한 사실이 발생한 때를 이행기한으로 정한 경우, 그 사실이 발생한 때는 물론 그 사실의 발생이 불가능하게 된 때에도 이행기한이 도래한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>불확정기한</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>판례는 불확정기한의 도래를 사실 발생 시뿐 아니라 발생 불가능 확정 시에도 인정한다.</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>대판 1989.6.27. 88다카10579</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>제152조</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>제작물공급계약에서 '도급인이 검사하여 합격하면 보수를 지급한다'는 약정은 보수 지급을 도급인의 일방적 의사에 좌우되게 하는 순수수의조건에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>조건성격</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>판례는 이 약정이 동시이행관계 확인에 불과하여 조건이 아니고, 설령 조건이라도 합격 여부가 객관적으로 결정되므로 순수수의조건이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>대판 2006.10.13. 2004다21862</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>제147조</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>유치권의 발생을 미리 막는 유치권 배제 특약은 유효하고, 그 특약에도 조건을 붙일 수 있다.</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>특약효력</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>판례는 유치권 배제 특약이 유효하며 그 효력은 특약 상대방 외의 사람도 주장할 수 있고, 특약에 조건을 붙일 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>대판 2018.1.24. 2016다234043</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3자간 등기명의신탁에서 명의신탁 약정과 등기가 무효로 된 경우, 매도인은 소유권에 기한 방해배제로 명의수탁자 명의 등기의 말소를 청구할 수 있고, 명의신탁자도 매도인을 대위하여 그 말소를 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>권리구성</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>판례는 무효로 부동산 소유권이 매도인에게 복귀하고 매도인-신탁자 간 매매계약은 유효하므로, 신탁자가 이전등기청구권 보전을 위해 대위 말소를 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>대판 1999.9.17. 99다21738</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>3자간 등기명의신탁이 무효로 된 경우, 명의신탁자는 명의수탁자를 상대로 부당이득반환을 원인으로 한 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>청구가부</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>판례는 신탁자가 매도인에 대한 이전등기청구권을 보유하여 손해가 없고 소유권이 매도인에게 복귀하므로, 수탁자를 상대로 부당이득반환 이전등기를 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>대판 2008.11.27. 2008다55290</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>부동산실명법상 명의신탁에 따른 물권변동 무효로 대항할 수 없는 '제3자'에는 명의수탁자가 물권자임을 기초로 새로운 이해관계를 맺은 압류·가압류채권자도 선의·악의를 묻지 않고 포함된다.</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 제4조 제3항의 제3자에 물권 취득자뿐 아니라 압류·가압류채권자도 포함되며 선악을 불문한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>대판 2013.3.14. 2012다107068</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>계약명의자가 명의수탁자로 되어 있더라도, 계약상 법률효과를 명의신탁자에게 직접 귀속시킬 의도로 계약을 체결한 사정이 인정되면 그 명의신탁관계는 3자간 등기명의신탁으로 보아야 한다.</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>유형구별</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>판례는 계약당사자 확정 문제로 귀결되며, 계약당사자를 명의신탁자로 볼 수 있으면 3자간 등기명의신탁이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>판례(명의신탁 유형의 구별)</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>유류분반환청구권의 행사로 발생하는 목적물의 이전등기청구권에 대하여도 민법 제1117조의 유류분반환청구권에 관한 소멸시효가 그대로 적용된다.</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>권리구별</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>판례는 행사로 발생하는 이전등기청구권은 유류분반환청구권과 다른 권리이므로 제1117조의 시효가 적용되지 않고 그 권리의 성질에 따라 별도로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>대판 2015.11.12. 2011다55092</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>제1117조</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3자간 등기명의신탁에 의한 등기가 무효로 된 경우, 목적 부동산을 인도받아 점유하고 있는 명의신탁자의 매도인에 대한 소유권이전등기청구권은 소멸시효가 진행하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>판례는 매수인이 목적물을 인도받아 점유하면 등기청구권의 시효가 진행하지 않는 법리가 이 경우에도 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>대판 2013.12.12. 2013다26647</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>부동산실명법상 유예기간 경과 후 실명화 조치를 취하지 아니한 명의신탁자가 명의수탁자에 대하여 부당이득의 법리에 따라 가지는 소유권이전등기청구권의 소멸시효기간은 10년이다.</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>시효기간</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>판례는 이 청구권을 법률 규정에 의한 부당이득반환청구권으로 보아 제162조 제1항의 10년 시효를 적용한다.</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>대판 2009.7.9. 2009다23313</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>취득시효가 완성된 토지의 점유자가 점유를 상실하더라도, 시효완성으로 인한 소유권이전등기청구권의 소멸시효는 진행하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>판례는 점유 계속 중에는 시효가 진행하지 않지만, 점유를 상실한 때부터는 시효완성으로 인한 이전등기청구권의 소멸시효가 별도로 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>대판 1996.3.8. 95다34866 등</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>취득시효기간이 경과하기 전에 등기부상 소유명의자가 변경되더라도 그 사유만으로는 취득시효가 중단되지 않으므로, 시효완성자는 새로운 소유명의자에게 시효취득을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>중단여부</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>판례는 시효기간 경과 전 소유명의 변경은 점유의 계속을 파괴하지 않아 중단사유가 아니므로 새 소유자가 시효완성의 당사자가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>대판 2009.9.10. 2006다609</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>부동산 점유취득시효 완성 후 시효취득자가 등기하지 않은 사이에 제3자 명의의 소유권이전등기가 마쳐졌더라도, 당초 점유자가 계속 점유하고 그 변동 시점을 기산점으로 다시 시효기간이 경과하면 2차 취득시효의 완성을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2차시효</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>판례는 소유권 변동 시를 새로운 기산점으로 한 2차 취득시효의 완성 주장을 허용한다.</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>대판 2009.7.16. 2007다15172</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>취득시효기간 만료 당시의 점유자로부터 부동산을 양수하여 점유를 승계한 현 점유자는, 전 점유자의 취득시효 완성 효과를 주장하여 직접 자기 앞으로 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>승계범위</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>판례(전합)는 점유 승계인은 점유 자체와 하자만 승계할 뿐 시효완성의 법률효과는 승계하지 않으므로, 전 점유자의 등기청구권을 대위행사할 수 있을 뿐 직접 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>대판 1995.3.28. 93다47745 전합</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>제199조</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>시효취득자는 시효완성 당시 소유권보존등기나 이전등기가 무효인 경우, 그 무효등기 명의자를 상대로 직접 시효취득을 원인으로 한 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>상대방확정</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>판례는 진정한 소유자를 대위하여 무효등기의 말소를 구할 수 있을 뿐 무효등기 명의자에게 직접 시효취득 이전등기를 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>대판 1993.9.14. 93다10989</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>임차보증금반환채권 담보 목적으로 통정하여 마친 전세권설정계약이 무효인 경우, 그 전세권부채권을 가압류한 자는 선의인 이상 제108조 제2항의 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>판례는 허위표시로 형성된 법률관계로 생긴 채권을 가압류한 자를 새로운 이해관계를 맺은 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>대판 2010.3.25. 2009다35743</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>전세권의 존속기간이 만료되면 용익물권적 권능은 등기 말소 없이도 소멸하고 담보물권적 권능만 남으며, 그 전세권은 전세금반환채권과 함께 제3자에게 양도할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>권능분리</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>판례는 전세권의 용익·담보 겸유 성격상 기간 만료 후에도 담보물권적 권능 범위에서 전세금반환 시까지 등기 효력이 존속하고 채권과 함께 양도 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>대판 2005.3.25. 2003다35659 등</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>공동저당의 목적부동산 중 먼저 경매된 부동산의 후순위저당권자가 다른 부동산에 공동저당 대위등기를 하지 않은 사이에 그 부동산의 저당권등기가 말소되고 제3취득자가 새로 이해관계를 취득한 경우, 후순위저당권자는 그 제3취득자에게 제368조 제2항의 대위를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>대위제한</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>판례는 대위등기 부재 중 등기가 말소되고 새 이해관계인이 생긴 경우 제3취득자에 대한 대위 주장을 제한한다.</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>대판 2015.3.20. 2012다99341</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>공동저당의 목적인 채무자 소유 부동산과 물상보증인 소유 부동산의 경매대가를 동시에 배당하는 경우, 채무자 소유 부동산의 경매대가에서 먼저 배당하고 부족분이 있는 경우에 한하여 물상보증인 소유 부동산에서 추가 배당하며, 물상보증인이 연대보증인을 겸한 경우에도 같다.</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>배당순서</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>판례는 이 경우 제368조 제1항이 적용되지 않고 채무자 소유 부동산이 먼저 책임지며, 물상보증인의 연대보증 겸유 여부와 무관하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>대판 2016.3.10. 2014다231965</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>공동저당의 목적인 채무자 소유 부동산과 물상보증인 소유 부동산 중 채무자 소유 부동산이 먼저 경매되어 1번 공동저당권자가 변제받은 경우, 채무자 소유 부동산의 후순위저당권자는 선순위자를 대위하여 물상보증인 소유 부동산에 저당권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>대위제한</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인의 변제자대위 기대를 보호하기 위해 채무자 소유 부동산의 후순위저당권자의 물상보증인 부동산에 대한 대위를 부정한다.</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>판례(공동저당과 후순위저당권자의 대위)</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>저당권으로 담보된 채권에 질권을 설정하는 경우, 질권자와 질권설정자가 피담보채권만을 질권의 목적으로 하고 저당권은 질권의 목적으로 하지 않는 것도 가능하다.</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>판례는 이러한 약정이 저당권의 부종성에 반하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>판례(피담보채권에 대한 질권 설정)</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>제348조</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>임대차보증금반환채권이 양도된 후 그 양수인의 채권자가 채권압류·추심명령을 받았는데 그 채권양도계약이 허위표시로서 무효인 경우, 그 추심채권자는 통정허위표시에서 보호되는 제3자에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>판례는 가장양도된 채권에 압류·추심명령을 받은 추심채권자를 새로운 이해관계를 맺은 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>대판 2014.4.10. 2013다59753</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>파산자가 통정허위표시로 가장채권을 보유하다가 파산선고를 받은 경우, 파산관재인은 제108조 제2항의 제3자에 해당하고 그 선의·악의는 총파산채권자를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>선의기준</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>판례는 파산관재인을 제3자로 보고, 파산채권자 모두가 악의가 아닌 한 선의의 제3자라고 한다.</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>대판 2010.4.29. 2009다96083</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>통정허위표시의 무효로 대항할 수 없는 제108조 제2항의 제3자는 선의이면 족하고 무과실까지 요구되는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>요건범위</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>판례는 제108조 제2항의 제3자에게 선의만 요구하고 무과실은 요건이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>대판 2004.5.28. 2003다70041</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>고유 의미의 종중은 공동선조의 분묘 수호와 제사, 종원 상호 간 친목 등을 목적으로 하는 자연발생적 종족집단체로서 특별한 조직행위를 필요로 하지 않고, 공동선조의 후손은 성년이 되면 당연히 종원이 된다.</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>개념정의</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>판례는 고유 종중을 자연발생적 단체로 보아 특정 범위 후손만으로 구성된 종중은 종중 유사단체에 불과하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>대판 2019.2.14. 2018다264628</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>종중 소유 재산은 종원의 총유이므로 그 관리·처분은 종중규약이 있으면 그에 따르고 없으면 종중총회의 결의에 의하여야 하며, 종중 대표자가 그 절차를 거치지 않고 한 처분행위는 무효이다.</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>처분절차</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>판례는 총유물 처분에 규약 또는 총회결의를 요구하며 절차 위반 처분을 무효로 본다.</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>대판 1996.8.20. 96다18656</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>종중 토지 매각대금의 분배에 관한 종중총회의 결의가 무효인 경우, 종원은 새로운 종중총회의 결의 없이도 곧바로 종중을 상대로 자신이 공정하다고 주장하는 분배금의 지급을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>청구가부</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>판례는 분배는 총회결의에 의하여만 가능하므로 종원은 무효확인 승소 후 새 총회의 공정한 결의를 거쳐야 하고 곧바로 분배금 지급을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>대판 2010.9.9. 2007다42310</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>남자 종중원에게만 소집통지를 하여 개최된 종중 총회의 결의는 무효이다.</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>소집흠결</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>판례는 통지 가능한 모든 성년 종중원에게 개별 소집통지를 해야 하므로 여성 종원을 배제한 총회결의를 무효로 본다.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>판례(종중 총회의 소집통지)</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>부동산실명법을 위반하여 무효인 명의신탁약정에 따라 수탁자 명의로 등기를 한 경우, 명의신탁자가 수탁자를 상대로 그 등기의 말소를 구하는 것은 민법 제746조의 불법원인급여를 이유로 금지된다.</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>불법원인</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 위반 명의신탁등기를 불법원인급여로 볼 수 없으므로 신탁자의 말소청구가 허용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>대판 2019.6.20. 2013다218156 전합</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>농지법상의 처분명령을 회피할 목적으로 명의신탁을 한 경우에는, 그 명의신탁등기가 불법원인급여에 해당하여 신탁자의 말소청구가 금지된다.</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>불법원인</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>판례는 농지법상 처분명령 회피가 결합되어 있더라도 단순 행정명령 불이행에 불과하므로 불법원인급여 규정의 적용 여부를 달리 판단할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>대판 2019.6.20. 2013다218156 전합</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>무권리자가 타인의 권리를 처분한 경우 권리자가 이를 추인하면, 무권대리 추인에 관한 제130조·제133조를 유추적용하여 원칙적으로 계약을 체결한 때에 소급하여 그 효과가 권리자에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>유추적용</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>판례는 무권리자 처분의 추인에 무권대리 추인 규정을 유추적용하여 소급효를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>대판 2017.6.8. 2017다3499</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>제130조</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>무권대리인의 상대방이 계약의 이행을 선택한 경우, 무권대리인은 마치 자신이 계약의 당사자가 된 것처럼 계약에서 정한 채무를 이행할 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>책임범위</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>판례는 제135조의 이행책임을 무권대리인이 계약당사자처럼 계약상 채무를 이행하는 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>판례(무권대리인의 이행책임)</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>제135조</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>후견계약은 공정증서로 체결하여야 하고, 가정법원이 임의후견감독인을 선임한 때부터 효력이 발생한다.</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>방식요건</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>민법 제959조의14 제2항·제3항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>민법 제959조의14</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>제959조의14</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>임의후견감독인이 선임되기 전에는 본인 또는 임의후견인이 언제든지 공증인의 인증을 받은 서면으로 후견계약의 의사표시를 철회할 수 있으나, 선임 이후에는 정당한 사유가 있는 때에만 가정법원의 허가를 받아 후견계약을 종료할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>종료요건</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>민법 제959조의18의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>민법 제959조의18</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>제959조의18</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>착오를 이유로 매매계약을 취소한 후 부당이득반환을 구하는 경우, 당사자 쌍방의 원상회복의무는 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>판례는 취소로 무효가 된 계약의 쌍방 원상회복의무가 동시이행관계에 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>대판 2001.7.10. 2001다3764</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>제549조</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>동기의 착오를 이유로 법률행위를 취소하려면, 그 동기를 의사표시의 내용으로 삼을 것을 상대방에게 표시하는 외에 당사자 사이에 그 동기를 의사표시의 내용으로 삼기로 하는 별도의 합의까지 이루어져야 한다.</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>표시충분</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>판례는 동기가 상대방에게 표시되어 의사표시의 내용으로 인정되면 충분하고 별도의 합의까지 필요하지는 않다고 한다(다만 중요부분의 착오여야 함).</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>대판 1998.2.10. 97다44737</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>법률행위 내용의 중요부분에 착오가 있더라도 그 착오가 표의자의 중대한 과실로 인한 때에는 취소하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>취소제한</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>민법 제109조 제1항 단서의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>민법 제109조①</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>생산자 및 상인이 판매한 생산물 및 상품의 대가에 관한 채권의 소멸시효기간은 3년이다.</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>단기시효</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>민법 제163조 제6호의 명문 규정이며, 판례는 이를 매매대금 그 자체의 채권으로 상품 공급과 등가성 있는 청구권에 한정한다.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>민법 제163조 제6호 · 대판 1996.1.23. 95다39854</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>제163조</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>가압류에 의한 소멸시효 중단의 효력은 가압류명령이 채무자에게 송달된 때가 아니라 가압류를 신청한 때에 소급하여 발생한다.</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>중단시점</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>판례는 재판상 청구가 소 제기 시 중단되는 것과 마찬가지로, 가압류채권자의 권리행사가 가압류 신청 시 시작되므로 중단 효력이 신청 시로 소급한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>대판 2017.4.7. 2016다35451</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>원인채권의 지급을 확보하기 위하여 어음이 교부된 경우, 원인채권에 기한 청구를 한 것만으로도 어음채권의 소멸시효가 중단된다.</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>중단효력</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>판례는 어음채권의 행사는 원인채권의 시효를 중단시키지만, 원인채권의 행사만으로는 어음채권의 시효가 중단되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>판례(어음채권과 원인채권의 시효중단)</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>소장에서 청구 대상 채권 중 일부만 청구하면서 청구금액 확장의 뜻을 표시하였으나 소송 종료 시까지 실제로 확장하지 않은 경우, 나머지 부분에 대하여는 재판상 청구로 인한 시효중단의 효력이 발생하지 않지만 소송 계속 중에는 최고에 의한 권리행사가 지속된 것으로 볼 수 있다.</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>중단범위</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>판례는 미확장 부분에 재판상 청구의 중단효는 없으나, 소송 계속 중 최고가 지속되어 소송 종료 후 6월 내에 제174조 조치로 시효를 중단시킬 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>대판 2020.2.6. 2019다223723</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>제170조</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>확정판결에 의한 채권의 10년 소멸시효 완성이 임박한 경우, 시효중단을 위하여 다시 소를 제기할 소의 이익이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>소의이익</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>판례는 확정판결로 확정된 채권의 시효중단을 위한 재소의 이익을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>판례(시효중단을 위한 재소)</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>제165조</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>연대채무자 중 1인이 채무를 승인하여 그에 대한 소멸시효가 중단된 경우, 그 중단의 효력은 다른 연대채무자에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>승인은 제416조(이행청구)와 달리 절대적 효력 사유가 아니므로, 1인의 승인에 의한 시효중단은 다른 연대채무자에게 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>민법 제423조 · 제169조</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>제423조</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>공유물의 소수지분권자가 다른 공유자와 협의 없이 공유물을 독점적으로 점유·사용하는 경우, 다른 소수지분권자는 공유물의 보존행위로서 그 인도를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>보존행위</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소수지분권자는 보존행위로서 인도를 청구할 수 없고 자신의 지분권에 기초하여 방해 상태 제거나 방해행위 금지를 청구할 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>대판 2020.5.21. 2018다287522 전합</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>과반수 지분 공유자로부터 공유물의 특정 부분의 사용·수익을 허락받은 제3자의 점유는 적법하므로, 그 제3자는 소수지분권자에 대하여 점유로 인한 부당이득반환의무를 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>관리행위</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>판례는 과반수 지분권자의 사용·수익 허락이 관리행위로 적법하므로 제3자의 점유에 법률상 원인이 있다고 본다.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>대판 2002.5.14. 2002다9738</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>공유자 간의 공유물 사용·수익·관리에 관한 특약은 특정승계인에게 승계되지만, 특약 후 공유자가 변경되고 특약을 변경할 사정이 있는 경우에는 지분 과반수의 결정으로 기존 특약을 변경할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>특약변경</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>판례는 관리특약의 승계를 인정하면서도 제265조에 따른 과반수 결정으로의 변경 가능성을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>대판 2005.5.12. 2005다1827</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>부동산 공유자의 공유지분 포기 의사표시가 다른 공유자에게 도달하면, 등기 없이도 그 포기에 따른 물권변동의 효력이 발생한다.</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>등기요건</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>판례는 공유지분 포기도 법률행위에 의한 물권변동이므로 제186조에 따라 등기를 하여야 효력이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>대판 2016.10.27. 2015다52978 · 민법 제186조</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>저당권설정 당사자 사이의 특약으로 저당목적물인 토지에 대하여 법정지상권을 배제하는 약정을 하면 그 특약은 유효하다.</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>강행성</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>판례는 제366조가 공익상 지상권 설정을 강제하는 규정이므로 이를 배제하는 특약은 효력이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>대판 1988.10.25. 87다카1564</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>법정지상권을 취득한 자가 그 설정등기를 마치지 않은 사이에 토지가 매도된 경우, 법정지상권자는 등기 없이도 토지매수인에게 법정지상권을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>등기요부</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>법정지상권은 법률 규정에 의한 물권취득(제187조)이므로 등기 없이 성립하고 토지의 새 소유자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>민법 제187조 · 판례</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>법정지상권에 관한 지료가 아직 결정되지 않은 경우에도, 지료 지급이 2년 이상 연체되었음을 이유로 지상권소멸을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>연체요건</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>판례는 지료가 결정되지 않은 동안에는 지료 연체를 이유로 한 지상권소멸청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>판례(지료 미결정과 지상권소멸청구)</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>제287조</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>주택 신축공사를 한 수급인이 그 건물을 점유하면서 그 건물에 관하여 생긴 공사대금채권을 가지고 있는 경우, 수급인은 그 채권을 변제받을 때까지 건물을 유치할 권리가 있다.</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>판례는 신축건물에 관한 공사대금채권은 건물과 견련관계가 있어 유치권이 성립한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>대판 1995.9.15. 95다16202</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>유치권자가 점유를 침탈당하면 유치권은 소멸하지만, 점유회수의 소를 제기하여 승소판결로 점유를 회복하면 점유를 상실하지 않았던 것으로 되어 유치권이 되살아난다.</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>점유회복</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>판례는 점유 침탈 시 유치권 소멸을 인정하되, 점유회수의 소로 점유를 회복하면 유치권이 부활한다고 한다(회복 전에는 부활하지 않음).</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>대판 2012.2.9. 2011다72189 · 민법 제328조</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>제328조</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>소유자의 동의 없이 유치권자로부터 유치권의 목적물을 임차한 자의 점유는, 경락인에게 대항할 수 있는 권원에 기한 것이다.</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>처분권한</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>판례는 유치권자는 채무자의 승낙 없이 목적물을 임대할 처분권한이 없으므로, 소유자 동의 없는 임차인의 점유는 경락인에게 대항할 권원이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>대결 2002.11.27. 2002마3516</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>제324조</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>유치권의 성립요건인 점유에는 간접점유도 포함되며, 점유매개관계인 임대차 등이 종료한 후에도 직접점유자가 목적물을 점유한 채 반환하지 않고 있는 경우에는 점유매개관계가 단절되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>간접점유</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>판례는 간접점유에 의한 유치권 성립을 인정하고 매개관계 종료 후 미반환 시 매개관계 단절을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>판례(유치권과 간접점유)</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>유치권자가 소유자의 승낙을 받거나 보존에 필요한 범위에서 유치물을 사용하여 적법한 경우에는, 그 사용으로 얻은 차임 상당의 사용이익을 반환할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>이익반환</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>판례는 보존을 위한 사용 등으로 사용이 적법하더라도 유치권자는 차임 상당의 사용이익을 부당이득으로 반환해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>대판 2009.9.24. 2009다40684</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>제324조</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>제1차 부양의무자와 제2차 부양의무자가 동시에 존재하는 경우, 제1차 부양의무자는 특별한 사정이 없는 한 제2차 부양의무자에 우선하여 부양의무를 부담하므로, 제2차 부양의무자가 부양한 경우 소요 비용을 제1차 부양의무자에게 상환청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>순위구별</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>판례는 1차·2차 부양의무가 이행의 정도뿐 아니라 순위도 의미하므로 후순위자의 선행 부양 시 선순위자에 대한 상환청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>대판 2012.12.27. 2011다96932</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>제974조</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>부양료청구권 침해를 이유로 채권자취소권을 행사하는 경우, 그 제척기간은 부양료청구권이 협의·심판으로 구체적 권리로 성립한 시기부터 진행한다.</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>판례는 제척기간이 부양료청구권의 구체적 성립 시기가 아니라 제406조 제2항의 '취소원인을 안 날' 또는 '법률행위가 있은 날'부터 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>대판 2015.1.29. 2013다79870</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>친부가 사망한 후 계모와 생계를 같이 하는 계자녀는 인척으로서 계모에 대한 부양의무를 진다.</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>인척부양</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>계모자 관계는 인척이므로 제974조 제3호에 따라 생계를 같이 하는 경우에 한하여 부양의무가 있다.</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>민법 제974조 · 서울가법 2007브28</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>제974조</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>계약당사자가 상대방의 지시로 급부과정을 단축하여 상대방과 또 다른 계약관계에 있는 제3자에게 직접 급부한 경우(단축급부), 그 원인관계가 무효이거나 해제되었더라도 급부자는 제3자를 상대로 직접 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>삼각관계</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>판례는 단축급부 시 급부는 계약당사자 간에 이루어진 것이므로 제3자에 대한 직접 부당이득반환청구를 부정한다(위험 전가·항변권 침해 방지).</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>대판 2018.7.12. 2018다204992</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>제3자를 위한 계약에서 기본관계인 낙약자와 요약자 사이의 계약이 해제된 경우, 낙약자는 이미 제3자(수익자)에게 급부한 것을 제3자를 상대로 원상회복 또는 부당이득으로 반환을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>청산관계</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>판례는 제3자를 위한 계약의 청산은 계약당사자인 낙약자와 요약자 사이에서 이루어져야 하므로 낙약자가 수익자를 상대로 반환을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>대판 2005.7.22. 2005다7566</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>양도금지특약이 붙은 채권이 양도된 경우, 양수인의 악의 또는 중과실에 관한 증명책임은 채무자가 부담한다.</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>판례는 양도금지특약 위반 양도에서 양수인의 악의·중과실을 채무자가 증명해야 하며, 채무자는 채권자 불확지를 원인으로 변제공탁할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>대판 2000.12.22. 2000다55904</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>악의 또는 중과실로 양도금지특약부 채권을 양수한 후 채무자가 그 양도를 승낙한 경우, 그 양도는 추인되어 유효하게 되며 다른 약정이 없는 한 양도의 효과는 승낙 시부터 발생한다.</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>추인효과</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 사후승낙으로 무효인 양도가 추인되어 유효하되 소급효 없이 승낙 시부터 효과가 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>대판 2009.10.29. 2009다47685</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>물상보증인이 근저당권의 피담보채무만을 면책적으로 인수하고 이를 원인으로 근저당권 변경의 부기등기를 마친 경우, 그 변경등기는 물상보증인이 인수한 채무만 담보하고 그 후 다른 원인으로 부담하게 된 새로운 채무까지 담보하지는 않는다.</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>담보범위</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>판례는 면책적 채무인수에 따른 변경등기가 인수 채무에 한정되어 새로운 채무를 담보하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>대판 1999.9.3. 98다40657</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>근저당권의 채권 총액이 채권최고액을 초과하는 경우, 채무자인 근저당권설정자와 근저당권자 사이에서는 근저당권의 효력이 잔존 채무에 여전히 미친다.</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>최고액초과</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>판례는 채무자 겸 설정자에 대해서는 채권최고액을 초과해도 잔존 채무 전액에 근저당권 효력이 미친다고 한다(물상보증인·제3취득자는 최고액 한도).</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>판례(채권최고액 초과와 근저당권)</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>공동근저당권자가 목적 부동산 중 일부의 환가절차에서 우선하여 피담보채권 일부를 배당받은 경우, 나머지 목적 부동산에 대하여 행사할 수 있는 우선변제권은 최초의 채권최고액에서 이미 배당받은 금액을 공제한 나머지 채권최고액으로 제한된다.</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>누적배제</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>판례는 공동근저당권의 누적적 배당을 막기 위해 우선변제권 범위를 최고액에서 기배당액을 공제한 금액으로 제한하며, 초과채권이 이자·지연손해금인 경우에도 같다고 한다.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>대판 2017.12.21. 2013다16992 전합</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>대위변제자와 채무자 사이에 구상금에 관한 지연손해금 약정이 있는 경우, 그 약정은 변제자대위권을 행사하는 경우에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>권리구별</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>판례는 구상권과 변제자대위권은 별개의 권리이므로 구상금 지연손해금 약정은 구상권 행사에만 적용되고 변제자대위권 행사에는 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>대판 2009.2.26. 2005다32418</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>제481조</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>채권의 일부를 대위변제한 경우, 채권자는 대위변제자에 대하여 자기가 보유한 잔존 채권액의 범위에서 우선변제권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>일부대위</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>판례는 일부 대위변제 시에도 채권자가 대위변제자에 우선하여 잔존 채권액·피담보채권액 한도에서 후순위권리자보다 우선 배당받을 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>대판 2004.6.25. 2001다2426</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>제483조</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>물상보증인이 채무를 변제하거나 저당권 실행으로 저당물의 소유권을 잃었더라도 채무자에 대하여 구상권이 없는 경우에는, 채권자를 대위하여 채권 및 담보에 관한 권리를 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>구상전제</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>변제자대위는 구상권 확보를 위한 제도이므로 구상권이 없으면 대위도 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>민법 제481조 · 판례</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>제481조</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>이행지체를 이유로 계약을 해제하기 위한 이행의 최고는 반드시 미리 일정한 기간을 명시하여 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>방식</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>판례는 기간을 명시하지 않은 최고도 유효하며 최고 후 상당한 기간이 경과하면 해제권이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>대판 1994.11.25. 94다35930</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>신원보증인의 채무는 이행기의 정함이 없는 채무이므로, 피보증인의 불법행위가 있더라도 채권자로부터 이행청구를 받아야 비로소 지체책임이 생긴다.</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>지체시기</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>판례는 신원보증채무가 보증계약에 기한 별개의 이행기 없는 채무이므로 이행청구 시 지체에 빠진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>대판 2009.11.26. 2009다59671</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>매매계약이 무효인 경우, 악의의 매도인은 반환할 매매대금에 법정이자를 붙여 반환하여야 하며, 이 법정이자 지급은 부당이득반환의 성질을 가지므로 쌍방 의무가 동시이행관계에 있는지와 무관하다.</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>이자성질</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>판례는 제748조 제2항에 따른 악의 수익자의 법정이자 반환은 부당이득반환의 성질이지 이행지체 손해배상이 아니므로 동시이행 여부와 관계없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>대판 2017.3.9. 2016다47478</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>제748조</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>법정변제충당의 순서는 채무자의 변제제공 당시를 기준으로 정한다.</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>기준시</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>판례는 제477조 법정변제충당의 순서를 변제제공 시 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>대판 2015.11.26. 2014다71712</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>변제 제공 시 충당 지정이 없으면 법정충당에 따르며, 법정충당보다 유리한 충당효과를 주장하는 자가 그 사실을 증명하지 못하면 동순위 채무는 각 채무액에 안분비례하여 충당된다.</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>판례는 유리한 충당을 주장하는 자에게 증명책임이 있고 증명 실패 시 제477조 제4호에 따라 안분비례 충당된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>대판 2013.2.15. 2012다81913</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>비용·이자·원본에 대한 변제충당에서는 제479조의 법정 순서를 변제자가 일방적으로 지정하여 달리 변경할 수 없으나, 당사자 사이의 묵시적 합의에 의한 임의충당은 인정된다.</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>지정한계</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>판례는 제479조의 순서가 일방적 지정으로는 변경되지 않지만 당사자의 합의(묵시적 포함)로는 달리 정할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>판례(비용·이자·원본의 충당)</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>제479조</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>채권의 소멸시효가 완성된 경우, 채권자대위소송의 제3채무자는 피대위채권의 소멸시효 완성을 원용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>원용권자</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>판례는 시효이익을 직접 받는 자만 원용할 수 있고, 채권자대위소송의 제3채무자는 채무자가 채권자에 대해 갖는 항변으로 대항할 수 없어 시효를 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>대판 1997.7.22. 97다5749</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>채권자대위소송에서 제3채무자는 채무자의 항변권·형성권 등을 행사할 수는 없지만, 피보전채권의 발생원인인 법률행위가 무효라거나 그 권리가 변제로 소멸하였다는 등의 사실을 주장하여 다툴 수 있다.</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>항변범위</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>판례는 제3채무자가 채무자 권리의 존부 자체를 다투는 것은 허용하고 법원이 직권 심리·판단해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>대판 2015.9.10. 2013다55300</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>채권자대위소송 중 원고가 피대위채권 자체를 양수하여 양수금청구로 소를 변경한 경우, 당초의 채권자대위소송에 의한 시효중단의 효력은 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>중단유지</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>판례는 두 청구의 소송물이 동일한 권리에 관한 특정승계로서 시효중단의 효력이 특정승계인에게도 미치므로 당초의 시효중단 효력이 유지된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>대판 2010.6.24. 2010다17284</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사의 통지 후 채무자의 채무불이행을 이유로 제3채무자가 계약을 해제한 경우, 원칙적으로 제3채무자는 그 계약해제로써 대위채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>판례(전합)는 채무불이행에 따른 법정해제는 제405조 제2항의 처분이 아니므로 제3채무자가 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2011다87235 전합</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>사해행위 후 그 목적물에 제3자가 저당권 등을 취득한 경우, 채권자는 가액배상을 구할 수 있을 뿐 스스로 위험을 감수하면서 원물반환을 구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>선택권</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>판례는 채권자가 가액배상 대신 수익자 명의 등기 말소나 채무자 앞으로 직접 이전등기를 구하는 원물반환도 선택할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>대판 2018.12.28. 2017다265815</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>채권자가 사해행위취소 및 원상회복으로 수익자 명의 등기의 말소를 청구하여 승소판결이 확정된 후 그 등기 말소가 불가능하게 된 경우, 다시 수익자를 상대로 가액배상이나 채무자 앞으로의 이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>권리보호이익</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>판례는 원상회복청구권이 사실심 변론종결 시 선택에 따라 확정되므로, 말소 승소 확정 후 다시 다른 원상회복을 청구하는 것은 권리보호의 이익이 없어 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>대판 2018.12.28. 2017다265815</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>주택임대차보호법은 주택 소유자인 임대인과의 계약뿐 아니라 적법하게 임대차계약을 체결할 권한을 가진 임대인과의 계약에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>판례는 임대인이 소유자가 아니더라도 적법한 임대권한이 있으면 주임법이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>대판 2012.7.26. 2012다45689</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 대항요건인 주민등록은 임차인 본인의 것뿐만 아니라 그 배우자나 자녀 등 가족의 주민등록도 포함한다.</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>공시범위</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>판례는 점유보조자인 가족의 주민등록도 임차인의 대항요건으로 인정한다.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>대판 1996.1.26. 95다30338</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>매매계약 해제 전에 매수인으로부터 주택을 임차하여 대항요건을 갖춘 임차인은, 매매계약이 해제되면 새로운 소유자에게 자신의 임차권을 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>판례는 그 임차인이 제548조 제1항 단서의 보호받는 제3자에 해당하므로 매매계약 해제에도 불구하고 새 소유자에게 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>대판 2008.4.10. 2007다38908</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>매매계약에서 해약금의 기준이 되는 금원은 실제 교부받은 계약금이 아니라 약정한 계약금이므로, 계약금 일부만 지급된 경우 매도인이 실제 받은 금원의 배액을 상환하는 것으로는 계약을 해제할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>해약금기준</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>판례는 해약금 기준을 약정 계약금으로 보아 일부 수령액 배액 상환으로는 해제할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>대판 2015.4.23. 2014다231378</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>제565조</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>매매목적물 인도 전이라도 매수인이 매매대금을 완납한 때에는, 그 이후 목적물로부터 생긴 과실의 수취권은 매수인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>과실귀속</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>판례는 원칙적으로 인도 전 과실은 매도인에게 귀속하지만, 대금 완납 후에는 인도 전이라도 매수인에게 과실수취권이 귀속된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>대판 1993.11.9. 93다28928</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>부동산 매매대금 채권이 소유권이전등기청구권과 동시이행관계에 있더라도, 매매대금청구권은 그 지급기일 이후 소멸시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>판례는 동시이행항변권은 이행거절권능에 불과하므로 매매대금청구권의 시효 진행을 막지 못한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>대판 1991.3.22. 90다9797</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>토지 매수인이 소유권이전등기를 마치기 전에 매매계약의 이행으로 토지를 인도받아 점유·사용하는 경우, 매도인은 매수인에 대하여 그 점유·사용으로 인한 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>점유권원</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>판례는 매매계약의 이행으로 인도받아 점유하는 매수인은 적법한 권원이 있으므로 매도인이 부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>판례(매수인의 점유와 부당이득)</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>미성년자가 책임능력이 있어 스스로 불법행위책임을 지는 경우에도, 그 손해가 감독의무자의 의무 위반과 상당인과관계가 있으면 감독의무자는 일반불법행위자로서 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>감독책임</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>판례는 책임능력 있는 미성년자의 경우에도 감독의무 위반과 상당인과관계가 있으면 감독자의 제750조 책임을 인정하되, 그 증명책임은 주장하는 자에게 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>대판 2003.3.28. 2003다5061</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>제756조의 사용자와 피용자의 관계는 반드시 유효한 고용관계가 있는 경우에 한하며, 사실상의 지휘·감독관계만으로는 사용자책임이 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>관계범위</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>판례는 유효한 고용관계가 아니어도 사실상 지휘·감독 아래 사무를 집행하는 관계이면 사용자·피용자 관계가 인정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>대판 1998.8.21. 97다13702</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>도급인이 수급인의 일의 진행 및 방법에 관하여 구체적인 지휘·감독권을 유보한 경우, 수급인이 고용한 제3자의 불법행위로 인한 손해에 대하여 도급인은 제756조의 사용자책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>도급사용자</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>판례는 도급인이 구체적 지휘·감독권을 보유하면 실질적으로 사용자·피용자 관계와 같으므로 사용자책임을 면할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>대판 1988.6.14. 88다카102 · 민법 제757조</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>부부가 아직 이혼하지 않았더라도 실질적으로 부부공동생활이 파탄되어 회복할 수 없을 정도에 이른 경우, 제3자가 부부의 일방과 한 성적 행위는 배우자에 대한 불법행위를 구성하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>파탄예외</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>판례(전합)는 혼인이 실질적으로 파탄된 후의 제3자의 성적 행위는 배우자에 대한 불법행위가 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>대판 2014.11.20. 2011므2997 전합</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>부동산 매수인이 임대차보증금반환채무를 인수하면서 그 채무액을 매매대금에서 공제하기로 약정한 경우, 그 인수는 특별한 사정이 없는 한 면책적 채무인수가 아니라 이행인수로 보아야 한다.</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>인수성질</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>판례는 채권자(임차인)의 승낙이 없는 한 매도인을 면책시키는 면책적 채무인수가 아니라 이행인수로 본다.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>대판 2006.9.22. 2006다135</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>임대차보증금반환채무의 면책적 인수에 대한 임차인의 승낙은 반드시 명시적 의사표시에 의하여야 하고 묵시적 의사표시로는 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>승낙방식</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>판례는 임차인의 승낙이 묵시적 의사표시로도 가능하다고 한다(채무자·인수인은 제455조에 따라 최고할 수 있고 상당기간 내 확답 없으면 거절 간주).</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>대판 2015.5.29. 2012다84370</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>채권자의 승낙에 의하여 효력이 생기는 채무인수에서 채권자가 일단 승낙을 거절하면, 그 후 다시 승낙하여도 채무인수로서의 효력이 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>거절확정</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>판례는 채권자의 승낙 거절로 채무인수가 확정적으로 효력을 잃어 사후 승낙으로 부활하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>대판 1998.11.24. 98다33765</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>유류분반환청구로 반환되어야 할 유증 또는 증여의 목적 재산이 타인에게 양도된 경우, 그 양수인이 양도 당시 유류분권리자를 해함을 알았던 때에는 양수인에 대하여도 그 재산의 반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>악의양수인</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>판례는 악의의 양수인에 대한 유류분 반환청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>대판 2002.4.26. 2000다8878</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>제1115조</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>10001</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>유류분반환청구권의 행사로 생기는 원물반환의무 또는 가액반환의무는 이행기한의 정함이 없는 채무이므로, 반환의무자는 그 의무에 대한 이행청구를 받은 때에 비로소 지체책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>지체시기</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>판례는 유류분 반환의무를 기한의 정함이 없는 채무로 보아 이행청구를 받은 때부터 지체책임이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>대판 2013.3.14. 2010다42624</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>제1115조</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>10002</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>공동상속인 중에 피상속인으로부터 생전 증여로 특별수익을 한 자가 있는 경우, 그 증여는 제1114조의 적용이 배제되어 상속개시 1년 이전의 것인지 등을 묻지 않고 유류분 산정의 기초재산에 산입된다.</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>산입범위</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>판례는 공동상속인의 특별수익에 대해서는 제1114조가 적용되지 않아 시기·악의 여부와 무관하게 기초재산에 산입된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>대판 1996.2.9. 95다17885</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>제1114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>10003</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>유류분액 산정에서 반환의무자가 증여받은 재산의 시가는 상속개시 당시를 기준으로 산정하되, 원물반환이 불가능하여 가액반환을 명하는 경우 그 가액은 사실심 변론종결 시를 기준으로 산정한다.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>판례는 증여재산 시가는 상속개시 시, 가액반환액은 사실심 변론종결 시를 기준으로 산정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>대판 2005.6.23. 2004다51887</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>제1113조</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>10004</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>유류분반환청구 소송에서 법원은 처분권주의의 원칙상 유류분권리자가 특정한 대상과 범위를 넘어서 청구를 인용할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>처분권주의</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>판례는 유류분 반환의 목적물 이전·인도 청구에서 그 대상·범위를 특정해야 하고 법원이 이를 넘어 인용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>대판 2013.3.14. 2010다42624</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>제1115조</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>10005</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>공사도급계약의 도급인이 입찰절차를 거쳐 낙찰자를 결정한 경우, 입찰을 실시한 자와 낙찰자 사이에는 도급계약의 본계약 체결의무를 내용으로 하는 예약의 계약관계가 성립한다.</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>예약성립</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>판례는 낙찰자 결정으로 본계약 체결의무를 내용으로 하는 예약이 성립하고, 정당한 이유 없는 체결 거절 시 예약채무불이행 책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>대판 2011.11.10. 2011다41659</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>10006</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>매매의 일방예약이 성립하려면 본계약의 요소가 되는 매매목적물, 이전방법, 매매가액 및 지급방법 등의 내용이 확정되어 있거나 확정할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>성립요건</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>판례는 일방예약의 성립에 본계약 요소의 확정 가능성을 요구한다.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>대판 1993.5.27. 93다4908</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>10007</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>매매예약 완결권은 형성권으로서 행사기간의 약정이 있으면 그 기간 내에, 약정이 없으면 예약 성립 시부터 10년 내에 행사하여야 하며, 그 기간이 지나면 목적 부동산을 인도받은 경우라도 제척기간 경과로 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>제척기간</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>판례는 예약완결권을 형성권으로 보아 10년의 제척기간을 적용하고, 목적물 인도 여부와 무관하게 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>대판 1997.7.25. 96다47494</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>10008</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>예약완결권을 소장 부본 송달로 재판상 행사하는 경우, 소장 부본이 제척기간 내에 상대방에게 송달되어야 예약완결권을 제척기간 내에 적법하게 행사한 것이 된다.</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>행사시점</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>판례는 재판상 행사 시 소장 부본이 제척기간 내에 송달되어야 적법한 행사로 본다.</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>대판 2019.7.25. 2019다227817</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>10009</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>고의의 불법행위로 인한 손해배상채권의 양도가 사해행위에 해당하는 경우, 그 손해배상채권의 채무자가 양도인에 대한 별도의 채권자 지위에서 양수인에게 채권자취소권을 행사하여 채권양도의 취소와 자신 앞으로의 가액배상을 구하는 것은 제496조에 반하지 않아 허용된다.</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>상계금지</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>판례는 이러한 채권자취소권 행사가 상계가 아니므로 제496조 위반이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>대판 2011.6.10. 2011다8980</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>10010</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>수탁보증인의 주채무자에 대한 사전구상권에는 담보제공청구권의 항변권이 부착되어 있으므로, 주채무자가 사전에 담보제공청구권의 항변권을 포기한 경우에는 사전구상권을 자동채권으로 하는 상계가 허용된다.</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>항변권포기</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>판례는 사전구상권에 제443조 담보제공청구권 항변권이 붙어 원칙적으로 상계가 안 되지만, 그 항변권을 포기하면 상계가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>판례(사전구상권과 상계)</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>제442조</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>10011</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>가정법원 심판으로 구체적 내용과 범위가 확정된 양육비 채권 중 이미 이행기에 도달한 부분은 권리자의 의사에 따라 상계의 자동채권으로 사용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>상계가부</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>판례는 구체화되고 이행기가 도래한 양육비채권은 권리자의 의사에 따라 자동채권으로 상계할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>판례(양육비채권과 상계)</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>10012</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>상속의 포기는 민법 제406조 제1항의 '재산권에 관한 법률행위'에 해당하므로 사해행위취소의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>판례는 상속포기가 인격적 결단으로서 재산권에 관한 법률행위에 해당하지 않아 사해행위취소의 대상이 되지 못한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>대판 2011.6.9. 2011다29307</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>제1041조</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>10013</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>한정승인자로부터 상속재산에 관하여 저당권 등 담보권을 취득한 사람과 상속채권자 사이의 우열관계는 민법상 일반원칙에 따르며, 상속채권자는 한정승인 사유만으로 우선적 지위를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>우선권</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>판례는 한정승인이 상속재산 처분을 직접 제한하거나 상속채권자에게 우선권을 부여하지 않으므로 일반원칙에 따라 우열을 정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>대판 2010.3.18. 2007다77781 전합</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>제1028조</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>10014</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>상속인이 피상속인의 손해배상채권을 추심하여 변제받은 행위는 상속재산의 처분행위에 해당하여 단순승인으로 간주되므로, 그 이후에 한 상속포기는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>법정단순승인</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>판례는 상속재산의 처분행위를 제1026조 제1호의 법정단순승인 사유로 보아 이후의 상속포기를 무효로 본다.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>민법 제1026조 제1호 · 판례</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>제1026조</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>10015</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>유치권을 사후에 포기한 경우 유치권은 곧바로 소멸하며, 그 유치권 포기로 인한 소멸은 포기의 의사표시의 상대방뿐 아니라 그 이외의 사람도 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>포기효과</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>판례는 유치권 포기 특약이 유효하고 사후 포기 시 곧바로 소멸하며 그 소멸을 제3자도 주장할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>대판 2016.5.12. 2014다52087</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>10016</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>변시10</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>공사대금채권으로 유치권을 행사하는 자가 스스로 유치물인 주택에 거주하며 사용하는 경우, 이는 유치물의 보존에 필요한 사용에 해당하므로 채무자는 유치권 소멸을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>보존사용</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>판례는 유치권자의 주택 거주·사용을 보존에 필요한 사용으로 보아 제324조의 소멸청구 사유가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>대판 2009.9.24. 2009다40684</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>제324조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:H665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -22184,6 +22184,4886 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>901</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>정관에 의한 법인 이사의 대표권 제한은 등기하지 아니하면 제3자의 선의·악의를 묻지 않고 제3자에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>민법 제60조는 이사의 대표권 제한을 등기하지 않으면 제3자에게 대항할 수 없다고 정하며, 판례는 그 제3자에 악의자도 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>민법 제60조</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>제60조</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>902</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>제한능력을 이유로 한 법률행위의 취소는 선의의 제3자에게도 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>절대취소</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>제한능력자 보호의 취지상 제한능력을 이유로 한 취소는 선의의 제3자에게도 대항할 수 있는 절대적 취소이다.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>민법 제5조·제141조</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>제141조</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>903</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>불공정한 법률행위로서 무효인 대물변제계약의 목적부동산이 제3자에게 이전된 경우, 그 제3자가 선의라면 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>절대무효</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>제104조 위반은 절대적 무효이므로 누구에 대해서도 무효를 주장할 수 있고, 선의의 제3자도 보호되지 않는다는 것이 판례이다.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>대판 1963.11.7. 63다479 · 민법 제104조</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>904</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>무권대리행위의 추인은 계약시에 소급하여 효력이 생기지만, 그 소급효로 등기부상 권리를 취득한 제3자의 권리를 해할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>소급제한</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>민법 제133조 단서는 추인의 소급효로 제3자의 권리를 해하지 못한다고 하고, 판례는 그 제3자를 등기부상 권리를 주장할 수 있는 자로 본다.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>민법 제133조 · 대판 1963.4.18. 62다223</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>제133조</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>905</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>민법 제110조 제3항의 '선의의 제3자'는 사기에 의한 의사표시를 기초로 하여 새로운 이해관계를 맺은 자를 한정하여 가리킨다.</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>판례는 제110조 제3항의 제3자를 당사자·포괄승계인 외에 사기에 의한 의사표시를 기초로 새로운 이해관계를 맺은 자로 한정한다.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>민법 제110조 · 판례</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>제110조</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>906</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>여러 개의 계약이 전체적으로 일체로서 행하여져 하나의 계약과 같은 불가분의 관계에 있는 경우, 하나의 계약에 대한 기망 취소의 의사표시는 법률행위 일부취소의 법리에 따라 전체 계약에 대한 취소의 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>일부취소</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>판례는 불가분 관계의 여러 계약에서 일부에 대한 기망 취소가 전체 계약에 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>대판 2013.5.9. 2012다115120</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>제137조</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>907</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>무권리자의 처분이 계약으로 이루어진 경우 권리자가 추인하면, 그 효과는 추인한 때부터 장래를 향하여 권리자에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>소급효</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>판례는 무권대리 추인 규정(제130조·제133조)을 유추적용하여 무권리자 처분의 추인 효과가 원칙적으로 계약 체결 시로 소급하여 권리자에게 귀속된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>대판 2017.6.8. 2017다3499</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>제130조</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>908</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>무효행위의 추인은 당사자가 이전 법률행위가 무효임을 알고 그 효과를 자기에게 귀속시키도록 하는 것으로, 묵시적인 방법으로도 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>추인방식</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>판례는 무효행위의 추인을 인정하되 묵시적 추인은 본인이 법적 지위를 충분히 이해하고 결과 귀속을 승인한 것으로 볼 사정이 있어야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>대판 2014.3.27. 2012다106607</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>제139조</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>909</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>토지거래허가를 받지 않아 유동적 무효 상태인 매매계약에서도, 매도인은 민법 제565조 제1항에 따라 계약금의 배액을 상환하고 계약을 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>해약금</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>판례는 유동적 무효 상태에서도 해약금에 의한 해제는 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>대판 1997.6.27. 97다9369 · 민법 제565조</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>제565조</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>910</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>종중은 자기 명의로 신축건물의 소유권보존등기를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>등기능력</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>부동산등기법 제26조는 대표자·관리인이 있는 법인 아닌 사단을 등기권리자로 인정하므로 종중 명의 보존등기가 가능하다.</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>부동산등기법 제26조</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>911</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>비법인사단이 타인 간의 금전채무를 보증하는 행위는 총유물의 관리·처분행위에 해당하여 사원총회의 결의를 거쳐야 한다.</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>판례(전합)는 비법인사단의 금전채무 보증은 총유물 자체의 관리·처분이 따르지 않는 단순한 채무부담행위이므로 총유물의 관리·처분행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>대판 2007.4.19. 2004다60072 전합</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>912</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>대표자나 관리인이 있는 비법인사단은 그 이름으로 당사자가 될 수 있으므로, 비법인사단에 대한 집행권원으로 그 사단재산에 대하여 강제집행을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>당사자능력</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>민사소송법 제52조에 따라 비법인사단이 당사자능력을 가지므로 그 단체재산에 강제집행이 가능하다.</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>민사소송법 제52조</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>913</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>비법인사단의 대표자가 직무에 관하여 타인에게 손해를 가한 경우, 그 사단은 민법 제35조 제1항의 유추적용에 의하여 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>불법행위</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>판례는 비법인사단에 제35조 제1항을 유추적용하고 직무관련성을 외형상 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>대판 2003.7.25. 2002다27088</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>914</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>법인 대표자가 정관에 위반하여 한 대표행위는 그 제한을 등기하지 않았더라도 악의의 제3자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>법인의 경우 대표권 제한은 등기하지 않으면 제60조에 따라 악의의 제3자에게도 대항할 수 없다(비법인사단은 등기 없이도 상대방이 알았거나 알 수 있었으면 무효).</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>민법 제60조</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>제60조</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>915</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>공유물분할의 조정절차에서 현물분할의 협의가 성립하여 조서에 기재되면, 재판에 의한 공유물분할처럼 그 즉시 공유관계가 소멸하고 각 공유자가 단독소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>물권변동</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>판례(전합)는 조정 성립만으로는 물권변동이 일어나지 않고, 분필 후 다른 공유자의 지분을 이전받아 등기를 마쳐야 단독소유권을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>대판 2013.11.21. 2011두1917 전합</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>제187조</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>916</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>합유재산을 합유자 1인의 단독소유로 소유권보존등기를 한 경우, 그 등기는 원인무효이고 다른 합유자는 이를 말소시킨 다음 새로이 합유의 소유권보존등기를 신청할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>원인무효</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>판례는 합유물의 단독 보존등기는 실질관계에 부합하지 않는 원인무효 등기이므로 말소 후 합유등기를 신청할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>대판 2017.8.18. 2016다6309</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>제271조</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>917</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>부동산 공유자 1인이 공유물의 보존행위로서 일부 지분에 관해서만 재판상 청구를 한 경우, 시효중단의 효력은 그 공유자와 청구한 소송물에 한하여 발생한다.</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>중단범위</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>판례는 공유물 전부 말소를 구할 수 있더라도 일부 지분만 청구하면 시효중단도 그 범위에 한정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>대판 1999.8.20. 99다15146</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>918</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계를 표상하는 공유지분에 근저당권이 설정된 후 구분소유적 공유관계가 해소되면, 그 근저당권은 근저당권설정자의 단독소유로 분할된 토지에 집중된다.</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>권리존속</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>판례는 근저당권이 종전 지분 비율대로 분할된 토지 전부에 그대로 존속할 뿐 설정자 단독소유 토지에 당연히 집중되는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>대판 2014.6.26. 2012다25944</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>919</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에 있는 자는 제3자의 방해행위에 대하여 전체 토지에 관하여 공유물의 보존행위로서 그 배제를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>대외관계</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유관계가 대외적으로 단순한 공유관계이므로 자기 구분 부분 외에도 전체 토지에 대한 방해배제를 보존행위로 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>판례(구분소유적 공유와 보존행위)</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>920</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>신축 건물에 하자가 있고 그 하자·손해에 상응하는 금액이 공사잔대금액 이상이어서 도급인이 공사잔대금 채권 전부에 동시이행 항변을 한 경우, 수급인은 하자보수의무 등의 이행제공을 하지 않은 이상 공사잔대금 채권에 기한 유치권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>변제기</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>판례는 동시이행 항변으로 공사잔대금 채권의 변제기가 도래하지 않은 것과 마찬가지가 되어 유치권의 성립요건이 갖춰지지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>대판 2014.1.16. 2013다30653</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>921</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>계약명의신탁(부동산실명법 시행 후)에서 명의수탁자가 명의신탁자에게 반환하여야 할 부당이득은 매수자금이며 부동산 자체가 아니므로, 그 반환청구권은 부동산에 관하여 생긴 채권으로서 유치권의 피담보채권이 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 시행 후 계약명의신탁에서 수탁자의 부당이득 반환대상이 매수자금이므로 부동산과 견련성 있는 채권이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>대판 2009.3.26. 2008다34828</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>922</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>건물의 옥탑·외벽 등에 설치된 간판이 독립된 물건으로서 과다한 비용 없이 건물로부터 분리될 수 있는 경우, 간판 설치공사 대금채권은 그 건물 자체에 관하여 생긴 채권이 아니다.</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>판례는 분리 가능한 간판 설치공사 대금채권은 건물과 견련성이 없어 건물에 대한 유치권의 피담보채권이 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>대판 2007.9.7. 2005다16942</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>923</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>건축공사에 사용된 자재대금채권은 그 건축자재로 신축된 건물에 관하여 생긴 채권이므로, 이를 피담보채권으로 한 건물에 대한 유치권 행사는 적법하다.</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>판례는 자재대금채권은 자재를 공급받은 수급인과의 매매대금채권에 불과하여 건물과 견련성이 없으므로 그에 기한 유치권 행사는 부적법하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>대판 2012.1.26. 2011다96208</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>924</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>유치권의 피담보채권의 소멸시효기간이 확정판결에 의하여 10년으로 연장된 경우, 유치권이 성립된 부동산의 매수인은 종전의 단기소멸시효를 원용할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>시효원용</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>판례는 판결로 시효가 연장되면 그 부동산 매수인도 종전의 단기시효를 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>대판 2009.9.24. 2009다39530</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>제165조</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>925</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>의사표시의 착오가 표의자의 중대한 과실로 발생하였더라도, 상대방이 표의자의 착오를 알고 이를 이용한 경우에는 표의자가 의사표시를 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>중과실예외</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>판례는 제109조 제1항 단서가 상대방 보호를 위한 것이므로 상대방이 착오를 알고 이용한 경우에는 중과실이 있어도 취소할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>대판 2014.11.27. 2013다49794</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>926</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>보험모집종사자가 설명의무를 위반하여 고객이 보험계약의 중요사항에 착오를 일으켜 계약을 체결한 경우, 그 착오가 없었다면 계약을 체결하지 않았을 것이 명백하다면 고객은 착오를 이유로 보험계약을 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>동기착오</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>판례는 설명의무 위반으로 인한 동기의 착오라도 그 동기가 표시되어 중요부분의 착오로 인정되면 취소할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>대판 2018.4.12. 2017다229536</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>927</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>경과실에 의한 착오를 이유로 의사표시를 취소한 경우, 표의자는 상대방이 그 의사표시의 유효를 믿었음으로 인하여 발생한 손해에 대하여 불법행위 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>위법성</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>판례는 적법한 착오 취소권 행사는 위법하지 않으므로 경과실에 의한 착오 취소자는 상대방의 신뢰이익 손해에 대해 불법행위 책임을 지지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>대판 1997.8.22. 97다13023</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>928</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>동일 부동산에 등기명의인을 달리하여 중복된 소유권보존등기가 이루어진 경우, 선등기가 원인무효가 아니라면 후등기는 원칙적으로 무효이고 그 후등기를 근거로 등기부취득시효의 완성을 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>중복등기</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>판례는 1부동산1용지주의상 선등기가 유효하면 후행 보존등기는 무효이므로 그에 기한 등기부취득시효를 인정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>대판 1990.11.27. 87다카2961 전합</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>929</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>중복 소유권보존등기에서 후등기 명의인의 점유취득시효가 완성되었다면, 선등기가 원인무효가 아니더라도 후등기가 실체관계에 부합하므로 유효하다.</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>중복등기</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>판례는 선등기가 유효한 한 후행 보존등기는 실체관계 부합 여부와 관계없이 무효이고, 그 말소를 구하는 것이 신의칙 위반·권리남용이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>대판 2008.2.14. 2007다63690</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>930</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>건물을 매수하여 점유하고 있으나 아직 소유권이전등기를 갖추지 못한 자에 대하여도, 그 건물로 불법점유를 당하고 있는 토지소유자는 건물의 철거를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>철거상대방</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>판례는 건물 매수인이 사실상 처분권을 가지므로 등기 명의가 없어도 토지소유자가 그를 상대로 철거를 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>대판 1988.9.27. 88다카4017</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>931</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>미등기 무허가건물의 양수인은 소유권이전등기를 갖추지 못하였더라도 그 건물의 불법점거자에 대하여 직접 자신의 소유권에 기하여 명도를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>소유권취득</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>판례는 미등기 무허가건물 양수인은 등기 없이 소유권을 취득하지 못하고 관습상 물권도 없으므로 직접 소유권에 기한 명도청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>대판 2007.6.15. 2007다11347</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>제213조</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>932</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>미등기 또는 무허가 건물이라도 국민의 주거생활 용도로 사용되는 주택에 해당하면 주택임대차보호법의 적용대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>판례(전합)는 주임법이 등기·허가 여부를 구별하지 않으므로 미등기·무허가 주택도 적용대상이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>대판 2007.6.21. 2004다26133 전합</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>933</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>건물 소유를 목적으로 하는 토지 임대차에서 종전 임차인으로부터 미등기 무허가건물을 매수하여 점유하는 임차인은, 임대인에 대하여 지상물매수청구권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>매수청구</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>판례는 미등기 무허가건물이라도 제643조의 지상물매수청구권의 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>대판 2013.11.28. 2013다48364 등</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>934</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>계약명의신탁에서 명의신탁 약정 사실을 알지 못한 매도인과 매매계약을 체결한 경우, 명의신탁 약정은 무효이지만 명의수탁자 명의의 물권변동은 유효하여 수탁자가 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>선의매도인</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제2항 단서에 따라 선의의 매도인과 체결한 계약명의신탁에서는 수탁자가 완전한 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>민법 제4조②단서 · 판례</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>935</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>계약명의신탁에서 매도인이 명의신탁 약정을 알고 있었던 경우(악의), 명의수탁자 명의의 소유권이전등기는 무효이고 소유권은 매도인에게 남으며, 수탁자가 그 부동산을 제3자에게 처분하면 매도인에 대한 불법행위가 된다.</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>악의매도인</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>판례는 악의 매도인의 경우 수탁자 등기가 무효이고 수탁자의 처분이 매도인의 소유권 침해 불법행위가 되지만, 매매대금을 수령한 매도인에게는 손해가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>대판 2013.9.12. 2010다95185</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>936</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제2항 단서로 신탁부동산의 소유권을 취득한 계약명의신탁의 수탁자가 채무초과 상태에서 명의신탁자나 그가 지정하는 사람에게 신탁부동산을 양도하는 행위는 사해행위가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>판례는 수탁자가 완전한 소유권을 취득한 이상 그 양도가 일반채권자의 책임재산을 감소시키면 사해행위가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>대판 2008.9.25. 2007다74874</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>937</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>부동산실명법 시행으로 권리를 상실한 종전 명의신탁자가 부당이득의 법리에 따라 취득한 부동산에 대한 부당이득반환청구권(등기청구권)은, 명의신탁자가 그 부동산을 점유·사용하여 온 경우에도 소멸시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>판례는 이 부당이득반환청구권에 기한 등기청구권은 점유·사용 여부와 관계없이 10년의 소멸시효가 진행한다고 한다(매수인의 점유 등기청구권 법리와 구별).</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>대판 2009.7.9. 2009다23313</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>938</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>제3자가 개입된 처분행위로 소유권이전등기가 마쳐진 경우, 그 등기의 추정력을 번복하기 위하여 무효사실을 증명할 책임은 말소를 청구하는 전 소유명의인에게 있다.</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>판례는 제3자가 개입되어도 현 명의인의 등기가 적법히 이루어진 것으로 추정되므로, 무권한·서류위조 등 무효사실은 말소를 구하는 전 명의인이 증명해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>대판 2009.9.24. 2009다37831</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>939</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>매매계약을 체결할 대리권을 수여받은 대리인은 특별한 사정이 없는 한 그 매매계약에서 약정한 바에 따라 중도금이나 잔금을 수령할 권한이 있다.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>판례는 매매계약 체결 대리권에 중도금·잔금 수령권한이 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>대판 1992.4.14. 91다43107</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>제114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>940</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>진의 아닌 의사표시가 대리인에 의하여 이루어지고 그 대리인의 진의가 본인의 이익에 반하는 배임적인 것임을 상대방이 알았거나 알 수 있었던 경우, 제107조 제1항 단서의 유추해석상 본인은 그 대리행위에 대하여 책임을 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>대리권남용</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>판례는 배임적 대리행위에서 상대방이 악의·과실인 경우 제107조 제1항 단서 유추적용으로 본인에게 효과가 귀속되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>대판 1987.7.7. 86다카1004</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>제107조</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>941</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>무권대리인의 상대방에 대한 책임은 무과실책임이므로, 무권대리행위가 제3자의 위법행위로 야기되었더라도 책임이 부정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>무과실책임</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>판례는 제135조 책임을 무과실책임으로 보아 제3자의 기망·문서위조로 야기된 경우에도 책임이 부정되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>대판 2014.2.27. 2013다213038</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>제135조</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>942</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>무권대리인이 계약에서 정한 채무를 이행하지 않은 경우, 그 계약에 손해배상액 예정 조항이 있으면 무권대리인은 그 조항에서 정한 바에 따라 산정한 손해액을 지급하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>배상범위</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>판례는 무권대리인의 이행책임에 제398조의 손해배상액 예정 조항이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>대판 2018.6.28. 2018다210775</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>제135조</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>943</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>3자간 등기명의신탁에 의한 등기가 유효기간 경과로 무효로 된 경우, 부동산을 인도받아 점유하고 있는 명의신탁자의 매도인에 대한 소유권이전등기청구권은 소멸시효가 진행하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>판례는 매수인이 목적물을 인도받아 점유하면 등기청구권의 시효가 진행하지 않는 법리가 3자간 명의신탁 무효의 경우에도 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>대판 2013.12.12. 2013다26647</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>944</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>동일인 소유의 토지와 그 지상 건물에 공동저당권이 설정된 후 그 건물이 철거되고 다른 건물이 신축되어 저당물 경매로 토지와 신축건물이 다른 소유자에게 속하게 된 경우, 특별한 사정이 없는 한 신축건물을 위한 제366조의 법정지상권은 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>공동저당특칙</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>판례(전합)는 공동저당권자의 담보가치 파악 보호를 위해, 신축건물에 토지 저당권과 동순위 공동저당을 설정하는 등 특별한 사정이 없는 한 신축건물의 법정지상권을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>대판 2003.12.18. 98다43601 전합</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>945</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>채권의 양수인이 채권양도의 대항요건을 갖추지 못한 상태에서 채무자를 상대로 재판상 청구를 한 경우에도, 소멸시효 중단사유인 재판상 청구에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>중단효력</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>판례는 대항요건을 갖추지 못한 양수인의 재판상 청구도 채권의 동일성이 유지되어 시효중단 사유인 재판상 청구에 해당한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>판례(대항요건 미비 양수인의 재판상 청구)</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>946</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>소멸시효의 기산점인 '권리를 행사할 수 있는 때'는 권리행사에 법률상의 장애가 없는 경우를 말하며, 권리자의 법률지식 부족이나 권리존재의 부지 등 사실상의 장애는 시효 진행을 막지 못한다.</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>판례는 시효 기산점을 법률상 장애 부존재 기준으로 보고 사실상 장애는 고려하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>대판 1982.1.19. 80다2626</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>947</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성되기 전까지 점유자가 점유로 인하여 얻은 이익에 대하여, 소유명의자는 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>부당이득</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>판례는 시효취득자가 소유명의자에 대해 이전등기청구권을 가지므로 소유명의자는 점유로 인한 부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>대판 1993.5.25. 92다51280</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>948</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>점유취득시효 완성 후 등기 전에 시효취득자가 원소유자가 설정한 근저당권의 피담보채무를 변제한 경우, 시효취득자는 원소유자에게 대위변제를 이유로 구상권을 행사하거나 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>용인부담</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>판례는 피담보채무 변제가 시효취득자 자신이 용인해야 할 부담을 제거하여 완전한 소유권을 확보하기 위한 자기 이익을 위한 행위이므로 구상권·부당이득반환청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>대판 2006.5.12. 2005다75910</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>949</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>진정한 권리자가 아니었던 채무자 또는 물상보증인이 채권자에게 저당권설정등기를 마쳐준 후 그 부동산을 시효취득하는 경우, 저당목적물의 시효취득으로 저당권자의 권리는 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>용인부담</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>판례는 채무자·물상보증인이 이미 저당권의 존재를 용인하고 점유한 것이므로 시효취득으로도 저당권자의 권리가 소멸하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>대판 2015.2.26. 2014다21649</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>950</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>가등기가 경료된 부동산에 대해 점유취득시효가 완성된 후 그 가등기에 기한 본등기가 경료된 경우, 시효완성 후의 취득자인지 여부는 가등기 시가 아니라 본등기 시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>판례는 가등기는 순위보전의 효력만 있고 물권변동 효력은 본등기 시에 발생하므로, 시효완성 후 취득자 판단은 본등기 시를 기준으로 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>판례(가등기와 취득시효)</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>951</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>근저당권의 피담보채권이 확정되기 전에 채권의 일부를 양도하거나 대위변제한 경우, 그 근저당권은 양수인이나 대위변제자에게 이전한다.</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>확정전후</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>판례는 확정 전에는 채권이 계속 증감변동하므로 일부 양도·대위변제로 근저당권이 이전할 여지가 없고, 확정 후에야 잔여 담보 부분이 부기등기 여부와 관계없이 이전된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>대판 2002.7.26. 2001다53929</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>952</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>불법하게 말소된 근저당권설정등기의 회복등기청구는 그 등기말소 당시의 소유자를 상대로 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>청구상대방</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>판례는 말소회복등기청구의 상대방을 말소 당시의 소유자로 본다.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>대판 1969.3.18. 68다1617</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>953</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>근저당권자가 피담보채무 불이행을 이유로 경매신청을 한 경우 경매신청 시에 채무액이 확정되며, 그 후 경매개시결정이 있은 뒤 경매신청이 취하되더라도 채무확정의 효과는 번복되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>확정시기</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>판례는 근저당권자 자신의 경매신청 시 채무액이 확정되고 취하로도 번복되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>대판 2002.11.26. 2001다73022</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>954</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>사해행위 이전에 임대차계약이 체결되어 임차인이 임차보증금에 대해 우선변제권을 가진 경우, 수익자가 반환할 부동산 가액에서 그 우선변제권 있는 임차보증금 반환채권액을 공제하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>공제여부</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>판례는 사해행위 이전에 체결된 임대차의 우선변제권 있는 보증금은 일반채권자의 공동담보에서 제외되므로 가액반환액에서 공제한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>대판 2018.9.13. 2018다215756</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>955</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>사해행위 이후에 비로소 채무자가 부동산을 임대한 경우에도, 그 임차보증금을 가액반환의 범위에서 공제하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>공제여부</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>판례는 사해행위 이후의 임대차 보증금에 해당하는 부분도 일반채권자의 공동담보에 제공되어 있으므로 공제하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>대판 2018.9.13. 2018다215756</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>956</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>채무자가 유일한 재산에 관한 매매예약의 예약완결권이 제척기간 경과로 소멸할 예정인 상태에서 그 제척기간을 연장하기 위하여 새로 매매예약을 하는 행위는 사해행위가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>사해성</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>판례는 소멸 예정인 예약완결권의 제척기간을 연장하는 새 매매예약이 책임재산을 감소시키는 사해행위가 될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>대판 2018.11.29. 2017다247190</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>957</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>상속포기나 유증의 포기는 사해행위 취소의 대상이 되지 않지만, 상속재산 분할협의는 사해행위 취소의 대상이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>대상구별</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>판례는 상속포기·유증포기는 재산권에 관한 법률행위가 아니어서 취소 대상이 아니나, 상속재산 분할협의는 재산권을 목적으로 하므로 취소 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>대판 2011.6.9. 2011다29307 · 대판 2007.7.26. 2007다29119</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>958</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>수급인의 저당권설정청구권(제666조) 행사에 의한 도급인의 저당권설정행위는 사해행위가 되지 않으며, 수급인으로부터 공사대금채권을 양수받은 자의 저당권설정청구에 의한 도급인의 저당권설정행위도 사해행위가 아니다.</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>사해성</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>판례는 제666조의 저당권설정청구권 행사에 따른 설정행위는 사해행위가 아니며, 공사대금채권 양수인의 청구에 의한 경우도 같다고 한다.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>대판 2008.3.27. 2007다78616 등</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>제666조</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>959</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>손해배상액의 예정이 있는 경우, 채무자가 실제 손해발생이 없다거나 손해액이 예정액보다 적다는 것을 입증하면 그 예정액의 지급을 면하거나 감액을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>입증효과</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>판례는 손해배상액 예정의 취지상 채무자가 손해 부존재·과소를 입증해도 예정액 지급을 면하거나 감액을 청구할 수 없다고 한다(법원의 직권 감액은 별개).</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>대판 2008.11.13. 2008다46906</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>960</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정되어 있는 경우, 채무자는 채무불이행에 관하여 자신의 귀책사유가 없음을 주장·입증함으로써 예정배상액의 지급책임을 면할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>면책</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>판례는 무과실책임 약정이 없는 한 채무자가 귀책사유 부존재를 증명하여 예정배상액 책임을 면할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>대판 2007.12.27. 2006다9408</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>961</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정된 경우 손해의 발생·확대에 채권자의 과실이 있더라도, 제398조 제2항에 따라 예정액을 감액할 수 있을 뿐 채권자의 과실을 들어 과실상계를 할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>판례는 손해배상액 예정 시 과실상계는 허용되지 않고 제반사정을 참작한 감액만 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>대판 2016.6.10. 2014다200763</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>962</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>위약벌의 약정에 대하여는 민법 제398조 제2항을 유추적용하여 감액할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>위약벌</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>판례는 위약벌에 제398조 제2항을 유추적용할 수 없고, 다만 공서양속에 반하여 일부 또는 전부가 무효가 될 수는 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>대판 2016.1.28. 2015다239324</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>963</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>전세권을 목적으로 한 저당권이 설정된 후 전세권의 존속기간이 만료된 경우, 저당권자는 전세금반환채권에 대하여 물상대위권을 행사하여 전세금의 지급을 구하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>물상대위</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>판례는 전세권 기간 만료로 용익물권적 권능이 소멸하면 전세권 자체에 대한 저당권 실행이 불가능하므로 전세금반환채권에 물상대위해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>대판 1999.9.17. 98다31301</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>제371조</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>964</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>전세권저당권자가 전세금반환채권에 물상대위권을 행사한 경우, 전세금반환채권이 압류된 때에 전세권설정자가 전세권자에 대한 반대채권을 가지고 있고 상계적상에 있었다는 사정만으로 설정자는 그 상계로써 저당권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>상계대항</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>판례는 압류 시점에 상계적상에 있었다는 사정만으로는 대항할 수 없고, 저당권 설정 시 이미 반대채권이 있고 그 변제기가 전세금반환채권의 변제기와 동시 또는 먼저 도래하는 경우에만 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>대판 2014.10.27. 2013다91672</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>제371조</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>965</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>임대차보증금 반환채권을 담보할 목적으로 전세권설정등기를 마친 후 그 전세권에 저당권이 설정된 다음 임대차계약의 변경으로 전세권이 일부 소멸한 경우, 전세권설정자는 저당권자의 동의 없이 그 전세권의 일부 소멸을 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>동의요건</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>제371조 제2항의 취지상 전세권설정자는 저당권자의 동의 없이 전세권을 소멸시키는 행위를 할 수 없으므로 일부 소멸도 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>민법 제371조② · 판례</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>제371조</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>966</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>부동산이 전전 양도된 경우, 최종 양수인은 중간생략등기의 합의가 없는 한 최초 양도인에 대하여 직접 자기 명의로의 소유권이전등기를 청구할 수 없으며, 이를 위해서는 관계 당사자 전원의 합의가 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>전원합의</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>판례는 중간생략등기 청구권 행사에 최초 양도인·중간자·최종 양수인 전원의 의사합치가 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>대판 1995.8.22. 95다15575</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>967</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>중간생략등기의 합의가 있더라도, 그 합의로 최초의 매도인이 중간자에 대하여 가지는 매매대금청구권의 행사가 제한되는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>대금청구</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>판례는 중간생략등기 합의가 등기 방법에 관한 합의일 뿐이므로 최초 매도인의 중간자에 대한 대금청구권 행사를 제한하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>대판 2005.4.29. 2003다66431</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>968</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>당사자 간의 합의 없이 이미 경료된 중간생략등기라도 실체관계에 부합하면 유효하다.</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>기성등기</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>판례는 합의가 없었더라도 이미 마쳐진 중간생략등기는 실체관계에 부합하는 한 유효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>대판 2005.9.29. 2003다40651</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>969</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>임대차계약 존속 중 발생한 화재가 임대인이 지배·관리하는 영역에 존재하는 하자로 인하여 발생한 것으로 추단되는 경우, 임차인이 그 하자를 미리 알았던 등의 특별한 사정이 없는 한 임대인은 화재로 인한 목적물 반환의무 이행불능에 관한 손해배상책임을 임차인에게 물을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>지배영역</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>판례(전합)는 임대인 지배·관리 영역의 하자로 인한 화재의 책임을 임차인에게 물을 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>대판 2017.5.18. 2012다86895 전합</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>제623조</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>970</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>임차 외 건물 부분이 임차 부분과 구조상 불가분의 일체를 이루더라도, 그 부분 손해에 대해 임차인에게 채무불이행 책임을 묻기 위해서는 임차인의 의무위반, 그 위반과 손해 사이의 인과관계, 손해의 범위 등을 임대인이 증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>판례(전합)는 임차 외 건물 부분 손해의 배상을 구하려면 임대인이 임차인의 의무위반·인과관계·손해범위를 증명해야 한다고 종전 판례를 변경하였다.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>대판 2017.5.18. 2012다86895 전합</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>971</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>인지청구의 소의 확정판결로 부와 자 사이에 친자관계가 창설된 이상, 재심의 소로 다투는 것은 별론으로 하고 친생자관계부존재확인의 소로 그 친자관계의 부존재를 다툴 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>판례는 인지 확정판결로 창설된 친자관계를 친생자관계부존재확인의 소로 다툴 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>대판 2015.6.11. 2014므8217</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>제865조</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>972</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>민법 제844조의 친생추정을 번복하려면 친생부인의 소를 제기하여 확정판결을 받아야 하고, 친생자관계부존재확인의 소로써 그 부존재확인을 구하는 것은 부적법하다.</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>판례는 친생추정이 미치는 경우 그 번복은 친생부인의 소에 의하여야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>대판 1997.2.25. 96므1663</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>제847조</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>973</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>제3자가 친생자관계존부확인의 소를 제기할 때 당사자 쌍방이 모두 사망한 경우, 그 출소기간은 당사자 쌍방 모두가 사망한 사실을 안 날부터 2년 내이다.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>출소기간</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>민법 제865조 제2항은 당사자 일방 또는 쌍방 사망 시 그 사망을 안 날부터 2년 내에 소를 제기하도록 한다.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>민법 제865조②</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>제865조</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>974</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>동시이행관계에 있는 쌍방의 채무 중 어느 한 채무가 이행불능이 됨으로 인하여 발생한 손해배상채무는, 여전히 다른 채무와 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>판례는 이행불능으로 변형된 손해배상채무도 동시이행관계를 유지한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>대판 2014.4.30. 2010다11323</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>975</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>부동산 소유권이전등기 의무자가 그 부동산에 가등기를 경료한 것만으로도 소유권이전등기의무는 이행불능이 된다.</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>불능판단</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>판례는 가등기는 순위보전의 효력만 있고 의무자의 처분권한이 상실되지 않으므로 가등기만으로는 이행불능이 되지 않는다고 한다(다만 제3자 앞 담보 이전등기 + 무자력이면 불능).</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>대판 1991.7.26. 91다8104</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>976</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>매매 목적 부동산에 제3자의 처분금지가처분 등기가 기입되어 있으면, 그것만으로 매도인의 소유권이전의무는 이행불능이 된다.</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>불능판단</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>판례는 가처분등기는 저촉 범위에서 대항할 수 없을 뿐 처분 자체를 금지하는 것이 아니므로 곧바로 이행불능이 되는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>대판 1993.5.27. 92다20163</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>977</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>매매 목적물이 화재로 소실되어 매도인이 화재보험금을 지급받게 되는 경우, 매수인의 대상청구권은 지급되는 화재보험금 전부에 대하여 행사할 수 있고 매매대금 상당액 한도로 제한되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>판례는 대상청구권이 인정되는 이상 화재보험금·공제금 전부에 대해 행사할 수 있으며 매매대금 상당액 한도로 제한되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>대판 2016.10.27. 2013다7769</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>978</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>물권적 청구권이 이행불능이 된 경우에도 그 이행불능으로 인한 전보배상청구권이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>전보배상</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>판례는 물권적 청구권의 이행불능으로 인한 전보배상청구권을 인정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2010다28604 전합</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>979</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>보증채무 자체의 이행지체로 인한 지연손해금은 보증한도액과 별도이며, 그 연체이율은 특별한 약정이 있으면 그에 따르고 없으면 거래행위의 성질에 따른 법정이율에 따르는 것이지 주채무에 약정된 연체이율이 당연히 적용되는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>이율적용</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>판례는 보증채무가 주채무와 별개이므로 지연손해금 이율도 별도로 정해진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>대판 2014.3.13. 2013다205693</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>제429조</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>980</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>주채무자가 보증인에 대하여 부담하게 될 구상금채무를 연대보증한 자는, 특별한 사정이 없으면 주채무자와 같은 내용의 채무를 부담한다.</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>채무내용</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>판례는 구상금채무의 연대보증인이 특별한 사정이 없으면 주채무자와 동일한 내용의 채무를 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>대판 2014.3.27. 2012다8769</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>제428조</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>981</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>보증인 보호를 위한 특별법은 물상보증의 경우에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>판례는 보증인보호법이 제429조 제1항에 따른 보증채무를 부담하는 경우에만 적용되고, 담보물의 한도 내에서 책임지는 물상보증에는 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>대판 2015.3.26. 2014다83142</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>제428조</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>982</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인에 대하여 구상의무를 부담하는 다른 공동불법행위자가 수인인 경우, 그들의 구상권자에 대한 채무는 특별한 사정이 없는 한 분할채무이지만, 구상권자에게 과실이 없어 내부 부담부분이 전혀 없는 경우에는 부진정연대관계로 본다.</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>채무형태</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>판례는 구상의무자가 여럿인 경우 원칙적 분할채무, 구상권자 무과실 시 부진정연대로 본다.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>대판 2005.10.13. 2003다24147</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>983</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>불가분채권자 중 1인과 채무자 간에 경개나 면제가 있는 경우, 채무 전부의 이행을 받은 다른 채권자는 그 1인이 권리를 잃지 않았으면 그에게 분급할 이익을 채무자에게 상환하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>효력제한</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>민법 제410조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>민법 제410조②</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>제410조</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>984</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>여러 사람이 공동으로 법률상 원인 없이 타인의 재산을 사용한 경우의 부당이득 반환채무는 특별한 사정이 없는 한 불가분채무이다.</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>채무성질</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>판례는 공동 사용으로 인한 불가분적 이득의 반환채무를 불가분채무로 본다.</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>대판 2001.12.11. 2000다13948</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>제411조</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>985</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>제485조에 따라 채권자의 고의·과실로 담보가 상실·감소된 경우, 법정대위할 자는 그 상실·감소로 인하여 상환을 받을 수 없는 한도에서 책임을 면한다.</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>담보보존</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>민법 제485조의 명문 규정으로, 판례는 일부 대위변제자에게 근저당권 전부를 이전해 준 경우 다른 보증인의 면책을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>민법 제485조 · 대판 1996.12.6. 96다35774</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>제485조</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>986</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>무효인 채권압류 및 전부명령을 받은 자에 대한 변제라도, 변제자가 그 채권자가 피전부채권에 관하여 무권리자라는 사실을 과실 없이 알지 못하고 변제하였다면 채권의 준점유자에 대한 변제로서 유효하다.</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>준점유자변제</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>판례는 무효인 전부명령 채권자가 외관상 권리자이므로 선의·무과실의 변제는 제470조의 준점유자 변제로 유효하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>대판 2004.4.23. 2003다6781</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>제470조</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>987</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>채무자가 채권자의 승낙을 얻어 본래의 채무이행에 갈음하여 부동산으로 대물변제하였으나 본래의 채무가 존재하지 않았던 경우, 당사자가 특별한 의사표시를 하지 않는 한 그 대물변제로 부동산 소유권 이전의 효과가 발생한다.</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>무인성</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>판례는 본래의 채무가 존재하지 않으면 대물변제도 무효이므로 특별한 의사표시가 없는 한 부동산 소유권 이전의 효과가 발생하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>대판 1991.11.12. 91다9503</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>제466조</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>988</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>변제이익의 다과에서, 특별한 사정이 없는 한 변제자가 타인의 채무에 대한 보증인으로서 부담하는 보증채무는 변제자 자신의 채무보다, 연대채무는 단순채무보다 변제이익이 적다.</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>변제이익</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>판례는 변제이익의 순서를 자기 채무 &gt; 보증채무, 단순채무 &gt; 연대채무로 본다.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>대판 1999.7.9. 98다55543</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>989</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>채권자와 채무자가 미리 채권자가 적당하다고 인정하는 순서와 방법으로 충당하기로 약정한 경우, 채권자가 그 약정에 기하여 스스로 적당하다고 인정하는 순서·방법으로 변제충당하면 변제자에 대한 의사표시와 관계없이 충당의 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>합의충당</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>판례는 충당에 관한 사전 합의가 있으면 채권자의 일방적 충당이 변제자에 대한 의사표시 없이도 효력을 갖는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>대판 1987.3.24. 84다카1324</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>제476조</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>990</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>비용·이자·원본에 대한 변제충당에서 당사자의 일방적 지정이 있었더라도 상대방이 지체 없이 이의를 제기하지 않은 경우에는, 묵시적 합의로 보아 그 법정 충당순서와 달리 충당의 순서를 인정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>묵시합의</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>판례는 제479조의 순서를 일방적 지정으로 바꿀 수 없으나, 상대방이 지체 없이 이의하지 않으면 묵시적 합의로 보아 달리 충당할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>대판 1981.5.26. 80다3009 등</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>제479조</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>991</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>피용자의 고의에 의한 불법행위로 사용자책임이 성립하는 경우, 피해자에게 손해의 발생·확대에 기여한 과실이 있다면 사용자는 과실상계를 주장하여 책임을 제한할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>판례는 피용자의 고의 불법행위로 인한 사용자책임에서도 피해자의 과실을 고려하여 책임을 제한할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>대판 2002.12.26. 2000다56952</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>992</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>피용자의 고의의 불법행위로 사용자책임이 성립하는 경우, 사용자는 자신의 고의의 불법행위가 아니라는 이유로 제496조(불법행위채권을 수동채권으로 하는 상계금지)의 적용을 면할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>상계금지</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>판례는 사용자책임이 피용자 책임에 대한 대체책임이므로 피용자의 고의 불법행위 시 사용자도 제496조의 적용을 배제할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>대판 2006.10.26. 2004다63019</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>993</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인의 손해배상채무가 시효로 소멸한 후 다른 공동불법행위자 1인이 피해자에게 자기의 부담부분을 넘는 손해를 배상한 경우, 그 배상자는 시효 소멸한 공동불법행위자에게 구상권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>구상독립성</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>판례는 구상권이 피해자의 손해배상채권과 별개의 권리이므로 다른 공동불법행위자의 채무가 시효 소멸해도 구상권을 행사할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>대판 1997.12.23. 97다42830</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>994</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>부진정연대채무에서 채무자 1인에 대한 재판상 청구나 채무자 1인의 채무승인 등 소멸시효 중단사유나 시효이익의 포기는, 다른 채무자에게 효력이 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>판례는 부진정연대채무에서는 절대적 효력 규정이 적용되지 않아 시효중단·시효이익 포기가 다른 채무자에게 효력이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>대판 1997.9.12. 95다42027</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>995</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>계약해제에 따른 원물반환이 불가능하게 된 경우, 매수인이 원상회복의무로서 반환하여야 하는 목적물의 가액은 특별한 사정이 없는 한 그 처분 당시의 대가 또는 시가 상당액이다.</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>가액기준</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>판례는 원물반환 불능 시 가액반환액을 처분 당시의 대가 또는 시가 상당액으로 본다.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>대판 2013.12.12. 2012다58029</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>996</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>합의해제의 경우에도 특별한 약정이 없으면 반환할 금전에 그 받은 날부터의 이자를 가산하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>이자가산</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>판례는 합의해제에는 법정해제에 관한 제548조 제2항이 적용되지 않으므로 특약이 없는 한 받은 날부터의 이자를 가산할 의무가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>대판 2003.1.24. 2000다5336</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>997</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>계약 해제로 인한 원상회복청구권에 대하여, 해제자가 해제의 원인이 된 채무불이행에 원인의 일부를 제공하였다는 이유로 과실상계에 준하여 권리의 내용을 제한할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>판례는 원상회복청구권은 손해배상이 아니므로 과실상계나 그에 준한 권리 제한을 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>대판 2014.3.13. 2013다34143</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>998</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>금전채권의 질권자가 직접청구권을 행사하여 제3채무자로부터 변제받았으나 입질채권의 발생원인인 계약에 무효 등의 흠이 있어 입질채권이 부존재하는 경우, 제3채무자는 질권설정자를 상대로 부당이득반환을 구할 수 있을 뿐 질권자를 상대로 직접 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>반환상대방</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>판례는 직접청구권 행사 시 질권설정자의 급부가 이루어진 것으로 보므로 제3채무자는 계약 상대방인 질권설정자에게만 부당이득반환을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>대판 2015.5.29. 2012다92258</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>999</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>착오송금의 경우, 송금의뢰인은 수취은행이 아니라 수취인을 상대로 부당이득반환을 청구하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>반환상대방</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>판례는 착오송금 시 수취인이 예금채권을 취득하므로 송금의뢰인은 수취인을 상대로 부당이득반환을 구해야 하고 수취은행에 대해서는 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>대판 2007.11.29. 2007다51239</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>9001</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>유효한 도급계약에 기하여 수급인이 도급인으로부터 제3자 소유의 물건을 인도받아 수리한 결과 그 물건의 가치가 증가한 경우, 수급인은 그 제3자를 상대로 직접 제203조의 비용상환이나 제741조의 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>전용물소권</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>판례는 수급인이 도급계약 상대방에 대한 권리를 가질 뿐, 사실상 이익을 얻은 제3자(소유자)에게 직접 비용상환·부당이득반환을 청구할 수 없다고 한다(전용물소권 부정).</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>대판 2002.8.23. 99다66564</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>9002</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>가해행위와 피해자 측의 체질적 소인 등 귀책사유와 무관한 요인이 경합하여 손해가 발생·확대된 경우에도, 법원은 과실상계의 법리를 유추적용하여 그 요인을 참작할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>책임제한</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>판례는 피해자의 귀책사유와 무관한 체질적 소인·질병이라도 가해자에게 전부 배상시키는 것이 공평에 반하면 과실상계 법리를 유추하여 참작할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>대판 2014.7.10. 2014다16968</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>9003</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>표현대리행위가 성립하는 경우, 본인의 책임을 정함에 있어 상대방에게 과실이 있으면 과실상계의 법리를 유추적용하여 본인의 책임을 경감할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>판례는 표현대리가 성립하면 본인이 전적인 책임을 지며 상대방의 과실을 들어 과실상계로 책임을 경감할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>대판 1996.7.12. 95다49554</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>제126조</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>9004</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>민법 제581조·제580조에 기한 매도인의 하자담보책임에는 제396조의 과실상계 규정이 준용되지 않지만, 하자의 발생 및 확대에 가공한 매수인의 잘못을 참작하여 손해배상의 범위를 정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>과실참작</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>판례는 무과실책임인 하자담보책임에 과실상계가 준용되지 않으나, 손해배상 범위 산정에서 매수인의 잘못을 참작할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>대판 1995.6.30. 94다23920</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>제581조</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>9005</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>비법인사단인 채무자 명의로 제3채무자를 상대로 소가 제기되었으나 사원총회 결의 없이 총유재산에 관한 소가 제기되었다는 이유로 각하판결이 확정된 경우, 이는 채무자가 스스로 제3채무자에 대한 권리를 재판상 행사한 것으로 볼 수 없다.</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>대위요건</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>판례는 사원총회 결의 없는 소는 특별수권을 결하여 부적법하므로 채무자의 권리행사로 볼 수 없어 채권자대위권 행사가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>대판 2018.10.25. 2018다210539</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>9006</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>이행인수계약에서 인수인이 인수한 채무를 이행하지 않는 경우, 채권자는 인수인에 대하여 직접 자신에게 이행할 것을 청구할 수는 없으나 채무자의 인수인에 대한 청구권을 대위행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>이행인수</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>판례는 이행인수에서 인수인이 채권자에게 직접 의무를 부담하지 않으므로 채권자는 채무자의 인수인에 대한 청구권을 대위행사할 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>판례(이행인수와 채권자대위)</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>9007</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>채권자대위소송에서 채권자가 채무자를 상대로 보전되는 청구권에 기한 이행청구의 소를 제기하여 승소판결이 확정된 경우, 제3채무자는 그 청구권의 존재를 다툴 수 없으나 그 청구권의 취득이 강행법규에 위반되어 무효인 경우에는 그 존재를 다툴 수 있다.</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>기판력</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>판례는 피보전채권에 관한 확정판결의 효력에도 불구하고 강행법규 위반으로 무효인 경우 제3채무자가 그 존재를 다툴 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>판례(채권자대위와 피보전채권)</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>9008</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>전세기간 만료 이후 전세권양도계약 및 전세권이전의 부기등기가 이루어진 것만으로는, 전세금반환채권의 양도에 관하여 확정일자 있는 통지나 승낙이 있었다고 볼 수 없으므로 제3자인 전세금반환채권의 압류·전부 채권자에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>판례는 부기등기만으로는 채권양도의 확정일자 있는 대항요건을 갖춘 것이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>대판 2005.3.25. 2003다35659</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>9009</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>부동산 매매로 인한 소유권이전등기청구권의 양도는 통상의 채권양도와 달리 양도인의 채무자에 대한 통지만으로는 대항력이 생기지 않고 채무자의 동의나 승낙을 받아야 한다.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>양도방식</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>판례는 매매로 인한 등기청구권은 신뢰관계가 따르므로 양도에 채무자의 동의·승낙을 요한다고 한다(취득시효로 인한 등기청구권과 구별).</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>대판 2018.7.12. 2015다36167</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>9010</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>채권양도금지특약에도 불구하고 채권을 양도한 경우, 선의의 양수인으로부터 다시 채권을 양수한 전득자는 선의·악의를 불문하고 채권을 유효하게 취득한다.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>전득보호</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>판례는 선의 양수인 개입 후의 전득자는 악의여도 유효하게 채권을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>대판 2015.4.9. 2012다118020</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>9011</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>공동상속인 중 일부가 한정승인을 하여 그 청산절차가 종료되지 않은 경우에도, 상속재산분할청구가 가능하다.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>절차선후</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>판례는 한정승인 절차가 상속재산분할에 선행해야 한다는 규정이 없으므로 청산절차 종료 전에도 분할청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>대판 2014.7.25. 2011스226</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>9012</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>상속개시 당시 상속재산을 구성하던 재산이 그 후 처분되어 상속재산을 구성하지 않게 된 경우, 그 재산은 상속재산분할의 대상이 되지 않지만 상속인이 그 대가로 처분대금을 취득한 경우에는 그 대금이 분할 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>분할대상</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>판례는 처분된 재산은 분할 대상에서 제외하되 그 대가물(처분대금)은 분할 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>대판 2016.5.4. 2014스122</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>9013</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>채무초과 상태의 채무자가 상속재산 분할협의를 하면서 자신의 상속분에 관한 권리를 포기하여 일반채권자에 대한 공동담보가 감소된 경우, 이는 원칙적으로 사해행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>판례는 상속재산 분할협의가 재산권을 목적으로 하는 법률행위이므로 공동담보를 감소시키면 사해행위가 된다고 한다(상속포기와 구별).</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>대판 2007.7.26. 2007다29119</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>9014</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>공동상속인들은 이미 이루어진 상속재산 분할협의의 전부 또는 일부를 전원의 합의에 의하여 해제한 다음 다시 새로운 분할협의를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>합의해제</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>판례는 분할협의의 합의해제와 재분할협의를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>대판 2004.7.8. 2002다73203</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>9015</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>공동상속인 중 1인이 협의분할을 원인으로 상속부동산에 이전등기를 마쳤는데 그 협의분할이 다른 공동상속인의 동의 없이 이루어져 무효라는 이유로 다른 공동상속인이 그 등기의 말소를 청구하는 소는, 상속회복청구의 소에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>소송성질</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>판례는 무효인 협의분할에 따른 등기 말소청구도 상속회복청구의 소에 해당하여 제999조의 제척기간이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>대판 2011.3.10. 2007다17482</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>제999조</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>9016</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>상속인이 피상속인의 손해배상채권을 추심하여 변제받은 행위는 상속재산의 처분행위에 해당하여 단순승인으로 간주되므로, 그 이후에 한 상속포기는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>법정단순승인</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>판례는 피상속인의 채권 추심·변제 수령을 제1026조 제1호의 처분행위로 보아 법정단순승인이 성립하고 이후의 상속포기를 무효로 본다.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>대판 2010.4.29. 2009다84936</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>제1026조</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>9017</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>상속포기 신고 후 이를 수리하는 가정법원의 심판이 고지되기 이전에 상속재산을 처분한 경우, 이는 법정단순승인 사유에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>효력발생시기</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>판례는 상속포기는 심판 고지로 효력이 발생하므로 그 이전의 상속재산 처분은 제1026조 제1호의 단순승인 사유가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>대판 2016.12.29. 2013다73520</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>제1026조</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>9018</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>상속인 중 1인이 피상속인의 생존 시에 상속을 포기하기로 약정하였더라도 상속개시 후 법정 절차와 방식에 따라 상속포기를 하지 않았다면, 상속개시 후 자신의 상속권을 주장하는 것은 정당한 권리행사이다.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>사전포기</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>판례는 상속개시 전의 상속포기 약정은 효력이 없으므로 상속개시 후 상속권 주장이 정당하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>대판 1998.7.24. 98다9021</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>제1041조</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>9019</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>피상속인 사망 후 상속채무 초과로 배우자와 자녀들이 상속포기한 뒤 피상속인의 직계존속이 사망하여 대습상속이 개시된 경우, 대습상속인이 한정승인이나 상속포기를 하지 않으면 단순승인을 한 것으로 간주된다.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>대습상속</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>판례는 종전 상속포기의 효력이 별개의 대습상속에 미치지 않으므로 대습상속인이 별도로 한정승인·포기를 해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>대판 2017.1.12. 2014다39824</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>제1043조</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>9020</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>당사자가 이혼 성립 후에 재산분할을 청구하여 법원이 재산분할로 금전 지급을 명하는 판결이나 심판을 하는 경우, 분할의무자는 그 판결·심판이 확정된 다음 날부터 이행지체책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>지체시기</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>판례는 재산분할청구권이 협의·심판으로 구체화되기 전에는 불명확하므로 분할의무자는 판결·심판 확정 다음 날부터 지체책임을 진다고 한다(소촉법 이율 부적용).</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>대판 2014.9.4. 2012므1656</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>9021</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>재판상 이혼 시의 재산분할에서 분할의 대상이 되는 재산과 그 액수는 이혼소송의 사실심 변론종결일을 기준으로 정한다.</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>기준시</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>판례는 재판상 이혼의 재산분할 기준시를 사실심 변론종결일로 본다.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>대판 2000.9.22. 99므906</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>9022</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>협의 또는 심판에 의하여 구체화되지 않은 재산분할청구권을 혼인이 해소되기 전에 미리 포기하는 것은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>사전포기</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권의 혼인 해소 전 사전포기를 허용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>대판 2016.1.25. 2015스451</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>9023</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>변시9</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>이혼 시 재산분할로 금전의 지급을 명하는 부분은 판결 또는 심판이 확정되기 전이라도 가집행선고의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>가집행</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>판례는 재산분할로 금전 지급을 명한 부분은 형성적 효력이 확정되어야 발생하므로 가집행선고의 대상이 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>대판 2014.9.4. 2012므1656</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H665"/>
+  <dimension ref="A1:H766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27064,6 +27064,4046 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>801</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>무권대리행위의 추인은 상대방의 동의가 없는 한 의사표시의 일부에 대하여 하거나 그 내용을 변경하여 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>추인범위</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>판례는 추인이 단독행위로서 전부에 대하여 행해져야 하고 일부 추인·변경 추인은 상대방의 동의 없으면 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>대판 1982.1.26. 81다카549</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>제130조</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>802</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>무권리자가 타인의 권리를 처분한 경우 권리자가 추인하면, 무권대리 추인 규정을 유추적용하여 원칙적으로 계약을 체결한 때에 소급하여 그 효과가 권리자에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>유추적용</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>판례는 무권리자 처분의 추인에 제130조·제133조를 유추적용하여 소급효를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>대판 2017.6.8. 2017다3499</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>제130조</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>803</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>매매계약이 불공정한 법률행위에 해당하여 무효인 경우, 그 계약으로 불이익을 입는 당사자가 불공정성을 다투지 못하도록 하는 부제소합의도 특별한 사정이 없는 한 무효이다.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>부제소합의</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>판례는 불공정 법률행위가 무효이면 그에 관한 부제소합의도 사법적 구제수단을 봉쇄하므로 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>대판 2010.7.15. 2009다50308</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>804</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>취득시효 완성 후 소유자가 시효완성 사실을 알고 부동산을 제3자에게 처분하여 이전등기의무가 이행불능이 된 경우, 그 제3자가 소유자의 불법행위에 적극 가담하였다면 그 처분은 반사회질서 법률행위로서 무효이다.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>반사회성</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>판례는 시효완성을 알고 한 처분이 불법행위가 되고, 제3자가 적극 가담하면 제103조 위반으로 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>대판 1993.2.9. 92다47892</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>805</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>채무자가 소멸시효 완성 후 시효를 원용하지 아니할 것 같은 태도를 보여 권리자가 이를 신뢰하였고 권리자가 상당한 기간 내에 권리를 행사하였다면, 채무자의 소멸시효 완성 주장은 신의칙에 반하는 권리남용으로 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>신의칙</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소멸시효 항변권 행사도 신의칙·권리남용금지의 지배를 받는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>대판 2013.5.16. 2012다202819 전합</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>806</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>체납처분에 의한 채권압류로 시효가 중단된 경우, 피압류채권이 기본계약 해지·실효 또는 소멸시효 완성으로 소멸하여 압류의 대상이 존재하지 않게 되면 압류 자체가 실효되고 그때부터 시효가 새로이 진행한다.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>중단종료</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>판례는 압류의 대상이 소멸하여 압류가 실효된 경우 시효중단 사유가 종료한 것으로 보아 그때부터 시효가 새로 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>대판 2017.4.28. 2016다239840</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>807</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>동일 당사자 간 계속적 거래로 같은 종류의 수개 채권관계가 성립한 경우, 채무자가 특정채무를 지정하지 않고 일부 변제를 하면 다른 특별한 사정이 없는 한 잔존채무에 대하여도 승인을 한 것으로 보아 시효중단이나 포기의 효력을 인정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>묵시승인</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>판례는 잔존채무가 별개로 독립성을 갖지 않는 한 일부 변제를 잔존채무 전체의 승인으로 볼 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>대판 1993.10.26. 93다14936</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>808</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>원금채무는 시효가 완성되지 않았으나 이자채무는 시효가 완성된 상태에서 채무자가 채무를 일부 변제한 경우, 액수에 다툼이 없는 한 원금채무를 묵시적으로 승인하는 한편 이자채무의 시효이익을 포기한 것으로 추정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>시효포기</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>판례는 일부 변제를 원금채무의 묵시적 승인 및 이자채무의 시효이익 포기로 추정한다.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>대판 2013.5.23. 2013다12464</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>제184조</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>809</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>법률의 규정에 따른 적법한 가압류가 있었으나 제소기간의 도과로 가압류가 취소된 경우, 그 가압류에 의한 소멸시효 중단의 효력은 소급하여 상실된다.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>중단유지</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>판례는 제소기간 도과로 인한 가압류 취소는 제175조의 '권리자의 청구 또는 법률 규정에 따르지 않은 취소'에 해당하지 않으므로 시효중단 효력을 잃지 않고, 취소된 때부터 다시 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>대판 2011.1.13. 2010다88019</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>제175조</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>810</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>명의수탁자와 직접 이해관계를 맺은 것이 아니라 부동산실명법 제4조 제3항의 제3자가 아닌 자와 사이에서 무효인 등기를 기초로 다시 이해관계를 맺은 데 불과한 자는, 그 조항의 제3자에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 제4조 제3항의 제3자를 수탁자와 직접 새로운 이해관계를 맺은 자로 한정하므로, 무효 등기를 기초로 재차 이해관계를 맺은 자는 제외된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>대판 2005.11.10. 2005다34667</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>811</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>파산관재인은 통정허위표시(제108조 제2항) 및 사기·강박(제110조 제3항)의 제3자에 해당하고, 그 선의 여부는 총 파산채권자를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>선의기준</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>판례는 파산관재인을 제3자로 보고 파산채권자 모두가 악의가 아닌 한 선의의 제3자라고 한다.</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>대판 2010.4.29. 2009다96083</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>812</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>계약상의 채권을 양수한 자나 그 채권 자체를 압류·전부한 채권자는, 계약해제의 소급효로부터 보호되는 제548조 제1항 단서의 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>판례는 제548조 제1항 단서의 제3자는 해제된 계약을 기초로 새로운 권리를 취득한 자를 말하므로, 단순히 계약상 채권을 양수·압류·전부한 자는 제3자에 해당하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>대판 2003.1.24. 2000다22850</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>813</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>임대인이 소유권을 취득하였다가 계약해제로 소유권을 상실하게 된 경우, 그 계약해제 전에 주택임대차보호법상의 대항요건을 갖춘 임차인은 해제로부터 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>판례는 해제 전 대항요건을 갖춘 임차인을 제548조 제1항 단서의 보호받는 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>대판 2003.8.22. 2003다12717</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>814</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>소유권이전등기청구권에 대한 가압류나 압류가 행하여진 경우, 제3채무자는 채무자에게 등기이전을 하여서는 안 되지만 그 채권의 발생원인인 매매계약 자체를 해제할 수는 있다.</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>처분구속</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>판례는 가압류·압류가 채권의 발생원인 법률관계에 대한 처분까지 구속하지 않으므로 기본계약 해제가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>대판 2000.4.11. 99다51685</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>815</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>공유자 중 일부가 특정 부분을 배타적으로 점유·사용하는 경우, 그 특정 부분의 면적이 자신의 지분비율에 상당하는 범위 내라면 다른 공유자에 대한 부당이득반환의무를 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>배타적점유</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>판례는 지분 과반수의 합의 없이는 1인이 특정 부분을 배타적으로 점유·사용할 수 없으므로, 지분 범위 내라도 다른 공유자의 지분에 상응하는 부당이득반환의무(불가분채무)를 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>대판 2001.12.11. 2000다13948</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>제263조</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>816</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>조합이 부동산을 취득하면서 조합원들 명의로 공유등기를 한 경우, 이는 조합원들에게 각 지분에 관하여 명의신탁한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>합유명의신탁</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>판례는 조합재산은 합유이지만 조합원 명의 공유등기는 각 지분에 관한 명의신탁으로 본다.</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>대판 2002.6.14. 2000다30622</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>제271조</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>817</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>총유물에 관한 소송은 비법인사단의 명의로 총회결의를 거쳐 하거나 구성원 전원이 당사자가 되어 필수적 공동소송의 형태로 제기할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>판례는 총유물에 관한 소송을 비법인사단 명의(총회결의) 또는 구성원 전원의 필수적 공동소송으로 제기할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>대판 2005.9.15. 2004다44971 전합</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>818</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>근저당 거래관계가 계속되어 피담보채권이 확정되지 않은 동안에 채권의 일부가 대위변제된 경우, 그 근저당권은 대위변제자에게 이전된다.</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>확정전</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>판례는 확정 전에는 피담보채권이 계속 증감변동하므로 일부 대위변제로 근저당권이 이전될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>대판 2000.12.26. 2000다54451</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>819</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>부동산에 가압류등기가 먼저 되고 나서 근저당권설정등기가 마쳐진 경우, 그 근저당권등기는 가압류채권자에 대한 관계에서만 상대적으로 무효이다.</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>상대무효</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>판례는 선행 가압류의 처분금지효로 후행 근저당권은 가압류채권자에 대한 관계에서만 상대적으로 무효이고, 배당에서 가압류채권자와 안분배당 후 후순위 압류채권자에 대해 흡수배당받는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>대결 1994.11.29. 94마417</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>820</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>저당권자가 물상대위권을 행사하지 아니하여 저당부동산의 수용보상금을 다른 채권자가 지급받은 경우, 저당권자는 그 채권자에게 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>물상대위</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>판례는 저당권자가 물상대위권 행사에 나아가지 않아 우선변제권을 상실한 이상 보상금을 받은 다른 채권자에게 부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>대판 2010.10.28. 2010다46756</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>제370조</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>821</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>근저당권 이전의 부기등기가 마쳐진 후 근저당권설정등기가 원인무효가 된 경우, 그 말소는 주등기에 대한 말소청구로 충분하고 부기등기에 대한 말소청구는 소의 이익이 없다.</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>말소방법</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>판례는 부기등기는 주등기에 종속되므로 주등기 말소로 부기등기도 말소되며 부기등기 자체의 말소청구는 소의 이익이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>대판 1995.5.26. 95다7550</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>822</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>중간생략등기의 합의가 있더라도 그 합의로 중간매수인의 최초매도인에 대한 소유권이전등기청구권이 소멸하는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>청구권존속</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>판례는 중간생략등기 합의가 등기 방법에 관한 합의일 뿐이므로 중간매수인의 등기청구권이 소멸하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>대판 1991.12.13. 91다18316</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>823</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>최초매도인과 중간매수인 사이에 중간생략등기의 합의 후 매매대금을 인상하는 약정이 체결된 경우, 최초매도인은 인상된 매매대금이 지급되지 않았음을 이유로 최종매수인 명의로의 소유권이전등기의무 이행을 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>항변존속</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>판례는 중간생략등기 합의가 있어도 최초매도인의 중간매수인에 대한 대금 관련 항변권이 소멸하지 않으므로 인상 대금 미지급을 이유로 이행을 거절할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>대판 2005.4.29. 2003다66431</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>824</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>중간생략등기의 합의가 없더라도, 매매대금이 지급된 상태에서 이미 최종매수인 앞으로 경료된 중간생략등기는 실체관계에 부합하는 한 유효하다.</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>기성등기</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>판례는 합의가 없었더라도 이미 마쳐진 중간생략등기는 적법한 매매가 이행된 이상 유효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>대판 1967.5.30. 67다588</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>825</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>계약금 전액이 지급되지 않은 경우에는 계약금계약이 성립하지 않으므로, 민법 제565조에 의한 계약해제를 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>요물계약</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>판례는 계약금계약이 요물계약이므로 계약금 전액 지급 전에는 성립하지 않아 해약금 해제권이 발생하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>대판 2008.3.13. 2007다73611</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>제565조</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>826</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>매매계약이 취소된 경우, 선의의 매수인은 목적물의 점유로 인하여 얻은 사용이익을 반환할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>과실수취</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>판례는 선의 점유자의 과실수취권(제201조 제1항)에 따라 선의 매수인은 점유로 인한 사용이익을 반환할 의무가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>대판 1981.9.22. 81다233</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>제201조</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>827</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>매매계약이 해제된 경우, 매도인은 매매대금을 받은 날로부터의 이자를 가산하여 반환하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>이자가산</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>민법 제548조 제2항은 원상회복으로 반환할 금전에 받은 날부터의 이자를 가산하도록 한다.</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>민법 제548조②</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>828</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>해제된 매매계약에 의하여 채무자의 책임재산이 된 부동산을 가압류 집행한 가압류채권자는, 제548조 제1항 단서의 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>판례는 해제 전 그 부동산을 가압류한 채권자를 해제로부터 보호되는 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>대판 2005.1.14. 2003다33004</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>829</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>건물 신축공사의 수급인은 공사대금채권 및 그 채무불이행에 따른 손해배상청구권을 피담보채권으로 하여 완성된 신축건물에 관하여 유치권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>피담보채권</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>판례는 신축건물에 관한 공사대금채권에 기한 유치권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>대판 1995.9.15. 95다16202</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>830</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>다세대주택 전체의 창호공사를 완성한 수급인이 전체 공사대금 잔액을 변제받기 위하여 그 중 한 세대를 점유하여 유치권을 행사하는 경우, 그 유치권은 점유한 한 세대의 공사대금만이 아니라 다세대주택 전체에 대한 공사대금 잔액 전부를 담보한다.</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>불가분성</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>판례는 유치권의 불가분성(제321조)상 유치물의 각 부분이 피담보채권 전부를 담보한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>대판 2007.9.7. 2005다16942 · 민법 제321조</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>제321조</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>831</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>수급인이 경매개시결정의 기입등기 이후에 점유 및 피담보채권을 취득한 경우, 그 유치권으로 경매절차의 매수인에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>대항시점</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>판례는 압류의 효력 발생 후 점유 이전으로 유치권을 취득한 경우 압류의 처분금지효에 저촉되어 매수인에게 대항할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>대판 2005.8.19. 2005다22688</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>832</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>공사수급인과의 공급약정에 따른 건축자재대금채권은 그 자재로 신축된 건물에 관한 유치권의 피담보채권이 된다.</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>판례는 건축자재대금채권은 매매대금채권에 불과하여 건물과 견련성이 없으므로 건물에 관한 유치권의 피담보채권이 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>대판 2012.1.26. 2011다96208</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>833</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>법인의 정관에 이사의 해임사유에 관한 규정이 있는 경우, 법인은 이사의 중대한 의무위반이나 정상적 사무집행 불능 등 특별한 사정이 없는 한 정관에서 정하지 아니한 사유로 이사를 해임할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>해임제한</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>판례는 정관의 이사 해임사유 규정을 단순한 주의규정이 아니라 이사의 신분 보장 규정으로 보아 정관 외 사유로의 해임을 제한한다.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>대판 2013.11.28. 2011다41741</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>제57조</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>834</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>법인과 이사의 이익이 상반되는 사항에 관하여는 임시이사를 선임하여야 하고, 이사가 없거나 결원으로 손해가 생길 염려가 있는 경우에는 특별대리인을 선임하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>기관혼동</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>민법 제63조는 이사 부재·결원 시 임시이사 선임을, 제64조는 법인과 이사의 이익상반 시 특별대리인 선임을 규정한다. 설명이 서로 바뀌었다.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>민법 제63조·제64조</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>제64조</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>835</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>법인 직무대행자는 원칙적으로 법인의 통상사무에 속하는 행위만 할 수 있고, 이에 위반한 경우 법인은 선의의 제3자에 대하여 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>민법 제60조의2는 직무대행자가 통상사무만 할 수 있고 위반 시 법인이 선의의 제3자에게 책임을 진다고 정한다(가처분명령에 다른 정함 또는 법원 허가 시 예외).</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>민법 제60조의2</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>제60조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>836</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>가등기는 본등기의 순위보전의 효력만 있을 뿐, 본등기가 마쳐지더라도 그 물권변동의 효력이 가등기한 때로 소급하여 발생하는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>소급효</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>판례는 가등기 후 본등기 시 순위만 소급하고 중간처분이 실효될 뿐 물권변동 효력이 가등기 시로 소급하지는 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>대판 1981.5.26. 80다3117</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>837</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>가등기권리자는 중복된 소유권보존등기가 무효인 경우 그 말소를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>청구권한</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>판례는 가등기는 순위보전 효력만 있을 뿐 실체법상 효력이 없으므로 가등기권리자가 무효인 중복보존등기의 말소를 청구할 권리가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>대판 2001.3.23. 2000다51285</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>838</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>가등기에 기하여 본등기가 경료된 경우, 사해행위 요건의 구비 여부는 가등기의 원인된 법률행위와 본등기의 원인된 법률행위가 명백히 다르지 않은 한 가등기의 원인된 법률행위 당시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>기준시</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>판례는 가등기·본등기의 원인 법률행위가 명백히 다르지 않으면 사해행위 판단 기준을 가등기의 원인 법률행위 당시로 본다.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>대판 2001.7.27. 2000다73377</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>839</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>무효인 가등기를 유용하기로 합의하고 제3자가 가등기 이전의 부기등기를 마친 경우, 그 제3자는 언제든지 부동산 소유자에 대하여 가등기 유용의 합의를 주장할 수 있으나, 그 부기등기 전에 등기부상 이해관계를 가지게 된 자에 대하여는 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>유용대항</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>판례는 가등기 유용 합의의 효력이 부기등기 전 이해관계인에게는 미치지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>대판 2009.5.28. 2009다4787</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>840</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>채권질권의 효력은 질권의 목적이 된 채권의 지연손해금 등 부대채권에도 미치므로, 채권질권자는 목적 채권과 그에 대한 지연손해금채권을 자기 채권액에 대한 부분에 한하여 직접 추심하여 변제에 충당할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>효력범위</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>판례는 금전채권질권의 효력이 부대채권인 지연손해금에도 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>대판 2005.2.25. 2003다40668</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>제353조</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>841</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>질권자가 제3채무자로부터 자기 채권을 초과하여 금전을 지급받았으나 그 초과지급 부분을 질권설정자에게 그대로 반환한 경우에는, 제3채무자는 질권자를 상대로 그 초과지급 부분에 관하여 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>실질이익</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>판례는 부당이득 반환의 상대방은 실질적으로 이익이 귀속된 자여야 하므로, 초과지급분을 질권설정자에게 반환한 질권자에게는 실질적 이익이 없어 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>대판 2015.5.29. 2012다92258</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>842</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>대항요건을 갖춘 임차인이 임대차보증금반환채권에 질권을 설정하고 임대인이 이를 승낙한 후 임대주택이 양도된 경우, 임대인은 임대차관계에서 탈퇴하고 보증금반환채무를 면한다.</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>면책승계</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>판례는 주임법 제3조의 법정 지위승계에 따라 질권 설정 승낙이 있어도 양도인이 보증금반환채무를 면한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>대판 2018.6.19. 2018다201610</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>843</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>질권의 목적인 채권을 양도하는 행위에는 질권자의 동의가 필요하지 않다.</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>양도요건</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>판례는 입질채권의 양도가 질권자의 동의 없이도 가능하다고 한다(질권은 채권에 그대로 존속).</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>판례(입질채권의 양도)</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>제352조</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>844</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>질권자가 제3채무자에게 질권설정계약의 해지 사실을 통지하였으나 아직 해지되지 않은 경우, 선의인 제3채무자는 질권설정자에게 대항할 수 있는 사유로써 질권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>통지신뢰</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>판례는 제452조를 유추하여 해지 통지를 신뢰한 선의의 제3채무자를 보호한다.</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>대판 2014.4.10. 2013다76192</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>제452조</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>845</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>피해자의 부주의를 이용하여 고의로 불법행위를 저지른 자는 그 피해자의 부주의를 이유로 과실상계를 주장할 수 없으나, 피용자의 고의 불법행위에 대해 사용자가 사용자책임을 지는 경우에는 사용자는 피해자의 과실을 들어 과실상계를 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>판례는 고의의 직접 가해자는 과실상계를 주장할 수 없지만, 불법행위에 가담하지 않은 사용자는 피해자의 과실을 참작할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>대판 2008.6.12. 2008다22276</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>846</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인에 대한 권리의 포기, 채무면제, 합의 등은 다른 공동불법행위자에게도 효력이 미친다.</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위 책임이 부진정연대채무이므로 제419조가 적용되지 않아 1인에 대한 면제 등이 다른 채무자에게 효력이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>대판 1980.7.22. 79다1107</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>847</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>금액이 다른 채무가 부진정연대 관계에 있을 때 다액채무자가 일부 변제를 하는 경우, 변제로 먼저 소멸하는 부분은 다액채무자가 단독으로 부담하는 부분이다.</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>외측설</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>판례(전합)는 외측설을 채택하여 다액채무자의 일부 변제 시 단독 부담 부분이 먼저 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>대판 2018.3.22. 2012다74236 전합</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>848</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>타인 소유의 토지 위에 건립된 불법 미등기건물의 철거의무자에는 소유권자뿐 아니라 그 건물을 양수하여 법률상·사실상 처분권을 가진 미등기건물 양수인도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>철거의무자</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>판례는 미등기건물 양수인이 법률상·사실상 처분권을 가지므로 토지소유자가 그를 상대로 철거를 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>대판 1989.2.14. 87다카3073</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>849</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>토지의 매수인이 타인 권리의 매매에 의하여 목적 토지의 점유를 취득한 것만으로는, 그 점유가 자주점유라는 추정이 깨어진다고 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>자주점유</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>판례는 타인 권리의 매매라도 매도인의 처분권한 부존재를 알고 매수하였다는 등의 특별한 사정이 없는 한 자주점유 추정이 번복되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>대판 2000.3.16. 97다37661 전합</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>제197조</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>850</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>대지의 점유자가 점유취득시효는 완성하였으나 아직 이전등기를 경료하지 못한 경우, 대지소유자는 그 점유가 불법점유임을 이유로 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>점유권원</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>판례는 시효취득자가 소유자에 대해 이전등기청구권을 가지므로 소유자는 불법점유를 이유로 부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>대판 1993.5.25. 92다51280</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>851</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>기존채무의 이행과 관련하여 어음이 교부된 경우 원인채무의 이행과 어음 반환은 동시이행관계에 있지만, 어음상 권리가 시효완성으로 소멸한 경우에는 채무자가 어음 상환의 동시이행항변을 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>항변소멸</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>판례는 어음상 권리가 시효로 소멸하여 이중지급 위험이 없으면 어음 상환의 동시이행항변권이 부인된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>대판 2010.7.29. 2009다69692</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>852</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>주택임대차보호법 제3조의3의 임차권등기에서 임대인의 임대차보증금 반환의무와 임차인의 임차권등기 말소의무는 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>선이행</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>판례는 임차권등기가 이미 이행지체에 빠진 임대인에 대해 마쳐지는 담보적 기능의 등기이므로, 임대인의 보증금 반환의무가 임차권등기 말소의무보다 먼저 이행되어야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>대판 2005.6.9. 2005다4529</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>853</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>건물에 대한 저당권의 실행으로 경락인이 그 건물의 소유권을 취득한 경우, 경락인은 등기 없이도 건물 소유를 위한 지상권을 취득하고, 그 건물을 제3자에게 양도하면 특별한 사정이 없는 한 종된 권리인 지상권도 함께 양도한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>종된권리</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>판례는 제358조 본문 유추로 건물 저당권의 효력이 종된 권리인 지상권에 미치며, 제100조 제2항 유추로 건물 양도 시 지상권도 함께 양도된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>대판 1996.4.26. 95다52864</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>854</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>토지소유자가 지상건물의 소유명의를 타인에게 신탁한 후 토지에 저당권을 설정한 경우, 이후의 저당권 실행 경매절차에서 법정지상권이 성립한다.</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>동일인소유</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>판례는 명의신탁으로 건물이 대외적으로 타인 소유인 이상 저당권 설정 당시 토지·건물이 동일인 소유가 아니므로 법정지상권이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>대판 2004.2.13. 2003다29043 등</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>855</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>건물공유자 중 1인이 그 건물의 부지인 토지를 단독 소유하면서 토지에만 저당권을 설정하였다가 경매로 토지소유자가 달라진 경우, 건물공유자들은 건물 존속을 위한 제366조의 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>공유관계</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>판례는 토지소유자가 건물공유자 전원을 위해 토지 이용을 인정한 것으로 보아 법정지상권 성립을 긍정한다.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>대판 2011.1.13. 2010다67159</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>856</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에 있는 자가 자기 몫의 특정대지 위에 건물을 신축하여 점유하던 중 그 대지 지분을 다른 구분소유자가 경락·취득한 경우, 건물 소유자인 종전 구분소유자는 관습상 법정지상권을 취득할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>구분소유</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유에서 자기 특정 부분에 건물을 신축한 자가 그 부지 지분의 경락으로 소유자가 달라지면 관습상 법정지상권을 취득할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>대판 2004.6.11. 2004다13533</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>857</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에 있는 자가 자신의 특정 소유가 아닌 부분에 건물을 신축한 후 특정 부분대로 토지가 분할된 경우, 그 건물 소유자인 종전 구분소유자는 관습상 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>건물위치</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>판례는 자신의 특정 소유 부분이 아닌 곳에 건물을 신축한 경우에는 토지·건물 동일인 소유 요건을 갖추지 못하여 관습상 법정지상권이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>판례(구분소유적 공유와 법정지상권)</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>858</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>이행인수인은 채권자에 대하여 직접 이행의무를 부담하지는 않지만, 민법 제481조의 '변제할 정당한 이익이 있는 자'에 해당하여 법정대위를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>법정대위</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>판례는 이행인수인이 변제하지 않으면 채무자에 대해 채무불이행 책임을 지는 지위에 있으므로 변제할 정당한 이익이 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>대결 2012.7.16. 2009마461</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>제481조</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>859</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>이행인수인이 채권자에 대하여 채무자의 채무를 승인하더라도, 다른 특별한 사정이 없는 한 소멸시효 중단사유인 채무승인의 효력은 발생하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>승인주체</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>판례는 승인은 시효이익을 받을 당사자나 대리인만 할 수 있는데 이행인수인은 채권자에게 직접 의무를 부담하지 않으므로 시효중단 효력이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>대판 2016.10.27. 2015다239744</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>860</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>매수인이 매매목적물에 관한 근저당권의 피담보채무액을 매매대금에서 공제하기로 약정한 경우, 이는 이행인수로서 매수인은 인수한 채무액을 공제한 잔금을 지급하면 잔금지급의무를 다한 것이 된다.</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>이행인수</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>판례는 채무액 공제 약정을 이행인수로 보아 매수인이 채무를 현실 변제할 의무를 부담하지 않고 공제 후 잔금 지급으로 의무를 다한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>대판 2004.7.9. 2004다13083</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>861</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사의 통지 후 채무자가 자신의 채무불이행을 이유로 한 법정해제가 이루어진 경우, 제3채무자는 그 계약해제로써 대위채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>판례(전합)는 채무불이행에 따른 법정해제는 제405조 제2항의 처분이 아니므로 제3채무자가 대항할 수 있다고 한다(다만 실질이 합의해제이면 대항 불가).</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2011다87235 전합</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>862</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>채권자대위소송에서 제3채무자로 하여금 직접 대위채권자에게 금전 지급을 명하는 판결이 확정된 경우, 피대위채권이 변제 등으로 소멸하기 전이라면 채무자의 다른 채권자는 그 피대위채권을 압류·가압류할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>책임재산</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>판례는 대위소송 판결이 확정되어도 피대위채권은 채무자의 책임재산으로 남아 있으므로 다른 채권자가 압류·가압류할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>대판 2016.8.29. 2015다236547</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>863</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>대위채권자가 채무자에게 대위권 행사 사실을 통지하거나 채무자가 이를 안 후에 이루어진 피대위채권에 대한 전부명령은, 우선권 있는 채권에 기초한 것이라는 등의 특별한 사정이 없는 한 무효이다.</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>처분제한</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위권 행사 통지·인지 후의 피대위채권 처분(전부명령)은 제405조 제2항에 따라 원칙적으로 대위채권자에게 대항할 수 없어 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>대판 2016.8.29. 2015다236547</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>864</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>전세권의 존속기간이 만료되어 담보물권적 권능만 남은 경우, 그 전세권은 피담보채권인 전세금반환채권과 함께 제3자에게 양도할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>권능분리</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>판례는 기간 만료 후 담보물권적 권능만 남은 전세권도 전세금반환채권과 함께 양도할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>대판 2005.3.25. 2003다35659</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>865</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>전세권 소멸 시 목적물의 인도 및 전세권설정등기 말소에 필요한 서류 교부의무와 전세금반환의무가 동시이행관계에 있으므로, 전세권설정자가 이를 이유로 전세금 반환을 거부한 경우 특별한 사정이 없는 한 전세금에 대한 이자 상당액의 부당이득을 얻은 것이 아니다.</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>판례는 전세금반환의무와 목적물 인도·등기말소 서류 교부의무가 동시이행관계에 있으므로, 동시이행항변에 기한 반환 거부는 부당이득이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>민법 제317조 · 판례</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>제317조</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>866</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>대지와 건물의 소유자가 동일한 건물에 전세권이 설정된 후 그 대지가 양도된 경우, 대지의 특별승계인은 전세권설정자에 대하여 지상권을 설정한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>법정지상권</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>민법 제305조는 대지·건물 동일 소유자의 건물에 전세권을 설정한 후 대지가 양도된 경우 대지소유자가 전세권설정자에게 지상권을 설정한 것으로 본다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>민법 제305조</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>제305조</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>867</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>사해행위인 근저당권설정계약에 기한 근저당권설정등기가 경락으로 인하여 말소된 경우에도, 채권자는 여전히 그 근저당권설정계약의 취소를 구할 이익이 있다.</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>취소이익</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>판례는 수익자가 배당을 받는 등 부당한 이득을 보유하지 못하게 하기 위해 등기 말소 후에도 근저당권설정계약 취소의 이익을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>대판 1997.10.10. 97다8687</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>868</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>특정채권의 보전을 위해서도 채권자취소권을 행사할 수 있으므로, 소유권이전등기청구권을 가진 자가 양도인의 이중양도로 취득하게 되는 부동산 가액 상당의 손해배상채권은 사해행위취소권의 피보전채권이 된다.</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>피보전채권</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>판례는 채권자취소권은 금전채권 보전을 위한 것이므로 특정채권 보전을 위해서는 행사할 수 없고, 이중양도로 인한 손해배상채권도 그 발생이 불확실하여 피보전채권이 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>대판 1999.4.27. 98다56690</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>869</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>채권자취소권의 요건을 갖춘 각 채권자가 동시 또는 이시에 각각 사해행위취소의 소를 제기한 경우, 이는 각자 고유의 권리를 행사하는 것이므로 중복제소에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>중복제소</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>판례는 각 채권자의 채권자취소권 행사가 고유의 권리이므로 중복제소가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>대판 2003.7.11. 2003다19558</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>870</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>제3채무자의 압류채무자에 대한 자동채권이 수동채권인 피압류채권과 동시이행관계에 있는 경우, 압류의 효력 발생 후에 자동채권이 발생하였더라도 제3채무자는 그 자동채권에 의한 상계로 압류채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>상계대항</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>판례는 동시이행관계에 있는 자동채권은 그 발생 기초가 압류 전에 이미 존재하므로 제498조의 '압류 후 취득한 채권'이 아니어서 상계로 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>대판 2010.3.25. 2007다35152</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>제498조</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>871</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>고의의 불법행위로 인한 손해배상채권에 대한 상계금지 규정인 민법 제496조는, 중대한 과실로 인한 불법행위로 인한 손해배상채권에까지 유추 또는 확장 적용된다.</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>판례는 제496조는 고의의 불법행위에 한하여 적용되고 중과실 불법행위에는 유추·확장 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>대판 1994.8.12. 93다52808</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>872</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>제3자를 위한 계약에서 낙약자와 요약자 사이의 기본관계를 이루는 계약이 무효이거나 해제된 경우, 낙약자는 이미 제3자(수익자)에게 급부한 것을 제3자를 상대로 반환청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>청산관계</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>판례는 제3자를 위한 계약의 청산은 계약당사자인 낙약자와 요약자 사이에서 이루어져야 하므로 낙약자가 수익자를 상대로 반환을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>대판 2010.8.19. 2010다31860</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>873</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>제3자를 위한 계약에서 요약자와 수익자 사이의 대가관계가 부존재하거나 효력을 상실하면, 요약자는 이를 이유로 자신이 기본관계에 기하여 낙약자에게 부담하는 채무의 이행을 거부할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>대가관계</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>판례는 대가관계의 효력은 제3자를 위한 계약이나 기본관계에 영향을 미치지 않으므로 요약자가 대가관계 부존재를 이유로 채무 이행을 거부할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>대판 2003.12.11. 2003다49771</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>874</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>공동불법행위에서 피해자의 과실상계는 공동불법행위자 각인에 대한 과실비율이 서로 다르더라도, 피해자의 과실을 각인에 대해 개별적으로 평가하지 않고 전원에 대한 과실로 전체적으로 평가하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>과실상계방법</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위의 일체성상 피해자 과실을 전원에 대한 과실로 전체적으로 평가한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 96다55631</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>875</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>피해자가 공동불법행위자들 중 일부를 상대로 한 전소에서 승소한 금액을 전부 지급받았더라도, 그 금액이 나머지 공동불법행위자에 대한 후소에서 산정된 손해액에 미치지 못하면 후소의 피고는 그 차액을 지급할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>별소산정</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위자별 별소에서 과실상계비율·손해액을 달리 인정할 수 있으므로, 전소 지급액이 후소 손해액에 미달하면 후소 피고가 차액을 지급해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>대판 2001.2.9. 2000다60227</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>876</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>민법 제921조의 이해상반행위 해당 여부는 친권자의 의도나 그 행위의 결과 실제로 이해의 대립이 생겼는지를 묻지 않고, 행위의 객관적 성질상 이해의 대립이 생길 우려가 있는지에 따라 판단한다.</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>형식적판단설</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>판례는 이해상반행위 판단에 형식적 판단설을 취하여 행위의 객관적 성질을 기준으로 한다.</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>대판 1996.11.22. 96다10270</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>877</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>친권자인 모가 자신이 대표이사로 있는 주식회사의 채무 담보를 위하여 자신과 미성년 자녀의 공유재산에 자녀의 법정대리인 겸 본인 자격으로 근저당권을 설정한 행위는 이해상반행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>형식적판단설</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>판례는 행위의 객관적 성질상 회사 채무 담보에 불과하므로 친권자와 자녀 사이에 이해 대립이 생길 우려가 있는 이해상반행위로 볼 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>대판 1996.11.22. 96다10270</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>878</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>특별대리인 선임 심판에서 처리할 법률행위를 특정하지 않은 경우, 특별대리인은 선임신청서에 신청의 원인으로 적시한 특정의 법률행위에 한하여 처리권한을 가지고 신청서 외의 법률행위를 처리할 권한은 없다.</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>판례는 특별대리인이 이해상반되는 특정 법률행위에 관하여 개별적으로 선임되므로 신청서에 적시된 법률행위에 한하여 권한을 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>대판 1996.4.9. 96다1139</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>879</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>임대인이 임대차보증금반환채권의 양도를 아무런 이의를 보류하지 않고 승낙하였더라도, 임차인이 부담할 연체차임이나 손해배상액은 반환할 임대차보증금에서 당연히 공제된다.</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>당연공제</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>판례는 보증금반환의무가 목적물 반환 시까지 생긴 임차인의 모든 채무를 공제한 잔액에 관해서만 이행기에 도달하므로 이의 없는 승낙에도 당연 공제된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>대판 2002.12.10. 2002다52657</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>880</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>임대인의 수선의무 면제특약에서 면제의 범위를 명시하지 않은 경우, 대파손의 수리 등 대규모의 수선은 임대인이 수선의무를 부담한다.</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>면제범위</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>판례는 수선의무 면제특약에 범위를 명시하지 않으면 소규모 수선만 면제되고 대규모 수선은 여전히 임대인의 의무라고 한다.</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>대판 1994.12.9. 94다34692</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>제623조</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>881</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 대항력을 갖춘 임차인의 임대차보증금반환채권이 가압류된 상태에서 임대주택이 양도된 경우, 양수인이 채권가압류의 제3채무자 지위를 승계한다.</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>지위승계</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>판례는 임대주택 양수인이 임대인 지위를 승계하므로 보증금반환채권 가압류의 제3채무자 지위도 승계한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>대판 2013.1.17. 2011다49523 전합</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>882</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>제3자와의 약정에 따라 본인(타인)의 사무를 처리한 경우에는 사무관리가 성립하지 않으며, 그 처리자는 본인에게 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>사무관리</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>판례는 제3자와의 약정에 따른 사무 처리는 의무 없이 타인을 위한 관리가 아니므로 사무관리가 아니고, 본인에 대한 직접 부당이득반환청구(전용물소권)도 부정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>대판 2013.6.27. 2011다17106</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>제734조</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>883</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>사무관리가 성립하려면 타인을 위하여 사무를 관리한다는 관리의사가 필요하다.</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>성립요건</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>판례는 타인의 사무를 위한 관리의사가 없으면 사무관리가 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>대판 1995.9.15. 94다59943</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>제734조</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>884</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>사무관리자가 본인을 위하여 필요 또는 유익한 채무를 부담한 때에는 본인에게 자기에 갈음하여 변제하게 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>대변제청구</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>민법 제739조 제2항(제688조 제2항 준용)은 사무관리자의 본인에 대한 채무 대변제 청구권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>민법 제739조</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>제739조</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>885</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>기한이익 상실에 관한 민법 제1388조는 임의규정이므로, 당사자 사이에 다른 내용의 약정이 있으면 그 약정에 따라 기한이익 상실 여부를 판단한다.</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>임의규정</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>판례는 제388조를 임의규정으로 보아 당사자의 특약이 우선한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>대판 2001.10.12. 99다56192</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>886</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>기한이익 상실의 특약은 명백히 정지조건부 기한이익 상실특약이라고 볼 특별한 사정이 없는 한 형성권적 기한이익 상실특약으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>추정방향</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>판례는 기한이익 상실특약이 채권자를 위한 것임에 비추어 형성권적 특약으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>대판 2002.9.4. 2002다28340</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>887</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>형성권적 기한이익 상실특약이 있는 할부채무에서는 1회의 불이행이 있으면 그 즉시 잔존 채무 전액에 대하여 소멸시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>판례는 형성권적 특약의 경우 각 할부금이 변제기 도래 시마다 순차로 시효가 진행하고, 채권자가 잔존 채무 전액의 변제를 구하는 의사표시를 한 때에 한하여 그때부터 전액에 대하여 시효가 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>대판 2002.9.4. 2002다28340</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>888</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>정지조건부 기한이익 상실특약을 한 경우, 채권자의 별도 의사표시가 없더라도 기한이익 상실사유가 발생함과 동시에 이행기 도래의 효과가 발생하여 채무자는 이행지체 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>정지조건부</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>판례는 정지조건부 특약에서는 사유 발생과 동시에 채권자의 의사표시 없이도 이행기가 도래한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>대판 1999.7.9. 99다15184</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>889</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>사해행위 취소 및 원상회복으로 채무자에게 부당이득반환채무를 부담하게 된 수익자는, 그 사해행위 이후에 취득한 부당이득반환채권으로 원상회복된 부동산에 대한 강제경매절차에서 배당을 요구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>배당요구</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>판례는 사해행위 이후에 채권을 취득한 자는 회복되는 재산을 공동담보로 파악하지 않은 자여서 제407조의 효력을 받는 채권자에 포함되지 않으므로 배당을 요구할 권리가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>대판 2015.10.29. 2012다14975</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>제407조</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>890</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>채권자가 사해행위 취소 및 원상회복으로 소유권이전등기 말소를 명하는 판결을 받았으나 아직 말소등기를 마치지 않은 상태에서, 소송 당사자가 아닌 다른 채권자는 그 판결에 기하여 채무자를 대위하여 말소등기를 신청할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>판례는 취소의 상대적 효력상 소송 당사자가 아닌 다른 채권자는 그 판결로 채무자를 대위하여 말소등기를 신청할 수 없다고 한다(다만 마쳐지면 실체관계 부합으로 유효).</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>대판 2015.11.17. 2013다84995</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>891</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>채권자가 사해행위 취소소송에서 원상회복의 방법으로 등기 말소를 구하는 대신, 수익자를 상대로 채무자 앞으로 소유권이전등기절차를 이행할 것을 청구할 수도 있다.</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>원상회복방법</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>판례는 등기 말소 대신 채무자 앞으로의 직접 이전등기를 구하는 원상회복도 허용한다.</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>대판 2000.2.25. 99다53704</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>892</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>사해행위의 취소가 제척기간 내에 행사되었다면, 그에 따른 원상회복청구는 제척기간 도과 후에도 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>제척기간</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>판례는 취소권이 제척기간 내에 행사되면 원상회복청구는 기간 도과 후에도 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>대판 2001.9.4. 2001다14108</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>893</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>민법상 보증은 그 의사가 보증인의 기명날인 또는 서명이 있는 서면으로 표시되어야 효력이 발생하며, 보증의 의사가 전자적 형태로 표시된 경우에는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>방식</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>민법 제428조의2 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>민법 제428조의2</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>제428조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>894</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>공작물의 점유자가 손해 방지에 필요한 주의를 해태하지 아니한 때에는 그 소유자가 손해를 배상할 책임이 있으며, 이 소유자의 책임은 무과실책임이다.</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>무과실책임</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>민법 제758조 제1항 단서의 공작물 소유자 책임은 면책 규정이 없는 무과실책임이다.</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>민법 제758조</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>제758조</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>895</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>도급인이 수급인의 공사에 관하여 단순히 시공이 설계도대로 시행되는가를 확인하여 공정을 감독하는 데 불과한 이른바 감리를 한 경우에도, 도급인은 사용자책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>감리</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>판례는 구체적 지휘·감독권을 보유한 경우에만 사용자책임이 인정되고, 단순한 감리에 불과하면 사용자책임이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>대판 1992.6.23. 92다2615</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>제757조</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>896</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>금전채무에 관하여 약정이율이 법정이율보다 낮은 경우, 이행지체로 인한 지연손해금은 그 낮은 약정이율이 아니라 법정이율에 의하여 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>이율적용</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>판례는 제397조 제1항 단서가 약정이율이 법정이율 이상인 경우에만 적용되고, 약정이율이 법정이율보다 낮으면 본문으로 돌아가 법정이율에 의한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>대판 2009.12.24. 2009다85342</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>제397조</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>897</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>원본채권의 소멸시효 완성의 효력은 시효완성 전에 발생한 이자나 지연손해금에도 미치지만, 변제로 소멸한 원금 부분으로부터 변제 전에 발생한 이자나 지연손해금에는 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>시효효력</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>판례는 시효로 소멸한 원금의 부종성에 따라 그 이자·지연손해금도 소멸하나, 변제로 소멸한 원금의 변제 전 발생 이자에는 그러한 효력이 미치지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>민법 제183조 · 판례</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>제183조</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>898</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>불확정기한부 채무는 채무자가 기한이 도래함을 안 때부터 지체책임이 발생한다.</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>지체시기</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>민법 제387조 제1항 후단은 불확정기한부 채무에 관하여 채무자가 기한 도래를 안 때부터 지체책임을 진다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>민법 제387조①</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>899</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>부부 사이의 부양의무 중 과거의 부양료는, 원칙적으로 부양을 받을 자가 부양의무자에게 이행을 청구한 이후로 이행지체된 부분에 대하여만 지급을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>과거부양료</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>판례는 과거의 부양료는 원칙적으로 이행청구 이후 부분만 청구할 수 있으나, 형평상 특별한 사정이 있으면 그 이전 부분도 청구할 수 있다고 한다(자녀 양육비와 구별).</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>대결 2008.6.12. 2005스50</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>제826조</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>8001</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>성년의 자녀가 부모를 상대로 유학비용 충당을 위한 부양료를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>부양범위</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>판례는 부모가 성년 자녀에 대하여 부담하는 부양의무는 2차적 부양의무로서 자녀가 자력·근로로 생활을 유지할 수 없는 경우에 한하므로, 유학비용 충당을 위한 부양료 청구는 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>대결 2017.8.25. 2017스5</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>제974조</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>8002</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>변시8</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>부부간 상호부양의무는 혼인관계의 본질적 의무로서 제1차 부양의무이고, 부모가 성년의 자녀에 대하여 부담하는 부양의무는 제2차 부양의무이다.</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>부양순위</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>판례는 부부간 부양을 1차적 부양의무, 부모의 성년 자녀 부양을 2차적 부양의무로 구별한다.</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>대판 2012.12.27. 2011다96932</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>제826조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H766"/>
+  <dimension ref="A1:H866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31104,6 +31104,4006 @@
         </is>
       </c>
     </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>701</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>제3자가 금융기관의 대출 관련 서류에 주채무자 또는 연대보증인으로서 직접 서명·날인하였다면, 특별한 사정이 없는 한 이는 비진의표시나 통정허위표시가 아니라 그 제3자가 채무자가 된다.</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>명의대여</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>판례는 명의대여자가 대출서류에 서명·날인하면 경제적 효과를 타인에게 귀속시킬 의사에 불과하므로 진의와 표시의 불일치가 없다고 본다.</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>대판 2015.2.12. 2014다41223</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>702</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>피담보채권이 존재하지 않는 통정허위표시에 의한 근저당권에 대하여 제3자가 그 근저당권부 피담보채권을 가압류한 경우, 그 가압류는 무효이고 가압류권자는 등기상 이해관계 있는 제3자로서 근저당권 말소에 대한 승낙의 의사표시를 할 의무를 진다.</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>판례는 피담보채권이 없으면 근저당권도 성립하지 않으므로 그 채권을 가압류해도 무효이고, 가압류권자는 말소등기에 승낙할 의무가 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>대판 2004.5.28. 2003다70041</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>703</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>부동산 매수자금을 차용하고 담보조로 가등기를 하기로 약정한 후 채권자들의 강제집행을 우려하여 제3자에게 가장양도한 다음 그 제3자로부터 가등기를 경료받은 자는, 통정허위표시에서 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>판례는 실질적으로 새로운 법률원인에 의한 것이 아니므로 제3자에 해당하지 않고, 다만 그 가등기 자체는 실체관계에 부합하여 유효하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>대판 1982.5.25. 80다1403</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>704</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>법정대리인의 동의 없이 신용구매계약을 체결한 미성년자가 사후에 법정대리인의 동의 없음을 이유로 이를 취소하는 것은 신의칙에 위배된다.</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>신의칙</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>판례는 미성년자 보호 규정이 강행규정이므로 미성년자의 취소권 행사를 신의칙 위반으로 배척할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>대판 2007.11.16. 2005다71659</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>제5조</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>705</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>미성년자가 신용카드 이용계약을 취소하는 경우, 미성년자가 부당이득으로 반환하여야 할 것은 가맹점에 대한 매매대금 지급채무의 면제이익이고, 이는 금전상의 이득으로서 특별한 사정이 없는 한 현존하는 것으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>현존이익</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>판례는 신용카드 이용계약과 개별 매매계약이 별개이므로 취소 시 미성년자는 가맹점에 대한 대금지급채무를 면한 이익을 얻고, 그 금전적 이득은 현존 추정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>대판 2005.4.15. 2003다60297</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>제141조</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>706</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>전 등기명의인이 미성년자이고 당해 부동산을 친권자에게 증여하는 행위가 이해상반행위라 하더라도, 일단 이전등기가 경료된 이상 그 등기에 필요한 절차(특별대리인 선임)를 적법하게 거친 것으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>등기추정</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>판례는 등기가 경료되면 그 원인과 절차에 있어 적법하게 경료된 것으로 추정되므로 이해상반행위라도 특별대리인 선임 절차를 거친 것으로 추정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>대판 2002.2.5. 2001다72029</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>707</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>공동상속재산 분할협의는 이해상반행위에 해당하므로, 친권자가 여러 미성년 자녀를 대리하는 경우 각자마다 특별대리인을 선임하여 각각 대리하여야 하고, 이에 위배되면 피대리자 전원의 추인이 없는 한 무효이다.</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>판례는 공동상속인인 친권자와 여러 미성년 자녀 사이의 분할협의가 이해상반행위이므로 자녀 각자마다 특별대리인을 선임해야 하고 위반 시 전원 추인 없으면 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>대판 1994.9.9. 94다6680</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>708</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>법정대리의 경우에도 대리권 남용에 관한 법리가 적용될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>대리권남용</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>판례는 법정대리에도 제107조 제1항 단서 유추에 의한 대리권 남용 법리가 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>대판 2011.12.22. 2011다64669</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>제107조</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>709</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>미성년자의 불법행위에 기한 손해배상청구권의 소멸시효 기산점인 '손해 및 가해자를 안 날'은 미성년자 본인을 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>판단기준</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>판례는 미성년자의 경우 그 법정대리인이 손해 및 가해자를 안 날을 기준으로 단기소멸시효 기산점을 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>대판 2010.2.11. 2009다79897</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>제766조</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>710</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>법인 대표권의 제한은 정관에 기재되어 있더라도 등기하지 않으면 선의·악의를 불문하고 제3자에게 대항할 수 없으나, 비법인사단의 경우에는 등기가 없더라도 상대방이 대표권 제한을 알았거나 알 수 있었으면 그 거래행위는 무효이다.</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>판례는 법인은 제60조에 따라 등기 없으면 악의자에게도 대항할 수 없고, 비법인사단은 등기 방법이 없어 상대방의 악의·과실을 입증하면 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>대판 1992.2.14. 91다24564 · 대판 2003.7.22. 2002다64780</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>제60조</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>711</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>비법인사단이 타인 간의 금전채무를 보증하는 행위는 총유물의 관리·처분행위에 해당하므로 사원총회의 결의를 거쳐야 한다.</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>판례(전합)는 비법인사단의 보증행위는 총유물 자체의 관리·처분이 따르지 않는 단순한 채무부담행위이므로 총유물의 관리·처분행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>대판 2007.4.19. 2004다60072 전합</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>712</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>피용자의 불법행위가 외관상 사무집행 범위 내로 보이더라도, 그 행위가 사무집행에 해당하지 않음을 피해자가 알았거나 중대한 과실로 알지 못한 경우에는 사용자책임을 물을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>외형이론</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>판례는 외형이론을 취하되 피해자의 악의·중과실이 있으면 사용자책임이 부정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>대판 1983.6.28. 83다카217</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>713</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에 있는 자는 제3자의 방해행위에 대하여 자기의 구분소유 부분뿐 아니라 전체 토지에 대하여 공유물의 보존행위로서 그 배제를 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>대외관계</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유가 대외적으로 단순한 공유관계이므로 전체 토지에 대한 방해배제를 보존행위로 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>대판 1994.2.8. 93다42986</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>714</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에서 자기 몫의 건물 또는 토지지분에 저당권을 설정하였다가 저당권 실행으로 소유자가 달라지면, 건물 소유자는 그 건물의 소유를 위한 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>내부관계</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유에서 건물과 그 대지가 내부관계상 단독소유이므로 저당권 실행으로 소유자가 달라지면 법정지상권이 성립한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>대판 2004.6.11. 2004다13533</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>715</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계는 공유물분할청구의 방법으로 해소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>해소방법</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유는 명의신탁 해지를 원인으로 한 지분이전등기로 해소해야 하고 공유물분할청구로는 해소할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>대판 1989.9.12. 88다카10517</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>제268조</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>716</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>표현대리가 성립하는 경우, 상대방에게 과실이 있더라도 과실상계의 법리를 유추적용하여 본인의 책임을 경감할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>판례는 표현대리가 성립하면 본인이 전적인 책임을 지며 상대방의 과실을 들어 과실상계로 책임을 경감할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>대판 1996.7.12. 95다49554</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>제126조</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>717</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>민법 제125조의 대리권 수여의 표시는 반드시 '대리권' 또는 '대리인'이라는 말을 사용하여야 하는 것이 아니라, 사회통념상 대리권을 추단할 수 있는 직함이나 명칭 등의 사용을 승낙 또는 묵인한 경우에도 인정된다.</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>표시방법</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>판례는 대리권 수여 표시를 직함·명칭 사용의 승낙·묵인으로도 인정한다.</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 97다53762</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>제125조</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>718</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>복대리인 선임권이 없는 대리인에 의하여 선임된 복대리인의 권한도 민법 제126조의 기본대리권이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>기본대리권</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>판례는 복임권 없는 대리인이 선임한 복대리인의 권한도 제126조 표현대리의 기본대리권이 될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>대판 1998.3.27. 97다48982</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>제126조</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>719</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>신원보증서류에 서명·날인한다는 착각에 빠져 연대보증의 서면에 서명·날인한 경우 이는 동기의 착오에 해당하므로, 그 착오가 제3자의 기망에 의한 것이면 사기에 관한 제110조 제2항이 적용된다.</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>착오유형</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>판례는 이는 표시상의 착오에 해당하고 동기의 착오가 아니므로, 제3자의 기망에 의한 것이라도 제110조 제2항이 아니라 착오에 관한 제109조만 적용하여 취소 가부를 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>대판 2005.5.27. 2004다43824</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>720</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>착오를 이유로 의사표시를 취소한 자는, 그 취소가 적법하더라도 상대방이 의사표시의 유효를 믿었음으로 인하여 입은 손해에 대하여 불법행위 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>위법성</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>판례는 적법한 착오 취소권 행사는 위법성이 없으므로 불법행위 손해배상책임이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>대판 1997.8.22. 97다13023</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>721</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>채권질권자는 질권의 목적이 된 채권을 직접 청구할 수 있으며, 이 경우 질권설정자의 동의를 요하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>실행방법</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>민법 제353조 제1항에 따라 채권질권자는 입질채권을 직접 청구할 수 있고 질권설정자의 동의는 필요하지 않다.</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>민법 제353조</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>제353조</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>722</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>민사집행법이 정하는 집행방법으로 채권질권을 실행하는 경우, 집행권원 없이 질권의 존재를 증명하는 서류만 제출하면 절차가 개시된다.</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>실행방법</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>민사집행법 제273조는 담보권 실행에 집행권원이 아니라 담보권의 존재를 증명하는 서류 제출로 개시한다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>민사집행법 제273조</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>제353조</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>723</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>채무 담보를 위하여 가등기 등이 경료된 경우, 그 채무의 변제의무는 가등기 말소의무보다 선이행의무이다.</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>선이행</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>판례는 담보 목적 등기의 말소의무보다 피담보채무 변제의무가 선이행의무이므로 교환적 이행을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>대판 1991.4.12. 90다9872</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>724</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>가등기담보법 규정을 위반하여 담보가등기에 기한 본등기가 이루어진 경우, 그 본등기는 약한 의미의 양도담보로서 담보의 목적 범위 내에서는 유효하다.</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>본등기효력</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>판례는 가담법 제3조·제4조를 위반한 본등기는 무효이고 약한 의미의 양도담보로도 효력이 없으며, 다만 청산절차를 거치면 사후에 유효한 등기가 될 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>대판 2002.6.11. 99다41657</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>725</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>담보가등기권리자는 그 선택에 따라 권리취득에 의한 실행(귀속청산)을 하거나 담보목적부동산의 경매를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>실행선택</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>가등기담보법 제12조는 담보가등기권리자의 권리취득 실행과 경매청구 중 선택권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>가등기담보법 제12조</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>726</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>소유권이전등기의 추정력은 제3자에 대해서뿐 아니라 전 소유자에 대해서도 미치므로, 등기명의자는 전 소유자에 대해서도 적법한 등기원인에 의하여 소유권을 취득한 것으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>추정범위</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>판례는 등기의 추정력이 권리변동의 당사자인 전 소유자에 대해서도 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>대판 2014.3.13. 2009다105215</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>727</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>제3자가 처분행위에 개입되어 소유권이전등기가 마쳐진 경우, 그 등기의 무효를 주장하며 말소를 청구하는 전 등기명의인이 그 제3자의 무권한 등 무효사실에 대한 증명책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>판례는 제3자 개입에도 현 명의인의 등기가 적법하게 추정되므로 무효사실은 전 명의인이 증명해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>대판 1993.10.12. 93다18914</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>728</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>소유권보존등기 명의인 이외의 자가 당해 토지를 사정받은 것으로 밝혀지면, 그 보존등기의 추정력은 깨어진다.</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>추정복멸</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>판례는 보존등기 명의인이 아닌 자가 사정받은 사실이 밝혀지면 보존등기의 추정력이 복멸되어 명의인이 승계취득 사실을 증명하지 못하면 원인무효가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>대판 1982.9.14. 82다카707</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>729</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>연대채무자 중 상환할 자력이 없는 자가 있는 경우, 그 무자력자의 부담부분을 분담할 다른 채무자가 채권자로부터 연대의 면제를 받은 때에는 그 채무자가 분담할 부분은 채권자의 부담으로 한다.</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>무자력분담</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>민법 제427조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>민법 제427조②</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>제427조</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>730</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>연대채무자는 자기 부담부분 이상을 변제하지 않았더라도, 출재로 공동면책이 되면 부담비율에 따라 다른 연대채무자에게 구상권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>구상요건</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>판례는 연대채무자의 구상권(제425조)은 연대보증인의 구상(제448조 제2항, 부담부분 초과 변제 요건)과 달리 부담부분 초과를 요하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>민법 제425조 · 판례</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>제425조</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>731</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>피해자의 공동불법행위자 중 1인에 대한 손해배상채권이 시효로 소멸한 경우, 피해자에게 손해를 배상한 다른 공동불법행위자의 그 1인에 대한 구상권도 함께 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>구상독립성</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>판례는 구상권은 피해자의 손해배상채권과 별개의 권리이므로 일부 공동불법행위자에 대한 손해배상채권이 시효 소멸해도 구상권은 소멸하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>대판 1997.12.23. 97다42830</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>732</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인이 전체 채무를 변제한 경우, 나머지 부진정연대채무자들이 부담하는 구상채무는 원칙적으로 분할채무이나, 구상권자에게 내부적 부담부분이 없는 경우에는 부진정연대채무가 된다.</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>채무형태</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>판례는 구상의무자가 여럿인 경우 원칙적 분할채무, 구상권자 무과실(부담부분 전무) 시 부진정연대로 본다.</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>대판 2005.10.13. 2003다24147</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>733</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>기한이익 상실의 특약은 명백히 정지조건부 기한이익 상실특약이라고 볼 특별한 사정이 없는 한 형성권적 기한이익 상실특약으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>추정방향</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>판례는 기한이익 상실특약이 채권자를 위한 것임에 비추어 형성권적 특약으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>대판 2002.9.4. 2002다28340</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>734</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>변제기 이후에 지급하는 지연이자(지연손해금)는 이자가 아니라 손해배상금이므로, 민법 제163조 제1호의 1년 이내 기간으로 정한 채권에 해당하지 않아 단기소멸시효의 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>시효성격</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>판례는 지연이자가 이자가 아니라 지연손해금이므로 제163조 제1호의 단기소멸시효 대상이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>대판 1989.2.28. 88다카214</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>제163조</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>735</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>쌍무계약에서 일방이 한 번 현실의 제공을 하여 상대방을 수령지체에 빠지게 하였더라도, 그 이행제공이 계속되지 않으면 과거에 이행제공이 있었다는 사실만으로 상대방의 동시이행항변권이 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>계속제공</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>판례는 상대방을 이행지체에 빠뜨리려면 이행제공이 계속되어야 하고, 일시적 제공만으로는 상대방의 동시이행항변권이 소멸하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>대판 1995.3.14. 94다26646</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>736</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>저당목적물의 변형물에 대하여 일반채권자가 물상대위권을 행사하려는 저당채권자보다 단순히 먼저 압류·가압류의 집행을 한 데 지나지 않은 경우, 저당권자는 물상대위권을 행사하여 일반채권자보다 우선변제를 받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>물상대위</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>판례는 일반채권자의 선행 압류는 특정성 유지를 위한 것일 뿐이므로 저당권자가 그 전후에 물상대위권을 행사하여 우선변제받을 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>대판 1994.11.22. 94다25728</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>제370조</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>737</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>저당권자가 물상대위에 기한 압류 전에 저당목적물의 소유자가 그 인도청구권에 기하여 금전 등을 수령한 경우, 저당권자는 그 소유자를 상대로 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>부당이득</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>판례는 소유자가 채권최고액 한도의 피담보채권액 범위에서 이득을 얻은 것이므로 저당권자가 그 소유자에게 부당이득반환을 청구할 수 있다고 한다(다른 채권자가 받은 경우는 불가).</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>대판 2009.5.14. 2008다17656</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>제370조</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>738</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>무효인 등기에 대한 말소청구는 그 말소를 청구할 수 있는 권원이 인정되는 자에 한하여 할 수 있으므로, 단순한 채권자에 불과한 자는 제214조에 의한 말소등기청구를 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>청구권원</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>판례는 무효 등기라도 그 말소를 구할 권원(소유권 등)이 있어야 청구할 수 있고 단순 채권자는 직접 말소를 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>대판 1999.2.26. 98다17831</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>739</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>채권자대위권을 행사하는 경우, 채권자는 채무자가 제3채무자에 대하여 가지는 항변사유를 주장할 수 있으나 자기와 제3채무자 사이의 독자적인 사정에 기한 사유는 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>대위범위</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위권은 채무자의 권리를 행사하는 것이므로 채권자는 채무자의 항변사유를 주장할 수 있을 뿐 자기 고유의 사유를 주장할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>판례(채권자대위권의 범위)</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>740</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>등기부취득시효에서 선의·무과실은 등기에 관한 것이 아니라 점유의 취득에 관한 것이므로, 그 무과실 여부는 점유개시 당시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>판단시점</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>판례는 등기부취득시효의 선의·무과실은 점유 개시 당시를 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>대판 1994.11.11. 93다28089</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>741</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>순차 경료된 이전등기 말소청구소송에서 최종 등기명의자의 등기부취득시효 완성이 증명된 경우, 원래의 소유자는 소유권을 상실하므로 선순위 등기명의자에 대한 등기말소청구는 기각되고, 물권적 청구권의 이행불능을 이유로 한 손해배상청구도 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>손해배상</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>판례는 소유권 상실로 물권적 청구권 자체가 소멸하므로 그 이행불능을 이유로 한 제390조 손해배상청구권이 발생하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2010다28604 전합</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>742</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>위약금은 손해배상액의 예정으로 추정되므로, 위약벌로 해석되려면 특별한 사정이 주장·증명되어야 한다.</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>민법 제398조 제4항은 위약금을 손해배상액 예정으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>대판 2009.12.24. 2009다60169 · 민법 제398조④</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>743</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>계약 당시 손해배상액을 예정한 경우, 다른 특약이 없는 한 통상손해만 예정액에 포함되고 특별손해는 별도로 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>범위</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>판례는 손해배상액 예정 시 다른 특약이 없으면 통상손해는 물론 특별손해까지 예정액에 포함되고 채권자의 손해가 예정액을 초과해도 초과분을 따로 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>대판 1993.4.23. 92다41719</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>744</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>지체상금을 계약 총액에 지체상금률을 곱하여 산출하기로 정한 경우, 손해배상 예정액의 과다 여부는 1일당 지체상금률이 아니라 지체상금 총액을 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>감액기준</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>판례는 제398조 제2항의 손해배상 예정액은 예정한 손해배상액의 총액을 의미하므로 지체상금의 과다 여부도 총액 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>대판 2002.12.24. 2000다54536</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>745</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>손해배상액의 예정은 이행의 청구나 계약의 해제에 영향을 미치지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>효력</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>민법 제398조 제3항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>민법 제398조③</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>746</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>근저당권설정등기가 위법하게 말소된 경우, 회복등기가 마쳐지기 전이라도 말소된 등기의 명의인은 적법한 권리자로 추정되므로, 배당기일에 출석하여 이의하고 배당이의의 소를 제기하여 구제받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>권리추정</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>판례는 등기가 물권의 효력발생요건이지 존속요건이 아니므로 원인 없이 말소되어도 물권의 효력에 영향이 없고 명의인이 적법한 권리자로 추정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>대판 2002.10.22. 2000다59678</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>747</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>근저당권설정등기가 위법하게 말소되어 회복등기 전에 배당받지 못한 근저당권자는, 배당표가 확정되었더라도 실제로 배당받은 자에 대하여 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>부당이득</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>판례는 확정된 배당표에 의한 배당 실시가 실체법상 권리를 확정하는 것이 아니므로 위법 말소로 배당받지 못한 근저당권자가 실제 배당받은 자에게 부당이득반환을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>대판 2002.10.22. 2000다59678</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>748</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>확정일자 있는 채권양도 통지와 가압류·압류명령이 제3채무자에게 동시에 송달되어 상호 우열이 없는 경우, 각 채권자는 모두 완전한 대항력을 갖추어 전액 이행청구를 할 수 있고, 양수채권액과 압류채권액의 합계가 채권액을 초과하면 각 채권액에 안분하여 내부적으로 정산할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>동시도달</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>판례(전합)는 동시도달 시 각 채권자가 전액 청구할 수 있고 채무자는 누구에게든 변제로 면책되며 채권자 간 안분 정산의무가 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223 전합</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>749</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>채권양도금지특약부 채권에 대한 전부명령은 집행채권자의 선의·악의를 불문하고 유효하며, 그 전부채권자로부터 다시 채권을 양수한 자가 특약을 알았거나 중과실로 알지 못하였더라도 채무자는 특약을 근거로 양도의 무효를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>집행우선</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>판례는 전부명령의 효력이 집행채권자의 선악과 무관하므로 유효한 전부 후의 양도에는 특약을 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>대판 2003.12.11. 2001다3771</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>750</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>채권양도통지서가 배달된 장소가 민사소송법상의 적법한 송달장소가 아니더라도, 채무자가 사회통념상 그 통지의 내용을 알 수 있는 객관적 상태에 놓였다고 인정되면 채권양도의 통지로서 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>도달주의</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>판례는 채권양도 통지가 도달주의에 따라 채무자가 알 수 있는 객관적 상태에 놓이면 효력이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>대판 2010.4.15. 2010다57</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>751</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>민법 제451조 제1항의 이의를 보류하지 아니한 채권양도 승낙은 관념의 통지로서, 대리인에 의하여도 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>승낙성질</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>판례는 이의 없는 승낙을 관념의 통지로 보고 대리인에 의한 승낙도 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>판례(이의 없는 승낙의 성질)</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>제451조</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>752</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>점유자가 유익비를 지출할 당시 계약관계 등 적법한 점유권원을 가졌던 경우, 그 점유자는 계약관계의 상대방이 아닌 점유회복 당시의 소유자에 대하여 민법 제203조 제2항에 따른 지출비용의 상환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>청구상대방</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>판례는 적법한 점유권원이 있었던 경우 그 계약관계를 규율하는 법리에 따라 계약 상대방에게 비용상환을 구할 수 있을 뿐, 점유회복 당시 소유자에게 제203조 제2항의 상환을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>대판 2003.7.25. 2001다64752</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>제203조</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>753</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>유효한 도급계약에 기하여 수급인이 도급인으로부터 제3자 소유 물건의 점유를 이전받아 수리한 결과 그 가치가 증가한 경우, 소유자에 대한 관계에서 제203조의 비용상환청구권을 행사할 수 있는 비용지출자는 수급인이 아니라 도급인이다.</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>비용지출자</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>판례는 수급인은 도급계약 상대방인 도급인에 대해 권리를 가질 뿐이고, 소유자에 대한 관계에서는 도급인만이 제203조의 비용상환청구권을 행사할 수 있는 비용지출자라고 한다.</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>대판 2002.8.23. 99다66564</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>제203조</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>754</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>면책적 채무인수에서 인수인은 전 채무자가 채권자에 대하여 가지는 항변할 수 있는 사유로 채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>항변승계</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>민법 제458조는 인수인이 전 채무자의 항변사유로 채권자에게 대항할 수 있다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>민법 제458조</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>제458조</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>755</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>채무자와 제3자 사이의 계약에 의한 면책적 채무인수는 채권자의 승낙이 있어야 효력이 생기고, 채권자가 승낙을 거절하면 그 이후에는 다시 승낙하여도 채무인수로서의 효력이 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>승낙거절</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>민법 제454조와 판례는 채권자의 승낙을 효력요건으로 보고, 일단 거절하면 사후 승낙으로 부활하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>민법 제454조 · 대판 1998.11.24. 98다33765</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>756</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>중첩적 채무인수에서 인수인이 채무자의 부탁을 받아 채무를 인수한 경우 채무자와 인수인은 연대채무관계에 있고, 부탁 없이 인수한 경우에는 부진정연대관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>관계형태</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>판례는 부탁 있는 경우 연대채무, 부탁 없는 경우 부진정연대로 본다.</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>대판 2009.8.20. 2009다32409</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>제453조</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>757</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>중첩적 채무인수인이 채권자에 대한 채권을 자동채권으로 상계한 경우, 그 상계의 효력은 연대채무자 1인의 상계의 절대효를 규정한 제418조 제1항에 의하여 원채무자에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>상계절대효</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>판례는 부탁 있는 중첩적 채무인수가 연대채무관계이므로 인수인의 상계가 제418조 제1항에 의해 원채무자에게 절대효를 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>대판 2010.9.16. 2008다97218 등</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>758</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>매수인이 중도금을 약정 일자에 지급하지 아니하면 계약이 해제된 것으로 한다는 실권약관부 매매계약에서, 매수인이 중도금 지급의무를 이행하지 않으면 그 계약은 그 일자에 자동적으로 해제된다.</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>실권약관</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>판례는 중도금에 관한 실권약관부 매매는 미지급 시 자동 해제된다고 한다(중도금은 선이행의무).</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>대판 1980.2.12. 79다2035</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>759</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>계약상 채무자가 계약을 이행하지 아니할 의사를 명백히 표시한 경우, 채권자는 신의칙상 이행기 전이라도 이행의 최고 없이 채무자의 이행거절을 이유로 계약을 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>이행거절</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>판례는 이행거절이 명백한 경우 이행기 전이라도 최고 없이 해제할 수 있다고 한다(제544조 단서).</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>대판 2005.8.19. 2004다53173</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>760</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>부동산 매매에서 잔대금 지급기일까지 대금을 지급하지 못하면 계약이 자동 해제된다는 실권조항이 있는 경우, 매수인이 약정 기한을 도과하기만 하면 매도인의 이행제공이 없어도 자동으로 해제된다.</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>판례는 잔대금 지급의무와 소유권이전등기의무가 동시이행관계에 있으므로, 매도인이 이행제공을 하여 매수인을 이행지체에 빠지게 하여야 비로소 자동 해제된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 98다505</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>761</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>채무자 소유의 여러 부동산에 공동저당권이 설정되어 있는 경우, 사해행위 취소에 따른 가액배상에서 각 부동산이 부담하는 피담보채권액은 특별한 사정이 없는 한 각 부동산의 가액에 비례하여 안분한 금액이다.</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>안분</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>판례는 제368조의 취지에 비추어 공동저당의 피담보채권액을 각 부동산 가액에 비례하여 안분한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>대판 2017.5.30. 2017다205073</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>762</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>공동저당의 목적 부동산 중 일부는 채무자 소유이고 다른 일부는 물상보증인 소유인 경우, 채무자 소유 부동산에 관하여 공제할 피담보채권액은 안분액이 아니라 공동저당권의 피담보채권액 전액이다.</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>공제액</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인이 변제자대위로 채무자 소유 부동산에 저당권을 행사할 수 있는 지위에 있으므로, 채무자 소유 부동산의 책임재산 산정 시 피담보채권 전액을 공제한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>대판 2017.5.30. 2017다205073</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>763</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>종전 임차인으로부터 미등기 무허가건물을 매수하여 점유하고 있는 토지 임차인은, 소유권 등기명의가 없더라도 임대인에 대하여 지상물매수청구권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>매수청구</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>판례는 미등기 무허가건물 매수인이 사실상 처분권을 가지므로 제643조의 지상물매수청구권을 행사할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>대판 2013.11.28. 2013다48364</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>764</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>기간의 정함이 없는 토지임대차에서 임대인의 해지통고에 의하여 임차권이 소멸된 경우에도, 토지임차인의 지상물매수청구권이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>매수청구</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>판례는 기간 약정 없는 임대차의 해지통고로 종료된 경우에도 지상물매수청구권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>대판 1995.7.11. 94다34265 전합</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>765</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>토지소유자가 아닌 제3자가 임대차계약의 당사자로서 토지를 임대한 경우, 임대인이 아닌 토지소유자가 직접 지상물매수청구권의 상대방이 된다.</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>상대방</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>판례는 지상물매수청구권의 상대방은 원칙적으로 임대차계약의 당사자인 임대인이고, 임대인이 아닌 토지소유자가 직접 상대방이 되는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>대판 1996.6.14. 96다14517</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>766</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>토지임대차 종료 시 임대인의 건물철거 및 부지인도 청구에는, 건물매수대금 지급과 동시에 건물명도를 구하는 청구가 당연히 포함되어 있는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>청구취지</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>판례는 철거·인도 청구와 매수대금 상환 동시 명도 청구는 별개이므로 전자에 후자가 포함되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>대판 1995.7.11. 94다34265 전합</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>767</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>채권자가 채무자의 채권자취소권을 대위행사하는 경우, 그 제척기간 준수 여부는 대위채권자가 아니라 채무자를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위권의 객체인 채권자취소권의 제척기간은 그 권리자인 채무자를 기준으로 준수 여부를 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>대판 2001.12.27. 2000다73049</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>768</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>무자력 상태의 채무자가 자백으로 패소확정판결을 받아 수익자 앞으로 소유권이전등기가 마쳐진 경우, 그 일련의 행위의 실질적 원인이 되는 채무자와 수익자 사이의 이전합의는 사해행위가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>사해성</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>판례는 형식적으로 판결에 의한 등기라도 실질적 원인인 채무자·수익자 간 이전합의가 사해행위에 해당할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>대판 2017.4.7. 2016다204783</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>769</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>채권자가 어느 수익자에 대하여 사해행위취소 및 원상회복청구의 승소판결을 받아 확정되었더라도 재산이나 가액의 회복을 마치지 아니한 경우, 다른 수익자에 대하여 별도로 사해행위취소 및 원상회복을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>중복청구</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>판례는 회복이 마쳐지지 않은 이상 채권자가 다른 수익자를 상대로 별도의 사해행위취소·원상회복을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>대판 2005.11.25. 2005다51457</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>770</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>명의대여자의 사용자책임에서 사용관계는 실제로 지휘·감독을 하였는지가 아니라 객관적·규범적으로 사용자가 그 불법행위자를 지휘·감독해야 할 지위에 있었는지를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>사용관계</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>판례는 명의대여관계의 사용관계를 객관적·규범적 지휘·감독 지위 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>대판 2001.8.21. 2001다3658</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>771</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>노무도급의 경우 도급인이 수급인에 대하여 특정한 행위를 지휘하거나 특정한 사업을 도급시킨 때에는, 도급인에게도 사용자책임의 사용관계가 인정된다.</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>노무도급</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>판례는 노무도급에서 도급인의 지휘·감독이 있으면 사용자책임의 사용관계가 인정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>대판 1998.6.26. 97다58170</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>772</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>지입차량의 차주 또는 그가 고용한 운전자의 과실로 타인에게 손해를 가한 경우, 지입회사는 객관적으로 지입차주를 지휘·감독하는 사용자의 지위에 있으므로 사용자책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>지입</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>판례는 지입회사가 명의대여자로서 객관적 지휘·감독 지위에 있으므로 사용자책임을 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>대판 2000.10.13. 2000다20069</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>773</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>이혼으로 인한 재산분할청구권은 협의 또는 심판에 의하여 구체화되기 전에는, 이를 보전하기 위하여 채권자대위권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>피보전적격</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권은 범위·내용이 불확정하여 채권자대위권의 피보전채권이 될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>대판 1999.4.9. 98다58016</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>774</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>수임인이 위임인에 대한 대변제청구권을 보전하기 위하여 채무자인 위임인의 채권을 대위행사하는 경우에는, 채무자의 무자력을 요건으로 하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>무자력요건</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>판례는 특정채권 보전을 위한 채권자대위(전용형)에서는 채무자의 무자력을 요하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>대판 2002.1.25. 2001다52506</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>775</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사에서 피보전채권은 보전의 필요성이 인정되고 이행기가 도래한 것이면 충분하며, 채권의 발생원인이나 제3채무자에 대한 대항 여부는 묻지 않는다.</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>피보전요건</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>판례는 피보전채권은 보전 필요성과 이행기 도래로 충분하고 그 발생원인을 묻지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>판례(채권자대위권의 피보전채권)</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>776</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>동업을 목적으로 하는 조합이 조합재산으로 부동산 소유권을 취득하였으나 합유등기를 하지 않고 조합원들 명의로 각 지분에 관하여 공유등기를 한 경우, 이는 조합체가 조합원들에게 각 지분에 관하여 명의신탁한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>명의신탁</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>판례는 조합재산이 합유이지만 조합원 명의 공유등기는 각 지분에 관한 명의신탁으로 본다.</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>대판 2002.6.14. 2000다30622</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>제271조</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>777</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>조합에서 업무집행자를 정하지 아니한 경우 조합의 통상사무는 각 조합원이 단독으로 집행할 수 있으나, 특별사무는 출자액과 관계없이 조합원의 과반수로써 결정한다.</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>업무집행</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>민법 제706조 제2항·제3항은 통상사무의 각자 집행과 특별사무의 조합원 과반수 결정을 규정한다.</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>민법 제706조</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>제706조</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>778</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>조합의 임의탈퇴는 업무집행자가 있는 경우에는 그 업무집행자에 대한 의사표시만으로 충분하다.</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>탈퇴방식</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>판례는 임의탈퇴가 잔존 조합원의 지위에 중대한 영향을 미치므로 업무집행자가 있어도 다른 조합원 전원에 대한 의사표시로 하여야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>대판 1959.7.9. 4291민상668</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>제716조</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>779</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>조합원이 사망하면 그 조합관계로부터 당연히 탈퇴하지만, 조합계약에서 지위 승계 약정이 있으면 그 지위가 상속인에게 승계될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>탈퇴사유</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>민법 제717조는 사망을 당연 탈퇴 사유로 정하나, 판례는 지위 승계 약정이 있으면 상속인 승계가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>민법 제717조 · 판례</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>제717조</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>780</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>임차인이 임대인의 동의 없이 임차물을 제3자에게 전대하여 사용·수익하게 한 경우, 임대차계약이 존속하는 한 임대인은 그 제3자에게 불법점유를 이유로 한 차임 상당 손해배상이나 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>차임청구권</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>판례는 임대차가 적법하게 종료되지 않는 한 임대인이 임차인에 대해 차임청구권을 가지므로 제3자에 대한 손해배상·부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>대판 2008.2.28. 2006다10323</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>제629조</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>781</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>강박행위에 의하여 금원을 교부받은 자는 그 의사표시가 취소되지 않더라도 법률상 원인 없이 이득한 것이므로 부당이득으로 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>법률상원인</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>판례는 강박에 의한 의사표시라도 취소되어 소멸하지 않는 한 그 금원 보유에 법률상 원인이 있으므로 부당이득반환의무가 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>대판 1990.11.13. 90다카17153</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>782</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>부동산실명법 시행 후 매도인이 선의인 계약명의신탁에서 명의수탁자가 소유권을 취득한 경우, 명의신탁자는 명의수탁자에 대하여 부동산 자체의 반환을 부당이득으로 청구할 수 없고 자신이 교부한 매수대금의 반환을 청구할 수 있을 뿐이다.</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>반환대상</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>판례는 선의 매도인 계약명의신탁에서 수탁자가 완전한 소유권을 취득하므로 신탁자의 부당이득 반환대상은 부동산이 아니라 매수자금이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>대판 2005.1.28. 2002다66922</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>783</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>채무 일부에 대한 변제공탁은 그 부분에 관하여도 효력이 생기지 않지만, 채권자가 채권의 일부에 충당한다는 유보의 의사표시를 하고 이를 수령한 때에는 채권의 일부 변제에 충당되며, 그 유보의 의사표시는 반드시 명시적일 필요는 없다.</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>일부공탁</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>판례는 채무 일부 공탁은 무효이나 채권자가 유보 의사표시(묵시적 포함)를 하고 수령하면 일부 변제에 충당된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>대판 2009.10.29. 2008다51359</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>제487조</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>784</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>변제자와 변제수령자는 이해관계 있는 제3자의 이익을 해하지 않는 이상, 이미 급부를 마친 뒤에도 기존의 충당방법을 배제하고 제공된 급부를 다른 채무에 다시 충당할 것인지를 약정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>재충당</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>판례는 급부 후에도 당사자의 합의로 충당방법을 변경할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>대판 2013.9.12. 2012다118044</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>제476조</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>785</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>경개로 인한 신채무가 원인의 불법 또는 당사자가 알지 못한 사유로 성립하지 아니하거나 취소된 때에는, 구채무는 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>의존성</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>민법 제504조는 구채무 소멸이 신채무 성립에 의존함을 정한다.</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>민법 제504조</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>제504조</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>786</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>채권자를 지정권자로 하는 변제충당의 약정이 있는 경우, 채권자는 변제자에 대한 충당의 의사표시 없이도 변제충당을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>합의충당</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>판례는 채권자를 지정권자로 하는 충당 약정이 있으면 변제자에 대한 의사표시 없이도 충당의 효력이 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>대판 1987.3.24. 84다카1324</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>제476조</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>787</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>미성년자에게 친권을 행사하는 부모는 유언으로 미성년후견인을 지정할 수 있으나, 법률행위의 대리권과 재산관리권이 없는 친권자는 그러하지 아니하다.</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>지정요건</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>민법 제931조 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>민법 제931조</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>제931조</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>788</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>가정법원은 유언으로 미성년후견인이 지정된 경우라도 미성년자의 복리를 위하여 필요하면 미성년자의 청구에 의하여 후견을 종료하고 생존하는 부 또는 모를 친권자로 지정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>친권회복</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>민법 제931조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>민법 제931조②</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>제931조</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>789</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>일반양자는 친양자와 달리 양자가 사망한 경우 생가와의 관계가 존속하므로, 양부모와 친부모가 동순위로 공동상속한다.</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>입양효과</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>판례는 일반양자는 친생부모와의 관계가 존속하므로 직계존속인 양부모와 친부모가 공동상속한다고 한다(친양자와 구별).</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>민법 제1000조 · 판례</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>제1000조</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>790</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>상속인이 피상속인과 동시에 사망한 경우에는 그들 사이에 상속이 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>동시사망</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>민법 제30조의 동시사망 추정에 따라 동시사망자 사이에는 상속이 일어나지 않는다(다만 대습상속은 가능).</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>민법 제30조</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>제1000조</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>791</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>구수증서에 의한 유언은 그 증인 또는 이해관계인이 급박한 사유가 종료한 날부터 7일 내에 법원에 검인을 신청하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>검인기간</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>민법 제1070조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>민법 제1070조②</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>제1070조</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>792</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>민법 제1091조의 검인이나 제1092조의 개봉절차를 거치지 아니한 유언증서는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>검인효력</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>판례는 검인·개봉은 증거보전·검증절차에 불과하므로 적법한 유언은 검인·개봉 여부와 관계없이 유언자의 사망으로 곧바로 효력이 생긴다고 한다.</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 97다38510</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>제1091조</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>793</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>유언집행자가 있는 경우 유증 목적물에 관한 소송에서 상속인은 원고적격이 없으며, 지정 유언집행자가 해임된 후 새로운 유언집행자가 선임되지 아니한 경우에도 상속인의 원고적격은 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>원고적격</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>판례는 유언집행자가 있으면 그가 관리처분권을 가지므로 상속인의 원고적격이 없고, 해임 후 미선임 상태에서도 상속인의 원고적격이 회복되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>대판 2010.10.28. 2009다20840</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>제1101조</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>794</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>제한능력자와 파산선고를 받은 자는 유언집행자가 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>결격사유</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>민법 제1098조는 제한능력자와 파산선고를 받은 자의 유언집행자 결격을 정한다.</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>민법 제1098조</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>제1098조</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>795</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>수인의 유언집행자에게 유증의무의 이행을 구하는 소송은 유언집행자 전원을 피고로 하여야 하는 고유필수적 공동소송이다.</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>공동소송</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>판례는 수인의 유언집행자에 대한 유증의무 이행청구를 고유필수적 공동소송으로 본다.</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>대판 2011.6.24. 2009다8345</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>제1102조</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>796</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>부부 일방의 특유재산은 원칙적으로 재산분할의 대상이 되지 않지만, 다른 일방이 적극적으로 그 특유재산의 유지에 협력하여 감소를 방지하였거나 증식에 협력한 경우에는 분할의 대상이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>특유재산</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>판례는 특유재산도 다른 일방의 유지·증식 협력이 인정되면 재산분할 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>대판 1998.2.13. 97므1486</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>797</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>이혼 당시 부부 일방이 아직 재직 중이어서 실제 퇴직급여를 수령하지 않았더라도, 이혼소송의 사실심 변론종결 시에 잠재적으로 존재하는 퇴직급여채권은 재산분할의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>분할대상</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>판례(전합)는 장래의 퇴직급여채권도 재산분할의 대상으로 본다.</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>대판 2014.7.16. 2013므2250 전합</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>798</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>이혼 시 재산분할에서 소극재산의 총액이 적극재산의 총액을 초과하여 재산분할 청구가 받아들여지는 경우, 적극재산을 분할할 때처럼 기여도 등을 중심으로 일률적 비율을 정하여 당연히 분할 귀속되게 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>분할방법</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소극재산 초과 시에도 재산분할이 가능하지만, 적극재산 분할처럼 일률적 비율로 당연 분할 귀속시켜야 하는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>대판 2013.6.20. 2010므4071 전합</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>799</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>부부의 일방이 혼인 중 제3자에게 부담한 채무라도 그것이 공동재산의 형성에 수반하여 부담한 채무인 경우에는 재산분할에서 청산의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>채무청산</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>판례는 공동재산 형성에 수반한 채무는 재산분할에서 청산 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>대판 2013.6.20. 2010므4071 전합</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>7001</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>변시7</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>협의 또는 심판에 의하여 구체화되지 않은 재산분할청구권은 혼인이 해소되기 전에 미리 포기할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>사전포기</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권의 혼인 해소 전 사전포기를 허용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>대판 2016.1.25. 2015스451</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H866"/>
+  <dimension ref="A1:H971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -35104,6 +35104,4206 @@
         </is>
       </c>
     </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>601</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>채권의 목적을 종류로만 지정한 경우 법률행위의 성질이나 당사자의 의사로 품질을 정할 수 없는 때에는, 채무자는 중등품질의 물건으로 이행하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>품질기준</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>민법 제375조 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>민법 제375조</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>제375조</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>602</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>지참채무인 종류채권에서 채무자가 인도할 목적물을 분리하여 운송기관에 위탁하여 발송하면, 그것만으로 목적물이 특정되어 발송 후 도달 전에 불가항력으로 멸실되어도 채무자는 다시 인도할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>특정시기</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>지참채무는 목적물이 채권자의 주소에 도달하여 수령할 수 있는 상태에 놓인 때 특정되므로, 발송만으로는 특정되지 않아 발송 후 멸실 시 채무자는 다른 물건으로 변제해야 한다.</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>민법 제375조②·제467조② · 통설</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>제375조</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>603</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>종류채권의 변제장소는 특정물 인도 이외의 채무이므로 채무의 성질이나 의사표시로 정하지 않은 때에는 채권자의 현주소에서 변제하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>변제장소</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>민법 제467조 제2항은 특정물 인도 외의 채무변제를 채권자의 현주소(영업채무는 현영업소)에서 하도록 정한다.</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>민법 제467조②</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>제467조</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>604</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>채권자의 수령지체 중에 당사자 쌍방의 책임 없는 사유로 채무가 이행할 수 없게 된 경우, 채무자는 상대방의 이행을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>위험부담</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>민법 제538조 제1항 후단은 채권자의 수령지체 중 쌍방 무책의 이행불능 시 채무자가 반대급부를 청구할 수 있도록 한다.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>민법 제538조①</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>제538조</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>605</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>채무자의 이행거절로 인한 채무불이행에서 손해액의 산정은, 이행거절 당시의 급부목적물의 시가를 표준으로 한다.</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>손해액기준</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>판례는 이행거절이 명백하여 최고 없이 해제·손해배상을 청구할 수 있는 경우 손해액을 이행거절 당시의 시가로 산정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>대판 2007.9.20. 2005다63337</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>606</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>특별손해에서 특별사정의 존재 및 채무자의 예견가능성에 대한 증명책임은 채무자가 부담한다.</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>판례는 제393조 제2항의 특별사정 존재와 채무자의 예견가능성에 대한 증명책임을 채권자가 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>대판 1964.6.9. 63다1023</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>제393조</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>607</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>계약 당시 손해배상액을 예정한 경우, 그 예정은 계약상 채무불이행으로 인한 손해뿐 아니라 그 계약과 관련된 불법행위상의 손해까지 예정한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>예정범위</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>판례는 손해배상액 예정은 채무불이행 손해에 관한 것이고 불법행위상의 손해까지 예정한 것으로 볼 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>대판 1999.1.15. 98다48033</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>608</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>손해배상청구권 중 일부만 소송상 청구된 경우 과실상계는, 손해의 전액에서 과실비율에 의한 감액을 한 후 그 잔액과 청구액 중 적은 금액을 인용한다.</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>외측설</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>판례는 일부청구 시 손해 전액에서 과실상계한 잔액과 청구액 중 적은 금액을 인용하는 것이 당사자의 통상적 의사라고 한다.</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>대판 1976.6.22. 75다819</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>제396조</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>609</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>손해배상 예정액이 부당하게 과다한 경우, 법원은 당사자의 주장이 없더라도 직권으로 이를 감액할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>직권감액</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>민법 제398조 제2항에 따라 법원은 부당히 과다한 예정액을 직권으로 감액할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>민법 제398조② · 판례</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>610</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>담보권 실행을 위한 경매에서 배당금이 담보권자의 수개의 피담보채권 전부를 소멸시키기에 부족한 경우, 지정변제충당이나 합의충당은 허용되지 않고 법정변제충당의 방법에 따라야 한다.</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>법정충당</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>판례는 경매 배당금의 충당은 획일적·공평한 법정변제충당(제477조·제479조)에 따라야 하고 지정·합의충당이 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>대판 2000.12.8. 2000다51339</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>611</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>변제자가 주채무자인 경우, 보증인이 있는 채무와 보증인이 없는 채무 사이에는 변제이익에 차이가 없다.</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>변제이익</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>판례는 변제자가 주채무자인 경우 보증인 유무, 물상보증인의 물적 담보 유무, 제3자 발행 약속어음 교부 유무 등에 따라 변제이익이 달라지지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>대판 2014.4.30. 2013다8250</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>612</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>비용·이자·원본에 대한 변제충당은 원칙적으로 비용·이자·원본의 순서로 하여야 하지만, 당사자 사이의 합의나 일방의 지정에 상대방이 지체 없이 이의하지 않은 묵시적 합의가 있으면 그 순서와 달리 충당할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>충당순서</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>판례는 제479조의 순서를 일방적 지정으로 바꿀 수 없으나 합의(묵시적 포함)로는 달리 정할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>대판 2009.6.11. 2009다12399</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>제479조</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>613</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>채무자가 원본뿐 아니라 지연이자도 지급할 의무가 있는 경우, 채무자가 원본과 지연이자를 합한 전액에 미치지 못하는 이행제공을 하면서 이를 원본에 대한 변제로 지정하였다면 채권자는 그 수령을 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>수령거절</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>판례는 비용·이자·원본의 법정 충당순서에 어긋나는 일부 변제제공은 채무 본지에 따른 것이 아니므로 채권자가 수령을 거절할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>대판 1990.11.9. 90다카7262</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>제479조</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>614</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>공동이행방식 공동수급체의 구성원들이 상인인 경우, 공사도급계약에 따라 도급인에게 하자보수를 이행할 의무는 구성원 전원의 상행위로 부담한 채무로서 구성원들은 연대하여 이를 이행할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>연대책임</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>판례는 공동수급체가 민법상 조합이지만 조합채무가 상행위로 부담된 경우 상법 제57조 제1항에 따라 구성원의 연대책임을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>대판 2015.3.26. 2012다25432</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>제704조</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>615</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>민법상 조합에서 조합원 중 1인만을 가압류채무자로 한 가압류명령으로는 조합재산에 가압류집행을 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>합유집행</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>판례는 조합재산에 대한 강제집행·가압류에는 조합원 전원에 대한 집행권원·가압류명령이 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>대판 2015.10.29. 2012다21560</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>제704조</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>616</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>공동이행방식 공동수급체가 공사 시행으로 도급인에 대하여 가지는 채권은 원칙적으로 구성원에게 합유적으로 귀속하지만, 개별 구성원으로 하여금 지분비율에 따라 직접 권리를 취득하게 하는 약정이 있으면 구성원 각자에게 지분비율로 귀속될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>채권귀속</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>판례는 공동수급체의 도급인에 대한 채권이 원칙적으로 합유적 귀속이나, 명시적·묵시적 약정으로 구성원 각자에게 지분비율로 귀속될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2009다105406 전합</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>제704조</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>617</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>공동저당의 목적 부동산 중 일부는 채무자 소유, 일부는 물상보증인 소유인 경우 동시배당을 하는 때에는, 채무자 소유 부동산의 경매대가에서 우선적으로 배당하고 부족분이 있는 경우에 한하여 물상보증인 소유 부동산에서 추가 배당한다.</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>배당순서</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>판례는 이 경우 제368조 제1항이 적용되지 않고 물상보증인의 변제자대위 보호를 위해 채무자 소유 부동산이 먼저 책임진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>대판 2010.4.15. 2008다41475</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>618</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>공동저당의 목적인 채무자 소유 부동산과 물상보증인 소유 부동산 중 채무자 소유 부동산이 먼저 경매되어 1번 공동저당권자가 변제받은 경우, 채무자 소유 부동산의 후순위저당권자는 제368조 제2항 후단에 의하여 물상보증인 소유 부동산에 대한 저당권을 대위행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>대위제한</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인의 변제자대위 기대를 보호하기 위해 채무자 소유 부동산의 후순위저당권자가 물상보증인 소유 부동산에 대위행사할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>대결 1995.6.13. 95마500</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>619</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>물상보증인 소유 부동산이 먼저 경매되어 변제받은 경우, 물상보증인 소유 부동산의 후순위저당권자는 채무자 소유 부동산에 대한 저당권을 대위행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>대위인정</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인이 변제자대위로 채무자 소유 부동산에 대한 선순위 저당권을 취득하고, 그 후순위저당권자는 물상대위 법리에 따라 이를 대위행사할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>대판 1994.5.10. 93다25417</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>620</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>여러 사람이 공동임대인으로서 임차인과 하나의 임대차계약을 체결한 경우, 그 임대차의 해지는 공동임대인 전원의 해지의 의사표시로 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>해지방식</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>판례는 공동임대인의 해지에 제547조(해지·해제의 불가분성)가 적용되어 전원의 의사표시를 요한다고 하며, 일부 양도로 공동임대인이 된 경우에도 같다고 한다.</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>대판 2015.10.29. 2012다5537 · 민법 제547조</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>제547조</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>621</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>보증금이 수수된 임대차에서 차임채권이 양도된 경우라도, 임차인은 임대차가 종료되어 목적물을 반환할 때까지 연체한 차임 상당액을 보증금에서 공제할 것을 주장하여 양수인의 양수금 청구를 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>당연공제</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>판례는 보증금이 임차인의 모든 채무를 담보하므로 차임채권이 양도되어도 임차인은 연체차임의 보증금 공제를 주장할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>대판 2015.3.26. 2013다77225</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>622</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>임대인이 수선의무를 이행함으로써 목적물의 사용·수익에 지장이 초래된 경우, 임차인은 그 지장을 받는 한도 내에서 차임의 지급을 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>차임거절</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>판례는 임대인의 사용·수익하게 할 의무와 차임지급의무가 대응관계에 있으므로 수선의무 이행으로 사용·수익에 지장이 생기면 그 한도에서 차임지급을 거절할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>대판 2015.2.26. 2014다65724</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>제627조</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>623</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>부동산 매수인이 매매목적물에 관한 임대차보증금 반환채무 등을 인수하면서 그 채무액을 매매대금에서 공제하기로 약정한 경우, 이는 원칙적으로 이행인수이고 면책적 채무인수로 보려면 채권자인 임차인의 승낙이 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>인수성질</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>판례는 채무액 공제 약정을 원칙적으로 이행인수로 보고, 임차인의 승낙이 있어야 면책적 채무인수가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>대판 2008.9.11. 2008다39663</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>624</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>채권자대위권을 행사하는 경우, 제3채무자는 채무자에 대해 가지는 모든 항변사유로 채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>항변범위</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>판례는 제3채무자가 채무자에 대해 가지는 모든 항변사유로 대위채권자에게 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>대판 2009.5.28. 2009다4787</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>625</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>채권자대위소송이 계속 중인데 채무자가 동일한 내용의 소송을 별도로 제기한 경우, 이는 중복제소금지 원칙에 위반된다.</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>중복제소</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위소송 계속 중 채무자의 동일 소송 제기를 중복제소로 본다.</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>대판 1992.5.22. 91다41187</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>626</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>채무자가 채권자대위소송이 제기된 사실을 알았을 경우, 그 채권자대위소송의 기판력이 채무자에게 미친다.</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>기판력</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>판례는 채무자가 대위소송 제기 사실을 안 경우 그 판결의 기판력이 채무자에게 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>대판 1975.5.13. 74다1664 전합</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>627</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>지명채권 양도통지를 한 후 그 양도계약이 해제된 경우, 양도인이 해제를 이유로 채무자에게 대항하려면 양수인이 채무자에게 해제사실을 통지하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>통지주체</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>판례는 양도계약 해제 시 양도인이 다시 대항하려면 양수인의 해제사실 통지가 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>대판 1993.8.27. 93다17379</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>제452조</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>628</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>선순위 근저당권부채권을 양수하였으나 아직 대항요건을 갖추지 못한 경우, 후순위 근저당권자는 그 대항요건 흠결을 이유로 채권양도의 효력을 부인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>판례는 대항요건 흠결을 주장할 수 있는 제3자를 양수인과 양립할 수 없는 법률상 지위 취득자로 한정하므로 후순위 근저당권자는 이에 포함되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>대판 2005.6.23. 2004다29279</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>629</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>채권양도에서 채무자의 승낙은 양도인 또는 양수인 중 누구에 대하여 하여도 대항요건으로서 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>승낙상대방</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>판례는 제450조의 채무자의 승낙은 양도인 또는 양수인에 대하여 하면 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>대판 1986.2.25. 85다카1529</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>630</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>확정일자 있는 채권양도 통지와 채권가압류결정 정본이 같은 날 도달되었는데 그 선후관계에 대하여 달리 입증이 없으면, 동시에 도달된 것으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>동시도달</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>판례(전합)는 도달의 선후가 불명한 경우 동시도달로 추정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223 전합</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>631</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>채권양도에서 양도인이 양도통지만을 한 때에는, 채무자는 그 통지를 받은 때까지 양도인에 대하여 생긴 사유로써 양수인에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>대항사유</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>민법 제451조 제2항의 명문 규정이다(이의 보류 없는 승낙이 아닌 단순 통지의 경우).</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>민법 제451조②</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>제451조</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>632</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>채무자의 법률행위가 통정허위표시인 경우에도 채권자취소권의 대상이 되고, 채권자취소권의 대상이 된 법률행위가 통정허위표시의 요건을 갖춘 경우에는 무효이다.</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>경합</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>판례는 통정허위표시도 채권자취소권의 대상이 되고 동시에 무효라고 한다(무효와 사해행위취소의 경합).</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>대판 1998.2.27. 97다50985</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>633</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>채권자취소권을 행사하려면 수익자나 전득자를 상대로 소를 제기하여야 하고, 채무자를 상대로 취소소송을 제기할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>피고적격</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>판례는 사해행위취소의 소의 피고는 수익자 또는 전득자이고 채무자는 피고적격이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>대판 2004.8.30. 2004다21923</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>634</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>사해행위 후 그 목적물에 제3자가 저당권을 취득한 경우, 채권자는 원상회복 방법으로 가액배상 대신 수익자를 상대로 채무자 앞으로 직접 소유권이전등기절차를 이행할 것을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>원상회복방법</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>판례는 채권자가 가액배상 대신 수익자 명의 등기 말소 또는 채무자 앞으로의 직접 이전등기를 구하는 원물반환도 선택할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>대판 2001.2.9. 2000다57139</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>635</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>사해행위가 취소되어 원물반환이 아닌 가액배상을 명하는 경우, 그 부동산의 가액은 특별한 사정이 없는 한 사해행위취소소송의 사실심 변론종결 당시를 기준으로 산정한다.</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>가액기준시</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>판례는 가액배상액의 산정 기준시를 사실심 변론종결 시로 본다.</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>대판 2010.2.25. 2007다28819</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>636</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>국가의 사무라도 사인이 국가를 대신하여 처리할 수 있는 성질의 것으로서 사무 처리의 긴급성 등 사인의 개입이 정당화되는 경우에는 사무관리가 성립할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>국가사무</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>판례는 원칙적으로 사인이 법령 근거 없이 국가사무를 수행할 수 없지만 개입이 정당화되는 경우 사무관리 성립을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>대판 2014.12.11. 2012다15602</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>제734조</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>637</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>제3자와의 약정에 따라 타인의 사무를 처리한 경우에는, 의무 없이 타인의 사무를 처리한 것이 아니므로 원칙적으로 그 타인과의 관계에서 사무관리가 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>의무없이</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>판례는 제3자와의 약정에 따른 사무 처리는 '의무 없이'라는 사무관리 요건을 결하므로 사무관리가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>대판 2013.9.26. 2012다43539</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>제734조</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>638</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>채권자가 자신의 채권을 보전하기 위하여 채무자가 다른 상속인과 공동으로 상속받은 부동산에 관하여 공동상속등기를 대위신청하여 등기가 된 경우, 다른 상속인에 대하여도 사무관리에 기한 비용상환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>사무관리</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>판례는 공동상속등기 대위신청이 다른 상속인의 사무도 함께 처리한 것이므로 그에 대하여 사무관리에 기한 비용상환청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>대판 2013.8.22. 2013다30882</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>제734조</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>639</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>보증계약 체결 후 채권자가 보증인의 승낙 없이 주채무자에 대하여 변제기를 연장하여 준 경우, 그 효력은 원칙적으로 보증채무에도 미친다.</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>판례는 변제기 연장이 반드시 보증인의 책임을 가중하는 것이 아니므로 원칙적으로 보증채무에도 효력이 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>대판 1996.2.23. 95다49141</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>제428조</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>640</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>주채무자가 면책행위를 하고도 수탁보증인에게 통지하지 아니한 동안에 보증인도 사전통지 없이 이중의 면책행위를 한 경우, 먼저 이루어진 주채무자의 면책행위가 유효하고 보증인은 주채무자에게 구상권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>이중면책</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>판례는 제446조가 제445조 제1항의 사전통지를 한 보증인을 보호하는 규정이므로, 사전통지 없이 이중 면책행위를 한 보증인은 면책의 유효를 주장할 수 없어 구상권을 행사할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>대판 1997.10.10. 95다46265</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>제446조</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>641</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>연대보증인은 최고·검색의 항변권을 가지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>항변권</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>민법 제437조 단서는 보증인이 주채무자와 연대하여 채무를 부담한 때에는 최고·검색의 항변권이 없다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>민법 제437조 단서</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>제437조</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>642</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>주채무자가 시효의 이익을 포기하면 그 효력은 보증인에게도 미쳐 보증인도 주채무의 시효소멸을 원용할 수 없게 된다.</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>포기효력</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>판례는 주채무자의 시효이익 포기가 보증인에게는 효력이 없으므로 보증인은 여전히 주채무의 시효소멸을 원용할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>대판 1991.1.29. 89다카1114 · 민법 제433조</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>제433조</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>643</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>임대인이 임차인과의 임대차계약상 약정에 따라 제3자에게 도급을 주어 임대차목적 시설물을 수선한 경우, 그 수급인은 임대인에 대하여 종속적인지 여부를 불문하고 이행보조자로서의 피용자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>이행보조자</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>판례는 임대인의 수선의무 이행을 위한 수급인이 종속 여부와 무관하게 이행보조자가 되므로, 그 과실로 인한 화재에 임대인이 채무불이행 책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>대판 2002.7.12. 2001다44338</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>제391조</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>644</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>채무자가 타인을 사용하여 채무를 이행하는 경우, 그 피용자의 고의나 과실은 채무자의 고의나 과실로 본다.</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>이행보조자</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>민법 제391조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>민법 제391조</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>제391조</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>645</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>수 개의 권리를 일괄하여 매매의 목적으로 정하였으나 그 중 일부의 권리를 이전할 수 없는 경우, 선의의 매도인은 민법 제571조 제1항에 의하여 계약의 일부를 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>판례는 제571조 제1항은 권리 전부를 이전할 수 없는 경우에 적용되고 권리 일부(일괄매매 중 일부 포함)에는 적용되지 않으며, 이 경우 제572조의 담보책임이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>대판 2004.12.9. 2002다33557</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>제572조</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>646</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>하자담보책임으로 확대손해의 배상책임을 지우기 위해서는, 하자 없는 목적물을 인도하지 못한 의무위반 외에 그 의무위반에 대하여 매도인에게 귀책사유가 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>확대손해</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>판례는 하자로 인한 확대손해 배상에는 매도인의 귀책사유가 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>대판 1997.5.7. 96다39455</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>제580조</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>647</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>매매목적물의 하자로 인한 매수인의 완전물급부청구권 행사는 공평의 원칙에 의하여 제한될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>권리제한</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>판례는 하자가 경미하여 수선이 가능한데도 완전물급부를 요구하는 것이 공평에 반하는 경우 완전물급부청구권의 행사를 제한할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>대판 2014.5.16. 2012다72582</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>제581조</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>648</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>타인의 권리를 매매하였으나 이행불능이 된 경우, 선의의 매수인이 받을 손해배상의 범위에는 매수인이 그 권리를 취득하였더라면 얻을 수 있었던 이익의 상실(이행이익)도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>배상범위</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>판례는 타인 권리 매매의 이행불능 시 선의 매수인의 손해배상 범위에 이행이익 상당의 일실이익이 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>대판 1967.5.18. 66다2618 전합</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>제570조</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>649</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>제3자를 위한 계약이 무효·취소·해제된 경우, 수익자는 제107조 내지 제110조, 제548조에 규정된 보호되는 제3자에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>판례는 수익자가 계약으로부터 직접 발생한 효과를 향유하는 자일 뿐 무효 등의 법률관계를 기초로 새로운 이해관계를 맺은 자가 아니므로 보호되는 제3자가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>대판 1997.12.26. 96다44860</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>650</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>제3자를 위한 유상·쌍무계약에서 요약자는 낙약자의 채무불이행을 이유로 제3자(수익자)의 동의 없이 계약을 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>해제권</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>판례는 요약자가 수익자의 동의 없이 낙약자의 채무불이행을 이유로 계약을 해제할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>대판 1970.2.24. 69다1410</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>제541조</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>651</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>제3자를 위한 계약의 기본관계를 이루는 계약이 해제된 경우, 낙약자는 원상회복 또는 부당이득반환을 수익자가 아니라 계약당사자인 요약자를 상대로 구하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>청산관계</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>판례는 제3자를 위한 계약의 청산이 계약당사자(낙약자·요약자) 사이에서 이루어져야 하므로 수익자를 상대로 반환을 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>대판 2005.7.22. 2005다7566</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>652</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>단독친권자로 정하여진 부모의 일방이 사망한 경우, 생존하는 다른 일방이 자동적으로 친권자가 된다.</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>친권회복</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>민법 제909조의2 제1항은 단독친권자 사망 시 생존하는 부 또는 모, 친족 등의 청구로 가정법원이 친권자를 지정하도록 하므로 생존 부모가 자동으로 친권자가 되는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>민법 제909조의2</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>제909조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>653</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>법정대리인인 친권자는 정당한 사유가 있는 때에는 법원의 허가를 얻어 그 법률행위의 대리권과 재산관리권을 사퇴할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>사퇴요건</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>민법 제927조 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>민법 제927조</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>제927조</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>654</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>공동상속인인 친권자가 미성년 자녀를 법정대리인으로서 대리하여 상속재산 분할협의를 한 경우, 특별대리인 선임 없이 이루어졌다면 피대리자의 추인이 없는 한 그 전체가 무효이다.</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>판례는 상속재산 분할협의가 이해상반행위이고 제921조가 강행규정이므로 특별대리인 없이 한 협의는 추인 없으면 전체가 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>대판 2016.2.18. 2015다51920</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>655</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인이 피해자의 부주의를 이용하여 고의의 불법행위를 한 경우, 그러한 사유가 없는 다른 불법행위자도 피해자의 과실을 들어 과실상계를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>과실상계</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>판례는 고의의 불법행위자 본인은 과실상계를 주장할 수 없지만, 그러한 사유가 없는 다른 불법행위자는 과실상계를 주장할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>대판 2007.6.14. 2005다32999</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>656</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>피해자가 공동불법행위자 중 일부만을 상대로 손해배상을 청구하는 경우에도, 과실상계에서 참작할 쌍방의 과실은 공동불법행위자 전원에 대한 과실을 전체적으로 평가하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>과실상계방법</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위의 일체성상 피해자 과실을 공동불법행위자 전원에 대한 과실로 전체적으로 평가한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>대판 1991.5.10. 90다14423</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>657</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>피해자가 공동불법행위자별로 별개의 소를 제기하는 경우, 각 소송에서 과실상계비율과 손해액을 서로 달리 인정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>별소산정</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>판례는 별소 진행 시 제출 증거가 달라 사고 경위·손해액이 달리 인정될 수 있으므로 과실상계비율·손해액을 달리 인정할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>대판 2001.2.9. 2000다60227</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>658</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>부동산의 공동매수인들이 전매차익을 얻으려는 공동의 목적 달성을 위하여 협력하였으나 공동사업을 경영할 목적이 있었다고 인정되지 않는 경우, 그 법률관계는 조합이 아니라 공유관계에 불과하다.</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>귀속형태</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>판례는 공동사업 경영 목적이 인정되지 않으면 공동매수인 간 법률관계가 공유에 불과하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>대판 2012.8.30. 2010다39918</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>제262조</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>659</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>1동 건물 중 각 일부분의 위치·면적이 특정되지 않거나 구조상·이용상 독립성이 인정되지 않는 경우에는, 공유자들 사이에 구분소유의 약정이 있더라도 일반적인 공유관계만 성립한다.</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>구분소유</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>판례는 구분소유의 객체가 될 독립성 요건을 갖추지 못하면 구분소유 약정이 있어도 일반 공유관계만 성립한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>대판 2014.2.27. 2011다42430</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>제215조</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>660</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>계약의 일방 당사자가 상대방의 지시로 급부과정을 단축하여 제3자에게 직접 급부한 경우(단축급부), 그 계약이 무효·해제되더라도 일방 당사자는 제3자를 상대로 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>삼각관계</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>판례는 단축급부 시 급부가 계약당사자 간에 이루어진 것이므로 제3자에 대한 직접 부당이득반환청구를 부정한다.</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>대판 2003.12.26. 2001다46730</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>661</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>계약해제 시 반환할 금전에 가산할 이자에 관하여 당사자 사이에 약정이 있는 경우, 이행지체로 인한 지연손해금도 그 약정이율에 의하지만, 약정이율이 법정이율보다 낮은 경우에는 법정이율에 의한 지연손해금을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>이율적용</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>판례는 약정이율이 있으면 지연손해금도 약정이율에 의하되, 약정이율이 법정이율보다 낮으면 법정이율에 의한 지연손해금을 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>대판 2013.4.26. 2011다50509</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>662</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>대리인에 의해 체결된 계약이 채무불이행을 이유로 상대방에 의하여 유효하게 해제된 경우, 원상회복의무를 부담하는 자는 대리인이 아니라 본인이다.</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>의무주체</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>판례는 대리행위의 효과가 본인에게 귀속되므로 계약해제에 따른 원상회복의무도 본인이 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>대판 2011.8.18. 2011다30871</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>663</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>매매계약 해제로 매수인이 반환할 목적물의 사용이익을 산정할 때에는, 매수인이 투입한 현금자본의 기여분 및 운용이익을 공제하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>이익산정</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>판례는 사용이익 반환 시 매수인이 투입한 자본의 기여분·운용이익을 공제한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>대판 1995.4.28. 94다16083</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>664</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>등기의 공신력이 인정되지 않으므로, 무효인 등기를 신뢰하여 소유권이전등기를 마친 자도 그 부동산의 소유권을 취득하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>공신력</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>판례는 현행 등기제도상 공신력이 없으므로 실체상 권리관계에 부합하지 않는 등기를 신뢰해도 소유권을 취득할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>대판 1969.6.10. 68다199</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>665</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>건축자재 등의 동산이 건물에 부착·합체되어 독립한 경제적 효용을 갖지 못하고 별개의 소유권 객체가 될 수 없는 정도에 이른 때에는, 타인의 권원에 의하여 부합되었더라도 그 동산의 소유권은 부동산 소유자가 취득한다.</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>부합</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>판례는 분리 불가능하거나 독립 효용이 없는 정도로 부합된 동산의 소유권은 부동산 소유자에게 귀속한다고 한다(제256조 본문).</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>대판 2012.11.29. 2010다8624</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>제256조</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>666</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>임대인의 동의 없는 전대차에서 임차인과 전차인 사이의 전대차계약은 유효하지만 임대인에게 대항할 수 없으므로, 임대인은 임대차계약을 해지할 수 있고 전차인에 대하여 소유권에 기한 물권적 청구권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>무단전대</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>판례는 무단전대차계약은 당사자 사이에서는 유효하나 임대인에게 대항할 수 없어 임대인이 해지 및 전차인에 대한 물권적 청구권 행사를 할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>민법 제629조 · 판례</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>제629조</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>667</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>저당권으로 담보한 채권을 질권의 목적으로 한 때에는, 그 저당권등기에 질권의 부기등기를 하여야 그 효력이 저당권에 미친다.</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>부기등기</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>민법 제348조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>민법 제348조</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>제348조</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>668</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>질권의 목적인 채권을 양도하는 행위는 질권자의 이익을 해하는 변경에 해당하므로 질권자의 동의를 요한다.</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>양도요건</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>판례는 입질채권의 양도가 제352조의 질권자 이익을 해하는 변경에 해당하지 않으므로 질권자의 동의를 요하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>대판 2005.12.22. 2003다55059</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>제352조</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>669</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>질권자는 그 권리의 범위 내에서 자기의 책임으로 질물을 전질할 수 있으며, 이 경우 전질을 하지 않았으면 면할 수 있는 불가항력으로 인한 손해에 대하여도 책임을 부담한다.</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>책임전질</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>민법 제336조의 명문 규정으로, 책임전질은 책임이 가중된다.</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>민법 제336조</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>제336조</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>670</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>임대차계약서와 같이 계약당사자 쌍방의 권리의무관계의 내용을 정한 서면은, 채권질권 설정 시 교부를 요하는 민법 제347조의 '채권증서'에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>채권증서</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>판례는 제347조의 채권증서는 변제 시 반환을 청구할 수 있는 채권 존재 증명 문서여야 하므로, 권리의무관계를 정한 임대차계약서는 채권증서에 해당하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>대판 2013.8.22. 2013다32574</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>제347조</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>671</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제3항의 '제3자'는 명의신탁 약정의 당사자 및 포괄승계인 이외의 자로서 명의수탁자가 물권자임을 기초로 그와 직접 새로운 이해관계를 맺은 사람을 말하므로, 명의수탁자로부터 저당권을 설정받은 자는 명의신탁의 무효로 대항받지 않아 그 저당권은 유효하다.</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 제4조 제3항의 제3자에 수탁자와 직접 새 이해관계를 맺은 저당권자가 포함되어 보호된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>대판 2005.11.10. 2005다34667</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>672</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>3자간 등기명의신탁에서 신탁부동산이 수용·협의취득으로 제3취득자 명의로 이전등기가 마쳐진 경우, 명의수탁자가 받은 보상금은 명의신탁자에 대한 부당이득반환의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>부당이득</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>판례는 3자간 명의신탁에서 매도인의 신탁자에 대한 이전등기의무가 이행불능이 되고 수탁자가 보상금을 취득하므로 그 보상금을 신탁자에게 부당이득으로 반환해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>대판 2011.9.8. 2009다49193</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>673</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>계약명의신탁(매도인 선의)에서 명의수탁자가 명의신탁자에게 반환하여야 할 부당이득의 범위에는 매수자금뿐 아니라 취득세·등록세 등 소유권이전등기를 위하여 지출한 비용도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>반환범위</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>판례는 선의 매도인 계약명의신탁에서 수탁자의 부당이득 반환범위에 매수자금 및 취득 관련 비용이 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>대판 2010.10.14. 2007다90432</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>674</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>계약명의신탁(매도인 선의)에서 명의수탁자가 부동산의 완전한 소유권을 취득하므로, 명의수탁자가 채무초과 상태에서 그 부동산을 처분하는 행위는 일반채권자에 대한 사해행위가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>판례는 수탁자가 완전한 소유권을 취득하여 그의 책임재산을 구성하므로 채무초과 상태의 처분이 사해행위가 될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>대판 2008.9.25. 2007다74874</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>675</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>부동산에 가압류등기가 먼저 되고 근저당권설정등기가 마쳐진 후 강제경매가 진행된 경우, 근저당권자는 선순위 가압류채권자에 대하여 1차로 채권액에 따라 안분 평등배당을 받은 다음, 후순위 경매신청압류채권자가 받을 배당액에서 자기 채권액을 만족할 때까지 흡수배당받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>흡수배당</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>판례는 선행 가압류에 대해서는 안분배당, 후순위 압류채권자에 대해서는 우선변제권에 따른 흡수배당을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>대결 1994.11.29. 94마417</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>제356조</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>676</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>대항요건과 확정일자를 갖춘 주택임차인들 상호간에는, 대항요건과 확정일자를 최종적으로 갖춘 순서대로 우선변제받을 순위가 정해진다.</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>판례는 주임법 제3조의2 제2항에 따라 대항요건과 확정일자를 최종적으로 갖춘 시점 순서로 우선변제 순위가 정해진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>대판 1997.12.12. 97다22393</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>677</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성된 경우, 시효취득자는 원인무효의 소유권이전등기에 대한 말소청구소송에서 그 등기가 실체관계에 부합하는 등기가 되었다는 항변을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>실체부합</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>판례는 점유취득시효 완성으로 원인무효 등기가 실체관계에 부합하게 되었다는 항변을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>민법 제245조① · 판례</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>678</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>등기명의인을 달리하여 소유권보존등기가 이중으로 경료된 경우, 먼저 이루어진 보존등기가 원인무효가 아니어서 뒤의 보존등기가 무효로 되는 때에는, 그 뒤의 보존등기나 이에 터잡은 이전등기를 근거로 등기부취득시효의 완성을 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>중복등기</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>판례(전합)는 1부동산1용지주의상 무효인 후행 보존등기에 기초한 등기부취득시효를 인정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>대판 1996.10.17. 96다12511 전합</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>679</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>부동산 등기는 현실의 권리관계에 부합하는 한 그 권리취득의 경위나 방법이 사실과 다르더라도 효력에 영향이 없으므로, 증여로 취득하였으나 등기원인을 매매로 기재한 등기도 유효하다.</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>실체부합</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>판례는 실체관계에 부합하는 등기는 원인의 경위·방법이 달라도 유효하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>대판 1980.7.22. 80다791</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>680</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>공동상속인 중 1인이 자신의 법정상속분 상당의 상속채무 분담액을 초과하여 유류분권리자의 상속채무 분담액까지 변제한 경우, 그 사정은 유류분권리자의 유류분 부족액 산정 시 고려하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>부족액산정</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>판례는 초과 변제한 공동상속인이 별도로 구상권을 행사하거나 상계할 수 있을 뿐, 그 사정을 유류분권리자의 유류분 부족액 산정에 고려할 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>대판 2013.3.14. 2010다42624</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>제1115조</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>681</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>유류분반환청구권의 행사는 재판상 또는 재판 외에서 상대방에 대한 의사표시로 할 수 있고, 침해를 받은 유증 또는 증여행위를 지정하여 반환청구의 의사를 표시하면 족하며, 제1117조의 소멸시효 진행도 그 의사표시로 중단된다.</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>행사방법</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>판례는 유류분반환청구권의 행사에 목적물의 구체적 특정을 요하지 않으며 그 의사표시로 소멸시효가 중단된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>대판 2002.4.26. 2000다8878</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>제1117조</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>682</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>유류분 산정에서 기여분은 상속재산분할의 전제문제일 뿐 유류분과 무관하므로, 유류분 산정 시 기여분을 공제하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>기여분</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>판례는 기여분이 유류분 산정의 기초가 되지 않으며 유류분 반환청구의 대상도 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>대판 2015.10.29. 2013다60753</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>제1118조</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>683</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>유류분 산정 시 산입할 증여가 금전인 경우, 그 증여 금액을 상속개시 당시의 화폐가치로 환산하여 가산하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>화폐환산</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>판례는 금전 증여의 경우 증여 당시 액수가 아니라 상속개시 당시의 화폐가치로 환산하여 산입한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>대판 2009.7.23. 2006다28126</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>제1113조</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>684</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>경매개시결정 기입등기로 압류의 효력이 발생한 후에 점유를 이전받아 유치권을 취득한 경우, 그 유치권으로 경매절차의 매수인에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>대항시점</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>판례는 압류 후 점유 이전으로 취득한 유치권은 처분금지효에 저촉되어 매수인에게 대항할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>대판 2005.8.19. 2005다22688</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>685</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>경매개시결정 기입등기 전에 점유를 이전받았더라도 그 기입등기 이후에 공사대금채권을 취득하여 유치권이 성립한 경우, 그 유치권으로 매수인에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>성립시점</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>판례는 유치권은 피담보채권의 변제기 도래로 성립하므로, 압류 후에 채권을 취득하여 성립한 유치권은 매수인에게 대항할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>대판 2011.10.13. 2011다55214</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>686</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>경매개시결정등기 전에 민사유치권을 취득한 경우에는, 그보다 앞서 저당권설정등기나 가압류등기 또는 체납처분압류등기가 되어 있더라도 그 유치권으로 경매절차의 매수인에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>대항가부</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>판례는 압류(경매개시결정등기) 전에 성립한 민사유치권은 선행 저당권·가압류·체납처분압류가 있어도 매수인에게 대항할 수 있다고 한다(상사유치권과 구별).</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>대판 2014.3.20. 2009다60336 전합</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>687</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>대리행위의 하자 유무는 원칙적으로 대리인을 표준으로 판단하지만, 대리인이 본인의 지시에 좇아 그 행위를 한 경우에는 본인이 안 사정이나 과실로 알지 못한 사정에 관하여 대리인의 부지를 주장하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>판단기준</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>민법 제116조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>민법 제116조</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>제116조</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>688</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>계약 체결의 대리권을 가진 대리인은 특별한 사정이 없는 한 그 계약을 해제할 권한도 가진다.</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>판례는 계약 체결의 대리권이 있다고 하여 곧바로 계약 해제 등의 처분권한까지 가지는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>대판 1987.4.28. 85다카971</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>제114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>689</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>사채알선업자가 대주와 차주 쌍방을 대리하여 소비대차계약과 담보권설정계약을 체결한 경우, 특별한 사정이 없는 한 그 소비대차계약에서 정한 바에 따라 차주로부터 변제를 수령할 권한도 가진다.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>수령권한</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>판례는 쌍방대리한 사채알선업자가 차주로부터 변제를 수령할 권한도 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>대판 1997.7.8. 97다12273</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>제114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>690</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>실질적으로 부부공동생활이 파탄되어 회복할 수 없을 정도의 상태에 이른 경우, 제3자가 부부의 일방과 성적인 행위를 하더라도 불법행위가 성립한다고 보기 어렵다.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>파탄예외</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>판례(전합)는 혼인이 실질적으로 파탄된 후의 제3자의 성적 행위는 배우자에 대한 불법행위가 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>대판 2014.11.20. 2011므2997 전합</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>제840조</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>691</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>민법 제841조의 부정행위로 인한 이혼청구권의 제척기간은 부권침해를 원인으로 한 위자료 청구에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>판례는 제841조의 제척기간은 이혼청구권 소멸에 관한 규정이므로 위자료 청구에는 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>대판 1985.6.25. 83므18</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>제841조</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>692</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>성년후견인은 재판상 이혼사유가 있고 피성년후견인의 이혼의사가 객관적으로 추정되는 경우, 의사무능력자인 피성년후견인을 대리하여 이혼을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>대리이혼</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>판례는 재판상 이혼사유가 있고 이혼의사가 객관적으로 추정되는 경우 성년후견인의 대리 이혼청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>대판 2010.4.29. 2009므639</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>제840조</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>693</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>소멸시효 이익의 포기 당시에는 이해관계를 맺은 적이 없다가 나중에 시효이익을 이미 포기한 자와의 법률관계를 통하여 비로소 시효이익을 원용할 이해관계를 형성한 자는, 이미 이루어진 시효이익 포기의 효력을 부정할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>판례는 시효이익 포기의 상대효를 인정하면서도, 포기 후에 이해관계를 맺은 자는 포기의 효력을 부정할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>대판 2015.6.11. 2015다200227</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>제184조</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>694</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>소멸시효 완성 후 채무를 승인한 경우, 시효이익 포기의 의사가 추가적으로 인정되어야 시효이익을 포기한 것이 된다.</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>승인과포기</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>판례는 시효완성 후 채무승인이 곧바로 시효이익 포기가 되는 것은 아니고 포기 의사가 인정되어야 한다고 본다.</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>대판 2013.2.28. 2011다21556</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>제184조</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>695</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>가등기에 기한 본등기 청구의 상대방은 가등기 당시의 소유자인 가등기의무자이고, 가등기 후 소유권을 취득한 현재의 등기명의인이 아니다.</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>청구상대방</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>판례는 본등기청구의 상대방을 가등기의무자인 전 소유자로 보고, 가등기 후의 제3자 본등기는 직권말소될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>대결 1962.12.24. 4294민재항675 전합</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>696</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>법률행위의 해석은 당사자의 내심의 의사를 고려하여 그 표시행위에 부여한 의미를 확정하는 것이다.</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>해석대상</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>판례는 법률행위 해석이 당사자의 내심의 의사와 관계없이 표시행위에 부여한 객관적 의미를 합리적으로 확정하는 것이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>대판 1996.10.25. 96다16049</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>제105조</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>697</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>쌍방의 동기의 착오가 있는 경우, 당사자가 그러한 착오가 없었을 때에 약정하였을 것으로 보이는 내용으로 보충적 해석을 하여야 하며, 그 보충되는 당사자의 의사는 당사자의 실제 의사가 아니라 객관적으로 추인되는 정당한 이익조정 의사이다.</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>보충적해석</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>판례는 공통의 동기 착오 시 보충적 해석을 하되 그 기준을 객관적으로 추인되는 정당한 이익조정 의사로 본다.</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>대판 2006.11.23. 2005다13288</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>698</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>비법인사단은 구성원이 없게 되더라도 곧바로 권리능력이 소멸하는 것이 아니라 청산사무가 완료되어야 비로소 당사자능력이 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>소멸시기</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>판례는 비법인사단도 사원이 없게 됨은 해산사유일 뿐이고 청산사무 완료 시 당사자능력이 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>대판 1992.10.9. 92다23087</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>699</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>미성년자의 법률행위를 법정대리인이 추인한 후에는, 미성년자 본인이 다시 이를 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>추인효과</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>민법 제143조 제1항은 추인 후에는 취소하지 못한다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>민법 제143조</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>제143조</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>6001</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>강박에 의한 의사표시임을 이유로 일단 유효하게 취소되어 무효로 된 법률행위는, 그 취소사유인 강박 상태에서 벗어난 후에 무효행위의 추인 요건을 갖추어 추인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>무효행위추인</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>판례는 취소로 무효가 된 법률행위는 무효 원인(취소사유)이 소멸한 후, 즉 강박 상태에서 벗어난 후에 무효행위의 추인으로 추인할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>대판 1997.12.12. 95다38240</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>제139조</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>6002</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>채권자와 채무인수인 사이의 중첩적 채무인수 합의는 채무자의 의사에 반하여도 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>동의요부</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>판례는 제3자의 중첩적 채무인수가 원채무자의 의사에 반하여도 무효가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>대판 1962.4.4. 4294민상1087</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>제453조</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>6003</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>이행인수에서 채무자는 인수인이 채무를 이행하지 않는 경우 인수인에 대하여 채권자에게 이행할 것을 요구할 권리를 가지지만, 채권자는 직접 인수인에게 이행을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>이행인수</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>판례는 이행인수에서 인수인이 채권자에게 직접 의무를 부담하지 않으므로 채권자는 직접 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>대판 2012.7.16. 2009마461</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>6004</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>한정승인이 있는 경우 상속채무 자체가 상속재산의 한도로 감축되는 것이 아니라 책임만 한정되므로, 법원은 상속채무 전부에 대한 이행판결을 선고하되 주문에서 상속재산의 한도에서 집행할 수 있음을 명시하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>채무와책임</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>판례는 한정승인이 채무가 아니라 책임을 한정하므로 채무 전부에 대한 이행판결을 하되 상속재산 한도 집행을 주문에 명시한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>대판 2003.11.14. 2003다30968</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>제1028조</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>6005</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>한정승인을 한 상속인이 있는 경우에도 상속재산분할청구를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>분할가부</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>판례는 한정승인 절차가 상속재산분할에 선행해야 한다는 규정이 없으므로 한정승인이 있어도 분할청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>대판 2014.7.25. 2011스226</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>6006</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>변시6</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>채무 일부에 대한 변제공탁은 그 부분에 대해서도 변제의 효력이 생기지 않으나, 채권자가 일부에 충당한다는 유보의 의사표시를 하고 수령한 때에는 채권의 일부 변제에 충당된다.</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>일부공탁</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>판례는 채무 일부 공탁은 무효이나 채권자가 유보 의사표시를 하고 수령하면 일부 변제에 충당된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>대판 2009.10.29. 2008다51359</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>제487조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H971"/>
+  <dimension ref="A1:H1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -39304,6 +39304,3886 @@
         </is>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>501</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>물상보증인이 피담보채무의 부존재나 소멸을 이유로 제기한 저당권설정등기 말소소송에서 채권자가 청구기각을 구하며 피담보채권의 존재를 주장한 경우, 이는 채무자에 대한 재판상 청구로서 시효중단 사유가 된다.</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>응소중단</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인이 제기한 소송에서 채권자의 응소는 채무자에 대한 직접 재판상 청구로 볼 수 없어 제168조 제1호의 청구에 해당하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>대판 2004.1.16. 2003다30890</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>502</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>부동산 매매대금 채권이 소유권이전등기청구권과 동시이행관계에 있더라도, 매매대금청구권은 그 지급기일 이후 소멸시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>판례는 동시이행항변권은 이행거절권능에 불과하므로 매매대금청구권의 시효 진행을 막지 못한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>대판 1991.3.22. 90다9797</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>503</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>부동산 매수인이 목적물을 인도받아 사용·수익하다가 보다 적극적인 권리행사의 일환으로 이를 처분하고 점유를 승계하여 준 경우에도, 그 소유권이전등기청구권의 소멸시효는 진행하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>시효진행</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>판례(전합)는 처분·점유 승계도 적극적 권리행사이므로 스스로 사용·수익하는 경우와 다를 바 없어 시효가 진행하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>대판 1999.3.18. 98다32175 전합</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>504</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>소유권이전등기청구권 보전을 위한 가등기가 경료된 부동산을 양수하여 소유권이전등기를 마친 제3자는, 시효의 이익을 받는 자로서 독자적으로 소멸시효를 원용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>원용권자</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>판례는 가등기 부동산의 양수인을 시효이익을 받는 자로 보아 독자적 시효원용권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>대판 1995.7.11. 95다12446</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>505</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>토지거래허가구역 내 토지의 매매계약 체결 후 계약금만 수수한 상태에서 토지거래허가를 받은 경우, 그 허가만으로는 이행의 착수가 있다고 볼 수 없어 매도인은 민법 제565조에 의하여 계약금의 배액을 상환하고 계약을 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>이행착수</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>판례는 허가신청 협력의무 이행과 허가만으로는 매매계약상 의무 이행에 착수한 것이 아니므로 해약금 해제가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>대판 2009.4.23. 2008다62427</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>제565조</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>506</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>유동적 무효 상태인 토지거래허가구역 내 토지 매매계약에서 계약의 쌍방 당사자는 공동허가신청절차에 협력할 의무가 있고, 협력하지 않는 당사자에 대하여 상대방은 그 협력의무의 이행을 소구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>협력의무</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>판례는 유동적 무효 상태에서도 허가신청 협력의무가 있고 그 이행을 소구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>대판 2009.4.23. 2008다62427</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>제105조</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>507</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>토지거래허가를 받지 않아 유동적 무효인 매매계약에서도, 일방 당사자는 상대방의 채무불이행을 이유로 계약을 해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>해제가부</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>판례는 유동적 무효 상태에서는 계약의 효력이 아직 발생하지 않으므로 채무불이행을 이유로 한 해제를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>대판 1997.7.25. 97다4357</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>제105조</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>508</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>대리인이 본인을 위한 것임을 표시하지 아니한 때에는 그 의사표시는 자기를 위한 것으로 보지만, 상대방이 대리인으로서 한 것임을 알았거나 알 수 있었을 때에는 본인에게 효과가 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>현명주의</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>민법 제115조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>민법 제115조</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>제115조</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>509</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>계약이 적법한 대리인에 의하여 체결된 경우, 대리인은 특별한 사정이 없는 한 본인을 위하여 계약상 급부를 변제로서 수령할 권한도 가지며, 수령한 급부의 법률효과는 직접 본인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>판례는 계약 체결 대리권에 급부 수령권한이 포함되고 그 효과가 본인에게 귀속되므로, 계약해제 시 원상회복의무도 본인이 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>대판 2011.8.18. 2011다30871</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>제114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>510</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>진의 아닌 의사표시가 대리인에 의하여 이루어지고 그 대리인의 진의가 자기 또는 제3자의 이익을 위한 배임적인 것임을 상대방이 알았거나 알 수 있었던 경우, 제107조 제1항 단서의 유추해석상 본인은 그 대리행위에 대하여 책임을 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>대리권남용</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>판례는 배임적 대리행위에서 상대방이 악의·과실인 경우 본인에게 효과가 귀속되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>대판 1987.7.7. 86다카1004</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>제107조</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>511</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>대표자가 있는 비법인사단은 소송법상 당사자능력과 부동산등기법상 등기능력을 가진다.</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>능력</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>민사소송법 제52조와 부동산등기법 제26조가 비법인사단의 당사자능력·등기능력을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>민사소송법 제52조·부동산등기법 제26조</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>512</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>법인 아닌 사단의 구성원들이 집단적으로 탈퇴하여 사단이 2개로 분열되고 분열되기 전 사단의 재산이 분열된 각 사단의 구성원들에게 각각 총유적으로 귀속되는 형태의 분열은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>분열</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>판례(전합)는 사단법인·비법인사단의 분열을 인정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>대판 2006.4.20. 2004다37775 전합</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>제275조</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>513</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>총유물의 처분에는 정관 기타 계약에 의하는 외에 사원총회의 결의가 필요하며, 이를 위반한 처분행위는 무효이고 표현대리 규정도 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>처분절차</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>판례는 총유물 처분에 총회결의를 요하고 위반 시 절대적 무효이며 표현대리 규정이 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>대판 2009.2.12. 2006다23312</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>514</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>비법인사단이 타인 간의 금전채무를 보증하는 행위는 총유물의 관리·처분행위에 해당하여 사원총회의 결의를 거쳐야 한다.</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>판례(전합)는 비법인사단의 금전채무 보증은 총유물 자체의 관리·처분이 따르지 않는 단순한 채무부담행위이므로 총유물의 관리·처분행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>대판 2007.4.19. 2004다60072 전합</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>515</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>가등기담보법은 재산권 이전을 예약할 당시 그 재산의 가액이 차용액 및 이에 붙인 이자의 합산액을 초과하는 경우에만 적용된다.</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>가등기담보법 제1조는 예약 당시 목적물 가액이 차용액 및 이자 합산액을 초과하는 경우에 적용된다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>가등기담보법 제1조</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>516</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>가등기담보법 규정을 위반하여 담보가등기에 기한 본등기가 이루어진 경우, 그 본등기는 약한 의미의 양도담보로서 담보 목적 범위 내에서는 유효하다.</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>본등기효력</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>판례는 가담법 제3조·제4조를 위반한 본등기는 무효이고 약한 의미의 양도담보로도 효력이 없으며, 청산절차를 거쳐야 사후에 유효가 될 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>대판 2002.6.11. 99다41657</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>517</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>가등기담보권자가 청산절차 없이 본등기를 한 후 부동산을 제3자에게 처분한 경우, 그 제3자가 선의이면 소유권을 취득하고 담보설정자는 담보권자에게 불법행위로 인한 손해배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>제3자보호</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>판례는 채무자등의 말소청구권(가담법 제11조 단서)에 따라 선의의 제3자가 소유권을 취득하면 설정자는 담보권자에게 손해배상을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>가등기담보법 제11조 · 판례</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>518</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>미성년자가 단순히 자기가 능력자라고 사언한 것만으로는 민법 제17조의 '속임수(사술)'를 쓴 것에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>속임수</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>판례는 제17조의 속임수란 적극적으로 사기수단을 쓴 것을 의미하고 단순히 성년자라고 칭한 것만으로는 속임수가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>대판 1971.12.14. 71다2045</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>제17조</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>519</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>미성년자가 법정대리인으로부터 허락을 얻은 특정한 영업에 관하여는 성년자와 동일한 행위능력이 있으며, 법정대리인은 그 허락을 취소 또는 제한할 수 있으나 이로써 선의의 제3자에게 대항하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>영업허락</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>민법 제8조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>민법 제8조</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>제8조</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>520</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>친권자인 모가 자기 오빠의 제3자에 대한 채무의 담보로 미성년 자녀 소유의 부동산에 근저당권을 설정한 행위는, 자녀에게 불이익만을 주더라도 민법 제921조의 이해상반행위에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>판례는 형식적 판단설에 따라 제3자(오빠)의 채무 담보를 위한 것은 친권자와 자녀 사이의 이해상반행위가 아니라고 한다(다만 친권남용이 될 수는 있음).</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>대판 1991.11.26. 91다32466</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>521</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>친권자가 자신이 금전을 차용하면서 그 담보로 미성년 자녀를 대리하여 자녀 소유의 부동산에 저당권을 설정한 행위는 이해상반행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>판례는 친권자 자신의 채무 담보를 위해 자녀 부동산에 저당권을 설정하는 것은 친권자와 자녀 사이에 이해 대립이 있는 이해상반행위라고 한다.</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>판례(친권자 자기채무 담보)</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>522</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>친권에 따르는 수인의 자녀 사이에 이해가 상반되는 경우, 친권자는 그중 1인을 위하여만 특별대리인을 선임하면 된다.</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>특별대리인수</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>판례는 친권에 따르는 수인의 자녀 사이 이해상반의 경우에도 친권자와 자녀 사이의 경우와 달리 자녀 각자(또는 1인)를 위한 특별대리인을 선임해야 한다고 보며, 공동상속재산분할협의에서는 미성년자 각자마다 특별대리인을 선임해야 한다.</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>대판 1994.9.9. 94다6680</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>523</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>부동산 경매에서 매수인은 매각대금을 다 낸 때에 등기 없이도 매각 목적인 권리를 취득한다.</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>취득시기</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>민사집행법 제135조와 민법 제187조에 따라 경매 매수인은 매각대금 완납 시 등기 없이 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>민법 제187조·민사집행법 제135조</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>제187조</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>524</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>타인이 권원에 의하여 부동산에 부속시킨 물건이라도, 그것이 사실상 분리·복구가 불가능하여 거래상 독립한 권리의 객체성을 상실하고 부동산의 구성부분이 된 경우에는 그 소유권이 부동산 소유자에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>부합</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>판례는 제256조 단서가 분리하여 경제적 가치가 있는 경우에만 권원자의 권리를 인정하므로, 독립성을 상실하고 구성부분이 된 부합물은 부동산 소유자에게 귀속한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>대판 2008.5.8. 2007다36933</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>제256조</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>525</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>공동상속인들의 건물철거의무는 그 성질상 불가분채무로서, 각자 그 지분의 한도 내에서 건물 전체에 대한 철거의무를 진다.</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>불가분채무</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>판례는 공동상속인의 건물철거의무를 불가분채무로 보아 각자 지분 한도에서 건물 전체에 대한 철거의무를 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>대판 1980.6.24. 80다756</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>제411조</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>526</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>공유자 중 일부가 특정 부분을 배타적으로 점유·사용하는 경우, 다른 공유자들에 대한 부당이득 반환채무는 불가분채무이다.</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>불가분채무</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>판례는 여러 사람이 공동으로 법률상 원인 없이 타인의 재산을 사용한 경우의 부당이득반환채무를 불가분채무로 본다.</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>대판 2001.12.11. 2000다13948</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>제411조</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>527</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>건물의 소유자는 현실적으로 그 건물이나 부지를 점거하고 있지 아니하더라도, 그 건물의 소유를 위하여 그 부지를 점유하는 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>점유개념</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>판례는 건물 소유자가 부지를 현실 점거하지 않아도 건물 소유를 통하여 부지를 점유한다고 본다.</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>대판 1991.6.25. 91다10329</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>제192조</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>528</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>경매개시결정 기입등기로 압류의 효력이 발생한 후에 수급인이 공사를 완공하여 공사대금채권을 취득함으로써 비로소 유치권이 성립한 경우, 수급인은 그 유치권으로 경매절차의 매수인에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>성립시점</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>판례는 압류 후에 채권을 취득하여 성립한 유치권은 처분금지효에 저촉되어 매수인에게 대항할 수 없다고 한다(점유를 미리 이전받았어도 같다).</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>대판 2013.6.27. 2011다50165</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>529</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>경매개시결정등기 전에 이미 민사유치권을 취득한 사람은, 그 취득에 앞서 저당권설정등기나 가압류등기 또는 체납처분압류등기가 먼저 되어 있더라도 경매절차의 매수인에게 자기의 유치권으로 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>대항가부</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>판례(전합)는 압류 전에 성립한 민사유치권은 선행 저당권·가압류·체납처분압류가 있어도 매수인에게 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>대판 2014.3.20. 2009다60336 전합</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>530</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>불법하게 말소된 근저당권설정등기의 회복등기청구는 등기말소 당시의 소유자를 상대로 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>청구상대방</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>판례는 말소회복등기청구의 상대방을 말소 당시의 소유명의인으로 본다.</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>대판 1969.3.18. 69다1617</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>531</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>말소된 등기의 회복을 신청하는 경우 등기상 이해관계 있는 제3자가 있을 때에는, 그 제3자의 승낙이 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>회복요건</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>부동산등기법 제59조는 말소회복등기에 등기상 이해관계 있는 제3자의 승낙을 요구한다.</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>부동산등기법 제59조</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>532</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>근저당권설정등기가 원인 없이 말소된 후 다른 권리자의 신청으로 경매절차가 진행되어 경락인이 경락대금을 완납한 경우, 원인 없이 말소된 근저당권은 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>경락소멸</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>판례는 등기가 효력존속요건이 아니어서 원인 없이 말소되어도 효력에 영향이 없으나, 경매로 매수인이 대금을 완납하면 그 근저당권도 다른 저당권처럼 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>대판 1998.10.2. 98다27197</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>제356조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>533</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>공동저당의 목적인 물상보증인 소유 부동산에 후순위저당권이 설정되어 있는 경우, 그 부동산이 먼저 경매되어 선순위 공동저당권자가 변제받으면 물상보증인은 변제자대위로 채무자 소유 부동산에 대한 선순위 저당권을 대위취득하고, 그 후순위저당권자는 이에 물상대위를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>대위</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인의 변제자대위로 취득한 저당권에 후순위저당권자가 물상대위할 수 있고, 그 저당권은 말소가 아니라 물상보증인 앞으로 이전 부기등기되어야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>대결 2009.5.28. 2008마109</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>534</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>토지조사부에 토지소유자로 등재된 자가 사망한 경우, 그 재산상속인은 그 토지의 소유자로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>사정추정</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>판례는 토지조사부 사정명의자로 확정 추정되고 그 재산상속인이 소유자로 추정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>대판 2001.3.23. 2000다66522</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>535</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>진정명의 회복을 원인으로 한 소유권이전등기청구는, 이미 자기 앞으로 소유권을 표상하는 등기가 되어 있었거나 법률에 의하여 소유권을 취득한 자가 현재의 등기명의인을 상대로 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>청구권자</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>판례(전합)는 진정명의회복 이전등기청구의 권리자를 등기를 가졌던 자 또는 법률에 의한 소유권 취득자로 한정한다.</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>대판 2001.9.20. 99다37894 전합</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>536</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>순차로 마쳐진 이전등기의 말소청구소송에서 최종 등기명의자의 등기부취득시효 항변이 받아들여진 경우, 소유권을 상실한 원 소유자는 중간등기에 대한 말소청구를 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>손해배상</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>판례는 최종 명의자의 등기부취득시효로 원 소유자가 소유권을 상실하므로 중간등기 말소청구가 기각되고 물권적 청구권 자체가 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2010다28604 전합</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>537</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>신원보증서류에 서명·날인한다는 착각에 빠진 상태로 연대보증의 서면에 서명·날인한 경우, 이는 표시상의 착오에 해당하므로 그 착오가 제3자의 기망에 의한 것이라도 제110조 제2항이 아니라 착오에 관한 제109조를 적용하여 취소 가부를 판단한다.</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>착오유형</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>판례는 이를 표시상의 착오로 보아 제3자 기망 시에도 제109조만 적용한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>대판 2005.5.27. 2004다43824</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>538</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>착오를 이유로 의사표시를 취소하는 경우, 표의자에게 중대한 과실이 있다는 점에 대한 증명책임은 취소하고자 하는 표의자 자신이 부담한다.</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>판례는 착오의 존재·중요부분 해당성은 표의자가, 중대한 과실의 존재는 취소를 막으려는 상대방이 증명한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>대판 2005.5.12. 2005다6228</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>539</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>상대방이 표의자의 착오를 알고 이를 이용한 경우에는, 그 착오가 표의자의 중대한 과실로 인한 것이라도 표의자는 의사표시를 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>중과실예외</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>판례는 제109조 제1항 단서가 상대방 보호를 위한 것이므로 상대방이 착오를 알고 이용한 경우에는 중과실이 있어도 취소할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>대판 2014.11.27. 2013다49794</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>540</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>과실로 착오에 빠져 의사표시를 한 자가 그 착오를 이유로 의사표시를 적법하게 취소한 경우, 그 취소행위가 상대방에 대한 위법한 행위가 되어 불법행위 책임이 성립한다.</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>위법성</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>판례는 적법한 착오 취소권 행사는 위법성이 없으므로 불법행위 책임이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>대판 1997.8.22. 97다13023</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>541</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계에 있는 자는 제3자의 방해행위에 대하여 자기의 구분소유 부분뿐 아니라 전체 토지에 대하여 공유물의 보존행위로서 그 배제를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>대외관계</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유가 대외적으로 공유관계이므로 전체 토지에 대한 방해배제를 보존행위로 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>대판 1994.2.8. 93다42986</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>542</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>상호명의신탁(구분소유적 공유관계)에서 건물의 특정 부분을 구분소유하는 자는, 그 부분에 대해 신탁적으로 지분등기를 가진 자를 상대로 명의신탁 해지를 원인으로 한 지분이전등기를 구할 수 있을 뿐 건물 전체에 대한 공유물분할을 구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>해소방법</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유의 해소를 명의신탁 해지로 하여야 하고 공유물분할청구로는 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>대판 2010.5.27. 2006다84171</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>제268조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>543</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>보증인과 물상보증인 사이에서는 그 인원수에 비례하여 채권자를 대위하고, 물상보증인이 수인인 때에는 보증인의 부담부분을 제외한 잔액에 대하여 각 재산의 가액에 비례하여 채권자를 대위한다.</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>대위비율</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>민법 제482조 제2항 제5호의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>민법 제482조②5호</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>제482조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>544</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>토지와 지상 건물이 함께 양도되었다가 채권자취소권의 행사로 그중 건물에 관하여만 양도가 취소되고 수익자·전득자 명의의 이전등기가 말소된 경우, 이는 관습상 법정지상권의 성립요건인 '동일인 소유의 토지와 건물이 매매 등으로 소유자가 달라진 경우'에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>판례는 채권자취소의 효과가 채권자와 수익자·전득자 사이에서만 발생하고 채무자가 권리를 취득하는 것이 아니므로 관습상 법정지상권이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>대판 2014.12.24. 2012다73158</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="n">
+        <v>545</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>강제경매로 토지 또는 지상 건물의 소유권이 매수인에게 이전된 경우, 관습상 법정지상권의 성립요건인 '토지와 건물이 동일인 소유였는지'는 매각대금 완납 시가 아니라 압류(또는 가압류)의 효력 발생 시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>판례(전합)는 강제경매에서 동일인 소유 여부 판단 기준시를 압류 효력 발생 시로 본다.</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>대판 2012.10.18. 2010다52140 전합</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="n">
+        <v>546</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>외화채권을 채무자가 우리나라 통화로 변제하는 경우, 그 환산시기는 이행기가 아니라 현실로 이행하는 때의 외국환 시세에 의한다.</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>환산시기</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>판례는 제378조가 '지급할 때'로 규정하므로 현실이행 시의 환시세로 환산한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>대판 2012.10.25. 2009다77754</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>제378조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="n">
+        <v>547</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>채권자가 외화채권을 우리나라 통화로 환산하여 청구하는 경우, 법원은 사실심 변론종결 당시의 외국환 시세를 기준으로 채권액을 환산하여 이행을 명한다.</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>환산기준</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>판례는 현실이행에 가장 가까운 사실심 변론종결 당시의 환시세를 기준으로 환산한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>대판 2012.10.25. 2009다77754</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>제378조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n">
+        <v>548</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>대금 지급을 위하여 지급기일이 물품공급일자 이후로 된 약속어음을 발행·교부한 경우, 물품대금 지급채무의 이행기는 다른 특별한 사정이 없는 한 그 약속어음의 지급기일이다.</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>이행기</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>판례는 지급을 위하여 교부된 약속어음의 지급기일이 원인채무의 이행기가 되며, 지급정지로 기일 전 지급거절되어도 그때 이행기가 도래하는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>대판 1999.8.24. 99다24508</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="n">
+        <v>549</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>채권이 가압류된 경우에는, 그 채권의 이행기가 도래하더라도 제3채무자는 지체책임을 면한다.</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>지체책임</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>판례는 채권 가압류가 있어도 이행기가 도래하면 제3채무자는 지체책임을 면할 수 없다고 한다(가압류는 현실 추심만 금지).</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>대판 1994.12.13. 93다951</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="n">
+        <v>550</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>특정물 매매에서 매수인의 대금지급채무가 이행지체에 빠졌더라도, 그 목적물이 매수인에게 인도될 때까지는 매수인은 매매대금의 이자를 지급할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>대금이자</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>민법 제587조 단서는 매수인이 목적물 인도를 받지 않은 동안에는 대금의 이자를 지급할 의무가 없다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>민법 제587조</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="n">
+        <v>551</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>보증인은 주채무자의 채권에 의한 상계로 채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>상계원용</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>민법 제434조는 보증인이 주채무자의 채권에 의한 상계로 채권자에게 대항할 수 있다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>민법 제434조</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>제434조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="n">
+        <v>552</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인이 한 상계 또는 상계계약은 다른 부진정연대채무자에게는 효력이 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>절대효</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>판례는 상계가 변제와 같이 현실적 만족을 주므로 소멸한 채무 전액에 관하여 다른 부진정연대채무자에게도 효력이 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>대판 2010.9.16. 2008다97218 전합</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="n">
+        <v>553</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>채권자대위권을 행사하는 채권자가 채무자를 상대로 보전되는 청구권에 기한 이행청구의 소를 제기하여 승소판결이 확정되면, 제3채무자는 그 피보전채권의 존재를 다툴 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>기판력</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>판례는 피보전채권에 관한 확정판결이 있으면 제3채무자가 그 존재를 다툴 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>대판 2007.5.10. 2006다82700</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="n">
+        <v>554</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>채권자대위소송 계속 중 다른 채권자가 동일한 채무자를 대위하여 채권자대위권을 행사하면서 공동소송참가신청을 하는 경우, 양 청구의 소송물이 동일하다면 그 참가신청은 적법하다.</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>공동소송참가</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>판례는 소송물이 동일하면 합일확정의 필요가 있어 공동소송참가가 적법하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>대판 2015.7.23. 2013다30301</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="n">
+        <v>555</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사 사실을 채무자가 안 후에 행한 처분행위는 금지되지만, 제3채무자가 채무자에게 하는 변제(채무자의 변제수령)는 그러한 처분행위에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 변제수령은 제405조 제2항의 처분행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>판례(채권자대위권과 변제수령)</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="n">
+        <v>556</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>채권자대위권의 행사는 법정위임관계로서, 대위채권자는 제688조를 준용하여 채무자에게 비용상환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>비용상환</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>판례는 채권자대위권 행사를 법정위임으로 보아 위임 규정(제688조)을 준용하여 비용상환청구를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>판례(채권자대위권의 법정위임)</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n">
+        <v>557</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>매매로 인한 소유권이전등기청구권의 양도는 통상의 채권양도와 달리 양도인의 통지만으로는 채무자에 대한 대항력이 생기지 않고, 반드시 채무자의 동의나 승낙을 받아야 대항력이 생긴다.</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>양도방식</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>판례는 매매로 인한 등기청구권은 이행과정에 신뢰관계가 따르므로 양도에 채무자의 동의·승낙을 요한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>대판 2001.10.9. 2000다51216</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="n">
+        <v>558</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>채권양도금지특약은 양수인이 악의 또는 중대한 과실로 그 특약을 알지 못한 경우에 그 양수인에게 대항할 수 있고, 그 악의·중과실은 양도금지를 주장하는 자가 증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>증명책임</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>판례는 양도금지특약으로 대항하려면 양수인의 악의·중과실을 주장하는 자가 증명해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>대판 1999.12.28. 99다8834</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="n">
+        <v>559</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>채무 변제와 관련하여 다른 채권을 양도한 경우, 특별한 사정이 없는 한 변제에 갈음하여 양도된 것으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>추정방향</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>판례는 변제를 위한 담보 또는 변제의 방법으로 양도된 것으로 추정하고 변제에 갈음(대물변제)한 것으로 추정하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>대판 1995.12.22. 95다16660</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>제466조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="n">
+        <v>560</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>부동산 이중매매에서 제1매수인이 양도인에 대하여 갖는 부동산 가액 상당의 손해배상채권은, 이중양도행위에 대한 사해행위취소권을 행사할 수 있는 피보전채권이 된다.</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>피보전채권</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>판례는 채권자취소권이 금전채권 보전을 위한 것이고 이중양도로 인한 손해배상채권은 발생이 불확실하여 피보전채권이 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>대판 1999.4.27. 98다56690</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="n">
+        <v>561</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>사해행위의 무자력(소극재산이 적극재산을 초과하는 상태)은 처분행위 당시뿐만 아니라 사실심 변론종결 시까지 유지되어야 하고, 그 후 채무자가 자력을 회복하였다는 사실은 취소소송의 상대방이 증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>무자력유지</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>판례는 사해성 요건이 처분 당시와 사실심 변론종결 시 모두 갖춰져야 하고, 자력 회복 사실은 상대방이 증명한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>대판 2007.11.29. 2007다54849</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="n">
+        <v>562</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>채권자가 채무자의 사해의사를 증명하면 수익자나 전득자의 악의는 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>악의추정</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 사해의사가 증명되면 수익자·전득자의 악의는 추정되고 그 선의는 수익자·전득자가 증명해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>대판 2007.11.29. 2007다54849</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="n">
+        <v>563</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>채권자가 채무자의 채권자취소권을 대위행사하는 경우, 제척기간 준수 여부는 채무자를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>판례는 대위의 객체인 채권자취소권의 제척기간은 그 권리자인 채무자를 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>대판 2001.12.27. 2000다73049</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="n">
+        <v>564</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>채무자가 변제공탁으로 채무를 면하려면 채무액 전부를 공탁하여야 하므로, 일부공탁은 특별한 사정이 없는 한 채권자가 수락하지 않는 이상 채무의 일부 소멸 효과도 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>일부공탁</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>판례는 채무 일부 공탁이 원칙적으로 무효이고 채권자가 수락하지 않는 한 일부 소멸 효과도 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>대판 1983.11.22. 83다카161</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>제487조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="n">
+        <v>565</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>특정물의 인도는 채무 성립 당시 그 물건이 있었던 장소에서 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>변제장소</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>민법 제467조 제1항은 특정물 인도를 채권성립 당시 물건이 있던 장소에서 하도록 정한다.</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>민법 제467조①</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>제467조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="n">
+        <v>566</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>채권의 준점유자에 대한 변제가 유효하려면, 준점유자는 진정한 채권자로 믿을 만한 외관을 갖추었으나 실질적 변제 수령권한이 없는 자여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>준점유자</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>판례는 채권의 준점유자를 거래관념상 채권을 행사할 정당한 권한을 가진 것으로 믿을 외관을 가진 자로 본다.</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>민법 제470조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>제470조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="n">
+        <v>567</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>민법 제472조의 '채권자가 이익을 받은' 경우에는, 권한 없는 자에 대한 변제를 채권자가 사후에 추인한 때도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>추인</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>판례는 무권한자에 대한 변제를 채권자가 추인하면 제472조의 채권자가 이익을 받은 경우에 해당하여 변제가 유효하게 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>민법 제472조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>제472조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="n">
+        <v>568</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>채권이 이중으로 양도된 경우 양수인 상호간의 우열은 통지 또는 승낙에 붙여진 확정일자의 선후가 아니라, 확정일자 있는 양도통지가 채무자에게 도달한 일시 또는 확정일자 있는 승낙의 일시의 선후에 의하여 결정한다.</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>우열기준</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>판례(전합)는 채권 이중양도의 우열을 확정일자 자체가 아니라 채무자에 대한 도달(승낙) 시점의 선후로 결정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223 전합</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="n">
+        <v>569</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>채권양도에서 채무자에 대한 대항요건은 통지나 승낙이고, 제3자에 대한 대항요건은 확정일자 있는 증서에 의한 통지나 승낙이며, 전부명령은 확정일자 있는 증서에 준한다.</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>민법 제450조와 판례는 단순 통지·승낙(채무자 대항)과 확정일자 있는 통지·승낙(제3자 대항)을 구별하고 전부명령을 확정일자 있는 증서에 준한다고 본다.</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>민법 제450조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="n">
+        <v>570</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>상계를 하기 위해서는 자동채권의 변제기는 반드시 도래하여야 하지만, 수동채권의 변제기는 도래하지 않아도 된다.</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>변제기</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>판례는 상계자가 수동채권의 기한의 이익을 포기할 수 있으므로 수동채권의 변제기 도래는 요하지 않고 자동채권의 변제기만 도래하면 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>대판 1979.6.12. 79다662</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="n">
+        <v>571</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>지급금지명령을 받기 이전에 취득한 채권을 자동채권으로 상계하기 위해서는, 압류의 효력 발생 당시 이미 상계적상에 있거나 자동채권이 수동채권의 변제기와 동시에 또는 그보다 먼저 변제기에 도달하는 경우여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>상계요건</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>판례는 압류 전 취득한 자동채권의 상계 대항요건으로 변제기 선도래 등을 요구한다(제498조).</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>대판 2012.2.16. 2011다45521 전합</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>제498조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="n">
+        <v>572</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>자녀의 양육비청구권은 협의나 심판에 의하여 구체적으로 확정된 경우 이를 자동채권으로 하여 상계할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>상계가부</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>판례는 구체화되고 이행기가 도래한 양육비채권을 자동채권으로 한 상계를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>판례(양육비채권과 상계)</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="n">
+        <v>573</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>이행지체를 이유로 한 해제에서 이행의 최고는 기간을 정하지 않고 하였더라도, 최고한 때로부터 상당한 기간이 경과하면 해제권이 발생한다.</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>최고방식</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>판례는 기간을 명시하지 않은 최고도 유효하며 상당한 기간 경과로 해제권이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>대판 1994.11.25. 94다35930</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="n">
+        <v>574</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>부동산 매매에서 잔대금 지급기일까지 대금을 지급하지 못하면 계약이 자동 해제된다는 약정이 있는 경우, 매수인의 잔대금 지급의무와 매도인의 소유권이전등기의무가 동시이행관계에 있으면 매도인의 이행제공 없이도 자동 해제된다.</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>자동해제</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>판례는 동시이행관계에 있는 잔대금 실권조항의 경우 매도인이 이행제공을 하여 매수인을 이행지체에 빠지게 하여야 비로소 자동 해제된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 98다505</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="n">
+        <v>575</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>착오송금의 경우 수취인은 수취은행에 대하여 입금액 상당의 예금채권을 취득하고, 송금의뢰인은 수취은행이 아니라 수취인에 대하여 부당이득반환청구권을 가진다.</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>반환상대방</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>판례는 착오송금 시 자금이체의 원인관계 유무와 관계없이 수취인이 예금채권을 취득하므로 송금의뢰인은 수취인을 상대로 부당이득반환을 구한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>대판 2010.11.11. 2010다41263</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="n">
+        <v>576</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>예금명의자가 아닌 실제 출연자에게 예금반환청구권이 귀속되려면, 금융기관과 출연자 등 사이에 예금명의자가 아닌 출연자에게 예금반환청구권을 귀속시키겠다는 명확한 의사의 합치가 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>예금주확정</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>판례(전합)는 실명확인 절차를 거친 경우 예금명의자를 예금계약 당사자로 보고, 출연자에게 귀속시키려면 명확한 의사합치라는 예외적 사정이 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>대판 2009.3.19. 2008다45828 전합</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>제702조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="n">
+        <v>577</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>협의에 의한 상속재산 분할은 공동상속인 전원의 동의가 있어야 유효하므로, 공동상속인 중 1인의 동의가 없거나 그 의사표시에 대리권의 흠결이 있으면 그 분할은 무효이다.</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>전원동의</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>판례는 상속재산 분할협의에 전원의 참여를 요하고 1인의 의사표시 흠결 시 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>대판 1987.3.10. 85므80</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="n">
+        <v>578</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>상속재산 분할협의 과정에서 채무초과 상태의 상속인이 자신의 상속분에 관한 권리를 포기하여 일반채권자에 대한 공동담보가 감소한 경우, 이는 원칙적으로 사해행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>판례는 상속재산 분할협의가 재산권을 목적으로 하는 법률행위이므로 그 과정에서의 상속분 포기는 사해행위가 될 수 있다고 한다(상속포기 자체는 사해행위 아님).</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>대판 2007.7.26. 2007다29119</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="n">
+        <v>579</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>인지 전 상속재산을 분할한 공동상속인이 분할받은 상속재산으로부터 발생한 과실은, 나중에 인지된 피인지자가 부당이득으로 반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>과실귀속</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>판례는 인지 전 적법하게 분할받은 공동상속인이 취득한 과실은 피인지자가 부당이득으로 반환을 청구할 수 없다고 한다(제1014조는 가액지급청구만 인정).</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>대판 2007.7.26. 2006므2757 등</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>제1014조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="n">
+        <v>580</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>공사도급계약에서 당사자 사이에 특약이 있거나 일의 성질상 수급인 자신이 하지 않으면 안 되는 등의 특별한 사정이 없는 한, 반드시 수급인 자신이 직접 일을 완성하여야 하는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>이행대행</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>판례는 도급에서 특약·성질상 제한이 없으면 이행보조자·이행대행자를 사용하여도 무방하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>대판 2002.4.12. 2001다82545</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>제664조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="n">
+        <v>581</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>수급인이 자기의 노력과 재료로 건물을 신축한 경우 원칙적으로 수급인이 그 소유권을 원시취득하지만, 도급인 명의로 건축허가·보존등기를 하기로 하는 등 완성된 건물의 소유권을 도급인에게 귀속시키기로 합의한 경우에는 도급인이 원시취득한다.</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>소유귀속</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>판례는 신축건물의 원시취득자를 원칙적으로 수급인으로 보되 도급인 귀속 합의가 있으면 도급인이 원시취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>대판 1996.9.20. 96다24804</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>제664조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="n">
+        <v>582</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>재산분할에 관한 협의는 아직 이혼하지 않은 당사자가 장차 협의상 이혼할 것을 전제로 한 것이므로, 그 협의 후 협의상 이혼이 이루어지지 않고 재판상 이혼이 된 경우에는 그 협의의 효력이 발생하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>조건부협의</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>판례는 협의이혼을 전제로 한 재산분할 협의는 조건부 의사표시로서 협의이혼이 이루어진 경우에만 효력이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>대판 2000.10.24. 99다33458</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="n">
+        <v>583</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>이혼으로 인한 재산분할청구권은 협의·심판에 의하여 구체적 내용이 형성되기 전까지는 채권자대위권의 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>대위대상</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권은 범위·내용이 불확정하여 채권자대위권의 객체가 될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>대판 1999.4.9. 98다58016</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="n">
+        <v>584</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>이혼소송과 재산분할청구가 병합된 상태에서 배우자 일방이 사망하면, 이혼소송과 재산분할청구가 모두 종료된다.</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>소송종료</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>판례는 이혼소송 계속 중 당사자 일방의 사망으로 이혼소송이 종료되고 이에 부수한 재산분할청구도 함께 종료된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>대판 1994.10.28. 94므246</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="n">
+        <v>585</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>도박채무의 담보로 근저당권설정등기를 마친 경우, 근저당설정자는 그 근저당권설정등기의 말소를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>종국성</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>판례는 근저당권설정은 수령자가 경매신청 등 별도 조치를 해야 이익을 얻는 것이어서 종국적 급여가 아니므로 설정자의 말소청구를 허용한다.</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>대판 1995.8.11. 94다54108</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="n">
+        <v>586</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>불법원인급여를 한 사람은 그 원인행위가 무효임을 이유로 부당이득반환을 청구할 수 없을 뿐 아니라, 급여한 물건의 소유권에 기한 반환청구도 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>소유권반환</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>판례는 제746조가 부당이득뿐 아니라 소유권에 기한 반환청구도 배제하여 급여물의 소유권이 수익자에게 귀속된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>대판 1979.11.13. 79다483 전합</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="n">
+        <v>587</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>불법원인급여가 성립한 경우, 수익자가 그 불법의 원인에 가공하였다면 급여자는 수익자의 불법행위를 이유로 그 재산의 급여로 발생한 자신의 손해의 배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>손해배상</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>판례는 불법원인급여물의 반환을 구할 수 없는 이상 그 급여로 발생한 손해의 배상도 불법행위를 이유로 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>대판 2013.8.22. 2013다35412</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="n">
+        <v>588</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>적법하게 공동상속등기가 마쳐진 부동산에 대하여 공동상속인 중 1인이 단독명의로 소유권이전등기를 한 경우, 다른 공동상속인들이 그 말소를 청구하는 것은 상속회복청구에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>상속회복</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>판례는 이미 취득한 소유권이 위법하게 침해된 경우의 회복청구이지 상속권 침해의 회복청구가 아니므로 제999조의 제척기간이 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>대판 2011.9.29. 2009다78801</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>제999조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="n">
+        <v>589</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>상속회복청구에서 상속재산의 일부에 대하여 제척기간을 준수하여 청구하였다면, 청구의 목적물로 하지 아니한 다른 상속재산에 대하여도 제척기간이 준수된 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>기간준수</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>판례는 청구 목적물로 한 상속재산에 대해서만 제척기간이 준수되고 청구하지 않은 다른 상속재산은 기간이 준수되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>대판 1981.6.9. 80므84 등</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>제999조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="n">
+        <v>590</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>상속회복청구의 제척기간이 경과하면 상속개시 시로 소급하여 진정상속인은 상속인의 지위를 상실하고 참칭상속인이 상속인의 지위를 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>제척효과</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>판례는 상속회복청구권의 제척기간 경과 시 진정상속인의 지위가 소급 상실되고 참칭상속인이 확정적으로 상속인이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>대판 1994.3.25. 93다57155</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>제999조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="n">
+        <v>591</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>비록 출생신고가 되어 있더라도 친생추정이 미치지 않는 경우에는, 부(父)는 인지청구의 소를 제기할 수 있고 친생자관계존부확인의 소가 아니라 친생자관계부존재확인의 소를 거쳐야 한다.</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>판례는 친생추정이 미치지 않는 경우 친생자관계부존재확인의 소에 의하며, 제3자(조부 등)는 부모와 자 쌍방을 상대로 소를 제기할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>대판 1981.10.13. 80므60 전합</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>제865조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="n">
+        <v>592</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>인지청구의 소는 일신전속적인 신분관계상의 권리이므로 포기할 수 없고, 실효의 법리도 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>일신전속</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>판례는 인지청구권이 본질상 포기할 수 없는 신분상의 권리이고 실효의 법리가 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>대판 2001.11.27. 2001므1353</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>제863조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="n">
+        <v>593</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>혼인 외 출생자의 생부가 사망한 후 생모는 자를 상대로 사망한 친부와 자 사이의 친생자관계 존재확인의 소를 제기할 수 없고, 자가 직접 검사를 상대로 인지청구의 소를 제기하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>소송형태</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>판례는 생부 사망 후 친자관계 형성은 인지청구의 소에 의하여야 하고, 자가 사망을 안 날부터 2년 내에 검사를 상대로 인지청구의 소를 제기해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>판례(사망한 부에 대한 인지청구)</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>제864조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="n">
+        <v>594</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인의 불법행위 가공 정도가 경미하더라도, 피해자에 대한 관계에서 그 가해자의 책임 범위를 손해배상액의 일부로 제한할 수 없고 전체 손해액에 대하여 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>책임범위</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위 책임의 범위를 전원의 행위를 전체적으로 평가하여 정하고 가공 정도가 경미한 자도 전액 책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>대판 2001.9.7. 99다70365</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="n">
+        <v>595</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>채권자가 공동불법행위자 중 1인에 대하여 채무를 면제하였더라도, 다른 공동불법행위자의 구상권 행사에는 영향을 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>판례는 부진정연대채무에서 1인에 대한 면제가 다른 채무자에게 효력이 없어 구상권 행사에 영향이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>대판 1997.12.12. 96다50896</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="n">
+        <v>596</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>부진정연대채무에서 채무자 1인에 대한 이행청구는 다른 채무자에게 소멸시효 중단의 효력이 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>판례는 부진정연대채무에 절대적 효력 규정이 적용되지 않아 1인에 대한 이행청구가 다른 채무자의 시효를 중단시키지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>대판 1997.9.12. 95다42027</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="n">
+        <v>597</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>변시5</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>불법행위로 인한 손해배상액 산정에서 과실상계와 손익상계를 모두 하는 경우, 과실상계를 한 후에 손익상계를 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>산정순서</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>판례는 과실상계를 먼저 하고 그 다음에 손익상계를 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>대판 1990.5.8. 89다카29129</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1068"/>
+  <dimension ref="A1:H1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -43184,6 +43184,3046 @@
         </is>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" t="n">
+        <v>401</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>주택임대차보호법은 주택 소유자인 임대인과의 임대차계약뿐 아니라 주택에 관하여 적법하게 임대차계약을 체결할 권한을 가진 임대인과의 계약에도 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>판례는 임대인이 소유자가 아니더라도 적법한 임대권한이 있으면 주임법이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>대판 2012.7.26. 2012다45689</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="n">
+        <v>402</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>주택임차인이 임차주택에 대하여 보증금반환청구소송의 확정판결 등 집행권원에 따라 경매를 신청하는 경우, 반대의무의 이행이나 이행의 제공을 집행개시의 요건으로 하지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>집행개시</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>주택임대차보호법 제3조의2 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>주택임대차보호법 제3조의2</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="n">
+        <v>403</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>실제 임대차계약의 주된 목적이 주택을 사용·수익하려는 것이 아니라 소액임차인으로 보호받아 채권을 회수하려는 데 있는 경우, 그 임차인은 주택임대차보호법에 따라 보호받을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>판례는 채권회수 목적의 가장 임대차는 주임법의 소액보증금 우선변제 등 보호를 받을 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>대판 2008.5.15. 2007다23203</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="n">
+        <v>404</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>주택임차인이 임대인의 승낙을 받아 임대주택을 전대하고 전차인이 주택을 인도받아 자신의 주민등록을 마친 경우, 임차인은 대항력을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>대항력</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>판례는 적법한 전대 시 전차인의 점유·주민등록으로 원래 임차인이 대항력을 취득(유지)한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>대판 1994.6.24. 94다3155</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="n">
+        <v>405</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>계약명의신탁에서 매도인이 명의신탁 약정 사실을 알지 못한 경우, 명의신탁 약정은 무효이지만 명의수탁자 명의의 물권변동은 유효하여 수탁자가 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>선의매도인</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제2항 단서에 따라 선의 매도인과 체결한 계약명의신탁에서는 수탁자가 완전한 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>민법 제4조②단서 · 판례</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="n">
+        <v>406</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>계약명의신탁(매도인 악의)에서 명의신탁자로부터 부동산을 매수한 자는, 명의수탁자가 물권자임을 기초로 새로운 이해관계를 맺은 자가 아니므로 부동산실명법 제4조 제3항의 제3자에 해당하여 유효하게 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>판례는 신탁자로부터의 매수인은 수탁자와 직접 이해관계를 맺은 제3자가 아니므로 제4조 제3항으로 보호되지 않고, 매도인 악의 시 수탁자 등기가 무효여서 무권한자로부터의 매수에 불과해 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>대판 2004.8.30. 2002다48771</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="n">
+        <v>407</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>계약명의신탁이 무효임이 밝혀진 후 매도인이 명의신탁자에게 부동산을 양도할 의사를 표시한 경우, 매도인과 명의신탁자 사이에 별도의 양도약정이 성립하여 명의신탁자는 매도인에게 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>별도약정</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>판례는 무효 확인 후 매도인의 양도 의사표시가 있으면 종전 매매와 같은 내용의 별도 양도약정이 성립한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>대판 2003.9.5. 2001다32120</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="n">
+        <v>408</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제3항의 제3자에는 명의수탁자가 물권자임을 기초로 물권을 취득한 자뿐 아니라 압류·가압류채권자도 포함되며, 그 선의·악의를 묻지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>판례는 제4조 제3항의 제3자에 물권 취득자와 압류·가압류채권자를 포함하고 선악을 불문한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>대판 2000.3.28. 99다56529</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="n">
+        <v>409</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>부동산실명법 시행 후 계약명의신탁(매도인 선의)에서 명의신탁자가 입은 손해는 부동산 자체가 아니라 명의수탁자에게 제공한 매수자금이므로, 명의수탁자는 매수자금을 부당이득으로 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>반환대상</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>판례는 선의 매도인 계약명의신탁에서 수탁자가 완전한 소유권을 취득하므로 부당이득 반환대상이 부동산이 아니라 매수자금이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>대판 2005.1.28. 2002다66922</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="n">
+        <v>410</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>부동산 매수인이 매매목적물에 관한 근저당권의 피담보채무 등을 인수하면서 그 채무액을 매매대금에서 공제하기로 약정한 경우, 이는 면책적 채무인수가 아니라 이행인수이고 매수인은 인수한 채무액을 공제한 잔금을 지급하면 잔금지급의무를 다한 것이 된다.</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>이행인수</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>판례는 채무액 공제 약정을 이행인수로 보아 매수인이 채무를 현실 변제할 의무가 없고 공제 후 잔금 지급으로 의무를 다한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>대판 1993.2.12. 92다23193</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>제454조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="n">
+        <v>411</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>부동산 매매와 함께 이행인수계약이 이루어진 경우, 매도인이 매수인의 인수채무 불이행으로 또는 임의로 인수채무를 대신 변제하여 취득한 구상채무 이행의무와 매도인의 소유권이전등기의무는 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>판례는 인수채무가 매매대금지급채무에 갈음한 것이므로 그 변형인 구상채무와 소유권이전의무가 대가적 견련관계로 동시이행관계에 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>대판 1993.2.12. 92다23193</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="n">
+        <v>412</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>매매예약 완결권은 형성권으로서 당사자 사이에 행사기간을 약정한 때에는 그 기간 내에, 약정이 없는 때에는 예약이 성립한 때로부터 10년 내에 행사하여야 하고, 그 기간이 지나면 예약 목적물을 인도받은 경우라도 제척기간 경과로 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>제척기간</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>판례는 예약완결권을 형성권으로 보아 10년의 제척기간을 적용하고, 목적물 인도 여부와 무관하게 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>대판 1997.7.25. 96다47494</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="n">
+        <v>413</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>당사자 사이에 매매예약 완결권을 행사할 수 있는 시기를 특별히 약정한 경우에는, 그 제척기간은 권리 발생일이 아니라 약정에 따라 권리를 행사할 수 있는 때로부터 10년이 되는 날까지로 연장된다.</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>판례는 제척기간 기산점이 원칙적으로 권리 발생 시이고, 행사시기 약정이 있어도 권리 발생일로부터 10년으로 만료되며 약정 행사가능 시점부터 10년으로 연장되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>대판 1995.11.10. 94다22682</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="n">
+        <v>414</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>수인의 채권자를 공동매수인으로 하는 1개의 매매예약을 체결하고 공동명의로 담보가등기를 마친 경우, 해석상 수인이 공동으로 예약완결권을 가지면 본등기청구는 전원이 하여야 하고, 각자 지분별로 별개의 예약완결권을 가지면 1인이 단독으로 자기 지분에 기한 본등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>준공유</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>판례(전합)는 예약완결권의 귀속형태를 매매예약의 내용에 따라 정하고, 공동 준공유이면 전원 행사, 지분별 별개이면 단독 행사를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>대판 2012.2.16. 2010다82530 전합</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>제564조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="n">
+        <v>415</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>계약상 급부가 채권자의 지시에 따라 제3자에게 직접 이루어진 단축급부의 경우, 그 계약의 효력이 발생하지 않았다면 급부를 한 계약당사자는 제3자가 아니라 계약의 상대방 당사자에게 부당이득반환을 청구하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>삼각관계</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>판례는 단축급부 시 급부가 계약당사자 간에 이루어진 것이므로 제3자가 아닌 계약 상대방에게 부당이득반환을 구해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>대판 2010.3.11. 2009다98706</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="n">
+        <v>416</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>사실혼관계가 일방 당사자의 사망으로 종료된 경우에도, 생존 배우자에게 재산분할청구권이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>분할청구권</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>판례는 사실혼이 생전에 해소된 경우에는 재산분할청구권이 인정되나, 일방의 사망으로 종료된 경우에는 인정되지 않는다고 한다(법률혼도 사망 시 상속만 인정).</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>대판 2006.3.24. 2005두15595</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="n">
+        <v>417</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>이혼으로 인한 재산분할청구권은 협의 또는 심판에 의하여 구체적 내용이 형성되기 전에는 채무자의 책임재산에 해당하지 않으므로, 이를 포기하는 행위는 채권자취소권의 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>권리구체화</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>판례는 구체화되지 않은 재산분할청구권의 포기는 사해행위취소의 대상이 될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>대판 2013.10.11. 2013다7936</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="n">
+        <v>418</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>이혼 당시 부부 일방이 아직 재직 중이어서 실제 퇴직급여를 수령하지 않았더라도, 장래의 퇴직급여는 재산분할의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>분할대상</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>판례(전합)는 장래의 퇴직급여채권도 재산분할의 대상으로 본다.</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>대판 2014.7.16. 2013므2250 전합</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="n">
+        <v>419</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>채무초과 상태의 채무자가 이혼에 따른 재산분할로 상당한 정도를 초과하지 않는 재산을 양도하여 공동담보가 감소하였더라도, 특별한 사정이 없는 한 사해행위에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>사해행위</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>판례는 재산분할이 민법 제839조의2의 상당한 정도를 초과하지 않는 한 사해행위가 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>대판 2000.7.28. 2000다14101</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="n">
+        <v>420</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>부부간의 명의신탁 해지를 원인으로 한 소유권이전등기청구는 가사소송사건이 아니라 통상의 민사사건이다.</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>사건구분</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>판례는 부부간 명의신탁 해지를 원인으로 한 이전등기청구를 통상의 민사사건으로 보아 가사소송사건인 이혼·재산분할청구와 병합할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>대판 2006.1.13. 2004므1378</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>제830조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="n">
+        <v>421</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>등기명의자가 전 소유자로부터 부동산을 취득함에 있어 등기부상 기재된 등기원인이 아닌 다른 원인으로 적법하게 취득하였다고 하면서 등기원인 행위의 태양이나 과정을 다소 다르게 주장하더라도, 그 주장만으로 등기의 추정력이 깨어지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>추정번복</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>판례는 등기가 현재의 진실한 권리상태를 공시하면 족하므로 등기원인 행위의 태양·과정을 다소 다르게 주장한다는 사정만으로 추정력이 깨지지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>대판 1995.4.28. 94다23524</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="n">
+        <v>422</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>원인무효 등기명의자 중 1인을 상대로 소유권에 기한 물권적 청구권으로 승소판결을 받았으나 다른 자에 대해 등기부취득시효가 인정되어 패소한 경우, 소유권을 상실한 자는 승소판결을 받은 등기말소의무자에 대하여 그 권리의 이행불능을 이유로 제390조의 전보배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>전보배상</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>판례는 소유권 상실로 물권적 청구권 자체가 소멸하므로 그 이행불능을 이유로 한 제390조 손해배상청구는 할 수 없고, 다만 불법행위를 이유로 소유권 상실에 관한 손해배상을 구할 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>대판 2012.5.17. 2010다28604 전합</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n">
+        <v>423</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>순차로 경료된 소유권이전등기에서 후순위 등기에 대한 말소청구가 패소 확정된 경우에도, 전순위 등기에 대한 말소청구는 소의 이익이 있다.</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>소의이익</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>판례는 후순위 등기 말소청구의 패소 확정이 전순위 등기 말소청구의 소의 이익을 없애지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>판례(순차등기 말소청구의 소의 이익)</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>제214조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="n">
+        <v>424</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>각 적법한 매매계약에 기하여 중간생략등기의 합의 없이 중간생략등기가 이루어진 경우에도, 그 등기는 실체관계에 부합하는 등기로서 유효하다.</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>기성등기</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>판례는 합의가 없었더라도 이미 마쳐진 중간생략등기는 적법한 매매가 이행된 이상 실체관계에 부합하여 유효하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>대판 1980.2.12. 79다2104</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="n">
+        <v>425</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>임의후견(후견계약)에서 임의후견감독인이 선임되기 전에는 본인 또는 임의후견인이 가정법원의 허가를 받아야 후견계약의 의사표시를 철회할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>철회방식</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>민법 제959조의18 제1항은 임의후견감독인 선임 전에는 공증인의 인증을 받은 서면으로 '언제든지' 철회할 수 있다고 정한다(가정법원 허가 불요).</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>민법 제959조의18</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>제959조의18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="n">
+        <v>426</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>피성년후견인의 신체를 침해하는 의료행위에 성년후견인이 대신 동의하는 경우, 그 의료행위의 직접적인 결과로 사망하거나 상당한 장애를 입을 위험이 있을 때에는 원칙적으로 가정법원의 허가를 받아야 한다.</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>허가요건</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>민법 제947조의2 제4항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>민법 제947조의2④</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>제947조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="n">
+        <v>427</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>전세기간 만료 이후 전세권양도계약 및 전세권이전의 부기등기가 이루어진 것만으로는 전세금반환채권 양도에 관한 확정일자 있는 통지나 승낙이 있었다고 볼 수 없어, 제3자인 전세금반환채권의 압류·전부 채권자에게 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>판례는 부기등기만으로는 채권양도의 확정일자 있는 대항요건을 갖춘 것이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>대판 2005.3.25. 2003다35659</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="n">
+        <v>428</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>전세권자는 목적물의 통상의 관리에 속한 수선을 할 유지·수선의무를 부담하므로, 유익비상환청구는 가능하나 필요비상환청구권은 없다.</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>비용상환</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>판례는 전세권자가 임차인과 달리 유지·수선의무를 부담하므로 필요비상환청구권이 없고 유익비상환청구만 가능하다고 한다(제310조).</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>민법 제310조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>제310조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="n">
+        <v>429</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>채권담보 목적의 전세권 설정도, 당사자가 장차 목적물의 사용·수익을 완전히 배제하는 것이 아니라면 허용된다.</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>담보전세권</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>판례는 전세권이 용익·담보 성격을 겸비하므로 사용·수익을 완전히 배제하지 않는 한 채권담보 목적의 전세권 설정을 허용한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>대판 1995.2.10. 94다18508</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="n">
+        <v>430</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>건물의 증축부분이 기존 건물에 부합하여 거래상 독립성이 없는 경우, 그 증축부분이 기존 건물에 대한 경매절차에서 목적물로 평가되지 않았더라도 매수인은 그 부분의 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>부합</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>판례는 부합된 증축부분이 평가에서 누락되어도 기존 건물과 함께 경락되므로 매수인이 소유권을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>대판 1981.12.8. 80다2821</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>제256조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="n">
+        <v>431</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>주채권의 양도에 대하여 채권양도의 대항요건을 갖춘 경우, 보증채권에 대하여는 별도로 대항요건을 갖출 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>부종성</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>판례는 보증채무의 부종성·수반성상 주채권 이전 시 보증채권도 함께 이전하고 대항요건도 주채권에 관하여만 구비하면 족하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>대판 2002.9.10. 2002다21509</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n">
+        <v>432</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>임대인이 임대차보증금반환채권의 양도통지를 받은 후에 임대인과 임차인 사이에 임대차계약의 갱신이나 기간 연장에 관한 합의를 하더라도, 그 합의의 효과는 보증금반환채권의 양수인에게 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>대항사유</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>판례는 양도통지 후의 임대차기간 연장 합의는 양수인에게 효력이 없다고 한다(통지 후 생긴 사유로 대항 불가).</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>대판 1989.4.25. 88다카4253</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>제451조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="n">
+        <v>433</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>채권자지체 중에는 이자 있는 채권이라도 채무자는 이자를 지급할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>채권자지체</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>민법 제402조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>민법 제402조</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>제402조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="n">
+        <v>434</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>채권자가 그 채권의 목적인 물건 또는 권리의 가액 전부를 손해배상으로 받은 때에는, 채무자는 그 물건 또는 권리에 관하여 당연히 채권자를 대위한다.</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>손해배상자대위</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>민법 제399조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>민법 제399조</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>제399조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="n">
+        <v>435</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>당사자가 금전이 아닌 것으로써 손해의 배상에 충당할 것을 예정한 경우에도, 위약금은 손해배상액의 예정으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>예정추정</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>민법 제398조 제4항·제5항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>민법 제398조④⑤</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="n">
+        <v>436</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>변제할 정당한 이익이 있는 자가 근저당권의 피담보채무 일부를 대위변제한 경우, 대위변제자는 근저당권 일부이전의 부기등기 경료 여부와 관계없이 변제한 가액의 범위에서 채권 및 담보에 관한 권리를 법률상 당연히 취득하며, 이때에도 채권자는 일부 대위변제자에 대하여 우선변제권을 가진다.</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>일부대위</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>판례는 일부 대위변제 시 대위변제자가 변제 가액 범위에서 권리를 당연 취득하나, 채권자가 잔존 채권에 관하여 우선변제권을 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>대판 2002.7.26. 2001다53929</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>제483조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="n">
+        <v>437</v>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>유치권에 의한 경매는 우선변제를 받기 위한 경매가 아니라 환가를 위한 경매에 불과하므로, 일반채권자의 배당요구도 허용되고 유치권자는 일반채권자와 동일한 순위로 배당을 받는다.</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>매각조건</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>판례는 유치권에 의한 경매도 부담 소멸주의로 진행되고 유치권자가 일반채권자와 동순위로 배당받는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>대결 2011.6.15. 2010마1059</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>제322조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="n">
+        <v>438</v>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>경매절차의 매수인이 유치권자에게 그 유치권으로 담보하는 채권을 변제할 책임이 있다는 것은 부동산상의 부담을 승계한다는 취지이므로, 유치권자는 매수인에 대하여 그 피담보채권의 변제를 직접 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>변제청구</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>판례는 매수인의 변제책임은 부담 승계의 취지일 뿐 인적 채무 인수가 아니므로, 유치권자는 인도를 거절할 수 있을 뿐 변제를 직접 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>대판 1996.8.23. 95다8713</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="n">
+        <v>439</v>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>유치권의 성립요건인 점유는 직접점유이든 간접점유이든 무방하지만, 채무자를 직접점유자로 하는 간접점유는 유치권의 점유로 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>점유형태</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>판례는 채무자를 직접점유자로 하는 간접점유로는 유치권의 점유 요건을 충족하지 못한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>대판 2008.4.11. 2007다27236</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="n">
+        <v>440</v>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>피용자와 제3자가 공동불법행위로 손해를 가하여 사용자가 피용자의 부담부분을 초과하여 피해자에게 손해를 배상한 경우, 사용자는 제3자에 대하여도 그 부담부분 범위 내에서 구상권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>구상범위</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>판례(전합)는 사용자가 제3자와 부진정연대관계에 있으므로 피용자 부담부분 초과 배상 시 제3자에게 그 부담부분 범위에서 구상할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>대판 1992.6.23. 91다33070 전합</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="n">
+        <v>441</v>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>공작물의 설치·보존의 하자로 손해가 발생한 경우, 공작물의 소유자는 직접점유자가 손해 방지에 필요한 주의를 해태하지 않은 경우에 한하여 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>책임순위</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>민법 제758조는 점유자가 1차적 책임을 지고 점유자가 면책되면 소유자가 2차적(무과실) 책임을 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>민법 제758조</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>제758조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="n">
+        <v>442</v>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>불법행위로 재산권이 침해된 경우, 재산적 손해의 배상만으로는 회복할 수 없는 정신적 손해는 특별한 사정으로 인한 손해로서 가해자가 그 사정을 알았거나 알 수 있었을 때에 한하여 배상책임이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>정신적손해</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>판례는 재산권 침해로 인한 정신적 손해를 특별손해로 보아 예견가능성을 요건으로 한다.</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>대판 2004.3.18. 2001다82507 전합 등</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>제751조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="n">
+        <v>443</v>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>인격권 침해에 대하여는 사후적 손해배상 외에 사전적·예방적 구제수단으로 침해행위의 정지·방지 등을 구하는 금지청구권도 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>금지청구</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>판례는 인격권의 침해에 대하여 금지청구권을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>대판 1996.4.12. 93다40614</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>제751조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="n">
+        <v>444</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>채권자가 전득자를 상대로 사해행위취소의 소를 제기한 경우, 취소의 대상이 되는 사해행위는 채무자와 수익자 사이의 법률행위에 국한되고 수익자와 전득자 사이의 법률행위는 취소의 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>취소대상</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>판례는 전득자 상대 취소에서도 취소의 대상은 채무자·수익자 간 법률행위라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>대판 2004.8.30. 2004다21923</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="n">
+        <v>445</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>사해행위가 취소되기 전에 수익자가 경매절차에서 배당금을 현실로 지급받은 경우, 채권자는 원상회복으로서 수익자를 상대로 그 수령한 금원 중 자신의 채권액 상당의 가액배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>가액배상</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>판례는 수익자가 배당금을 현실로 수령한 경우 채권자가 채권액 상당의 가액배상을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>대판 2004.6.25. 2004다9398</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="n">
+        <v>446</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>변제충당은 합의충당, 지정충당, 법정충당의 순서로 이루어지지만, 강제경매나 담보권 실행경매에서는 법정변제충당만 허용된다.</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>충당순서</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>판례는 경매 배당금의 충당에 지정·합의충당이 허용되지 않고 법정변제충당만 허용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>대판 2000.12.8. 2000다51339</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="n">
+        <v>447</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>주채무자 이외의 자가 변제자인 경우에는, 변제자가 발행 또는 배서한 어음에 의하여 담보되는 채무가 다른 채무보다 변제이익이 많다.</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>변제이익</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>판례는 주채무자 외의 변제자의 경우 자신이 어음상 책임을 지는 채무의 변제이익이 더 크다고 본다.</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>대판 1985.3.12. 84다카2093</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>448</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>동산담보권(동산·채권 등의 담보에 관한 법률)이 설정된 담보목적물에 대하여도 선의취득에 관한 민법 규정이 준용되어 선의취득이 가능하다.</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>선의취득</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>동산채권담보법 제32조는 동산담보권이 설정된 담보목적물의 소유권·질권 취득에 민법 제249조 내지 제251조를 준용한다.</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>동산채권담보법 제32조</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>제249조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>449</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>동산에 점유개정의 방법으로 이중의 양도담보를 설정한 경우, 뒤의 양도담보권자가 목적물을 처분하는 것은 원래의 양도담보권자의 담보권을 침해하는 위법한 행위이다.</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>이중양도담보</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>판례는 점유개정으로는 선의취득이 인정되지 않아 뒤의 채권자가 담보권을 취득하지 못하므로, 그 처분이 원래 양도담보권자의 담보권을 침해하는 위법행위가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>대판 2000.6.23. 99다65066</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>제249조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>450</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>과반수 지분의 공유자로부터 공유물의 특정 부분의 사용·수익을 허락받은 점유자에 대하여, 소수지분 공유자는 그 점유자의 건물 철거나 퇴거 등 점유배제를 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>관리행위</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>판례는 과반수 지분권자의 사용·수익 허락이 적법한 관리행위이므로 소수지분권자가 그 점유자의 점유배제를 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>대판 2002.5.14. 2002다9738</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>451</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>채권질권의 효력은 질권의 목적이 된 채권의 지연손해금 등 부대채권에도 미치므로, 채권질권자는 목적 채권과 그에 대한 지연손해금채권을 자기 채권액 부분에 한하여 직접 추심하여 변제에 충당할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>효력범위</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>판례는 금전채권질권의 효력이 부대채권인 지연손해금에도 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>대판 2005.2.25. 2003다40668</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>제353조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>452</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>지명채권을 목적으로 한 질권의 설정은 설정자가 제450조에 따라 제3채무자에게 질권설정의 사실을 통지하거나 제3채무자가 이를 승낙하지 아니하면 제3채무자 기타 제3자에게 대항하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>민법 제349조 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>민법 제349조</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>제349조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>453</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>입질채권의 변제기가 질권의 피보전채권의 변제기보다 먼저 도래하는 경우, 질권자는 제3채무자에 대하여 그 변제금액의 공탁을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>공탁청구</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>민법 제353조 제3항은 입질채권이 먼저 변제기에 도래하면 질권자가 제3채무자에게 공탁을 청구할 수 있다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>민법 제353조③</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>제353조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="n">
+        <v>454</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>계약의 합의해제(해제계약)에는 민법 제543조 이하의 해제 규정이 적용되지 않지만, 제548조 제1항 단서의 제3자 보호규정은 적용될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>적용규정</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>판례는 합의해제가 새로운 계약이어서 법정해제 규정이 적용되지 않으나 제3자 보호규정은 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>대판 2005.6.9. 2005다6341</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>제543조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="n">
+        <v>455</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>계약해제를 주장하며 이미 받은 계약금과 중도금을 공탁하였는데 상대방이 아무런 이의 없이 그 공탁금을 수령하였다면, 특단의 사정이 없는 한 묵시적 합의해제로 인정될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>묵시적해제</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>판례는 일방의 원상회복 공탁을 상대방이 이의 없이 수령하면 묵시적 합의해제가 성립할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>대판 1979.10.10. 79다1457</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>제543조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="n">
+        <v>456</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>가등기담보법은 차용물의 반환에 갈음하여 다른 재산권을 이전할 것을 예약한 경우에 적용되며, 매매대금의 지급을 담보하기 위하여 부동산 소유권을 이전하는 경우에는 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>적용범위</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>판례는 가담법이 (준)소비대차에 기한 채권 담보에만 적용되고 매매대금채무 담보에는 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>대판 2001.1.5. 2000다47682</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="n">
+        <v>457</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>가등기담보권 실행의 통지에는 채권자가 주관적으로 평가한 통지 당시의 목적부동산 가액과 피담보채권액을 명시하여 청산금의 평가액을 통지하면 족하고, 그 평가액이 객관적 청산금에 미치지 못하더라도 통지의 효력이나 청산기간 진행에는 영향이 없다.</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>실행통지</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>판례는 주관적 평가액 통지로 족하고 그 부족이 통지·청산기간 진행에 영향이 없으며, 채무자는 정당한 청산금을 받을 때까지 이행을 거절할 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>대판 1996.7.30. 96다6974</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="n">
+        <v>458</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>부동산 매매에서 목적물의 인도 전이라도 매수인이 매매대금을 완납한 때에는, 그 이후 목적물로부터 생긴 과실은 매수인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>과실귀속</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>판례는 대금 완납 후에는 인도 전이라도 과실수취권이 매수인에게 귀속된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>대판 1993.11.9. 93다28928</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="n">
+        <v>459</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>종물은 동산뿐 아니라 부동산도 될 수 있으며, 종물이 타인의 소유라 하더라도 그 타인의 권리를 해하지 아니하는 범위에서 민법 제100조가 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>종물범위</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>판례는 부동산 종물을 인정하고, 타인 소유 종물의 경우에도 그 권리를 해하지 않는 범위에서 종물 법리를 적용하며 주물 처분 시 동의·추인 또는 선의취득으로 소유권을 취득할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>대판 2008.5.8. 2007다36933 등</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>제100조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="n">
+        <v>460</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>제한능력자의 상대방은 제한능력자가 능력자가 된 후에 1개월 이상의 기간을 정하여 추인 여부의 확답을 촉구할 수 있고, 능력자가 된 사람이 그 기간 내에 확답을 발송하지 아니하면 그 행위를 추인한 것으로 본다.</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>최고권</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>민법 제15조 제1항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>민법 제15조</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>제15조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="n">
+        <v>461</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>제한능력을 이유로 법률행위가 취소된 경우, 제한능력자는 선의·악의를 불문하고 그 행위로 받은 이익이 현존하는 한도에서만 상환할 책임이 있다.</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>반환범위</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>민법 제141조 단서는 제한능력자의 반환범위를 현존이익으로 한정한다(선악 불문).</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>민법 제141조</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>제141조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="n">
+        <v>462</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>매매계약이 사기·강박을 이유로 취소되면 소급적으로 무효가 되므로, 그 계약상 채무불이행을 이유로 한 손해배상책임은 발생하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>취소효과</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>판례는 취소로 계약이 소급적으로 무효가 되면 채무불이행 손해배상책임이 발생하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>민법 제141조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>제141조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="n">
+        <v>463</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>채권양도의 대항요건을 갖추지 못한 상태에서 양수인이 채무자를 상대로 한 재판상 청구도, 소멸시효 중단사유인 재판상 청구에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>중단효력</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>판례는 채권양도로 채권이 동일성을 유지하며 이전되므로 대항요건 미비 양수인의 재판상 청구도 시효중단 사유라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>대판 2005.11.10. 2005다41818</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="n">
+        <v>464</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>악의의 점유자가 권원 없이 타인 소유물을 점유하여 얻은 이익을 반환하는 경우, 받은 이익에 이자를 붙여 반환하여야 할 뿐 아니라 그 이자의 이행지체로 인한 지연손해금도 지급하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>반환범위</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>판례는 악의 수익자의 반환범위가 제748조 제2항에 따라 정해지므로 이자와 그 지연손해금까지 지급해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>대판 2003.11.14. 2001다61869</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>제748조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="n">
+        <v>465</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>불법원인급여 후 급부를 이행받은 자가 별도의 약정으로 그 급부를 반환하기로 약정한 경우, 그 반환약정 자체가 사회질서에 반하여 무효가 되지 않는 한 그 약정은 유효하다.</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>반환약정</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>판례는 불법원인급여 후의 임의 반환약정은 그 자체가 사회질서에 반하지 않는 한 유효하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>대판 2010.5.27. 2009다12580</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="n">
+        <v>466</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>법률행위의 동기가 표시되거나 상대방에게 알려진 동기가 반사회질서적인 경우에는, 그 법률행위에 따른 급여가 불법원인급여에 해당할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>동기불법</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>판례는 표시되거나 알려진 동기가 반사회적이면 그 급여가 불법원인급여가 된다고 한다(동기표시설).</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>판례(동기의 불법과 불법원인급여)</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="n">
+        <v>467</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>어느 연대채무자에 대한 법률행위의 무효나 취소의 원인은 다른 연대채무자의 채무에 영향을 미치지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>독립성</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>민법 제415조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>민법 제415조</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>제415조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="n">
+        <v>468</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>연대채무자 1인의 소유 부동산에 대한 압류로 그 채무자에 대한 채권의 소멸시효가 중단된 경우, 그 압류에 의한 시효중단의 효력은 다른 연대채무자에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>판례는 압류가 제416조(이행청구)와 달리 절대적 효력 사유가 아니므로 1인에 대한 압류의 시효중단 효력이 다른 연대채무자에게 미치지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>대판 2001.8.21. 2001다22840</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>제423조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="n">
+        <v>469</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인이 자신의 채권자에 대한 반대채권으로 상계를 한 경우, 그 상계로 인한 채무소멸의 효력은 소멸한 채무 전액에 관하여 다른 부진정연대채무자에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>절대효</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>판례(전합)는 상계가 변제와 같이 현실적 만족을 주므로 부진정연대채무에서 소멸한 채무 전액에 관하여 다른 채무자에게도 효력이 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>대판 2010.9.16. 2008다97218 전합</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="n">
+        <v>470</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인을 위하여 보증인이 된 자가 그 채무를 변제한 경우, 다른 공동불법행위자에 대하여 그 부담부분에 한하여 구상권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>구상권</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>판례는 공동불법행위자의 보증인이 변제 시 다른 공동불법행위자에게 부담부분 한도에서 구상할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>대판 2008.7.24. 2007다37530</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="n">
+        <v>471</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>상대방 있는 의사표시에서 상대방의 대리인 등 상대방과 동일시할 수 있는 자의 사기·강박은, 민법 제110조 제2항의 제3자에 의한 사기·강박에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>제3자사기</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>판례는 상대방과 동일시할 수 있는 자(대리인 등)의 사기·강박은 제3자 사기가 아니라 상대방의 사기로 보아 곧바로 취소할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>대판 1999.2.23. 98다60828</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>제110조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="n">
+        <v>472</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>임의대리인은 본인의 승낙이 있거나 부득이한 사유가 있는 때에만 복대리인을 선임할 수 있으므로, 이에 반하여 선임된 복대리인의 대리행위는 무권대리에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>복임권</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>민법 제120조는 임의대리인의 복임권을 본인의 승낙 또는 부득이한 사유가 있는 때로 제한한다.</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>민법 제120조</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>제120조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="n">
+        <v>473</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>매매계약 체결의 대리권에는 특별한 사정이 없는 한 중도금 및 잔금에 대한 수령권한이 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>권한범위</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>판례는 매매계약 체결 대리권에 중도금·잔금 수령권한이 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>대판 1992.4.14. 91다43107</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>제114조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="n">
+        <v>474</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>부동산 이중매매에서 제2매수인의 행위가 불법행위가 되려면 단순히 매도인의 배임행위에 가담한 것을 넘어 매도인과 적극 공모하는 등 채권침해의 고의·과실 및 위법성이 인정되어야 한다.</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>채권침해</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>판례는 제3자의 채권침해가 불법행위가 되려면 적극 공모 또는 사회상규에 반하는 부정한 수단 사용 등이 있어야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>대판 2007.9.6. 2005다25021</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>제750조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="n">
+        <v>475</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>부동산 이중매매가 제1매수인에 대한 배임행위로서 반사회적 법률행위에 의한 것이라면, 제1매수인은 매도인을 대위하여 제2매수인 명의 등기의 말소를 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>대위말소</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>판례는 반사회적 이중매매가 무효이므로 제1매수인이 매도인을 대위하여 제2매수인 등기의 말소를 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>대판 1980.5.27. 80다565</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="n">
+        <v>476</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>변시4</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>부동산의 제1매수인은 자신의 소유권이전등기청구권을 보전하기 위하여 매도인과 제2매수인 사이의 이중양도행위에 대하여 채권자취소권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>피보전채권</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>판례는 채권자취소권은 금전채권 보전을 위한 것이므로 특정물에 대한 소유권이전등기청구권 보전을 위해서는 행사할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>대판 1999.4.27. 98다56690</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1144"/>
+  <dimension ref="A1:H1217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -46224,6 +46224,2926 @@
         </is>
       </c>
     </row>
+    <row r="1145">
+      <c r="A1145" t="n">
+        <v>301</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>매매계약이 합의해제된 경우 매도인의 원상회복청구권은 소유권에 기한 물권적 청구권이므로, 소멸시효의 대상이 되지 아니한다.</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>시효대상</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>판례는 합의해제 시 소유권이 매도인에게 복귀하므로 원상회복청구권이 물권적 청구권이어서 소멸시효에 걸리지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>대판 1982.7.27. 80다2968</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>제213조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="n">
+        <v>302</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>송전선이 토지 위를 통과하고 있다는 점을 알고서 토지를 취득한 경우, 그 취득자는 소유권 행사가 제한된 상태를 용인한 것이므로 송전선 철거 청구는 신의칙에 반한다.</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>신의칙</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>판례는 방해 사실을 알고 취득하였다는 점만으로 소유권 행사 제한을 용인한 것이 아니므로 철거 청구가 신의칙에 반하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>대판 1995.8.25. 94다27069</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="n">
+        <v>303</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>실효의 원칙을 적용함에 있어 종전 토지 소유자가 자신의 권리를 행사하지 않았다는 사정은, 그 토지의 소유권을 적법하게 취득한 새로운 권리자에게 실효의 원칙을 적용할 때 고려할 사정이 아니다.</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>실효</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>판례는 전 소유자의 권리 불행사 사정이 새 권리자에 대한 실효 원칙 적용에서 고려되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>대판 1995.8.25. 94다27069</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="n">
+        <v>304</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>권리행사가 권리남용이 되려면 객관적으로 권리행사가 사회질서에 위반되고, 주관적으로 권리행사의 목적이 오직 상대방에게 고통을 주고 손해를 입히려는 데 있을 뿐 권리자에게 아무런 이익이 없어야 하며, 그 주관적 요건은 객관적 사정에 의하여 추인할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>남용요건</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>판례는 권리남용의 객관적·주관적 요건을 제시하고 주관적 요건의 객관적 추인을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>대판 2003.2.14. 2002다62319</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>제2조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="n">
+        <v>305</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>통정허위표시에 기한 채무를 보증하고 그 보증채무를 이행한 보증인은, 민법 제108조 제2항의 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>판례는 허위표시에 기초하여 구상권 취득의 이해관계를 가지게 된 보증인을 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>대판 2000.7.6. 99다51258</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="n">
+        <v>306</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>통정허위표시인 채권양도계약에서 양수인에게 아직 채무를 변제하지 않은 채무자는, 그 허위표시의 무효로 대항받지 않는 선의의 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>판례는 양도계약이 허위표시임이 밝혀진 이상 미변제 채무자는 선의의 제3자임을 내세워 진정한 채권자에게 지급을 거절할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>대판 1983.1.18. 82다594</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="n">
+        <v>307</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>가장소비대차계약에 기해 발생한 가장채권을 양수한 한국자산관리공사는, 민법 제108조 제2항의 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>제3자범위</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>판례는 부실채권을 유상으로 인수하며 새로운 이해관계를 맺은 자산관리공사를 허위표시의 제3자로 본다.</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>대판 2004.1.15. 2002다31537</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="n">
+        <v>308</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>법인 대표자의 업무에 관한 포괄적 위임과 그에 따른 수임인의 대행행위는 민법 제62조에 위반되어 법인에 대하여 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>복임제한</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>판례는 대표자가 특정행위만 대리하게 할 수 있을 뿐 업무를 포괄적으로 위임할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>민법 제62조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>제62조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="n">
+        <v>309</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>법인의 불법행위책임에 관한 민법 제35조의 '대표자'에는 명칭이나 등기 여부를 불문하고 당해 법인을 실질적으로 운영하면서 법인을 사실상 대표하여 사무를 집행하는 사람도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>대표자범위</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>판례는 제35조의 대표자에 등기 여부와 무관하게 사실상 대표자도 포함되며 이는 비법인사단에도 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>대판 2011.4.28. 2008다15438</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n">
+        <v>310</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>법인 대표자의 행위가 외형상 직무행위로 인정되는 것이라면, 그것이 대표자 개인의 사리를 도모하기 위한 것이거나 법령에 위배된 것이라도 제35조의 직무에 관한 행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>외형이론</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>판례는 직무관련성을 외형이론에 따라 판단한다.</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>대판 2004.2.27. 2003다15280</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="n">
+        <v>311</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>법인 대표자의 행위가 직무에 관한 행위에 해당하지 아니함을 피해자 자신이 알았거나 중대한 과실로 알지 못한 경우에는, 법인에게 손해배상책임을 물을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>악의중과실</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>판례는 외형이론에도 불구하고 피해자의 악의·중과실이 있으면 법인의 불법행위책임이 부정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>대판 2004.3.26. 2003다34045</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="n">
+        <v>312</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>법정대리인이 미성년자에게 어떠한 재산에 대한 처분을 허락하였더라도, 법정대리인의 그 재산에 대한 처분 대리권은 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>대리권존속</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>판례·통설은 처분 허락으로 미성년자에게 행위능력이 생기는 것이 아니므로 법정대리인의 처분 대리권이 소멸하지 않고 병존한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>민법 제6조 · 통설</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>제6조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="n">
+        <v>313</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>미성년자가 법정대리인으로부터 허락을 얻은 특정한 영업에 관하여는 성년자와 동일한 행위능력이 있으므로, 그 영업에 관하여는 법정대리인의 동의권과 대리권이 모두 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>영업허락</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>통설은 제8조 제1항의 영업허락 시 그 영업에 관한 법정대리인의 동의권·대리권이 소멸한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>민법 제8조 · 통설</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>제8조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="n">
+        <v>314</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>미성년후견인은 한 명으로 하여야 하지만, 성년후견인은 여러 명을 둘 수 있고 법인도 성년후견인이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>수와자격</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>민법 제930조의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>민법 제930조</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>제930조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="n">
+        <v>315</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>후견인과 피후견인 사이에 이해상반행위가 있는 경우 특별대리인을 선임하여야 하지만, 후견감독인이 있는 경우에는 특별대리인을 선임할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>민법 제949조의3은 후견감독인이 있는 경우 그가 피후견인을 대리하므로 특별대리인 선임이 필요 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>민법 제949조의3</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>제949조의3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>316</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>피성년후견인의 법률행위는 성년후견인의 동의가 있었더라도 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>취소가부</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>민법 제10조상 피성년후견인의 법률행위는 동의 유무와 관계없이 취소할 수 있다(일용품 구입 등 예외 제외).</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>민법 제10조</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>제10조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>317</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>본인이 무권대리인에게 무권대리행위를 추인한 경우, 상대방이 그 추인 사실을 알지 못하는 동안에는 상대방은 여전히 철회를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>추인상대방</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>판례는 제132조상 무권대리인에 대한 추인은 상대방이 알지 못하는 동안에는 상대방에게 대항하지 못하므로 상대방이 철회할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>대판 1981.4.14. 80다2314</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>제132조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>318</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>피보험자의 서면 동의를 결여한 타인의 생명보험계약은 강행규정 위반으로 확정적 무효이므로, 사후에 동의가 있더라도 추인에 의하여 유효로 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>강행규정</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>판례는 상법 제731조 위반의 타인 생명보험계약을 확정적 무효로 보아 추인을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>대판 2006.9.22. 2004다56677</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>제139조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>319</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>무효인 소송행위를 추인하는 경우에는 추인의 소급효를 제한하는 민법 제133조 단서가 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>소송행위추인</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>판례는 소송행위 추인에는 제133조 단서(제3자 권리 보호)가 적용되지 않고 전체적으로 소급하여 유효하게 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>대판 1997.3.14. 96다25227</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>제133조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>320</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>재단법인 설립을 위하여 출연한 재산이 지명채권인 경우, 견해 대립 없이 법인이 성립한 때에 법인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>귀속시기</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>판례·통설은 지명채권은 별도의 공시방법이 필요 없어 제48조에 따라 법인 성립 시 귀속된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>민법 제48조</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>제48조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>321</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>생전처분으로 재단법인을 설립하는 경우, 출연재산이 부동산인 때에는 출연자와 법인 사이의 관계에서는 법인 성립 외에 등기를 필요로 하지 않으나, 제3자에 대한 관계에서는 등기를 갖추어야 법인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>절충설</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>판례(절충설)는 출연자-법인 사이에서는 법인 성립 시 귀속하지만 제3자에 대한 관계에서는 등기를 갖추어야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>대판 1979.12.11. 78다481 전합 · 대판 1993.9.14. 93다8054</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>제48조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>322</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>친양자를 입양하려는 사람은 원칙적으로 3년 이상 혼인 중인 부부로서 공동으로 입양하여야 하지만, 1년 이상 혼인 중인 부부의 한쪽이 그 배우자의 친생자를 친양자로 하는 경우에는 그러하지 아니하다.</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>입양요건</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>민법 제908조의2 제1항 제1호의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>민법 제908조의2</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>제908조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>323</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>친양자가 될 사람은 미성년자여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>입양요건</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>민법 제908조의2 제1항 제2호의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>민법 제908조의2</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>제908조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>324</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>친양자 입양에서도 일반입양과 마찬가지로 일정한 사유가 있는 때에는 가정법원은 친생부모의 동의가 없어도 친양자 입양을 허가하는 심판을 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>동의예외</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>민법 제908조의2 제2항은 법정대리인의 부당한 동의·승낙 거부, 친생부모의 부양·면접교섭 불이행, 학대·유기 등의 경우 동의 없이도 인용할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>민법 제908조의2②</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>제908조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>325</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>친양자 입양의 취소는 소급효가 없다.</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>취소효과</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>민법 제908조의7은 친양자 입양 취소·파양의 효력이 소급하지 않고 장래에 향하여만 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>민법 제908조의7</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>제908조의7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>326</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>혼인 중 부부 일방이 사망하여 상대방이 배우자로서 상속받은 후 그 혼인이 취소되었더라도, 혼인취소는 소급효가 없으므로 그 전에 이루어진 상속관계가 소급하여 무효가 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>소급효</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>판례는 민법 제824조상 혼인취소의 소급효가 없으므로 상속이 유효하게 유지된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>대판 1996.12.23. 95다48308</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>제824조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>327</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>인지청구의 소에 의하여 상속인이 된 자가 상속회복청구를 하는 경우, 제척기간의 기산점이 되는 '상속권 침해를 안 날'은 인지심판 확정일이다.</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>판례는 사후 인지된 자의 상속회복청구권 제척기간 기산점을 인지심판 확정일로 본다.</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>대판 2007.10.25. 2007다36223</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>제999조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>328</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>대습상속에서 피대습자는 피상속인의 직계비속 또는 형제자매에 한정되므로, 피상속인의 배우자는 피대습자가 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>피대습자</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>민법 제1001조는 직계비속·형제자매를 피대습자로 정하므로 배우자는 피대습자가 될 수 없다(다만 배우자는 대습상속인은 될 수 있음).</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>민법 제1001조</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>제1001조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>329</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>상속포기는 대습상속의 원인이 된다.</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>대습원인</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>민법 제1001조의 대습상속 원인은 상속인의 사망 또는 결격이고, 상속포기는 대습상속의 원인이 아니다.</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>민법 제1001조</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>제1001조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>330</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>근저당권 설정 후 경매로 인한 압류의 효력이 발생하기 전에 취득한 유치권으로는 경매절차의 매수인에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>대항시점</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>판례는 압류 전 취득한 유치권은 선행 근저당권이 있어도 매수인에게 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>대판 2009.1.15. 2008다70763</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>331</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>부동산 매도인이 매매대금을 다 지급받지 않은 상태에서 매수인에게 소유권이전등기를 마쳐주고 부동산을 계속 점유하는 경우, 매매대금채권을 피담보채권으로 하여 그 부동산의 소유권을 취득한 제3자에게 유치권을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>견련성</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>판례는 매매대금채권은 매매목적물에 관하여 생긴 채권이 아니어서 견련성이 없으므로 유치권이 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>대판 2012.1.12. 2011마2380</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>332</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>저당부동산의 제3취득자가 저당권의 피담보채무를 변제하고 저당권의 소멸을 청구하는 것은, 경매신청이 있은 후라도 그 매각이 종료되기 전까지는 허용된다.</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>변제시기</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>통설은 제3취득자의 변제가 경매신청 전후를 불문하고 매각 종료 전까지 허용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>민법 제364조 · 통설</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>제364조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>333</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>후순위 저당권자는 민법 제364조의 제3취득자에 해당하여 저당권 소멸을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>제3취득자</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>판례는 후순위 저당권자는 제364조의 '소유권·지상권·전세권을 취득한 제3취득자'에 해당하지 않으므로 저당권 소멸청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>대판 2006.1.26. 2005다17341</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>제364조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>334</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>공동저당의 목적인 채무자 소유 부동산과 물상보증인 소유 부동산을 동시에 경매하여 배당하는 경우, 민법 제368조 제1항이 적용되어 각 부동산 경매대가에 비례하여 채권 분담을 정한다.</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>동시배당</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>판례는 이 경우 물상보증인의 변제자대위 보호를 위해 제368조 제1항이 적용되지 않고 채무자 소유 부동산에서 우선 배당한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>대판 2010.4.15. 2008다41475</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>335</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>공동저당에서 '각 부동산의 경매대가'란 매각대금에서 당해 부동산이 부담할 경매비용과 선순위채권을 공제한 잔액을 의미한다.</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>경매대가</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>판례는 제368조 제1항의 경매대가를 경매비용·선순위채권 공제 후의 잔액으로 본다.</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>대판 2003.9.5. 2001다66291</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>336</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>가등기가 경료된 부동산에 점유취득시효가 완성된 후 그 가등기에 기한 본등기가 경료된 경우, 시효완성 후의 취득자인지 여부는 본등기 시를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>기준시점</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>판례는 가등기는 순위보전 효력만 있고 본등기 시 물권변동 효력이 발생하므로 시효완성 후 취득자 판단을 본등기 시 기준으로 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>대판 1992.9.25. 92다21258</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>337</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>토지의 점유자가 소유자를 상대로 매매를 원인으로 한 소유권이전등기청구소송을 제기하였다가 패소하고 그 판결이 확정되었다는 사정만으로는, 그 점유가 자주점유에서 타주점유로 전환되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>점유전환</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>판례는 이전등기청구 패소 확정만으로는 자주점유 추정이 번복되어 타주점유로 전환되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>대판 2009.12.10. 2006다19177</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>제197조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>338</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>취득시효가 완성된 후 소유권이전등기의무가 이행불능이 된 경우, 시효취득자는 부동산 소유자에 대하여 채무불이행을 원인으로 한 손해배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>손해배상</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>판례는 부동산 소유자와 시효취득자 사이에 계약상 채권채무관계가 성립하는 것이 아니므로 채무불이행을 원인으로 한 손해배상을 청구할 수 없다고 한다(불법행위 책임은 별론).</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>대판 1995.7.11. 94다4509</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="n">
+        <v>339</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>악의의 점유자는 수취한 과실을 반환하여야 하며, 소비하였거나 과실로 인하여 훼손 또는 수취하지 못한 경우에는 그 과실의 대가를 보상하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>과실반환</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>민법 제201조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>민법 제201조②</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>제201조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="n">
+        <v>340</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>점유물이 점유자의 책임 있는 사유로 멸실·훼손된 경우, 소유의 의사가 없는 점유자는 선의인 경우에도 손해의 전부를 배상하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>배상범위</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>민법 제202조의 명문 규정으로, 타주점유자는 선의라도 전부 배상한다.</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>민법 제202조</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>제202조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="n">
+        <v>341</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>점유자가 점유물을 보존하기 위하여 지출한 필요비의 상환을 청구할 수 있으나, 점유자가 과실을 취득한 경우에는 통상의 필요비는 청구하지 못한다.</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>상환제한</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>민법 제203조 제1항 단서의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>민법 제203조①</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>제203조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="n">
+        <v>342</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>공유토지의 1/2 지분권자가 다른 공유자와 협의 없이 단독으로 토지 전부를 제3자에게 임대한 경우, 다른 소수지분권자는 공유물의 보존행위로서 임차인에 대하여 토지 전부의 인도를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>보존행위</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소수지분권자가 보존행위로서 인도를 청구할 수 없고 자신의 지분권에 기초하여 방해 상태 제거나 방해행위 금지를 청구할 수 있을 뿐이라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>대판 2020.5.21. 2018다287522 전합</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="n">
+        <v>343</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>부동산 공유자 중 1인은 자신의 공유지분이 아닌 다른 공유자의 공유지분을 침해하는 제3자 명의의 원인무효 등기에 대하여, 공유물의 보존행위로서 그 부분 등기의 말소를 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>보존행위</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>판례는 다른 공유자의 지분을 침해하는 등기의 말소는 그 지분권자가 구할 수 있을 뿐 보존행위로 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>대판 1994.11.11. 94다35008</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="n">
+        <v>344</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>채무자가 횡령한 금전을 채권자에 대한 채무변제에 사용한 경우, 채권자가 그 금전이 횡령된 것임에 대하여 단순한 과실이 있는 경우에는 피해자가 채권자에게 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>악의중과실</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>판례는 채권자에게 악의 또는 중대한 과실이 없는 한 그 변제 수령에 법률상 원인이 있어 부당이득이 되지 않으므로, 단순 과실만으로는 부당이득반환을 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>대판 2008.3.13. 2006다53733</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="n">
+        <v>345</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>취득시효 완성 후 등기명의인이 설정한 저당권의 피담보채무를 시효완성자가 변제한 경우, 시효완성자는 원소유자에게 대위변제를 이유로 구상권을 행사하거나 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>용인부담</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>판례는 그 변제가 시효취득자가 용인해야 할 부담을 제거하여 완전한 소유권을 확보하기 위한 자기 이익을 위한 행위이므로 구상권·부당이득반환청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>대판 2006.5.12. 2005다75910</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="n">
+        <v>346</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>토지에 대하여 가압류가 집행된 후 그 토지가 수용되어 가압류의 효력이 소멸한 경우, 토지소유자가 받은 보상금은 법률상 원인이 없는 부당이득에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>법률상원인</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>판례는 토지소유자가 받은 수용보상금은 법률상 원인이 있으므로 부당이득이 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>대판 2009.9.10. 2006다61536</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="n">
+        <v>347</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>법인의 대표자가 법인에게 불법행위를 한 경우 그 손해배상청구권의 단기소멸시효는, 법인의 이익을 정당하게 보전할 권한을 가진 다른 임원·사원·직원 등이 손해배상청구권을 행사할 수 있을 정도로 이를 안 때부터 진행한다.</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>기산점</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>판례는 대표자가 가해자인 경우 그 대표자의 인식이 아니라 법인의 이익을 보전할 다른 자의 인식을 기준으로 시효 기산점을 정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>대판 2002.6.14. 2002다11441</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>제766조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="n">
+        <v>348</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>파견근로자가 사용사업주의 구체적인 지시·감독을 받아 사용사업주의 업무를 행하던 중 불법행위를 한 경우, 파견사업주가 파견근로자의 선발 및 일반적 지휘·감독에 주의를 다하였다고 인정되면 파견사업주는 사용자책임을 면할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>파견근로</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>판례는 원칙적으로 파견사업주가 사용자책임을 지나, 사용사업주의 구체적 지시·감독 중의 불법행위에서 파견사업주가 선발·일반적 감독에 주의를 다하면 면책될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>대판 2003.10.9. 2001다24655</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>제756조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="n">
+        <v>349</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>호의동승은 그 자체만으로 손해배상액의 감경사유가 된다.</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>호의동승</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>판례는 단순한 호의동승 사실만으로는 배상액 감경사유가 되지 않고, 운행 목적·동승 경위 등에 비추어 신의칙·형평상 부당한 경우에 한하여 감경할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>대판 1992.5.12. 91다40993</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>제763조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="n">
+        <v>350</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>수급인이 자기의 노력과 재료로 건물을 신축한 경우 원칙적으로 수급인이 원시취득하지만, 도급인 명의로 건축허가·보존등기를 하기로 하는 등 완성된 건물의 소유권을 도급인에게 귀속시키기로 합의한 경우에는 도급인에게 원시적으로 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>소유귀속</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>판례는 신축건물의 원시취득자를 원칙적으로 수급인으로 보되 귀속 합의가 있으면 도급인이 원시취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>대판 2005.11.25. 2004다36352</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>제664조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="n">
+        <v>351</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>수급인의 하자담보책임은 법이 특별히 인정한 무과실책임이므로 민법 제396조의 과실상계 규정이 준용되지 않지만, 공평의 원칙상 하자 발생 및 확대에 가공한 도급인의 잘못을 참작할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>과실참작</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>판례는 무과실책임인 하자담보책임에 과실상계가 준용되지 않으나 손해배상 범위 산정에서 도급인의 잘못을 참작할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>대판 2004.8.20. 2001다70337</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>제667조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="n">
+        <v>352</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>제3자를 위한 도급계약에서 수익의 의사표시를 한 수익자는, 요약자가 낙약자의 채무불이행을 이유로 계약을 해제한 경우 낙약자에게 자기가 입은 손해의 배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>수익자손해배상</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>판례는 수익의 의사표시를 한 제3자가 낙약자의 채무불이행으로 입은 손해의 배상을 낙약자에게 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>대판 1994.8.12. 92다41559</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>제539조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="n">
+        <v>353</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>임차인의 채무불이행으로 임대차계약이 해지된 경우, 임차인은 부속물매수청구권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>채무불이행</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>판례는 임차인의 채무불이행으로 인한 해지의 경우 부속물매수청구권이 인정되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>대판 1990.1.23. 88다카7245</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>제646조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="n">
+        <v>354</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>권리금이 일정 기간 이상 임차권을 보장하는 약정 하에 지급된 경우, 그 보장기간 동안의 이용이 유효하게 이루어졌다면 임대인은 권리금의 반환의무를 지지 않지만, 임대인의 사정으로 중도 해지되면 임대인은 권리금의 반환의무를 진다.</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>권리금</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>판례는 임차권 보장 약정 하의 권리금에서 보장기간 이용이 이루어지면 반환의무가 없으나, 임대인의 사정으로 중도 해지되면 잔여기간에 상응하는 반환의무를 진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>대판 2002.7.26. 2002다25013</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n">
+        <v>355</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>지상물매수청구권의 대상이 되는 건물은 반드시 임대차계약 당시의 기존 건물이거나 임대인의 동의를 얻어 신축한 것에 한정되며, 무허가건물은 그 대상이 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>매수청구</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>판례는 지상물매수청구권의 공익적 목적상 임대차 당시의 기존 건물이나 임대인 동의를 얻은 신축 건물에 한정되지 않고 무허가건물도 그 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>대판 1993.11.12. 93다34589 등</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="n">
+        <v>356</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>매도인이 매수인에 대하여 매매계약의 이행을 최고하고 매매잔대금의 지급을 구하는 소송을 제기한 것만으로는, 민법 제565조의 이행에 착수하였다고 볼 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>이행착수</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>판례는 이행청구·대금 지급 소송 제기만으로는 이행의 착수가 아니므로 해약금 해제가 여전히 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>대판 2008.10.23. 2007다72274</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>제565조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="n">
+        <v>357</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>부동산 매매계약 체결 후 매수인 앞으로 이전등기를 마치기 전에 제3자가 그 부동산을 다시 매수하여 처분금지가처분등기를 한 상태에서 매매계약이 해제된 경우, 가처분등기의 말소와 매도인의 대금반환의무는 동시이행관계에 있지 않다.</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>동시이행</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>판례는 가처분등기 말소의무와 매도인의 대금반환의무 사이에 견련관계가 없어 동시이행관계가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>대판 2009.7.9. 2009다18526</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="n">
+        <v>358</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>민법 제450조 제2항의 채권양도의 제3자에 대한 대항요건은 양도된 채권이 존속하는 동안 양수인의 지위와 양립할 수 없는 법률상 지위를 취득한 제3자가 있는 경우에 적용되므로, 양도된 채권이 이미 변제로 소멸한 경우에는 문제되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>대항요건</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>판례는 채권이 변제로 소멸한 경우 대항요건의 우열 문제가 발생하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>대판 2003.10.24. 2003다37426</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="n">
+        <v>359</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>연대채무자 1인에 대한 이행청구는 다른 연대채무자에게도 효력이 있으므로, 그 이행청구로 인한 이행지체의 효과도 다른 연대채무자에게 미친다.</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>절대효</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>판례는 제416조에 따라 연대채무자 1인에 대한 이행청구가 절대효를 가지므로 그로 인한 이행지체도 다른 연대채무자에게 효력이 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>민법 제416조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>제416조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="n">
+        <v>360</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>채권자대위권 행사의 통지를 받은 후 또는 채무자가 대위권 행사 사실을 안 후에도, 채무자가 자신의 명의로 소유권이전등기를 경료하는 것은 처분행위가 아니므로 채권자에게 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>처분해당성</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 변제수령이나 소유권이전등기 경료는 처분행위가 아니어서 대위권 행사 통지 후에도 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>대판 1991.4.12. 90다9407</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>제405조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="n">
+        <v>361</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>보증한도액을 정한 근보증에서 보증채무는 특별한 사정이 없는 한 보증한도 범위 안에서 확정된 주채무 및 그 이자, 위약금, 손해배상 기타 주채무에 종속한 채무를 모두 포함한다.</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>보증범위</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>판례는 근보증의 보증한도액에 주채무의 이자·위약금·손해배상 등 종속채무가 모두 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>대판 2000.4.11. 99다12123</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>제429조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="n">
+        <v>362</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>주채무자가 채무를 승인하여 소멸시효가 중단된 경우, 그 시효중단의 효력은 보증인에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>중단효력</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>민법 제440조는 주채무자에 대한 시효중단이 보증인에게도 효력이 있다고 정한다.</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>민법 제440조</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>제440조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="n">
+        <v>363</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>채권자취소소송에서 피보전채권의 존재는 본안판단 사항이므로 피보전채권이 인정되지 않으면 청구를 기각하지만, 채권자대위소송에서 피보전채권은 당사자적격의 문제이므로 인정되지 않으면 소를 각하한다.</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>소송요건</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>판례는 채권자취소소송의 피보전채권을 본안사항(기각), 채권자대위소송의 피보전채권을 소송요건(각하)으로 구별한다.</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>대판 2008.2.15. 2006다26243 등</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="n">
+        <v>364</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>저당권이 설정된 부동산에 관하여 사해행위가 이루어진 후 변제 등으로 저당권설정등기가 말소된 경우, 채권자는 부동산 자체의 회복이 아니라 부동산 가액에서 피담보채무액을 공제한 잔액의 한도에서 사해행위를 취소하고 가액배상을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>가액배상</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>판례는 사해행위 후 저당권이 말소된 경우 원물반환은 공평에 반하므로 가액배상에 의하도록 한다.</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>대판 1998.2.13. 97다6711</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="n">
+        <v>365</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>채권자취소권은 취소원인을 안 날로부터 1년, 법률행위가 있은 날로부터 5년 내에 행사하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>제척기간</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>민법 제406조 제2항의 명문 규정이다.</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>민법 제406조②</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="n">
+        <v>366</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>채권자가 수익자를 상대로 사해행위 취소를 구하여 승소판결이 확정된 경우, 그 판결의 효력은 소송 당사자가 아닌 전득자에게도 미친다.</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>상대효</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>판례는 취소판결의 효력이 소송 당사자가 아닌 전득자에게 미치지 않으므로, 전득자에 대해서는 별도로 제406조 제2항의 기간 내에 채무자·수익자 간 사해행위 취소의 소를 제기해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>대판 2004.8.30. 2004다21923</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="n">
+        <v>367</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>변제할 정당한 이익이 있는 자가 근저당권의 피담보채무 일부를 대위변제한 경우, 대위변제자는 근저당권 일부이전의 부기등기 경료 여부와 관계없이 변제한 가액 범위에서 채권 및 담보에 관한 권리를 법률상 당연히 취득하며, 이때에도 채권자는 일부 대위변제자에 대하여 우선변제권을 가진다.</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>일부대위</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>판례는 일부 대위변제 시 부기등기 여부와 무관하게 권리를 당연 취득하나 채권자가 잔존 채권에 관하여 우선변제권을 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>대판 2002.7.26. 2001다53929</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>제483조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="n">
+        <v>368</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>저당물의 후순위 근저당권자는 민법 제482조 제2항 제2호의 '제3취득자'에 포함되지 않으므로, 후순위 근저당권자는 보증인에 대하여 채권자를 대위할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>대위관계</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>판례는 후순위 근저당권자가 제482조 제2항 제2호의 제3취득자에 포함되지 않으므로, 오히려 저당물의 후순위 근저당권자가 보증인에 대하여 채권자를 대위할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>대판 2013.2.15. 2012다48855</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>제482조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="n">
+        <v>369</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>보증인은 미리 저당권의 등기에 그 대위를 부기하지 않고서도, 저당물에 후순위 근저당권을 취득한 제3자에 대하여 채권자를 대위할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>대위관계</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>판례는 후순위 근저당권자가 제482조 제2항 제1호의 '제3자'에 포함되지 않으므로 보증인이 부기등기 없이도 그에 대하여 채권자를 대위할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>대판 2013.2.15. 2012다48855</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>제482조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="n">
+        <v>370</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>제3자의 변제에서 이해관계 있는 제3자란 변제하지 않으면 채권자로부터 집행을 받거나 채무자에 대한 자기의 권리를 잃게 되는 지위에 있어 변제할 정당한 이익이 있는 자를 말하며, 물상보증인·담보물의 제3취득자 등이 이에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>이해관계인</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>판례는 이해관계 있는 제3자를 변제할 정당한 이익이 있는 자로 보고 물상보증인·제3취득자 등을 포함한다.</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>민법 제469조·제481조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>제469조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="n">
+        <v>371</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>매매계약상 금전채무자가 채권자의 지시에 따라 채권자의 채권자에게 직접 금전을 지급한 단축급부에서 매매계약이 무효·해제된 경우, 금전채무자는 매매계약의 상대방인 채권자에게 부당이득반환을 구할 수 있을 뿐 그 채권자의 채권자에게는 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>삼각관계</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>판례는 단축급부 시 급부가 계약당사자 간에 이루어진 것이므로 제3자가 아닌 계약 상대방에게 부당이득반환을 구해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>대판 2003.12.26. 2001다46730</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="n">
+        <v>372</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>인지 전에 공동상속인들에 의하여 이미 분할되거나 처분된 상속재산은, 분할받은 공동상속인이나 그로부터 양수한 자에게 소유권이 확정적으로 귀속되고, 사후 인지된 자는 가액의 지급을 청구할 수 있을 뿐이다.</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>인지후분할</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>판례는 제1014조에 따라 인지 전 분할·처분의 효력을 인정하고 사후 인지자에게는 가액지급청구권만 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>민법 제1014조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>제1014조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n">
+        <v>373</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>변시3</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>친권자가 수인의 미성년 자녀의 법정대리인으로서 상속재산 분할협의를 한 경우, 그 분할협의는 피대리자 전원에 의한 추인이 없는 한 무효이다.</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>이해상반</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>판례는 공동상속인인 친권자와 여러 미성년 자녀 사이의 분할협의가 이해상반행위이므로 각자 특별대리인을 선임해야 하고 위반 시 전원 추인 없으면 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>대판 1994.9.9. 94다6680</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>제921조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1217"/>
+  <dimension ref="A1:H1283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -49144,6 +49144,2646 @@
         </is>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" t="n">
+        <v>201</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>재단법인의 기존 기본재산을 처분하는 행위뿐만 아니라 새로이 기본재산으로 편입하는 행위도 정관변경을 초래하므로 주무관청의 허가가 있어야 유효하다.</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>기본재산</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>판례는 기본재산의 편입·처분 모두 정관변경사항이어서 주무관청 허가를 받아야 효력이 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>대판 1982.9.28. 82다카499</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>제42조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="n">
+        <v>202</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>비법인사단의 총유재산 보존을 위한 소송은 그 대표자가 개인 자격으로 당사자가 되어 제기하면 충분하고, 사원총회의 결의나 구성원 전원의 참여는 필요하지 않다.</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>총유보존</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>총유재산에 관한 소송은 사원총회 결의를 거쳐 사단 명의로 하거나 구성원 전원이 필수적 공동소송 형태로 제기해야 하고, 대표자 개인은 당사자가 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>대판(전) 2005.9.15. 2004다44971</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="n">
+        <v>203</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>통정허위표시에 의하여 외형상 형성된 법률관계를 토대로 새로 그 채권을 가압류한 자도 민법 제108조 제2항의 보호받는 선의의 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>허위표시제3자</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>판례는 허위표시에 기한 채권을 가압류한 자도 새로운 이해관계를 맺은 선의의 제3자로 보호된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>대판 2004.5.28. 2003다70041</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="n">
+        <v>204</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>제3자의 사기로 의사표시를 한 자는 그 계약을 취소하지 않고서도 제3자에 대하여 불법행위를 원인으로 한 손해배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>제3자사기</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>판례는 계약을 취소하지 않더라도 제3자의 기망으로 인한 손해에 관하여 불법행위 손해배상을 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>대판 1998.3.10. 97다55829</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>제110조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="n">
+        <v>205</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>통정허위표시에서 파산관재인이 민법 제108조 제2항의 제3자에 해당하는 경우, 그 선의·악의는 파산관재인 개인을 기준으로 판단하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>파산관재인</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>파산관재인은 총파산채권자를 대표하므로 선의 여부는 파산관재인 개인이 아니라 총파산채권자를 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>대판(전) 2006.11.23. 2004다3925</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="n">
+        <v>206</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>매매계약 체결에 관한 포괄적 대리권을 수여받은 대리인은 그 매매대금 지급기일을 연기하여 줄 권한도 가진다.</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>대리권범위</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>판례는 매매계약 체결의 포괄적 대리권에는 대금지급기일 연기 권한도 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>대판 1992.4.14. 91다43107</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>제118조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="n">
+        <v>207</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>대리인이 상대방에게 기망행위를 한 경우, 대리인은 민법 제110조 제2항의 '제3자'에 해당하므로 본인이 그 사실을 몰랐다면 상대방은 의사표시를 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>대리인사기</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>대리인은 제110조 제2항의 제3자에 해당하지 않으므로, 대리인의 기망이 있으면 본인의 선의 여부와 무관하게 상대방은 의사표시를 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>대판 1998.1.23. 96다41496</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>제110조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="n">
+        <v>208</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>선의의 점유자라도 본권에 관한 소에서 패소한 때에는 그 소가 제기된 때부터 악의의 점유자로 본다.</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>악의의제</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>민법 제197조 제2항에 따라 선의 점유자도 본권의 소에서 패소하면 소 제기 시부터 악의 점유자로 간주된다.</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>민법 제197조 제2항</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>제197조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="n">
+        <v>209</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성된 점유자는 아직 소유권이전등기를 마치기 전이라도 소유자를 상대로 소유권확인의 소를 제기하여 승소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>시효완성확인</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성되어도 등기 전에는 소유권을 취득하지 못하므로 소유권확인소송에서 승소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>민법 제245조 제1항 · 판례</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="n">
+        <v>210</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>점유취득시효기간이 만료된 후에 그 토지의 소유권을 취득한 제3자에 대하여, 시효완성자는 등기 없이도 시효취득을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>시효후취득자</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>시효완성 후 등기 전에 소유권을 취득한 제3자에게는 시효취득을 주장할 수 없다(이중매매 법리와 유사).</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>대판 1998.7.10. 97다45402</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="n">
+        <v>211</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>매매 등 쌍무계약이 불공정한 법률행위에 해당하여 무효인 경우, 그 계약에 관하여 별도로 체결한 부제소합의도 무효이다.</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>불공정합의</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>판례는 불공정한 법률행위로 무효인 계약에 부수된 부제소합의 역시 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>대판 2010.7.15. 2009다50308</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="n">
+        <v>212</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>무효인 가등기를 유효한 등기로 전용하기로 하는 약정은 무효행위의 추인에 해당하나, 그 추인에는 소급효가 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>무효행위추인</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>무효행위의 추인은 새로운 행위로 보므로 소급효가 없고 추인한 때부터 유효하다.</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>민법 제139조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>제139조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="n">
+        <v>213</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>수급인이 자기의 노력과 재료를 들여 건물을 신축한 경우, 도급인에게 소유권을 귀속시키기로 하는 특약이 없으면 그 건물의 소유권은 수급인이 원시취득한다.</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>신축건물귀속</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>판례는 특약이 없는 한 자기 재료로 건물을 신축한 수급인이 소유권을 원시취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>대판 2005.11.25. 2004다36352</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>제664조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="n">
+        <v>214</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>유치권자는 유치물을 경매에 부쳐 환가할 수는 있으나, 그 매각대금으로부터 다른 채권자에 우선하여 변제받을 우선변제권은 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>유치권환가</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>유치권자는 형식적 경매로 환가할 수 있지만 우선변제권은 없고 일반채권자로 배당받는다.</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>민법 제322조 · 제320조</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>제322조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="n">
+        <v>215</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>유치권의 행사, 즉 점유의 계속은 피담보채권의 소멸시효 진행을 중단시키는 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>유치권시효</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>민법 제326조에 따라 유치권의 행사는 피담보채권의 소멸시효 진행에 영향을 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>민법 제326조</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>제326조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="n">
+        <v>216</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>근저당권자가 피담보채무의 불이행을 이유로 경매를 신청한 경우 그 경매신청 시에 피담보채권액이 확정되며, 이후 경매신청을 취하하더라도 확정의 효과는 번복되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>근저당확정</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>판례는 근저당권자의 경매신청 시 채권이 확정되고 이후 취하해도 확정효과가 유지된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>대판 2002.11.26. 2001다73022</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="n">
+        <v>217</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>후순위 근저당권자가 경매를 신청한 경우, 선순위 근저당권의 피담보채권은 후순위권자의 경매신청 시가 아니라 경락인이 경락대금을 완납한 때에 확정된다.</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>후순위확정</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>판례는 후순위권자 경매신청 시 선순위 근저당 채권은 경락대금 완납 시에 확정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>대판 1999.9.21. 99다26085</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>제357조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n">
+        <v>218</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>미등기건물을 그 대지와 함께 매도하였으나 대지에 관하여만 매수인 앞으로 소유권이전등기가 경료된 경우, 매도인과 매수인 누구에게도 관습상의 법정지상권이 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>관습법정지상권</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>판례는 대지·건물을 함께 매도한 사안에서는 관습상 법정지상권을 인정할 필요가 없어 성립하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>대판 2002.6.20. 2002다9660</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>219</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>동산의 선의취득은 양도인이 무권리자라는 점을 제외하고는 거래행위 자체에 아무런 흠이 없어야 성립하므로, 기망을 이유로 취소된 거래로 점유를 승계한 자는 선의취득을 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>선의취득요건</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>판례는 유효한 거래행위를 전제로 선의취득이 성립하므로 취소된 거래의 점유 승계자는 선의취득할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>대판 1995.6.29. 94다22071</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>제249조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="n">
+        <v>220</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>손해배상 예정액은 부당히 과다한 경우 법원이 직권으로 감액할 수 있으나, 이미 예정된 손해배상액에 대하여 과실상계를 하는 것은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>예정액감액</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>판례는 손해배상 예정액은 직권 감액의 대상이나 과실상계는 따로 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>대판 2002.1.25. 99다57126</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>221</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>위약금 약정이 위약벌의 성질을 가지는 경우에도 법원은 민법 제398조 제2항을 유추적용하여 그 금액을 직권으로 감액할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>위약벌감액</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>위약벌은 손해배상액의 예정과 달라 제398조 제2항이 적용되지 않으므로 직권 감액의 대상이 아니다(공서양속 위반 시 일부 무효만 가능).</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>대판 2016.1.28. 2015다239324</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>222</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>부동산실명법상 명의신탁약정과 그 약정에 따른 등기에 의한 물권변동은 모두 무효이다.</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>명의신탁무효</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제1항·제2항에 따라 명의신탁약정과 그에 따른 물권변동은 무효이다.</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>223</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 제3항의 보호되는 '제3자'에는 소유권이나 저당권을 취득한 자만 포함되고, 압류 또는 가압류채권자는 포함되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>명의신탁제3자</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>판례는 수탁자가 물권자임을 기초로 새로운 이해관계를 맺은 자에는 압류·가압류채권자도 포함되며 선의·악의를 묻지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>대판 2000.3.28. 99다56529</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>224</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>계약상 급부가 그 계약 상대방이 아닌 제3자의 이익으로 귀결된 경우에도, 급부를 한 계약당사자는 계약 상대방에게 반대급부를 청구할 수 있을 뿐 그 제3자에게 직접 부당이득반환을 청구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>전용물소권</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>판례는 이른바 전용물소권을 부정하여 급부자는 계약 상대방에게만 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>대판 2002.8.23. 99다66564</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>225</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>공유물의 관리에 관한 사항은 공유자 지분의 과반수로 결정하며, 토지의 구체적인 이용방법도 과반수 지분으로 정할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>공유관리</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>민법 제265조에 따라 공유물의 관리는 지분 과반수로 결정한다.</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>민법 제265조</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>226</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>공유물을 협의 없이 자신의 지분을 초과하여 배타적으로 점유하는 소수지분권자에 대하여, 다른 소수지분권자는 보존행위로서 공유물 전부의 인도를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>소수지분인도</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소수지분권자는 다른 소수지분권자의 배타적 점유에 대해 보존행위로서 공유물 인도를 청구할 수 없고 방해배제만 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>대판(전) 2020.5.21. 2018다287522</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>227</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>변제충당에서 당사자 사이의 합의에 의한 충당이 최우선하며, 비용·이자·원본의 순서도 약정에 의하여 배제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>합의충당</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>판례는 합의충당이 지정·법정충당에 우선하고 제479조의 순서도 약정으로 배제할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>민법 제476조·제479조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>제476조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>228</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>강제경매나 담보권 실행을 위한 경매절차에서 배당금을 충당하는 경우에는 지정변제충당이 허용되지 않고 법정변제충당의 방법에 의하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>경매충당</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>판례는 경매절차의 배당충당에는 당사자의 지정충당이 허용되지 않고 법정충당만 인정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>대판 1996.5.10. 95다55504</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>229</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>저당권설정등기는 효력발생요건일 뿐 효력존속요건은 아니므로, 위조서류에 의하여 저당권설정등기가 원인 없이 말소되더라도 그 저당권은 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>불법말소</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>판례는 등기는 효력존속요건이 아니므로 부적법하게 말소되어도 물권이 소멸하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>대판 2001.1.16. 98다20110</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>230</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>불법 말소된 근저당권설정등기의 목적 부동산이 경매절차에서 경락되어 근저당권이 소멸한 경우, 근저당권자는 실제로 배당받은 자에 대하여 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>말소후경락</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>판례는 불법말소 후 경락으로 근저당권이 소멸하면 배당받은 자에게 부당이득반환을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>대판 1998.10.2. 98다27197</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>231</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>채무자 소유 부동산과 물상보증인 소유 부동산이 함께 경매되어 그 대가를 동시에 배당하는 경우, 공동저당권자는 먼저 채무자 소유 부동산의 경매대가에서 우선 배당받고 부족분에 한하여 물상보증인 소유 부동산에서 배당받는다.</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>공동저당동시배당</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인 보호를 위해 채무자 소유 부동산에서 우선 배당하고 부족분만 물상보증인 부동산에서 배당한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>대판 2010.4.15. 2008다41475</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>232</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>대상청구권은 채무자의 귀책사유 없이 후발적 이행불능이 발생한 경우에도 행사할 수 있으며, 이때 채권자는 대상청구권과 부당이득반환청구권 중 하나를 선택하여 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>대상청구권</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>판례는 쌍방 책임 없는 사유로 후발적 불능이 된 경우에도 대상청구권을 인정하고 부당이득반환청구권과 선택적으로 행사할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>대판 1992.5.12. 92다4581 · 판례</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>233</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>채무자가 미리 이행하지 아니할 의사를 명백히 표시한 경우, 채권자는 이행기 전이라도 이행의 최고 없이 계약을 해제하거나 손해배상을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>이행거절</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 명백한 이행거절 시 이행기 전이라도 최고 없이 해제·손해배상청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>대판 1993.6.25. 93다11821</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>234</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>매매계약에서 잔대금 지급의무와 소유권이전등기의무처럼 쌍방의 채무가 동시이행관계에 있는 경우, 자동해제(실권)약정이 있더라도 이행지체만으로 곧바로 계약이 자동해제되지는 않는다.</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>자동해제</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>판례는 동시이행관계인 채무에서는 자동해제약정이 있어도 상대방의 이행제공 없이는 자동해제되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>대판 1998.6.12. 98다505</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>제544조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>235</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>면책적 채무인수가 있으면 종전 채무에 대한 보증이나 제3자가 제공한 담보는 원칙적으로 소멸하나, 보증인이나 제3자가 채무인수에 동의한 경우에는 존속한다.</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>면책적인수</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>민법 제459조에 따라 면책적 채무인수 시 담보는 원칙 소멸하되 동의가 있으면 존속한다.</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>민법 제459조</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>제459조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>236</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>임대차가 종료된 후 임차인이 목적물을 계속 점유·사용한 경우, 임차인은 인도 완료일까지 차임 상당의 부당이득을 임대인에게 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>종료후점유</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>판례는 임대차 종료 후에도 점유·사용한 경우 차임 상당의 부당이득반환의무가 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>대판 1992.4.14. 91다45202</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>237</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 임대인의 임대차보증금 반환의무와 임차인의 임차권등기 말소의무는 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>보증금말소</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>판례는 임차권등기는 임대차보증금 반환을 담보하기 위한 것이므로 임대인의 보증금 반환의무가 임차권등기 말소의무보다 선이행의무라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>대판 2005.6.9. 2005다4529</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>238</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>과실상계는 채무불이행이나 불법행위로 인한 손해배상책임에 적용되지만, 고의의 불법행위를 저지른 가해자는 피해자의 과실을 들어 과실상계를 주장할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>고의과실상계</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>판례는 고의의 불법행위자가 피해자의 부주의를 이용한 경우 과실상계 주장은 신의칙상 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>대판 2007.10.25. 2006다16758</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>제396조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>239</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>예금계약은 예금자가 금융기관에 돈을 제공하고 금융기관이 이를 받아 확인하면 성립하는 요물계약이며, 그 직원이 받은 돈을 실제로 입금하였는지 여부는 예금계약의 성립에 영향이 없다.</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>예금성립</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>판례는 예금계약을 요물계약으로 보고 직원의 실제 입금 여부는 성립에 영향이 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>대판 1996.1.26. 95다26919</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>제702조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>240</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>착오로 송금·이체가 이루어진 경우에도, 그 원인인 법률관계의 존부와 관계없이 수취인은 수취은행에 대하여 이체금액 상당의 예금채권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>착오송금</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>판례는 착오송금이라도 원인관계 유무와 무관하게 수취인이 예금채권을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>대판 2007.11.29. 2007다51239</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>제702조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>241</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인에 대하여 채권자가 한 채무면제는 상대적 효력만 있을 뿐 다른 채무자에게는 영향을 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>부진정면제</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>판례는 부진정연대채무에서 면제는 상대적 효력만 가진다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>대판 2006.1.27. 2005다19378</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>제419조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>242</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>연대채무에서 소멸시효의 완성에 절대적 효력을 인정하는 규정은 공동불법행위자 상호간의 부진정연대채무에도 그대로 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>부진정시효</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>부진정연대채무에는 연대채무의 소멸시효 절대효 규정이 적용되지 않으므로, 1인에 대한 시효완성은 다른 채무자에게 영향을 주지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>대판 1997.12.23. 97다42830</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>제421조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>243</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>피상속인의 형제자매가 상속인이 되는 경우, 그 형제자매에는 아버지가 같고 어머니가 다른 동성이복형제뿐만 아니라 어머니가 같고 아버지가 다른 이성동복형제도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>형제자매범위</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>판례는 제3순위 상속인인 형제자매에 부계·모계를 불문하고 반혈족 형제자매가 모두 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>대판 1997.11.28. 96다5421</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>제1000조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>244</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>상속인이 될 직계비속이나 형제자매가 상속을 포기한 경우, 그 직계비속이 포기자를 대습하여 상속한다.</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>대습원인</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>대습상속의 원인은 상속개시 전 사망 또는 상속결격에 한하고 상속포기는 대습원인이 아니므로, 포기자의 직계비속은 대습상속하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>민법 제1001조</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>제1001조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>245</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>쌍무계약에서 채무자의 책임 있는 사유로 채무의 일부가 이행불능이 되었고 나머지 부분만으로는 계약의 목적을 달성할 수 없는 경우, 채권자는 이행이 가능한 부분만의 급부를 청구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>일부불능</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>판례는 일부 이행불능으로 계약목적을 달성할 수 없으면 전부불능으로 보아 가능 부분만의 급부청구는 허용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>대판 1995.7.25. 95다5929</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>246</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>사해행위취소소송에서 채무자의 악의가 입증되면 수익자나 전득자의 악의는 추정되므로, 수익자나 전득자가 자신의 선의를 증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>사해의사추정</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 사해의사가 인정되면 수익자·전득자의 악의가 추정되어 그들이 선의를 입증해야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>대판 2006.4.14. 2006다5710</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>247</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>채권자취소권은 채권자가 취소원인을 안 날부터 1년, 법률행위가 있은 날부터 5년 내에 행사하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>취소제척기간</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>민법 제406조 제2항에 따라 채권자취소권의 제척기간은 안 날 1년, 행위일 5년이다.</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>민법 제406조 제2항</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>248</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>채무자가 유일한 부동산을 매도하여 사해행위를 한 후에 비로소 신용카드 사용으로 카드대금채권이 발생한 경우, 그 카드대금채권도 사해행위취소의 피보전채권이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>피보전채권</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>사해행위 이후에 발생한 채권은 원칙적으로 피보전채권이 될 수 없으므로, 처분 후 발생한 카드대금채권은 피보전채권이 되지 못한다.</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>대판 2002.11.8. 2002다42957</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>249</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>형성권적 기한이익 상실의 특약이 있는 경우, 일정한 사유가 발생하더라도 채권자가 기한이익 상실의 의사표시를 하여야 비로소 이행기가 도래하여 지체책임이 생긴다.</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>기한이익상실</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>판례는 기한이익 상실특약은 원칙적으로 형성권적 특약으로 추정되어 채권자의 의사표시가 있어야 이행기가 도래한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>대판 2002.9.4. 2002다28340</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>제388조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>250</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>토지거래허가구역 내 토지에 관하여 허가를 받지 않아 유동적 무효 상태인 매매계약에서는, 이행지체를 이유로 한 계약해제나 손해배상청구를 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>유동적무효</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>판례는 유동적 무효 상태에서는 이행청구나 그를 전제로 한 이행지체·해제·손해배상청구를 할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>대판(전) 1991.12.24. 90다12243</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>제105조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>251</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>양육권이 없는 부모 일방이 임의로 자녀를 양육한 경우, 그 양육은 위법한 양육이므로 상대방에게 양육비를 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>임의양육</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>판례는 양육권 없는 자가 임의로 한 양육은 위법하여 상대방에게 양육비를 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>대판 2006.4.17. 2005스18</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>제837조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>252</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>주채무자가 소멸시효의 이익을 포기하더라도 그 효과는 보증인에게 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>시효이익포기</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>시효이익 포기의 효과는 상대적이어서 주채무자의 포기는 보증인에게 영향을 주지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>민법 제433조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>제433조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>253</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>부동산실명법에 위반되어 무효인 명의신탁약정에 기하여 명의수탁자 앞으로 경료된 등기는 불법원인급여에 해당하여 신탁자가 그 반환을 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>명의신탁급여</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>판례는 부동산실명법 위반 명의신탁등기는 불법원인급여에 해당하지 않으므로 신탁자가 그 반환(말소)을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>대판(전) 2019.6.20. 2013다218156</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>254</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>도박자금 채무를 담보하기 위하여 근저당권설정등기를 경료한 경우, 이는 종국적인 급여가 아니므로 근저당권설정자는 그 말소를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>도박담보</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>판례는 담보 목적의 근저당권설정등기는 종국적 급여가 아니어서 불법원인급여로 보지 않아 말소청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>대판 1995.8.11. 94다54108</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>255</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>혼인 중 부부가 협력하여 이룩한 재산이 있는 경우, 혼인 파탄에 책임이 있는 유책배우자라도 재산분할을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>유책재산분할</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>판례는 재산분할은 부양·청산의 성질을 가지므로 유책배우자도 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>대결 1993.5.11. 93스6</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>256</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>이혼에 따른 재산분할청구권은 이혼한 날부터 2년이 지나면 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>분할제척기간</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>민법 제839조의2 제3항에 따라 재산분할청구권은 이혼한 날부터 2년의 제척기간에 걸린다.</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>민법 제839조의2 제3항</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>257</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>한정승인을 한 채무자가 채권자의 소송에서 사실심 변론종결 시까지 그 사실을 주장하지 않아 패소 확정된 경우에도, 채무자는 그 후 한정승인 사실을 들어 청구이의의 소를 제기할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>한정승인이의</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>판례는 한정승인은 책임의 범위에 관한 것이어서 변론종결 후에도 청구이의의 소로 주장할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>대판(전) 2006.10.13. 2006다23138</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>제1028조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>258</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>상속포기를 한 채무자가 채권자의 소송에서 사실심 변론종결 시까지 이를 주장하지 않아 패소 확정된 경우, 그 후 상속포기 사실을 들어 청구이의의 소를 제기할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>상속포기이의</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>상속포기는 채무의 존부 자체에 관한 것이어서 변론종결 전에 주장했어야 하므로, 확정판결 후 청구이의의 소로 다툴 수 없다(기판력에 의해 차단).</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>대판 2009.5.28. 2008다79876</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>제1019조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>259</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>무효행위의 추인은 그 무효원인이 소멸한 후에 이루어지더라도 원칙적으로 법률행위를 한 때로 소급하여 효력이 생긴다.</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>추인소급효</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>무효행위의 추인은 새로운 법률행위로 보므로 소급효가 없고 추인한 때부터 장래를 향하여 효력이 생긴다.</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>민법 제139조</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>제139조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>260</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>강제경매나 담보권 실행을 위한 경매의 배당금 충당에서도 당사자가 지정한 변제충당이 법정변제충당에 우선하여 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>경매지정충당</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>경매절차의 배당충당에는 당사자의 지정충당이 허용되지 않고 법정변제충당만 적용된다.</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>대판 1996.5.10. 95다55504</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>제477조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>261</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>대상청구권은 채무자에게 이행불능에 관한 귀책사유가 있는 경우에 한하여 인정되고, 당사자 쌍방에게 책임 없는 사유로 불능이 된 때에는 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>대상청구귀책</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>대상청구권은 채무자의 귀책사유를 불문하고 인정되며, 쌍방에 책임 없는 후발적 불능의 경우에도 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>대판 1992.5.12. 92다4581</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>262</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>무효등기의 유용에 관한 합의는 그 합의 이전에 이미 등기상 이해관계를 가지게 된 제3자에 대하여도 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>무효등기유용</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>무효등기 유용의 합의는 그 전에 등기상 이해관계를 가진 제3자에게는 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>대판 2009.2.26. 2006다72802</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>263</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 우선변제권을 가진 임차인으로부터 임차권과 분리하여 임차보증금 반환채권만을 양수한 자도 주택임대차보호법상의 우선변제권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>보증금채권양수</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>판례는 임차권과 분리하여 보증금반환채권만을 양수한 자는 주임법상 우선변제권을 행사할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>대판 2010.5.27. 2010다10276</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>제3조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>264</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>혼인 중 부부의 일방 명의로 취득한 재산은 부부의 공유로 추정되므로, 상대방의 협력이 있었다는 사정만으로도 그 재산은 재산분할의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>특유재산추정</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>혼인 중 일방 명의로 취득한 재산은 명의자의 특유재산으로 추정되며, 단순한 내조의 공만으로는 그 추정이 번복되지 않는다(다만 유지·증식에 기여하면 분할대상).</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>대판 1998.4.10. 96므1434</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>제830조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>265</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>채권자가 주채무자에 대하여 변제기를 연장하여 준 경우, 그 효력은 연대보증채무에는 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>변제기연장</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>채권자가 주채무자에게 변제기를 연장해 주면 그 효력은 보증채무에도 미친다.</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>민법 제430조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>제430조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>266</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>변시2</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>수탁보증인이 주채무자에게 사전통지를 하지 않고 변제 등 면책행위를 하였는데, 그에 앞서 주채무자가 이미 면책행위를 하고도 보증인에게 통지하지 않은 경우, 보증인은 자신의 면책행위가 유효함을 주장하여 주채무자에게 구상할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>이중면책</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>주채무자가 먼저 면책행위를 한 이상 채무소멸의 일반원칙에 따라 선행 변제가 유효하므로, 사전통지 없이 이중으로 면책행위를 한 보증인은 주채무자에게 구상할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>민법 제446조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>제446조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1283"/>
+  <dimension ref="A1:H1355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -51784,6 +51784,2886 @@
         </is>
       </c>
     </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>101</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>고의의 불법행위로 인한 손해배상채권을 수동채권으로 하는 상계는 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>상계금지</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>민법 제496조에 따라 고의의 불법행위로 인한 손해배상채권을 수동채권으로 하는 상계는 금지된다.</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>민법 제496조</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>102</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>피용자의 고의의 불법행위로 사용자책임이 성립하는 경우, 그 사용자책임에 기한 손해배상채권을 수동채권으로 하는 상계도 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>사용자책임상계</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>판례는 사용자책임이 피용자의 고의 불법행위에 대한 대체적 책임이므로 이를 수동채권으로 하는 상계도 제496조 취지상 금지된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>대판 2006.10.26. 2004다63019</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>제496조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>103</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>상계의 수동채권은 상계자가 상대방에 대하여 부담하는 채무여야 하므로, 상대방이 제3자에 대하여 가지는 채권을 수동채권으로 하여 상계할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>수동채권요건</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>수동채권은 상계자가 상대방에게 부담하는 채무여야 하므로 상대방의 제3자에 대한 채권을 수동채권으로 삼을 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>민법 제492조</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>제492조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>104</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>혼인 외의 자를 혼인 중의 친생자로 출생신고한 경우, 그 신고는 인지신고로서의 효력이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>무효행위전환</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>판례는 혼인외 자를 친생자로 출생신고한 경우 인지의 효력을 인정한다(무효행위의 전환).</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>대판 1971.11.15. 71다1983</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>제855조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>105</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>비밀증서에 의한 유언이 그 방식에 흠결이 있더라도 자필증서에 의한 유언의 방식에 적합한 때에는 자필증서에 의한 유언으로서 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>유언전환</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>민법 제1071조에 따라 방식에 흠결 있는 비밀증서 유언이 자필증서 방식을 갖추면 자필증서 유언으로 전환된다.</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>민법 제1071조</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>제1071조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>106</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>법적 절차에 따라 진행되는 경매에는 민법 제104조의 불공정한 법률행위에 관한 규정이 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>경매불공정</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>판례는 경매에는 제104조가 적용되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>대결 1980.3.21. 80마77</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>107</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>불공정한 법률행위인지를 판단할 때 경솔·무경험은 대리인을 기준으로, 궁박 상태는 본인을 기준으로 판단한다.</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>불공정판단기준</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>판례는 대리행위의 경우 경솔·무경험은 대리인을, 궁박은 본인을 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>대판 2002.10.22. 2002다38927</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>108</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>불공정한 법률행위로서 무효인 경우에도 당사자가 이를 추인하면 유효한 것으로 된다.</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>불공정추인</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>불공정한 법률행위는 절대적 무효여서 추인에 의하여 유효로 될 수 없다(다만 무효행위 전환은 가능).</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>대판 1994.6.24. 94다10900</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>제104조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>109</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>강제집행을 면탈할 목적으로 통정하여 체결한 가장매매라도 그것만으로 민법 제103조 위반이나 불법원인급여에 해당하는 것은 아니어서, 급부한 자는 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>강제집행면탈</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>판례는 강제집행 면탈 목적의 가장매매가 제103조 위반이나 불법원인급여에 해당하지 않아 반환청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>대판 2004.5.28. 2003다70041</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>제746조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>110</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>통정허위표시로서 무효인 법률행위도 채권자취소권의 대상이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>허위표시취소</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>판례는 통정허위표시로 무효인 행위라도 사해행위가 되면 채권자취소권의 대상이 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>대판 1998.2.27. 97다50985</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>111</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>계약이 해제된 경우, 그 해제로 소멸하는 채권 자체를 양수하거나 그 채권을 압류·전부한 자는 민법 제548조 제1항 단서에서 보호되는 제3자에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>해제제3자</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>판례는 해제로 소멸하는 채권의 양수인이나 압류·전부채권자는 제548조 제1항 단서의 제3자가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>대판 2003.1.24. 2000다22850</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>112</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>계약 해제로 소멸하는 채권을 그 해제 전에 압류·전부한 자도 민법 제548조 제1항 단서의 보호되는 제3자에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>해제제3자</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>해제로 소멸하는 채권 자체를 압류·전부한 자는 제548조 제1항 단서의 제3자에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>대판 2000.4.11. 99다51685</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>제548조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>113</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>특정물 매매에서 매수인의 대금지급채무가 이행지체에 빠졌더라도, 그 목적물이 매수인에게 인도될 때까지는 매수인은 매매대금의 이자를 지급할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>대금이자</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>민법 제587조에 따라 목적물 인도 전에는 매수인이 대금 이자를 지급할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>민법 제587조</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>114</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>매매계약 후 아직 인도하지 아니한 목적물로부터 생긴 과실은 원칙적으로 매도인에게 귀속한다.</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>과실귀속</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>민법 제587조 제1문에 따라 인도 전 과실은 원칙적으로 매도인에게 귀속한다.</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>민법 제587조</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>115</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>부동산 이중매매가 반사회적 법률행위에 해당하여 무효인 경우, 제1매수인은 매도인을 대위하여 제2매수인 명의 등기의 말소를 구할 수 있을 뿐 직접 말소를 청구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>이중매매</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>판례는 반사회적 이중매매에서 제1매수인이 매도인을 대위하여 말소를 구할 수 있을 뿐 직접 청구권은 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>대판 1983.4.26. 83다카57</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>116</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>부동산 이중매매가 반사회적 법률행위로서 무효인 경우, 제2매수인으로부터 다시 매수한 선의의 전득자는 유효하게 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>절대적무효</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>반사회적 이중매매의 무효는 절대적 무효이므로 선의의 전득자도 보호되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>대판 1996.10.25. 96다29151</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>117</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>전세권이 소멸한 경우 전세권자의 목적물 인도 및 전세권설정등기 말소에 필요한 서류 교부의무와 전세권설정자의 전세금 반환의무는 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>전세동시이행</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>민법 제317조에 따라 전세권자의 인도·말소서류 교부의무와 전세금 반환의무는 동시이행관계이다.</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>민법 제317조</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>제317조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>118</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>금전소비대차에서 채권자가 변제를 받기 전 또는 변제와 상환으로 담보된 근저당권설정등기를 말소할 의무는 채무자의 변제의무와 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>담보말소</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>담보권설정등기 말소의무는 피담보채무 변제 후에 이행하는 후이행의무이므로 변제의무와 동시이행관계에 있지 않다.</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>대판 1969.9.30. 69다1173</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>119</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>재판상 이혼청구권은 일신전속적 권리이므로, 이혼소송 계속 중 당사자 일방이 사망하면 그 이혼소송은 종료된다.</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>이혼소송종료</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>판례는 재판상 이혼청구권의 일신전속성을 이유로 일방 사망 시 이혼소송이 종료된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>대판 1994.10.28. 94므246</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>제840조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>120</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>사실혼관계는 당사자 일방의 의사로 해소할 수 있고, 이 경우 상대방은 재산분할을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>사실혼분할</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>판례는 사실혼이 일방의 의사로 해소될 수 있고 그 경우 재산분할청구가 가능하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>대판 1995.3.28. 94므1584</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>121</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>소유권이전등기가 경료되어 있으면 그 등기는 권리의 귀속과 내용뿐만 아니라 등기원인과 그 절차의 적법까지 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>등기추정력</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>판례는 등기의 추정력이 등기원인과 절차의 적법에까지 미친다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>대판 2002.2.5. 2001다72029</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>122</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>점유의 추정력은 현재의 점유자뿐만 아니라 전(前) 점유자에게도 원용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>점유추정력</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>점유의 추정력은 현 점유자에게만 인정되고 전 점유자는 이를 원용할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>대판 1982.4.13. 81다780</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>제200조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="n">
+        <v>123</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>나대지에 저당권을 설정한 후 저당권설정자나 제3자가 건물 신축공사를 계속하여 저당부동산의 교환가치 하락으로 우선변제청구권 행사가 방해될 우려가 있는 경우, 저당권자는 방해배제청구권의 행사로 공사중지를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>방해배제</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>판례는 저당목적물의 교환가치를 해치는 행위에 대하여 저당권에 기한 방해배제로 공사중지를 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>대결 2006.1.27. 2003마1755</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>제370조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n">
+        <v>124</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>후순위 근저당권자는 민법 제364조의 제3취득자에 해당하므로, 선순위 근저당권의 피담보채무를 변제하고 그 근저당권의 소멸을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>제364조변제</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>후순위 근저당권자는 제364조의 제3취득자에 해당하지 않으므로 그에 기한 변제로 선순위 근저당권의 소멸을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>대판 2006.1.26. 2005다17341</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>제364조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="n">
+        <v>125</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>청구권보전을 위한 가등기는 본등기 전에는 그 자체로 실체법상 효력이나 순위보전적 효력이 없고, 본등기를 마치면 본등기의 순위가 가등기의 순위로 소급한다.</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>가등기효력</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>판례는 가등기는 본등기 전에는 실체법상 효력이 없고 본등기 시 순위만 소급한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>대판 1981.5.26. 80다3117</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="n">
+        <v>126</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>가등기에 기하여 본등기를 마치면 순위뿐만 아니라 물권변동의 효력도 가등기를 한 때로 소급하여 발생한다.</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>본등기소급</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>본등기를 하면 순위만 가등기 시로 소급할 뿐 물권변동의 효력은 본등기를 한 때에 발생한다.</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>대판 1982.6.22. 81다1298</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>127</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>가등기에 기한 본등기를 청구할 때 그 상대방은 가등기 당시의 소유자이고, 가등기 후 소유권을 취득한 현재의 등기명의인이 아니다.</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>본등기상대방</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>판례는 가등기에 기한 본등기청구의 상대방은 가등기 당시의 소유자라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>대판 1998.11.27. 97다41103</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>128</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>토지의 공유자 중 소수지분권자가 그 토지에 건물을 신축한 경우, 다른 소수지분권자는 공유물의 보존행위로서 그 건물의 철거와 토지의 인도를 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>공유보존행위</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소수지분권자의 무단 점유·사용에 대하여 다른 소수지분권자가 보존행위로 인도·철거를 구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>대판(전) 2020.5.21. 2018다287522</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>129</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>계약명의신탁에서 매도인이 선의여서 물권변동이 유효한 경우, 명의수탁자가 소유권을 취득하고 명의신탁자는 제공한 매수자금 상당액을 수탁자에게 부당이득으로 반환청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>계약명의신탁</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>판례는 매도인 선의의 계약명의신탁에서 수탁자가 소유권을 취득하고 신탁자는 매수자금의 부당이득반환을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>대판(전) 2005.1.27. 2002다42605</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>130</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>계약명의신탁에서 명의신탁자가 부동산을 인도받아 점유하고 있는 경우, 매수자금 상당의 부당이득반환채권을 피담보채권으로 하여 그 부동산에 유치권을 행사할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>명의신탁유치권</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>부당이득반환채권은 목적 부동산과 견련관계가 없으므로 이를 피담보채권으로 한 유치권은 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>대판 2009.3.26. 2008다34828</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>제320조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>131</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>매매로 인한 소유권이전등기청구권을 양도하는 경우에는 통상의 채권양도와 달리 양도인의 상대방인 채무자의 동의나 승낙이 있어야 양수인이 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>이전등기청구권양도</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>판례는 소유권이전등기청구권 양도에는 채무자의 동의나 승낙이 있어야 대항할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>대판 2001.10.9. 2000다51216</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>132</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>중간생략등기의 합의가 있으면 중간매수인의 최초매도인에 대한 소유권이전등기청구권은 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>중간생략등기</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>중간생략등기의 합의가 있더라도 중간매수인의 최초매도인에 대한 등기청구권이 소멸하는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>대판 1991.12.13. 91다18316</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>133</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>채권의 소멸시효가 완성되면 채무는 당연히 소멸하지만, 이는 변론에서 당사자가 시효의 이익을 주장(원용)하여야 법원이 이를 고려할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>시효원용</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>판례는 소멸시효 완성의 이익은 변론에서 당사자가 원용하여야 재판상 고려된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>대판 1979.2.13. 78다2157</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>134</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>소멸시효의 기산점은 변론주의의 적용대상이지만, 소멸시효의 기간은 법률상의 주장에 불과하여 법원이 직권으로 판단할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>시효기산점</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>판례는 기산점은 주요사실로 변론주의 대상이나, 시효기간은 법률적 판단으로 법원이 직권 판단할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>대판 2008.3.27. 2006다70929</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>제166조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>135</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>채무불이행으로 인한 손해배상액이 예정된 경우, 채권자는 채무불이행 사실만 증명하면 되고 손해의 발생이나 그 손해액을 증명할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>예정액증명</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>판례는 손해배상액 예정 시 채권자는 채무불이행만 증명하면 되고 손해발생·손해액 증명은 불요라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>대판 2000.12.8. 2000다50350</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>136</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>위약금의 약정은 손해배상액의 예정으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>위약금추정</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>민법 제398조 제4항에 따라 위약금은 손해배상액의 예정으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>민법 제398조 제4항</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>137</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정되어 있는 경우에도 법원은 채권자의 과실을 참작하여 따로 과실상계를 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>예정과실상계</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정된 경우에는 과실상계를 따로 할 수 없고, 예정액이 부당히 과다하면 직권 감액만 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>대판 2002.1.25. 99다57126</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>138</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>부진정연대채무자 중 1인이 채권자에 대하여 한 상계는 절대적 효력이 있어, 채무소멸의 효력이 다른 부진정연대채무자에게도 전액 미친다.</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>부진정상계</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>판례는 부진정연대채무에서 변제와 마찬가지로 상계도 절대적 효력이 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>대판(전) 2010.9.16. 2008다97218</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>제418조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>139</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>피용자와 제3자의 공동불법행위에 대하여 사용자책임이 인정되는 경우, 사용자가 피용자의 부담부분을 초과하여 피해자에게 배상하였다면 사용자는 제3자에게 그 부담부분의 한도에서 구상할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>사용자구상</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>판례는 사용자가 부담부분을 초과 배상하면 다른 공동불법행위자에게 그 부담부분 한도에서 구상할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>대판 1992.6.23. 91다33070</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>140</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>공동불법행위자 중 1인이 피해자의 부주의를 이용하여 고의의 불법행위를 한 경우, 그 가해자도 피해자의 과실을 들어 과실상계를 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>고의과실상계</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>피해자의 부주의를 이용하여 고의의 불법행위를 한 자는 과실상계를 주장할 수 없다(다만 다른 불법행위자는 주장 가능).</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>대판 2007.6.14. 2005다32999</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>제396조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>141</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>저당권이 설정되어 있는 부동산이 양도된 경우, 피담보채권액이 그 부동산의 가액을 초과하는 때에는 그 양도는 사해행위에 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>사해행위판단</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>판례는 피담보채권액이 부동산 가액을 초과하면 일반채권자의 공동담보가 없으므로 사해행위가 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>대판 2001.10.9. 2000다42618</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>142</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>사해행위취소소송에서 채무자의 사해의사는 채권자가 증명하여야 하나, 채무자가 유일한 재산을 처분한 경우에는 그 사해의사가 추정된다.</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>사해의사추정</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>판례는 채무자가 유일재산을 처분한 경우 사해의사가 추정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>대판 2001.4.24. 2000다41875</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>143</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>토지임차인의 지상물매수청구권에 관한 민법 제643조는 편면적 강행규정이므로, 이를 미리 포기하는 특약은 원칙적으로 무효이다.</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>지상물매수</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>판례는 제643조가 편면적 강행규정이어서 임차인에게 불리한 포기 특약은 무효라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>민법 제652조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>144</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>토지임대인이 제기한 건물철거 및 토지인도 청구소송에서 임차인이 패소하여 확정된 경우, 그 후 건물철거가 집행되지 않았더라도 임차인은 더 이상 지상물매수청구권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>매수청구기판력</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>판례는 패소 확정 후라도 건물철거가 집행되지 않은 이상 임차인은 별소로 건물매수청구권을 행사하여 매매대금을 청구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>대판 1995.12.26. 95다42195</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>제643조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>145</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>채권자대위소송에서 제3채무자는 채무자에 대하여 가지는 항변으로 채권자에게 대항할 수 있으나, 피보전채권의 소멸시효 완성은 채무자가 채권자에게 가지는 항변이므로 제3채무자가 이를 원용할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>제3채무자항변</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>판례는 피보전채권의 소멸시효 완성은 채무자의 항변이어서 제3채무자가 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>대판 1992.11.10. 92다35899</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>146</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>자기 소유 주택을 매도하고 그 주택에 임차인으로 계속 거주하는 경우, 임차인으로서의 대항력은 매수인 명의의 소유권이전등기가 마쳐진 다음 날에 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>대항력시기</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>판례는 매도 후 임차인으로 남은 경우 매수인 명의 이전등기 익일에 대항력을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>대판 2000.2.11. 99다59306</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>제3조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>147</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>대항요건과 확정일자를 갖춘 임차인이라도 경매절차에서 우선변제를 받으려면 배당요구의 종기까지 배당요구를 하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>배당요구</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>판례는 우선변제권 있는 임차인도 배당요구를 하여야 배당받을 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>대판 1998.10.13. 98다12379</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>제3조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>148</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>임시이사의 선임에 관한 민법 제63조는 비법인사단에도 유추적용된다.</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>비법인사단</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>판례는 제63조의 임시이사 선임 규정이 비법인사단에 유추적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>대결(전) 2009.11.19. 2008마699</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>제63조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>149</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>지교회가 교단을 탈퇴하거나 변경하려면 의결권을 가진 교인 과반수의 찬성으로 충분하다.</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>교단탈퇴</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>판례는 지교회의 교단 탈퇴·변경에는 의결권을 가진 교인 3분의 2 이상의 찬성이 필요하다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>대판(전) 2006.4.20. 2004다37775</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>제42조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>150</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>가등기담보법상 가등기담보의 사적 실행은 귀속정산의 방법만 인정되고, 청산절차 없이 목적물을 처분하는 처분정산형의 담보권 실행은 허용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>가등기담보실행</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>가등기담보법은 사적 실행으로 귀속정산만 인정하고 처분정산형 실행을 허용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>가등기담보법 제3조·제4조</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>151</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>가등기담보법은 목적물의 예약 당시 가액이 차용액 및 이에 붙인 이자의 합산액을 초과하는 경우에만 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>가등기담보적용</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>판례는 예약 당시 목적물 가액이 차용원리금을 초과하는 경우에만 가등기담보법이 적용된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>대판 2006.8.24. 2005다61140</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>제608조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>152</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>타인 소유의 토지 위에 권한 없이 건물을 소유하는 자는 그 건물을 실제로 사용·수익하지 않더라도 토지의 차임 상당액을 부당이득으로 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>무단건물소유</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>판례는 권한 없이 건물을 소유하여 토지를 점유하는 자는 사용·수익 여부와 무관하게 차임 상당 부당이득반환의무가 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>대판 1998.5.8. 98다2389</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>153</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성되었으나 아직 소유권이전등기를 마치지 못한 점유자에 대하여, 대지소유자는 그 점유가 불법점유임을 이유로 차임 상당의 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>시효완성점유</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>시효완성자의 점유는 권원 있는 점유로 보아야 하므로 소유자는 불법점유를 이유로 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>대판 1993.5.25. 92다51280</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>154</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>취득시효가 완성된 점유자가 그 후 점유를 상실하더라도 소유권이전등기청구권이 즉시 소멸하는 것은 아니나, 그때부터 소멸시효가 진행하여 10년이 지나면 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>점유상실</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>판례는 시효완성 후 점유를 상실해도 등기청구권이 곧바로 소멸하지 않고 다만 소멸시효가 진행한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>대판(전) 1996.3.8. 95다34866</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>155</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성된 사실을 알 수 없었던 부동산 소유자가 시효완성자가 시효를 주장하거나 이전등기를 청구하기 전에 그 부동산을 제3자에게 처분한 경우, 소유자는 시효완성자에 대하여 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>시효처분책임</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>시효완성 사실을 알 수 없는 소유자가 시효 주장 전에 처분한 경우에는 특별한 사정이 없는 한 손해배상책임을 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>대판 1995.7.11. 94다4509</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>156</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>채권이 이중으로 양도된 경우 양수인 상호간의 우열은 확정일자 있는 양도통지가 채무자에게 도달한 일시의 선후로 결정되며, 확정일자 자체의 선후로 결정되는 것이 아니다.</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>채권이중양도</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>판례는 이중양도 시 우열을 확정일자 있는 통지의 도달 선후로 결정한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>대판(전) 1994.4.26. 93다24223</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>157</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>확정일자 있는 채권양도통지와 압류명령 등이 제3채무자에게 동시에 도달하여 그들 상호간에 우열이 없는 경우, 제3채무자가 그중 한 사람에게 채무 전액을 변제하면 다른 채권자에 대한 관계에서도 유효하게 면책된다.</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>동시도달</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>판례는 동시도달로 우열이 없는 경우 채무자가 한 채권자에게 전액 변제하면 다른 채권자에 대하여도 면책된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>대판 1994.4.26. 93다24223</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>제450조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>158</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>특별손해는 채무자가 그 특별한 사정을 알았거나 알 수 있었을 때에만 배상책임이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>특별손해</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>민법 제393조 제2항에 따라 특별손해는 채무자가 그 사정을 알았거나 알 수 있었을 때 배상책임이 있다.</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>민법 제393조 제2항</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>제393조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>159</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>채권자가 연대보증인 1인에 대하여 채권을 포기하더라도 그 효력은 주채무자나 다른 연대보증인에게 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>연대보증포기</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>판례는 연대보증인 1인에 대한 채권포기는 상대적 효력만 있어 주채무자·다른 보증인에게 미치지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>민법 제419조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>제419조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>160</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>주채무자에 대한 시효중단의 효력은 보증채무에는 미치지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>보증시효중단</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>민법 제440조에 따라 주채무자에 대한 시효중단은 보증채무에도 효력이 미친다(반면 보증채무의 시효중단은 주채무에 영향 없음).</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>민법 제440조</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>제440조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>161</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>전세권의 존속기간이 만료되면 용익물권적 권능은 전세권설정등기의 말소 없이도 당연히 소멸하나, 담보물권적 권능은 전세금이 반환될 때까지 존속한다.</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>전세권존속</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>판례는 존속기간 만료로 용익권능은 소멸하고 담보물권적 권능만 전세금 반환 시까지 존속한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>대판 2005.3.25. 2003다35659</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>162</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>유증은 유언자의 사망 전에 수증자가 먼저 사망한 때에는 그 효력이 생기지 않으며, 이는 사인증여의 경우에도 같다.</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>유증실효</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>민법 제1089조에 따라 수증자가 유언자보다 먼저 사망하면 유증은 효력이 없고 사인증여도 같다.</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>민법 제1089조</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>제1089조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>163</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>증여와 유증이 함께 유류분을 침해하는 경우, 유류분 권리자는 유증(사인증여)을 먼저 반환받은 후 그것으로 부족할 때 증여를 반환받는다.</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>유류분반환순서</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>민법 제1116조에 따라 유류분 반환은 유증을 먼저, 그 다음 증여의 순서로 한다.</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>민법 제1116조</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>제1116조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>164</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>변제할 정당한 이익이 있는 제3자는 채무자의 의사에 반하여도 변제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>이해관계변제</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>민법 제469조 제2항에 따라 이해관계 있는 제3자는 채무자의 의사에 반하여도 변제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>민법 제469조</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>제469조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>165</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>채권의 일부를 대위변제한 경우, 그 일부 대위변제자는 채권자와 함께 권리를 행사하며 채권자에 우선하여 변제받는다.</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>일부대위우선</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>일부 대위변제 시 대위자는 채권자와 함께 권리를 행사하나, 채권자가 일부 대위변제자에 우선하여 변제받는다.</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>대판 1988.9.27. 88다카1797</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>제483조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>166</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>보증인과 물상보증인의 지위를 함께 가지는 자는 변제자대위의 비율을 산정할 때 1인으로 보아 인원수에 산입한다.</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>이중자격대위</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>판례는 보증인과 물상보증인의 지위를 겸하는 자는 대위비율 산정 시 1인으로 보아야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>대판(전) 2010.6.17. 2007다61113</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>제482조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>167</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>혼인 중 부부 일방이 사망하여 상대방이 배우자로서 망인의 재산을 상속받은 후 그 혼인이 취소된 경우, 취소의 소급효로 인하여 상속받은 재산은 부당이득으로 반환하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>혼인취소비소급</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>혼인의 취소에는 소급효가 없으므로(제824조), 취소 전에 배우자로서 상속받은 재산을 부당이득으로 반환할 의무는 없다.</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>민법 제824조</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>제824조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>168</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>쌍무계약이 취소된 경우, 선의의 매도인은 그가 받은 매매대금의 운용이익 내지 법정이자를 상대방에게 반환하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>선의반환범위</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>판례는 쌍무계약 취소 시 선의의 매도인은 받은 대금의 운용이익이나 법정이자까지 반환할 의무는 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>대판 1993.5.14. 92다45025</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>제748조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>169</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>가등기담보법이 적용되는 담보가등기의 피담보채권에는 소비대차에 의한 차용물반환채권뿐만 아니라 매매대금채권이나 공사대금채권도 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>담보가등기피담보</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>가등기담보법은 소비대차(준소비대차 포함)에 기한 차용물반환채권에만 적용되므로 매매대금·공사대금채권을 담보하는 가등기에는 적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>가등기담보법 제1조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>제607조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>170</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>채권에 대한 가압류가 있으면 제3채무자와 채무자는 그 채권의 발생원인인 계약을 합의해제할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>가압류합의해제</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>가압류는 채권 자체를 대상으로 할 뿐 그 발생원인인 법률관계를 구속하지 않으므로, 제3채무자와 채무자는 그 계약을 합의해제할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>대판 2001.6.1. 98다17930</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>171</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>사해행위취소권을 행사하려면 채무자의 무자력 상태가 사해행위 당시에 존재하면 충분하고, 사실심 변론종결 시까지 계속될 필요는 없다.</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>무자력계속</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>판례는 채무자의 무자력이 사해행위 시부터 사실심 변론종결 시까지 계속되어야 사해행위취소가 인정된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>대판 2009.3.26. 2007다63102</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>172</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>변시1</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>매도인에게 소유권이 유보된 자재가 제3자와 매수인 사이의 도급계약 이행으로 제3자 소유 건물에 부합된 경우, 그 제3자가 소유권 유보에 대하여 선의·무과실이더라도 매도인은 제3자에게 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>부합부당이득</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>제3자가 소유권 유보에 대하여 선의·무과실이면 선의취득에 준하여 법률상 원인이 있으므로, 매도인은 그 제3자에게 부당이득반환을 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>대판 2009.9.24. 2009다15602</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>제261조</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1355"/>
+  <dimension ref="A1:H1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -54664,6 +54664,3006 @@
         </is>
       </c>
     </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>타인의 성명을 모용한 자가 명의자 본인인 것처럼 상대방을 기망하여 직접 법률행위를 한 경우, 모용자에게 명의자를 대리할 기본대리권이 있었고 상대방이 명의자 본인의 권한 행사로 믿은 데 정당한 사유가 있었다면 민법 제126조의 표현대리 법리가 유추적용된다.</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>문1·성명모용</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>판례는 성명모용에 기본대리권과 정당한 사유가 있으면 제126조 표현대리를 유추적용한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>대판 1993.2.23. 92다52436</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>제126조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>비법인사단인 교회의 대표자가 총유물인 교회 재산 처분에 관하여 교인총회 결의를 거치지 않아 권한이 없는 경우에도, 상대방이 대표자에게 권한이 있다고 믿을 정당한 이유가 있으면 민법 제126조의 표현대리 법리가 유추적용된다.</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>문1·총유처분</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>총유물 처분에 사원총회 결의가 없으면 대표권 자체가 없어 제126조 표현대리 법리가 유추적용되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>대판(전) 2009.2.12. 2006다23312</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>제276조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>어떤 사람이 대리인의 외양을 갖추고 행위하는 것을 본인이 알면서도 이의하지 않고 방임하는 등 사실상의 태도에 의하여도 대리권 수여가 추단될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>문1·묵시수권</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>판례는 본인이 대리행위를 알면서 방임하는 태도로도 묵시적 대리권 수여가 추단될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>대판 1962.4.18. 4294민상1236</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>제125조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>타인 소유 토지 위에 무단으로 신축된 미등기건물을 매수하여 대금을 완납하고 이를 배타적으로 점유·사용하는 자는, 그 부지인 토지의 점유·사용으로 인한 부당이득을 토지소유자에게 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>문2·미등기건물</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>판례는 미등기건물의 매수인을 사실상 처분권자로서 부지의 점유자로 보아 부당이득반환의무를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>대판 2022.9.29. 2018다243133</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>무단으로 신축된 미등기건물을 매수하여 점유하는 자는 아직 소유권이전등기를 마치지 못한 이상 그 건물에 대하여 소유권은 물론 소유권에 준하는 관습상의 물권도 인정받을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>문2·관습물권</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>판례는 미등기건물 매수인에게 소유권이나 소유권에 준하는 관습상 물권을 인정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>대판(전) 2006.10.27. 2006다49000</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>법인 대표자의 직무에 관한 불법행위로 법인의 손해배상책임이 인정되고 그 행위가 피해자에 대한 불법행위를 구성하는 경우, 이에 가담한 사원은 피해자에 대하여 대표자와 연대하여 손해배상책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>문3·공동불법행위</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>가담한 사원은 공동불법행위자로서 대표자와 연대하여 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>민법 제760조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>제760조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>피해자가 법인 대표자의 행위가 직무에 관한 것이 아님을 알았거나 중대한 과실로 알지 못한 경우에는 법인에 대하여 손해배상책임을 물을 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>문3·외형이론</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>판례는 피해자가 직무 외 행위임을 알았거나 중과실로 몰랐으면 법인 책임을 부정한다.</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>대판 2004.3.26. 2003다34045</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>행위의 외형상 법인 대표자의 직무행위라고 인정될 수 있는 것이라면, 대표자 개인의 사리를 도모하기 위한 것이거나 법령에 위배된 것이더라도 민법 제35조 제1항의 직무에 관한 행위에 해당한다.</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>문3·직무관련성</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>판례는 외형상 직무행위로 보이면 사리도모·법령위배라도 직무관련성을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>대판 2004.2.27. 2003다15280</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>재개발조합 대표기관의 직무상 불법행위로 조합이 과다한 채무를 부담하여 조합원의 경제적 이익이 침해된 경우, 그 조합원의 간접적인 손해는 민법 제35조에서 말하는 손해의 개념에 포함되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>문3·간접손해</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>판례는 조합원이 입은 간접손해는 제35조의 손해에 포함되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>대판 1999.7.27. 99다19384</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>제35조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>장래에 발생할 막연한 사정을 예측·기대하고 법률행위를 한 경우 그 예측과 다른 사정이 발생하였더라도, 그로 인한 위험은 원칙적으로 행위자가 스스로 감수하여야 하므로 착오를 이유로 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>문4·장래예측착오</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>판례는 장래의 불확실한 사정에 대한 예측 착오의 위험은 원칙적으로 행위자가 부담한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>대판 2010.5.27. 2009다94841</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>표의자에게 중대한 과실이 있어 착오에 빠졌더라도 상대방이 표의자의 착오를 알면서 이를 이용한 경우에는, 표의자는 착오를 이유로 의사표시를 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>문4·중과실예외</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>판례는 상대방이 표의자의 착오를 알고 이용한 경우에는 표의자의 중과실에도 불구하고 취소를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>대판 2014.11.27. 2013다49794</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>보험회사의 설명의무 위반으로 고객이 계약의 중요 사항을 이해하지 못한 채 착오에 빠져 계약을 체결한 경우, 그 착오가 동기의 착오라도 그것이 없었다면 계약을 체결하지 않았을 것이 명백하면 중요 부분의 착오로서 취소할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>문4·동기착오</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>판례는 설명의무 위반으로 유발된 동기 착오도 중요 부분에 해당하면 취소를 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>대판 2018.4.12. 2017다229536</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>통정허위표시로 매매하고 등기를 마쳐 준 후, 그 사실을 과실로 알지 못한 채 목적물을 다시 매수하여 등기를 마친 자에 대하여, 매도인은 통정허위표시임을 이유로 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>문5·허위표시제3자</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>민법 제108조 제2항의 선의의 제3자는 과실이 있어도 보호되므로, 과실로 모른 선의의 제3자에게는 통정허위표시의 무효로 대항할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>민법 제108조 제2항</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>제108조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>매매목적물의 하자가 계약 내용의 중요 부분에 해당하여 하자담보책임으로 계약을 해제하거나 손해배상을 청구할 수 있는 경우, 매수인은 착오를 이유로는 그 매매계약을 취소할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>문5·담보책임착오경합</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>판례는 하자담보책임과 착오취소는 경합할 수 있으므로, 담보책임을 물을 수 있는 경우에도 착오를 이유로 취소할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>대판 2018.9.13. 2015다78703</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>제109조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>경제적·사실적으로 일체로 체결된 임차권양도계약과 권리금계약에서 당사자가 어느 한 계약 없이는 다른 계약을 의욕하지 않았을 것으로 보이는 경우, 권리금계약을 기망을 이유로 취소하면 임차권양도계약에도 취소의 효력이 미친다.</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>문5·일체계약취소</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>판례는 불가분적으로 결합된 계약 중 하나의 취소가 전체에 미친다고 본다.</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>대판 2013.5.9. 2012다115120</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>제137조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>사기로 매도하고 등기를 마쳐 준 후 그로부터 목적물을 매수하여 등기한 제3자에게 사기 취소의 효과를 주장하는 경우, 그 제3자의 악의에 대한 증명책임은 취소를 주장하는 자에게 있다.</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>문5·제3자악의입증</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>제110조 제3항의 제3자는 선의로 추정되므로 악의의 증명책임은 취소를 주장하는 자가 진다.</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>민법 제110조 제3항 · 판례</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>제110조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>동일한 채권자와 채무자 사이에 시효가 완성되지 않은 다수의 금전채무가 있고 채무자가 충당할 채무를 지정하지 않은 채 전부를 변제하기에 부족한 금액을 변제한 경우, 특별한 사정이 없는 한 그 변제는 모든 채무에 대한 승인으로서 시효중단의 효력이 있다.</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>문6·일부변제승인</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>판례는 충당 지정 없는 일부 변제는 다수 채무 전부에 대한 승인으로 시효를 중단시킨다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>대판 2021.9.30. 2021다239745</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>후순위 담보권자는 선순위 담보권의 피담보채권이 소멸하면 순위 상승과 배당액 증가의 이익을 얻으므로, 선순위 담보권의 피담보채권에 관한 소멸시효의 완성을 주장(원용)할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>문6·후순위시효원용</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>판례는 후순위 담보권자는 순위 상승의 이익이 반사적 이익에 불과하여 선순위 피담보채권의 소멸시효를 원용할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>대판 2021.2.25. 2016다232597</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>제162조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>매매계약의 무효를 원인으로 한 매매대금 상당의 부당이득반환청구권은 특별한 사정이 없는 한 매매대금을 지급한 때부터 소멸시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>문6·부당이득시효</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>부당이득반환청구권은 성립과 동시에 행사할 수 있으므로 급부(대금 지급) 시부터 시효가 진행한다.</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>대판 1993.9.14. 93다17324 · 판례</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>매도인이 선의인 계약명의신탁에서 신탁자가 수탁자에게 자금을 제공한 경우, 신탁자는 목적물의 소유권을 취득하지 못하고 수탁자에게 제공한 매수자금 상당액의 부당이득반환을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>문7·계약명의신탁</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>판례는 매도인 선의의 계약명의신탁에서 수탁자가 소유권을 취득하고 신탁자는 매수자금의 부당이득반환을 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>대판(전) 2005.1.27. 2002다42605</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>매도인이 선의인 계약명의신탁에서, 매도인이 매매계약 당시 명의신탁약정을 알았다면(악의) 명의신탁자는 매도인에게 직접 소유권이전등기절차의 이행을 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>문7·매도인악의</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>매도인이 악의이면 수탁자 명의 물권변동이 무효여서 소유권은 매도인에게 남고, 매매계약 당사자가 아닌 신탁자는 매도인에게 이전등기를 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>부동산실명법 제4조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>제103조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>매도인이 선의인 계약명의신탁에서 수탁자가 목적물을 제3자에게 매도하고 받은 대금 중 일부를 또 다른 제3자에게 지급한 경우, 그 금원을 받은 제3자는 명의신탁자에게 이를 부당이득으로 반환할 의무가 있다.</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>문7·제3자부당이득</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>수탁자로부터 금원을 받은 제3자는 신탁자와 사이에 아무런 법률관계가 없으므로 신탁자에게 부당이득반환의무를 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>민법 제741조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>선순위 근저당권과 후순위 근저당권, 그 후 가압류등기들이 차례로 마쳐진 부동산을 후순위 근저당권자가 매수하여 소유권을 취득한 경우, 그 후순위 근저당권은 혼동으로 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>문8·혼동근저당</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>후순위 근저당권자가 소유권을 취득해도 그 근저당권이 제3자(중간 가압류 등)의 권리의 목적이 되어 존속시킬 이익이 있으므로 혼동으로 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>민법 제191조 제1항 단서</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>제191조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>토지를 점유하던 자가 그 토지의 소유권을 취득한 경우, 그의 점유권은 혼동으로 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>문8·점유권혼동</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>민법 제191조 제3항에 따라 점유권에는 혼동에 관한 규정이 적용되지 않으므로 점유권은 혼동으로 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>민법 제191조 제3항</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>제191조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>주택임대차보호법상 대항력과 우선변제권을 갖춘 임차인이 그 후 설정된 저당권에 앞서는 지위에 있는 상태에서 임차주택의 소유권을 취득한 경우, 그 임차권은 혼동으로 소멸한다.</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>문8·임차권혼동</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>대항력·우선변제권 있는 임차권을 존속시킬 법률상 이익이 있는 경우에는 소유권 취득에도 임차권이 혼동으로 소멸하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>대판 2001.5.15. 2000다12693</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>제191조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>부동산이 전전 양도된 경우 적법한 원인행위에 기하여 일단 최종 양수인 명의로 중간생략등기가 이루어졌다면, 중간생략등기에 관한 합의가 없었다는 이유만으로는 그 등기가 무효가 되지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>문9·중간생략등기</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>판례는 실체관계에 부합하는 중간생략등기는 합의가 없었다는 사유만으로 무효가 되지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>대판 2005.9.29. 2003다40651</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>제186조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>채무자 소유 부동산과 물상보증인 소유 부동산에 공동저당권이 설정되고 두 부동산이 동시에 경매되는 경우, 공동저당권자는 두 부동산의 경매대가에 비례하여 안분 배당받는다.</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>문10·공동저당동시배당</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>채무자 소유와 물상보증인 소유 부동산이 함께 경매되는 경우에는 민법 제368조 제1항이 적용되지 않고, 채무자 소유 부동산의 경매대가에서 우선 배당받는다.</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>대판 2010.4.15. 2008다41475</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>물상보증인 소유 부동산이 먼저 경매되어 공동저당권자가 채권 전액을 배당받은 경우, 물상보증인 소유 부동산의 후순위 저당권자는 물상보증인을 대위하여 채무자 소유 부동산에 관한 저당권이전의 부기등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>문10·후순위대위</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>판례는 물상보증인의 변제자대위로 채무자 소유 부동산에 이전되는 저당권에 대하여 물상보증인 소유 부동산의 후순위 저당권자가 물상대위할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>대판 1994.5.10. 93다25417</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>제368조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>당사자는 합의로 대여금 채권의 소멸시효 기간을 20년으로 연장할 수 있고, 그 연장 합의로 연대보증채권의 소멸시효 기간도 20년으로 연장된다.</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>문11·시효연장합의</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>민법 제184조 제2항에 따라 소멸시효는 법률행위로 이를 배제·연장·가중할 수 없으므로 시효기간을 연장하는 합의는 효력이 없다.</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>민법 제184조 제2항</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>제184조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>채권자가 주채무자의 재산을 가압류하였으나 그 사실을 연대보증인에게 통지하지 않은 경우, 연대보증채권에 대해서는 시효중단의 효력이 발생하지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>문11·보증시효중단</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>민법 제440조에 따라 주채무자에 대한 시효중단은 보증인에게도 효력이 미치며, 보증인에 대한 별도의 통지는 필요하지 않다.</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>민법 제440조</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>제440조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>채무자가 제기한 채무부존재확인의 소에서 채권자가 청구기각을 구하며 채권의 존재를 적극적으로 주장하는 답변서를 제출한 경우, 그 응소는 재판상 청구에 준하여 답변서 제출 시에 시효중단의 효력이 생긴다.</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>문11·응소시효중단</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>판례는 채권자의 응소로 인한 시효중단은 현실적으로 권리를 주장한 때(답변서 제출 등)에 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>대판 2010.8.26. 2008다42416</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>부동산을 양수하여 소유권이전등기청구권을 가진 자가 양도인의 이중양도로 부동산 가액 상당의 손해배상채권을 취득한 경우, 그 손해배상채권은 이중양도행위에 대한 채권자취소권의 피보전채권이 된다.</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>문12·취소피보전채권</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>판례는 이중양도로 발생한 금전 손해배상채권이 사해행위인 이중양도에 대한 채권자취소권의 피보전채권이 될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>대판 1999.4.27. 98다56690</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>채무자가 신용카드 가입계약을 체결하였더라도 자신의 유일한 부동산을 매도한 후에 비로소 신용카드를 사용하여 카드대금을 연체한 경우, 그 카드대금채권은 사해행위 이후 발생한 채권이어서 채권자취소권의 피보전채권이 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>문12·사후발생채권</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>판례는 사해행위 후에 비로소 발생한 카드대금채권은 피보전채권이 될 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>대판 2004.11.12. 2004다40955</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>1534</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>채무초과 상태의 채무자가 소멸시효 완성 후에 한 소멸시효이익의 포기행위는 채권자취소권의 대상인 사해행위가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>문12·시효이익포기사해</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>판례는 채무초과 상태에서의 소멸시효이익 포기가 일반채권자를 해하는 사해행위가 될 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>대판 2013.5.31. 2012다4633</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>제406조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>토지와 그 지상 건물을 공유하던 자가 건물에 관한 자신의 공유지분만을 제3자에게 양도한 경우, 그 제3자는 토지 전부에 관하여 건물 소유를 위한 관습법상 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>문13·공유지분법정지상권</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>토지·건물 공유에서 건물 지분만의 양도로는 토지 공유자 전원의 처분이 아니어서 관습법상 법정지상권이 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>대판 2014.9.4. 2011다73038</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>토지와 미등기건물을 함께 매도하여 토지에 관하여만 매수인 명의로 소유권이전등기가 이루어진 경우, 매도인은 그 미등기건물의 소유를 위한 관습법상 법정지상권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>문13·미등기건물법정지상권</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>토지와 건물을 함께 매도한 경우에는 관습법상 법정지상권을 인정할 필요가 없어 매도인에게 성립하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>대판 2002.6.20. 2002다9660</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>제366조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>연대보증인은 채권자의 이행청구에 대하여 주채무자에게 변제자력이 있고 그 집행이 용이함을 증명하여 먼저 주채무자에게 집행할 것을 항변할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>문14·최고검색항변</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>연대보증인에게는 민법 제437조 단서에 따라 최고·검색의 항변권이 인정되지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>민법 제437조 단서</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>제437조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>부담부분 비율에 관한 특약이 없는 공동연대보증인 중 1인이 자신의 부담부분에 미치지 못하는 금액을 변제한 경우, 그는 다른 연대보증인에게 구상권을 행사할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>문14·보증인구상</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>공동보증인 사이의 구상은 자기의 부담부분을 넘는 변제를 한 경우에 인정된다.</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>민법 제448조</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>제448조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>면책적 채무인수에 관하여 채권자가 승낙을 거절하는 의사표시를 하였다가 이후 이를 번복하여 승낙한 경우, 면책적 채무인수의 효력은 채무인수계약이 성립한 때로 소급하여 발생한다.</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>문15·승낙거절후번복</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>채권자가 일단 승낙을 거절하면 그로써 채무인수의 효력이 확정적으로 발생하지 않게 되므로, 이후 다시 승낙하여도 소급효가 생기지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>민법 제457조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>제457조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>점유취득시효가 완성된 점유자가 그 권리를 행사하지 않는 동안 시효완성 사실을 모르는 소유자가 제3자에게 저당권을 설정해 준 후, 점유자가 시효완성을 원인으로 소유권이전등기를 마친 경우, 점유자는 저당권의 부담이 있는 채로 소유권을 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>문16·시효완성후저당</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>판례는 시효완성자가 등기 전에 설정된 저당권의 부담을 안은 채로 소유권을 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>대판 2006.5.12. 2005다75910</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>점유취득시효 완성자로부터 점유를 승계한 자는 전 점유자의 취득시효 완성의 효과를 주장하여 직접 자기에게 소유권이전등기를 청구할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>문16·점유승계</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>판례는 점유의 승계가 있어도 취득시효 완성으로 인한 소유권이전등기청구권 자체가 당연히 승계되는 것은 아니어서 직접 청구할 수 없다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>대판 1995.3.28. 93다47745</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>제245조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>채권자대위소송에서 제3채무자는 피대위채권에 대한 항변뿐만 아니라, 채권자의 채무자에 대한 피보전채권이 변제로 소멸하였다는 사정도 주장하여 다툴 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>문17·피보전채권다툼</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>제3채무자는 채권자와 채무자 사이의 피보전채권의 존부를 다툴 수 없고, 이는 채권자와 채무자 사이의 문제에 불과하다.</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>대판 2009.5.28. 2009다4787</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>1543</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>채무자의 부동산에 제3자 명의의 소유권이전등기청구권 보전 가등기가 있는 경우, 그 가등기가 담보가등기로서 강제집행을 통한 매각이 가능하다는 등의 특별한 사정이 없는 한, 채무자의 무자력 판단에서 그 부동산은 적극재산으로 산정할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>문17·무자력산정</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>판례는 순위보전 가등기가 있는 부동산은 책임재산으로 평가하기 어려워 적극재산에 산입하지 않는다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>대판 2009.2.26. 2008다76556</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>제404조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>구분소유적 공유관계를 표상하는 공유지분에 저당권이 설정된 후 특정 부분별로 토지가 분할되어 구분소유적 공유관계가 해소된 경우, 그 저당권은 종전의 구분소유적 공유지분의 비율대로 분할된 토지들 전부 위에 그대로 존속한다.</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>문18·구분공유저당</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>판례는 구분소유적 공유지분에 설정된 저당권은 분할 후에도 종전 지분 비율대로 분할된 각 토지 전부에 존속한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>대판 1989.8.8. 88다카24868</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>제356조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>공유물의 소수지분권자가 다른 공유자와 협의 없이 공유물의 전부 또는 일부를 독점적으로 점유하는 경우, 다른 소수지분권자는 보존행위로서 그 점유자를 상대로 공유물의 인도를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>문18·소수지분인도</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>판례(전합)는 소수지분권자는 다른 소수지분권자의 독점 점유에 대해 보존행위로 공유물 인도를 청구할 수 없고 방해배제만 구할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>대판(전) 2020.5.21. 2018다287522</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>1546</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>과반수 지분을 가진 공유자가 공유물을 제3자에게 임대하여 수익을 얻는 것은 적법한 관리행위이므로 다른 공유자에 대한 불법행위가 되지 않으나, 소수지분권자는 자신의 지분에 상응하는 차임 상당액을 부당이득으로 반환청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>문18·과반수임대</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>과반수 지분권자의 임대는 적법한 관리행위로 불법행위가 아니며, 소수지분권자는 지분 비율의 부당이득반환을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>대판 1991.9.24. 88다카33855</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>제265조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>불법행위로 건물이 훼손되어 사용·수리가 불가능한 경우, 특별한 사정이 없는 한 건물의 시가 외에 건물의 철거 비용도 통상손해의 범위에 포함된다.</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>문19·철거비용</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>판례는 건물의 멸실에 준하는 훼손의 경우 시가 외에 철거비용도 통상손해에 포함된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>대판 2022.6.30. 2022다214042 · 판례</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>제393조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>이행기의 정함이 없는 채권의 양수인이 대항요건을 갖추지 못한 채 채무자를 상대로 이행의 소를 제기하고 소송 계속 중 채권양도통지가 이루어진 경우, 특별한 사정이 없는 한 채무자는 그 통지가 도달한 다음 날부터 이행지체의 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>문23·이행지체기산</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>판례는 이행기 없는 채권에서 대항요건(통지)이 갖추어져 이행청구의 효력이 생긴 다음 날부터 지체책임이 발생한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>대판 2014.4.10. 2012다29557</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>채권이 가압류되면 제3채무자는 채무자에게 지급하는 것이 금지되므로, 그 채권의 이행기가 경과하더라도 제3채무자는 이행지체의 책임을 지지 않는다.</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>문23·가압류지체</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>채권의 가압류는 변제를 금지할 뿐이므로 이행기가 도래하면 제3채무자는 여전히 지체책임을 면하지 못한다.</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>대판 1994.12.13. 93다951</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>제387조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>매매목적 부동산에 이미 제3자의 처분금지가처분 등기가 기입되어 있다는 사정만으로는 소유권이전등기절차의 이행이 불가능하게 되어 곧바로 매매계약이 이행불능으로 되는 것은 아니다.</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>문23·가처분이행불능</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>판례는 처분금지가처분 등기가 있더라도 그 사정만으로 매매가 이행불능이 되는 것은 아니라고 한다.</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>대판 1999.6.11. 99다11045</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>제390조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>저당권과 함께 피담보채권을 양수한 자가 저당권이전의 부기등기를 마치고 저당권 실행 요건을 갖춘 경우, 채권양도의 대항요건을 갖추지 않았더라도 경매를 신청할 수 있고 경매개시결정 시 대항요건을 증명할 필요가 없다.</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>문24·저당권부채권경매</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>판례는 저당권부 채권 양수인이 부기등기를 마치면 대항요건 없이도 경매를 신청할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>대판 2005.6.23. 2004다29279</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>제361조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>1552</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>양도금지특약을 위반하여 양도된 채권을 선의이며 중과실 없는 양수인이 취득한 후 다시 전득한 자는, 그 전득자가 양도금지특약을 알았거나 중과실로 알지 못하였더라도 채권을 유효하게 취득한다.</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>문24·전득자취득</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>판례는 선의·무중과실의 양수인이 일단 유효하게 취득하면 그로부터의 전득자는 악의라도 채권을 유효하게 취득한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>대판 2015.4.9. 2012다118020</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>양도금지특약이 있는 채권의 양수인이 양수금 지급을 청구하는 경우, 양수인이 그 특약을 알지 못하였고 알지 못한 데 중과실이 없다는 점을 스스로 주장·증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>문24·증명책임</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>양도금지특약의 존재와 양수인의 악의·중과실은 이를 이유로 무효를 주장하는 채무자가 주장·증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>대판 2019.12.19. 2016다24284</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>제449조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>1554</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>저당물의 제3취득자가 그 부동산에 지출한 필요비·유익비는 민법 제367조에 따라 경매대가에서 우선 상환받을 수 있으므로, 제3취득자는 그 비용상환청구권을 피담보채권으로 하여 경매의 매수인에게 유치권으로 대항할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>문25·제367조유치권</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>제367조의 비용상환청구권은 경매대가에서 우선상환을 받을 수 있을 뿐이고, 이를 피담보채권으로 한 유치권으로 매수인에게 대항할 수는 없다.</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>대판 2023.7.13. 2022다265093</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>제367조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>유치권자가 피담보채권에 대한 별도의 시효중단 조치 없이 유치권확인의 소만을 제기하였더라도, 그 소송에서 피담보채권의 존재에 관한 주장에 대하여 실질적인 심리가 이루어졌다면 재판상 청구에 준하는 소멸시효 중단의 효력이 인정된다.</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>문25·유치권확인시효</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>판례는 유치권확인소송에서 피담보채권에 관한 실질적 심리가 이루어지면 재판상 청구에 준하여 시효중단 효력을 인정한다.</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>대판 2019.3.14. 2018다255648</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>제168조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>1556</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>착오송금을 이유로 부당이득반환을 청구하는 소송에서 송금에 착오가 있었는지에 대한 증명책임은 반환을 구하는 송금인에게 있다.</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>문26·착오송금입증</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>부당이득반환을 구하는 자가 법률상 원인 없음(착오)을 증명하여야 한다.</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>민법 제741조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>토지소유자가 불법점유자를 상대로 차임 상당 부당이득반환을 청구하는 소송에서 점유자가 '불법점유가 없었더라도 소유자에게 차임 상당 이익이 발생할 여지가 없었다'고 주장하는 경우, 그 특별한 사정에 대한 증명책임은 점유자가 진다.</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>문26·손실부존재입증</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>판례는 손실이 없었다는 특별한 사정은 이를 주장하는 점유자(이득자)가 증명하여야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>대판 2008.1.17. 2006다586</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>제741조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>기존 금전채무의 변제에 갈음하여 부동산 소유권을 이전하기로 하는 대물변제예약을 체결한 경우, 소유권이전등기를 완료하기 전에 기존 금전채무가 소멸하였더라도 당사자 사이에서는 예약된 대물변제 계약에 기하여 소유권이전등기를 청구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>문27·대물변제예약</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>대물변제예약은 기존 채무의 변제를 위한 것이므로 기존 채무가 소멸하면 대물변제할 이유가 없어 소유권이전등기를 청구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>민법 제466조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>제466조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>1559</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>변제기 전 변제에 관한 약정이 없는 이자부 금전소비대차의 채무자가 변제기 전에 변제하는 경우, 변제기까지의 약정이자 등 채권자의 손해를 함께 제공하지 않으면 채권자는 그 수령을 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>문27·기한전변제</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>판례는 이자부 소비대차에서 기한 전 변제 시 채권자의 기한이익(약정이자)을 배상하지 않으면 수령을 거절할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>민법 제468조 · 판례</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>제468조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>1560</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>공작물책임에서 공작물이 본래 갖추어야 할 안전성은 그 용도에 한정된 안전성만이 아니라, 공작물이 현실적으로 설치되어 사용되고 있는 상황에서 요구되는 안전성을 의미한다.</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>문28·공작물안전성</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>판례는 공작물의 안전성을 현실적 설치·사용 상황에서 요구되는 정도로 본다.</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>대판 2018.7.12. 2015다68348 · 판례</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>제758조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>공작물책임에서 공작물의 점유자는 자신의 과실 유무와 관계없이 책임을 지고, 소유자는 자신의 과실이 있는 경우에만 책임을 진다.</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>문28·점유자소유자책임</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>점유자는 손해 방지에 필요한 주의를 다하였음을 증명하면 면책되는 중간책임을 지고, 소유자는 면책이 인정되지 않는 무과실책임을 진다.</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>민법 제758조 제1항</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>제758조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>1562</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>부동산 매매에서 매수인이 선이행하여야 할 중도금을 지급하지 않은 채 잔대금 지급일을 경과한 경우, 특별한 사정이 없는 한 매수인의 중도금 및 그에 대한 지연손해금과 잔대금 지급의무는 매도인의 소유권이전등기의무와 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>문29·중도금동시이행</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>판례는 중도금 미지급 후 잔대금일이 지나면 중도금·지연손해금·잔대금 지급의무와 이전등기의무가 동시이행관계에 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>대판 1991.3.27. 90다19930</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>동시이행관계에 있는 쌍방 채무 중 어느 한 채무가 이행불능이 되어 손해배상채무로 변한 경우, 그 손해배상채무도 다른 채무와 여전히 동시이행관계에 있다.</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>문29·손배동시이행</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>판례는 동시이행관계의 채무가 손해배상채무로 변경되어도 동일성이 유지되어 동시이행관계가 존속한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>대판 2000.2.25. 97다30066</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>매수인이 매매대금을 완납하였다면 목적물을 아직 인도받지 못하였더라도 그 이후 목적물에서 생기는 과실의 수취권은 매수인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>문30·과실수취권</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>민법 제587조에 따라 매수인이 대금을 완납하면 그 후의 과실수취권은 매수인에게 귀속된다.</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>민법 제587조</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>제587조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>매매목적물을 인도받지 못하고 매수인 자신도 대금을 지급하지 않은 경우, 매수인은 매도인에게 인도의무의 지체로 인한 손해배상금의 지급을 구할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>문30·동시이행지체</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>매수인이 대금을 지급하지 않은 이상 매도인의 인도의무는 동시이행 항변으로 지체에 빠지지 않으므로 지체로 인한 손해배상을 구할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>민법 제536조 · 제587조</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>제536조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>1566</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>상가건물 임대차에서 임차인이 임대차기간 중 3기의 차임액에 이르도록 차임을 연체한 사실이 있다면, 계약갱신 요구 당시 연체액이 3기에 이르지 않게 되었더라도 임대인은 그 갱신 요구를 거절할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>문31·3기연체갱신</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>판례는 과거에 3기 연체 사실이 있으면 갱신 요구 당시 연체가 해소되었어도 갱신거절 사유가 된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>대판 2021.5.13. 2020다255429</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>제640조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>1567</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>임대차보증금이 수수된 임대차에서 차임채권에 압류 및 추심명령이 있었더라도, 임대차가 종료되어 목적물이 반환될 때까지 추심되지 않은 차임채권액은 임대차보증금에서 당연히 공제된다.</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>문31·차임공제</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>판례는 차임채권에 압류·추심명령이 있어도 종료 시까지 미추심 차임은 보증금에서 당연 공제된다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>대판 2004.12.23. 2004다56554</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>제618조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>자필증서에 의한 유언에서 유언자가 주소를 자서하지 않았더라도 유언자의 특정에 지장이 없다면 그 유언은 유효하다.</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>문32·자필증서주소</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>민법 제1066조는 자필증서 유언의 요건으로 주소의 자서를 요구하므로, 주소를 자서하지 않은 자필증서 유언은 무효이다.</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>민법 제1066조</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>제1066조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>유언증서가 성립한 후에 멸실되거나 분실되었더라도 유언자가 유언을 철회한 것으로 볼 수 없는 이상 그 사유만으로 유언이 실효되는 것은 아니고, 이해관계인은 유언증서의 내용을 증명하여 유언의 효력을 주장할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>문32·유언증서멸실</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>판례는 유언증서의 멸실·분실만으로 유언이 실효되지 않고 내용을 증명하여 효력을 주장할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>대판 1996.9.20. 96다21119</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>제1060조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>1570</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>가정법원은 부 또는 모가 친권을 남용하여 자녀의 복리를 현저히 해치거나 해칠 우려가 있는 경우, 일정한 기간을 정하여 그 친권을 상실시킬 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>문33·친권상실기간</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>친권상실 선고에는 기간을 정하지 않으며, 기간을 정하여 제한하는 것은 친권의 일시 정지에 해당한다.</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>민법 제924조</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>제924조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>상속재산분할에 관하여 공동상속인 사이에 협의가 성립되지 않거나 협의할 수 없는 경우, 각 공동상속인은 상속재산에 속하는 개별 재산에 관하여 공유물분할청구의 소를 제기할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>문34·상속공유물분할</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>상속재산분할은 가사비송인 상속재산분할심판에 의하여야 하고, 개별 재산에 관한 공유물분할청구의 소로 할 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>대판 2015.8.13. 2015다18367</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>제1013조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>협의분할로 공동상속인 중 일부가 자기 고유의 상속분을 초과하여 상속재산을 취득한 경우, 이는 상속개시 당시에 소급하여 피상속인으로부터 승계받은 것으로 보아야 하고 다른 공동상속인으로부터 증여받은 것으로 볼 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>문34·협의분할소급</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>민법 제1015조에 따라 상속재산분할은 상속개시 시로 소급하여 효력이 있으므로 증여로 보지 않는다.</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>민법 제1015조</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>제1015조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>이혼에 따른 재산분할에서 일방이 제3자와 합유하는 재산은 임의로 처분할 수 없어 직접 분할을 명할 수는 없으나, 그 지분의 가액을 산정하여 분할 대상으로 삼거나 다른 재산의 분할에 참작하는 방법으로 분할 대상에 포함하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>문35·합유재산분할</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>판례는 합유재산은 직접 분할을 명할 수 없으나 지분 가액을 산정하여 재산분할에 참작하여야 한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>대판 2009.11.12. 2009므2840</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>이혼에 따른 재산분할 사건에서 법원은 당사자가 특정한 분할 방법에 구애받지 않고 재산분할의 대상과 가액을 직권으로 조사·판단할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>문35·직권조사</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>재산분할은 가사비송사건으로 법원이 후견적 입장에서 직권으로 대상과 가액을 조사·판단한다.</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>대판 2022.1.27. 2018므11273 · 판례</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>재산분할청구권은 이혼이 성립한 때 법적 효과로서 발생하므로, 협의나 심판에 의하여 그 구체적 내용이 형성되기 전이라도 이혼 성립 후에는 곧바로 채권양도의 대상이 된다.</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>문35·분할청구권양도</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>협의나 심판으로 구체적 내용이 형성되기 전의 재산분할청구권은 범위와 내용이 불명확하여 양도의 대상이 될 수 없다.</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>대판 1999.4.9. 98다58016</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>제839조의2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/ox_civil_bar14.xlsx
+++ b/assets/ox_civil_bar14.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1430"/>
+  <dimension ref="A1:H1435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -55920,17 +55920,17 @@
       </c>
       <c r="D1387" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>문12·취소피보전채권</t>
+          <t>문12·이중양도피보전채권</t>
         </is>
       </c>
       <c r="F1387" t="inlineStr">
         <is>
-          <t>판례는 이중양도로 발생한 금전 손해배상채권이 사해행위인 이중양도에 대한 채권자취소권의 피보전채권이 될 수 있다고 한다.</t>
+          <t>판례는 이중양도로 취득하는 부동산 가액 상당의 손해배상채권은 사해행위(이중양도) 이후에 발생한 것이어서 그 이중양도행위에 대한 채권자취소권의 피보전채권이 될 수 없다고 한다.</t>
         </is>
       </c>
       <c r="G1387" t="inlineStr">
@@ -56315,27 +56315,27 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>채권자대위소송에서 제3채무자는 피대위채권에 대한 항변뿐만 아니라, 채권자의 채무자에 대한 피보전채권이 변제로 소멸하였다는 사정도 주장하여 다툴 수 있다.</t>
+          <t>채권자대위소송에서 제3채무자는 채권자의 채무자에 대한 피보전채권이 발생원인인 법률행위의 무효나 변제로 소멸하였다는 사정을 주장하여 다툴 수 있고, 이 경우 법원은 피보전채권의 존부를 직권으로 심리·판단하여야 한다.</t>
         </is>
       </c>
       <c r="D1397" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>문17·피보전채권다툼</t>
+          <t>문17·피보전채권소송요건</t>
         </is>
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>제3채무자는 채권자와 채무자 사이의 피보전채권의 존부를 다툴 수 없고, 이는 채권자와 채무자 사이의 문제에 불과하다.</t>
+          <t>피보전채권의 존재는 채권자대위소송의 당사자적격에 관한 소송요건으로 법원의 직권조사사항이므로, 제3채무자도 그 부존재(무효·변제소멸)를 주장하여 다툴 수 있다.</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>대판 2009.5.28. 2009다4787</t>
+          <t>대판 2009.4.23. 2009다3234</t>
         </is>
       </c>
       <c r="H1397" t="inlineStr">
@@ -56506,7 +56506,7 @@
     </row>
     <row r="1402">
       <c r="A1402" t="n">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>불법행위로 건물이 훼손되어 사용·수리가 불가능한 경우, 특별한 사정이 없는 한 건물의 시가 외에 건물의 철거 비용도 통상손해의 범위에 포함된다.</t>
+          <t>이행기의 정함이 없는 채권의 양수인이 대항요건을 갖추지 못한 채 채무자를 상대로 이행의 소를 제기하고 소송 계속 중 채권양도통지가 이루어진 경우, 특별한 사정이 없는 한 채무자는 그 통지가 도달한 다음 날부터 이행지체의 책임을 진다.</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr">
@@ -56525,28 +56525,28 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>문19·철거비용</t>
+          <t>문23·이행지체기산</t>
         </is>
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>판례는 건물의 멸실에 준하는 훼손의 경우 시가 외에 철거비용도 통상손해에 포함된다고 한다.</t>
+          <t>판례는 이행기 없는 채권에서 대항요건(통지)이 갖추어져 이행청구의 효력이 생긴 다음 날부터 지체책임이 발생한다고 한다.</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
-          <t>대판 2022.6.30. 2022다214042 · 판례</t>
+          <t>대판 2014.4.10. 2012다29557</t>
         </is>
       </c>
       <c r="H1402" t="inlineStr">
         <is>
-          <t>제393조</t>
+          <t>제387조</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="n">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
@@ -56555,27 +56555,27 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>이행기의 정함이 없는 채권의 양수인이 대항요건을 갖추지 못한 채 채무자를 상대로 이행의 소를 제기하고 소송 계속 중 채권양도통지가 이루어진 경우, 특별한 사정이 없는 한 채무자는 그 통지가 도달한 다음 날부터 이행지체의 책임을 진다.</t>
+          <t>채권이 가압류되면 제3채무자는 채무자에게 지급하는 것이 금지되므로, 그 채권의 이행기가 경과하더라도 제3채무자는 이행지체의 책임을 지지 않는다.</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>문23·이행지체기산</t>
+          <t>문23·가압류지체</t>
         </is>
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>판례는 이행기 없는 채권에서 대항요건(통지)이 갖추어져 이행청구의 효력이 생긴 다음 날부터 지체책임이 발생한다고 한다.</t>
+          <t>채권의 가압류는 변제를 금지할 뿐이므로 이행기가 도래하면 제3채무자는 여전히 지체책임을 면하지 못한다.</t>
         </is>
       </c>
       <c r="G1403" t="inlineStr">
         <is>
-          <t>대판 2014.4.10. 2012다29557</t>
+          <t>대판 1994.12.13. 93다951</t>
         </is>
       </c>
       <c r="H1403" t="inlineStr">
@@ -56586,7 +56586,7 @@
     </row>
     <row r="1404">
       <c r="A1404" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
@@ -56595,38 +56595,38 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>채권이 가압류되면 제3채무자는 채무자에게 지급하는 것이 금지되므로, 그 채권의 이행기가 경과하더라도 제3채무자는 이행지체의 책임을 지지 않는다.</t>
+          <t>매매목적 부동산에 이미 제3자의 처분금지가처분 등기가 기입되어 있다는 사정만으로는 소유권이전등기절차의 이행이 불가능하게 되어 곧바로 매매계약이 이행불능으로 되는 것은 아니다.</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>문23·가압류지체</t>
+          <t>문23·가처분이행불능</t>
         </is>
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>채권의 가압류는 변제를 금지할 뿐이므로 이행기가 도래하면 제3채무자는 여전히 지체책임을 면하지 못한다.</t>
+          <t>판례는 처분금지가처분 등기가 있더라도 그 사정만으로 매매가 이행불능이 되는 것은 아니라고 한다.</t>
         </is>
       </c>
       <c r="G1404" t="inlineStr">
         <is>
-          <t>대판 1994.12.13. 93다951</t>
+          <t>대판 1999.6.11. 99다11045</t>
         </is>
       </c>
       <c r="H1404" t="inlineStr">
         <is>
-          <t>제387조</t>
+          <t>제390조</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="n">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>매매목적 부동산에 이미 제3자의 처분금지가처분 등기가 기입되어 있다는 사정만으로는 소유권이전등기절차의 이행이 불가능하게 되어 곧바로 매매계약이 이행불능으로 되는 것은 아니다.</t>
+          <t>저당권과 함께 피담보채권을 양수한 자가 저당권이전의 부기등기를 마치고 저당권 실행 요건을 갖춘 경우, 채권양도의 대항요건을 갖추지 않았더라도 경매를 신청할 수 있고 경매개시결정 시 대항요건을 증명할 필요가 없다.</t>
         </is>
       </c>
       <c r="D1405" t="inlineStr">
@@ -56645,28 +56645,28 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>문23·가처분이행불능</t>
+          <t>문24·저당권부채권경매</t>
         </is>
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>판례는 처분금지가처분 등기가 있더라도 그 사정만으로 매매가 이행불능이 되는 것은 아니라고 한다.</t>
+          <t>판례는 저당권부 채권 양수인이 부기등기를 마치면 대항요건 없이도 경매를 신청할 수 있다고 한다.</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">
         <is>
-          <t>대판 1999.6.11. 99다11045</t>
+          <t>대판 2005.6.23. 2004다29279</t>
         </is>
       </c>
       <c r="H1405" t="inlineStr">
         <is>
-          <t>제390조</t>
+          <t>제361조</t>
         </is>
       </c>
     </row>
     <row r="1406">
       <c r="A1406" t="n">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>저당권과 함께 피담보채권을 양수한 자가 저당권이전의 부기등기를 마치고 저당권 실행 요건을 갖춘 경우, 채권양도의 대항요건을 갖추지 않았더라도 경매를 신청할 수 있고 경매개시결정 시 대항요건을 증명할 필요가 없다.</t>
+          <t>양도금지특약을 위반하여 양도된 채권을 선의이며 중과실 없는 양수인이 취득한 후 다시 전득한 자는, 그 전득자가 양도금지특약을 알았거나 중과실로 알지 못하였더라도 채권을 유효하게 취득한다.</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr">
@@ -56685,28 +56685,28 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>문24·저당권부채권경매</t>
+          <t>문24·전득자취득</t>
         </is>
       </c>
       <c r="F1406" t="inlineStr">
         <is>
-          <t>판례는 저당권부 채권 양수인이 부기등기를 마치면 대항요건 없이도 경매를 신청할 수 있다고 한다.</t>
+          <t>판례는 선의·무중과실의 양수인이 일단 유효하게 취득하면 그로부터의 전득자는 악의라도 채권을 유효하게 취득한다고 한다.</t>
         </is>
       </c>
       <c r="G1406" t="inlineStr">
         <is>
-          <t>대판 2005.6.23. 2004다29279</t>
+          <t>대판 2015.4.9. 2012다118020</t>
         </is>
       </c>
       <c r="H1406" t="inlineStr">
         <is>
-          <t>제361조</t>
+          <t>제449조</t>
         </is>
       </c>
     </row>
     <row r="1407">
       <c r="A1407" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
@@ -56715,27 +56715,27 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>양도금지특약을 위반하여 양도된 채권을 선의이며 중과실 없는 양수인이 취득한 후 다시 전득한 자는, 그 전득자가 양도금지특약을 알았거나 중과실로 알지 못하였더라도 채권을 유효하게 취득한다.</t>
+          <t>양도금지특약이 있는 채권의 양수인이 양수금 지급을 청구하는 경우, 양수인이 그 특약을 알지 못하였고 알지 못한 데 중과실이 없다는 점을 스스로 주장·증명하여야 한다.</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>문24·전득자취득</t>
+          <t>문24·증명책임</t>
         </is>
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>판례는 선의·무중과실의 양수인이 일단 유효하게 취득하면 그로부터의 전득자는 악의라도 채권을 유효하게 취득한다고 한다.</t>
+          <t>양도금지특약의 존재와 양수인의 악의·중과실은 이를 이유로 무효를 주장하는 채무자가 주장·증명하여야 한다.</t>
         </is>
       </c>
       <c r="G1407" t="inlineStr">
         <is>
-          <t>대판 2015.4.9. 2012다118020</t>
+          <t>대판 2019.12.19. 2016다24284</t>
         </is>
       </c>
       <c r="H1407" t="inlineStr">
@@ -56746,7 +56746,7 @@
     </row>
     <row r="1408">
       <c r="A1408" t="n">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
@@ -56755,7 +56755,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>양도금지특약이 있는 채권의 양수인이 양수금 지급을 청구하는 경우, 양수인이 그 특약을 알지 못하였고 알지 못한 데 중과실이 없다는 점을 스스로 주장·증명하여야 한다.</t>
+          <t>저당물의 제3취득자가 그 부동산에 지출한 필요비·유익비는 민법 제367조에 따라 경매대가에서 우선 상환받을 수 있으므로, 제3취득자는 그 비용상환청구권을 피담보채권으로 하여 경매의 매수인에게 유치권으로 대항할 수 있다.</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr">
@@ -56765,28 +56765,28 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>문24·증명책임</t>
+          <t>문25·제367조유치권</t>
         </is>
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>양도금지특약의 존재와 양수인의 악의·중과실은 이를 이유로 무효를 주장하는 채무자가 주장·증명하여야 한다.</t>
+          <t>제367조의 비용상환청구권은 경매대가에서 우선상환을 받을 수 있을 뿐이고, 이를 피담보채권으로 한 유치권으로 매수인에게 대항할 수는 없다.</t>
         </is>
       </c>
       <c r="G1408" t="inlineStr">
         <is>
-          <t>대판 2019.12.19. 2016다24284</t>
+          <t>대판 2023.7.13. 2022다265093</t>
         </is>
       </c>
       <c r="H1408" t="inlineStr">
         <is>
-          <t>제449조</t>
+          <t>제367조</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="n">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
@@ -56795,38 +56795,38 @@
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>저당물의 제3취득자가 그 부동산에 지출한 필요비·유익비는 민법 제367조에 따라 경매대가에서 우선 상환받을 수 있으므로, 제3취득자는 그 비용상환청구권을 피담보채권으로 하여 경매의 매수인에게 유치권으로 대항할 수 있다.</t>
+          <t>유치권자가 피담보채권에 대한 별도의 시효중단 조치 없이 유치권확인의 소만을 제기하였더라도, 그 소송에서 피담보채권의 존재에 관한 주장에 대하여 실질적인 심리가 이루어졌다면 재판상 청구에 준하는 소멸시효 중단의 효력이 인정된다.</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>문25·제367조유치권</t>
+          <t>문25·유치권확인시효</t>
         </is>
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>제367조의 비용상환청구권은 경매대가에서 우선상환을 받을 수 있을 뿐이고, 이를 피담보채권으로 한 유치권으로 매수인에게 대항할 수는 없다.</t>
+          <t>판례는 유치권 존재확인의 소에서 피담보채권에 관한 권리 실행의 의사가 표명되고 실질적으로 심리되면 재판상 청구에 준하여 그 피담보채권의 소멸시효 중단의 효력이 인정된다고 한다.</t>
         </is>
       </c>
       <c r="G1409" t="inlineStr">
         <is>
-          <t>대판 2023.7.13. 2022다265093</t>
+          <t>대판 2024.10.31. 2024다241152</t>
         </is>
       </c>
       <c r="H1409" t="inlineStr">
         <is>
-          <t>제367조</t>
+          <t>제168조</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="n">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>유치권자가 피담보채권에 대한 별도의 시효중단 조치 없이 유치권확인의 소만을 제기하였더라도, 그 소송에서 피담보채권의 존재에 관한 주장에 대하여 실질적인 심리가 이루어졌다면 재판상 청구에 준하는 소멸시효 중단의 효력이 인정된다.</t>
+          <t>착오송금을 이유로 부당이득반환을 청구하는 소송에서 송금에 착오가 있었는지에 대한 증명책임은 반환을 구하는 송금인에게 있다.</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
@@ -56845,28 +56845,28 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>문25·유치권확인시효</t>
+          <t>문26·착오송금입증</t>
         </is>
       </c>
       <c r="F1410" t="inlineStr">
         <is>
-          <t>판례는 유치권확인소송에서 피담보채권에 관한 실질적 심리가 이루어지면 재판상 청구에 준하여 시효중단 효력을 인정한다.</t>
+          <t>부당이득반환을 구하는 자가 법률상 원인 없음(착오)을 증명하여야 한다.</t>
         </is>
       </c>
       <c r="G1410" t="inlineStr">
         <is>
-          <t>대판 2019.3.14. 2018다255648</t>
+          <t>민법 제741조 · 판례</t>
         </is>
       </c>
       <c r="H1410" t="inlineStr">
         <is>
-          <t>제168조</t>
+          <t>제741조</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="n">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>착오송금을 이유로 부당이득반환을 청구하는 소송에서 송금에 착오가 있었는지에 대한 증명책임은 반환을 구하는 송금인에게 있다.</t>
+          <t>토지소유자가 불법점유자를 상대로 차임 상당 부당이득반환을 청구하는 소송에서 점유자가 '불법점유가 없었더라도 소유자에게 차임 상당 이익이 발생할 여지가 없었다'고 주장하는 경우, 그 특별한 사정에 대한 증명책임은 점유자가 진다.</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
@@ -56885,17 +56885,17 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>문26·착오송금입증</t>
+          <t>문26·손실부존재입증</t>
         </is>
       </c>
       <c r="F1411" t="inlineStr">
         <is>
-          <t>부당이득반환을 구하는 자가 법률상 원인 없음(착오)을 증명하여야 한다.</t>
+          <t>판례는 손실이 없었다는 특별한 사정은 이를 주장하는 점유자(이득자)가 증명하여야 한다고 한다.</t>
         </is>
       </c>
       <c r="G1411" t="inlineStr">
         <is>
-          <t>민법 제741조 · 판례</t>
+          <t>대판 2008.1.17. 2006다586</t>
         </is>
       </c>
       <c r="H1411" t="inlineStr">
@@ -56906,7 +56906,7 @@
     </row>
     <row r="1412">
       <c r="A1412" t="n">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
@@ -56915,38 +56915,38 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>토지소유자가 불법점유자를 상대로 차임 상당 부당이득반환을 청구하는 소송에서 점유자가 '불법점유가 없었더라도 소유자에게 차임 상당 이익이 발생할 여지가 없었다'고 주장하는 경우, 그 특별한 사정에 대한 증명책임은 점유자가 진다.</t>
+          <t>기존 금전채무의 변제에 갈음하여 부동산 소유권을 이전하기로 하는 대물변제예약을 체결한 경우, 소유권이전등기를 완료하기 전에 기존 금전채무가 소멸하였더라도 당사자 사이에서는 예약된 대물변제 계약에 기하여 소유권이전등기를 청구할 수 있다.</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1412" t="inlineStr">
         <is>
-          <t>문26·손실부존재입증</t>
+          <t>문27·대물변제예약</t>
         </is>
       </c>
       <c r="F1412" t="inlineStr">
         <is>
-          <t>판례는 손실이 없었다는 특별한 사정은 이를 주장하는 점유자(이득자)가 증명하여야 한다고 한다.</t>
+          <t>대물변제예약은 기존 채무의 변제를 위한 것이므로 기존 채무가 소멸하면 대물변제할 이유가 없어 소유권이전등기를 청구할 수 없다.</t>
         </is>
       </c>
       <c r="G1412" t="inlineStr">
         <is>
-          <t>대판 2008.1.17. 2006다586</t>
+          <t>민법 제466조 · 판례</t>
         </is>
       </c>
       <c r="H1412" t="inlineStr">
         <is>
-          <t>제741조</t>
+          <t>제466조</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="n">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
@@ -56955,38 +56955,38 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>기존 금전채무의 변제에 갈음하여 부동산 소유권을 이전하기로 하는 대물변제예약을 체결한 경우, 소유권이전등기를 완료하기 전에 기존 금전채무가 소멸하였더라도 당사자 사이에서는 예약된 대물변제 계약에 기하여 소유권이전등기를 청구할 수 있다.</t>
+          <t>변제기 전 변제에 관한 약정이 없는 이자부 금전소비대차의 채무자가 변제기 전에 변제하는 경우, 변제기까지의 약정이자 등 채권자의 손해를 함께 제공하지 않으면 채권자는 그 수령을 거절할 수 있다.</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1413" t="inlineStr">
         <is>
-          <t>문27·대물변제예약</t>
+          <t>문27·기한전변제</t>
         </is>
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>대물변제예약은 기존 채무의 변제를 위한 것이므로 기존 채무가 소멸하면 대물변제할 이유가 없어 소유권이전등기를 청구할 수 없다.</t>
+          <t>판례는 이자부 소비대차에서 기한 전 변제 시 채권자의 기한이익(약정이자)을 배상하지 않으면 수령을 거절할 수 있다고 한다.</t>
         </is>
       </c>
       <c r="G1413" t="inlineStr">
         <is>
-          <t>민법 제466조 · 판례</t>
+          <t>민법 제468조 · 판례</t>
         </is>
       </c>
       <c r="H1413" t="inlineStr">
         <is>
-          <t>제466조</t>
+          <t>제468조</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>변제기 전 변제에 관한 약정이 없는 이자부 금전소비대차의 채무자가 변제기 전에 변제하는 경우, 변제기까지의 약정이자 등 채권자의 손해를 함께 제공하지 않으면 채권자는 그 수령을 거절할 수 있다.</t>
+          <t>공작물책임에서 공작물이 본래 갖추어야 할 안전성은 그 용도에 한정된 안전성만이 아니라, 공작물이 현실적으로 설치되어 사용되고 있는 상황에서 요구되는 안전성을 의미한다.</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr">
@@ -57005,28 +57005,28 @@
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>문27·기한전변제</t>
+          <t>문28·공작물안전성</t>
         </is>
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>판례는 이자부 소비대차에서 기한 전 변제 시 채권자의 기한이익(약정이자)을 배상하지 않으면 수령을 거절할 수 있다고 한다.</t>
+          <t>판례는 공작물의 안전성을 현실적 설치·사용 상황에서 요구되는 정도로 본다.</t>
         </is>
       </c>
       <c r="G1414" t="inlineStr">
         <is>
-          <t>민법 제468조 · 판례</t>
+          <t>대판 2018.7.12. 2015다68348 · 판례</t>
         </is>
       </c>
       <c r="H1414" t="inlineStr">
         <is>
-          <t>제468조</t>
+          <t>제758조</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="n">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
@@ -57035,27 +57035,27 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>공작물책임에서 공작물이 본래 갖추어야 할 안전성은 그 용도에 한정된 안전성만이 아니라, 공작물이 현실적으로 설치되어 사용되고 있는 상황에서 요구되는 안전성을 의미한다.</t>
+          <t>공작물책임에서 공작물의 점유자는 자신의 과실 유무와 관계없이 책임을 지고, 소유자는 자신의 과실이 있는 경우에만 책임을 진다.</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>문28·공작물안전성</t>
+          <t>문28·점유자소유자책임</t>
         </is>
       </c>
       <c r="F1415" t="inlineStr">
         <is>
-          <t>판례는 공작물의 안전성을 현실적 설치·사용 상황에서 요구되는 정도로 본다.</t>
+          <t>점유자는 손해 방지에 필요한 주의를 다하였음을 증명하면 면책되는 중간책임을 지고, 소유자는 면책이 인정되지 않는 무과실책임을 진다.</t>
         </is>
       </c>
       <c r="G1415" t="inlineStr">
         <is>
-          <t>대판 2018.7.12. 2015다68348 · 판례</t>
+          <t>민법 제758조 제1항</t>
         </is>
       </c>
       <c r="H1415" t="inlineStr">
@@ -57066,7 +57066,7 @@
     </row>
     <row r="1416">
       <c r="A1416" t="n">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
@@ -57075,38 +57075,38 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>공작물책임에서 공작물의 점유자는 자신의 과실 유무와 관계없이 책임을 지고, 소유자는 자신의 과실이 있는 경우에만 책임을 진다.</t>
+          <t>부동산 매매에서 매수인이 선이행하여야 할 중도금을 지급하지 않은 채 잔대금 지급일을 경과한 경우, 특별한 사정이 없는 한 매수인의 중도금 및 그에 대한 지연손해금과 잔대금 지급의무는 매도인의 소유권이전등기의무와 동시이행관계에 있다.</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>문28·점유자소유자책임</t>
+          <t>문29·중도금동시이행</t>
         </is>
       </c>
       <c r="F1416" t="inlineStr">
         <is>
-          <t>점유자는 손해 방지에 필요한 주의를 다하였음을 증명하면 면책되는 중간책임을 지고, 소유자는 면책이 인정되지 않는 무과실책임을 진다.</t>
+          <t>판례는 중도금 미지급 후 잔대금일이 지나면 중도금·지연손해금·잔대금 지급의무와 이전등기의무가 동시이행관계에 있다고 한다.</t>
         </is>
       </c>
       <c r="G1416" t="inlineStr">
         <is>
-          <t>민법 제758조 제1항</t>
+          <t>대판 1991.3.27. 90다19930</t>
         </is>
       </c>
       <c r="H1416" t="inlineStr">
         <is>
-          <t>제758조</t>
+          <t>제536조</t>
         </is>
       </c>
     </row>
     <row r="1417">
       <c r="A1417" t="n">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>부동산 매매에서 매수인이 선이행하여야 할 중도금을 지급하지 않은 채 잔대금 지급일을 경과한 경우, 특별한 사정이 없는 한 매수인의 중도금 및 그에 대한 지연손해금과 잔대금 지급의무는 매도인의 소유권이전등기의무와 동시이행관계에 있다.</t>
+          <t>동시이행관계에 있는 쌍방 채무 중 어느 한 채무가 이행불능이 되어 손해배상채무로 변한 경우, 그 손해배상채무도 다른 채무와 여전히 동시이행관계에 있다.</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
@@ -57125,17 +57125,17 @@
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>문29·중도금동시이행</t>
+          <t>문29·손배동시이행</t>
         </is>
       </c>
       <c r="F1417" t="inlineStr">
         <is>
-          <t>판례는 중도금 미지급 후 잔대금일이 지나면 중도금·지연손해금·잔대금 지급의무와 이전등기의무가 동시이행관계에 있다고 한다.</t>
+          <t>판례는 동시이행관계의 채무가 손해배상채무로 변경되어도 동일성이 유지되어 동시이행관계가 존속한다고 한다.</t>
         </is>
       </c>
       <c r="G1417" t="inlineStr">
         <is>
-          <t>대판 1991.3.27. 90다19930</t>
+          <t>대판 2000.2.25. 97다30066</t>
         </is>
       </c>
       <c r="H1417" t="inlineStr">
@@ -57146,7 +57146,7 @@
     </row>
     <row r="1418">
       <c r="A1418" t="n">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>동시이행관계에 있는 쌍방 채무 중 어느 한 채무가 이행불능이 되어 손해배상채무로 변한 경우, 그 손해배상채무도 다른 채무와 여전히 동시이행관계에 있다.</t>
+          <t>매수인이 매매대금을 완납하였다면 목적물을 아직 인도받지 못하였더라도 그 이후 목적물에서 생기는 과실의 수취권은 매수인에게 귀속된다.</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
@@ -57165,28 +57165,28 @@
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>문29·손배동시이행</t>
+          <t>문30·과실수취권</t>
         </is>
       </c>
       <c r="F1418" t="inlineStr">
         <is>
-          <t>판례는 동시이행관계의 채무가 손해배상채무로 변경되어도 동일성이 유지되어 동시이행관계가 존속한다고 한다.</t>
+          <t>민법 제587조에 따라 매수인이 대금을 완납하면 그 후의 과실수취권은 매수인에게 귀속된다.</t>
         </is>
       </c>
       <c r="G1418" t="inlineStr">
         <is>
-          <t>대판 2000.2.25. 97다30066</t>
+          <t>민법 제587조</t>
         </is>
       </c>
       <c r="H1418" t="inlineStr">
         <is>
-          <t>제536조</t>
+          <t>제587조</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="n">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
@@ -57195,38 +57195,38 @@
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>매수인이 매매대금을 완납하였다면 목적물을 아직 인도받지 못하였더라도 그 이후 목적물에서 생기는 과실의 수취권은 매수인에게 귀속된다.</t>
+          <t>매매목적물을 인도받지 못하고 매수인 자신도 대금을 지급하지 않은 경우, 매수인은 매도인에게 인도의무의 지체로 인한 손해배상금의 지급을 구할 수 있다.</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1419" t="inlineStr">
         <is>
-          <t>문30·과실수취권</t>
+          <t>문30·동시이행지체</t>
         </is>
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>민법 제587조에 따라 매수인이 대금을 완납하면 그 후의 과실수취권은 매수인에게 귀속된다.</t>
+          <t>매수인이 대금을 지급하지 않은 이상 매도인의 인도의무는 동시이행 항변으로 지체에 빠지지 않으므로 지체로 인한 손해배상을 구할 수 없다.</t>
         </is>
       </c>
       <c r="G1419" t="inlineStr">
         <is>
-          <t>민법 제587조</t>
+          <t>민법 제536조 · 제587조</t>
         </is>
       </c>
       <c r="H1419" t="inlineStr">
         <is>
-          <t>제587조</t>
+          <t>제536조</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
@@ -57235,38 +57235,38 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>매매목적물을 인도받지 못하고 매수인 자신도 대금을 지급하지 않은 경우, 매수인은 매도인에게 인도의무의 지체로 인한 손해배상금의 지급을 구할 수 있다.</t>
+          <t>상가건물 임대차에서 임차인이 임대차기간 중 3기의 차임액에 이르도록 차임을 연체한 사실이 있다면, 계약갱신 요구 당시 연체액이 3기에 이르지 않게 되었더라도 임대인은 그 갱신 요구를 거절할 수 있다.</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>문30·동시이행지체</t>
+          <t>문31·3기연체갱신</t>
         </is>
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>매수인이 대금을 지급하지 않은 이상 매도인의 인도의무는 동시이행 항변으로 지체에 빠지지 않으므로 지체로 인한 손해배상을 구할 수 없다.</t>
+          <t>판례는 과거에 3기 연체 사실이 있으면 갱신 요구 당시 연체가 해소되었어도 갱신거절 사유가 된다고 한다.</t>
         </is>
       </c>
       <c r="G1420" t="inlineStr">
         <is>
-          <t>민법 제536조 · 제587조</t>
+          <t>대판 2021.5.13. 2020다255429</t>
         </is>
       </c>
       <c r="H1420" t="inlineStr">
         <is>
-          <t>제536조</t>
+          <t>제640조</t>
         </is>
       </c>
     </row>
     <row r="1421">
       <c r="A1421" t="n">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>상가건물 임대차에서 임차인이 임대차기간 중 3기의 차임액에 이르도록 차임을 연체한 사실이 있다면, 계약갱신 요구 당시 연체액이 3기에 이르지 않게 되었더라도 임대인은 그 갱신 요구를 거절할 수 있다.</t>
+          <t>임대차보증금이 수수된 임대차에서 차임채권에 압류 및 추심명령이 있었더라도, 임대차가 종료되어 목적물이 반환될 때까지 추심되지 않은 차임채권액은 임대차보증금에서 당연히 공제된다.</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr">
@@ -57285,28 +57285,28 @@
       </c>
       <c r="E1421" t="inlineStr">
         <is>
-          <t>문31·3기연체갱신</t>
+          <t>문31·차임공제</t>
         </is>
       </c>
       <c r="F1421" t="inlineStr">
         <is>
-          <t>판례는 과거에 3기 연체 사실이 있으면 갱신 요구 당시 연체가 해소되었어도 갱신거절 사유가 된다고 한다.</t>
+          <t>판례는 차임채권에 압류·추심명령이 있어도 종료 시까지 미추심 차임은 보증금에서 당연 공제된다고 한다.</t>
         </is>
       </c>
       <c r="G1421" t="inlineStr">
         <is>
-          <t>대판 2021.5.13. 2020다255429</t>
+          <t>대판 2004.12.23. 2004다56554</t>
         </is>
       </c>
       <c r="H1421" t="inlineStr">
         <is>
-          <t>제640조</t>
+          <t>제618조</t>
         </is>
       </c>
     </row>
     <row r="1422">
       <c r="A1422" t="n">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
@@ -57315,38 +57315,38 @@
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>임대차보증금이 수수된 임대차에서 차임채권에 압류 및 추심명령이 있었더라도, 임대차가 종료되어 목적물이 반환될 때까지 추심되지 않은 차임채권액은 임대차보증금에서 당연히 공제된다.</t>
+          <t>자필증서에 의한 유언에서 유언자가 주소를 자서하지 않았더라도 유언자의 특정에 지장이 없다면 그 유언은 유효하다.</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>문31·차임공제</t>
+          <t>문32·자필증서주소</t>
         </is>
       </c>
       <c r="F1422" t="inlineStr">
         <is>
-          <t>판례는 차임채권에 압류·추심명령이 있어도 종료 시까지 미추심 차임은 보증금에서 당연 공제된다고 한다.</t>
+          <t>민법 제1066조는 자필증서 유언의 요건으로 주소의 자서를 요구하므로, 주소를 자서하지 않은 자필증서 유언은 무효이다.</t>
         </is>
       </c>
       <c r="G1422" t="inlineStr">
         <is>
-          <t>대판 2004.12.23. 2004다56554</t>
+          <t>민법 제1066조</t>
         </is>
       </c>
       <c r="H1422" t="inlineStr">
         <is>
-          <t>제618조</t>
+          <t>제1066조</t>
         </is>
       </c>
     </row>
     <row r="1423">
       <c r="A1423" t="n">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
@@ -57355,38 +57355,38 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>자필증서에 의한 유언에서 유언자가 주소를 자서하지 않았더라도 유언자의 특정에 지장이 없다면 그 유언은 유효하다.</t>
+          <t>유언증서가 성립한 후에 멸실되거나 분실되었더라도 유언자가 유언을 철회한 것으로 볼 수 없는 이상 그 사유만으로 유언이 실효되는 것은 아니고, 이해관계인은 유언증서의 내용을 증명하여 유언의 효력을 주장할 수 있다.</t>
         </is>
       </c>
       <c r="D1423" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>문32·자필증서주소</t>
+          <t>문32·유언증서멸실</t>
         </is>
       </c>
       <c r="F1423" t="inlineStr">
         <is>
-          <t>민법 제1066조는 자필증서 유언의 요건으로 주소의 자서를 요구하므로, 주소를 자서하지 않은 자필증서 유언은 무효이다.</t>
+          <t>판례는 유언증서의 멸실·분실만으로 유언이 실효되지 않고 내용을 증명하여 효력을 주장할 수 있다고 한다.</t>
         </is>
       </c>
       <c r="G1423" t="inlineStr">
         <is>
-          <t>민법 제1066조</t>
+          <t>대판 1996.9.20. 96다21119</t>
         </is>
       </c>
       <c r="H1423" t="inlineStr">
         <is>
-          <t>제1066조</t>
+          <t>제1060조</t>
         </is>
       </c>
     </row>
     <row r="1424">
       <c r="A1424" t="n">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
@@ -57395,38 +57395,38 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>유언증서가 성립한 후에 멸실되거나 분실되었더라도 유언자가 유언을 철회한 것으로 볼 수 없는 이상 그 사유만으로 유언이 실효되는 것은 아니고, 이해관계인은 유언증서의 내용을 증명하여 유언의 효력을 주장할 수 있다.</t>
+          <t>가정법원은 부 또는 모가 친권을 남용하여 자녀의 복리를 현저히 해치거나 해칠 우려가 있는 경우, 일정한 기간을 정하여 그 친권을 상실시킬 수 있다.</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>문32·유언증서멸실</t>
+          <t>문33·친권상실기간</t>
         </is>
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>판례는 유언증서의 멸실·분실만으로 유언이 실효되지 않고 내용을 증명하여 효력을 주장할 수 있다고 한다.</t>
+          <t>친권상실 선고에는 기간을 정하지 않으며, 기간을 정하여 제한하는 것은 친권의 일시 정지에 해당한다.</t>
         </is>
       </c>
       <c r="G1424" t="inlineStr">
         <is>
-          <t>대판 1996.9.20. 96다21119</t>
+          <t>민법 제924조</t>
         </is>
       </c>
       <c r="H1424" t="inlineStr">
         <is>
-          <t>제1060조</t>
+          <t>제924조</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="n">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>가정법원은 부 또는 모가 친권을 남용하여 자녀의 복리를 현저히 해치거나 해칠 우려가 있는 경우, 일정한 기간을 정하여 그 친권을 상실시킬 수 있다.</t>
+          <t>상속재산분할에 관하여 공동상속인 사이에 협의가 성립되지 않거나 협의할 수 없는 경우, 각 공동상속인은 상속재산에 속하는 개별 재산에 관하여 공유물분할청구의 소를 제기할 수 있다.</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -57445,28 +57445,28 @@
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>문33·친권상실기간</t>
+          <t>문34·상속공유물분할</t>
         </is>
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>친권상실 선고에는 기간을 정하지 않으며, 기간을 정하여 제한하는 것은 친권의 일시 정지에 해당한다.</t>
+          <t>상속재산분할은 가사비송인 상속재산분할심판에 의하여야 하고, 개별 재산에 관한 공유물분할청구의 소로 할 수 없다.</t>
         </is>
       </c>
       <c r="G1425" t="inlineStr">
         <is>
-          <t>민법 제924조</t>
+          <t>대판 2015.8.13. 2015다18367</t>
         </is>
       </c>
       <c r="H1425" t="inlineStr">
         <is>
-          <t>제924조</t>
+          <t>제1013조</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
@@ -57475,38 +57475,38 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>상속재산분할에 관하여 공동상속인 사이에 협의가 성립되지 않거나 협의할 수 없는 경우, 각 공동상속인은 상속재산에 속하는 개별 재산에 관하여 공유물분할청구의 소를 제기할 수 있다.</t>
+          <t>협의분할로 공동상속인 중 일부가 자기 고유의 상속분을 초과하여 상속재산을 취득한 경우, 이는 상속개시 당시에 소급하여 피상속인으로부터 승계받은 것으로 보아야 하고 다른 공동상속인으로부터 증여받은 것으로 볼 수 없다.</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>문34·상속공유물분할</t>
+          <t>문34·협의분할소급</t>
         </is>
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>상속재산분할은 가사비송인 상속재산분할심판에 의하여야 하고, 개별 재산에 관한 공유물분할청구의 소로 할 수 없다.</t>
+          <t>민법 제1015조에 따라 상속재산분할은 상속개시 시로 소급하여 효력이 있으므로 증여로 보지 않는다.</t>
         </is>
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>대판 2015.8.13. 2015다18367</t>
+          <t>민법 제1015조</t>
         </is>
       </c>
       <c r="H1426" t="inlineStr">
         <is>
-          <t>제1013조</t>
+          <t>제1015조</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="n">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>협의분할로 공동상속인 중 일부가 자기 고유의 상속분을 초과하여 상속재산을 취득한 경우, 이는 상속개시 당시에 소급하여 피상속인으로부터 승계받은 것으로 보아야 하고 다른 공동상속인으로부터 증여받은 것으로 볼 수 없다.</t>
+          <t>이혼에 따른 재산분할에서 일방이 제3자와 합유하는 재산은 임의로 처분할 수 없어 직접 분할을 명할 수는 없으나, 그 지분의 가액을 산정하여 분할 대상으로 삼거나 다른 재산의 분할에 참작하는 방법으로 분할 대상에 포함하여야 한다.</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -57525,28 +57525,28 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>문34·협의분할소급</t>
+          <t>문35·합유재산분할</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
         <is>
-          <t>민법 제1015조에 따라 상속재산분할은 상속개시 시로 소급하여 효력이 있으므로 증여로 보지 않는다.</t>
+          <t>판례는 합유재산은 직접 분할을 명할 수 없으나 지분 가액을 산정하여 재산분할에 참작하여야 한다고 한다.</t>
         </is>
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>민법 제1015조</t>
+          <t>대판 2009.11.12. 2009므2840</t>
         </is>
       </c>
       <c r="H1427" t="inlineStr">
         <is>
-          <t>제1015조</t>
+          <t>제839조의2</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>이혼에 따른 재산분할에서 일방이 제3자와 합유하는 재산은 임의로 처분할 수 없어 직접 분할을 명할 수는 없으나, 그 지분의 가액을 산정하여 분할 대상으로 삼거나 다른 재산의 분할에 참작하는 방법으로 분할 대상에 포함하여야 한다.</t>
+          <t>이혼에 따른 재산분할 사건에서 법원은 당사자가 특정한 분할 방법에 구애받지 않고 재산분할의 대상과 가액을 직권으로 조사·판단할 수 있다.</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -57565,17 +57565,17 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>문35·합유재산분할</t>
+          <t>문35·직권조사</t>
         </is>
       </c>
       <c r="F1428" t="inlineStr">
         <is>
-          <t>판례는 합유재산은 직접 분할을 명할 수 없으나 지분 가액을 산정하여 재산분할에 참작하여야 한다고 한다.</t>
+          <t>재산분할은 가사비송사건으로 법원이 후견적 입장에서 직권으로 대상과 가액을 조사·판단한다.</t>
         </is>
       </c>
       <c r="G1428" t="inlineStr">
         <is>
-          <t>대판 2009.11.12. 2009므2840</t>
+          <t>대판 2022.1.27. 2018므11273 · 판례</t>
         </is>
       </c>
       <c r="H1428" t="inlineStr">
@@ -57586,7 +57586,7 @@
     </row>
     <row r="1429">
       <c r="A1429" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
@@ -57595,27 +57595,27 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>이혼에 따른 재산분할 사건에서 법원은 당사자가 특정한 분할 방법에 구애받지 않고 재산분할의 대상과 가액을 직권으로 조사·판단할 수 있다.</t>
+          <t>재산분할청구권은 이혼이 성립한 때 법적 효과로서 발생하므로, 협의나 심판에 의하여 그 구체적 내용이 형성되기 전이라도 이혼 성립 후에는 곧바로 채권양도의 대상이 된다.</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>문35·직권조사</t>
+          <t>문35·분할청구권양도</t>
         </is>
       </c>
       <c r="F1429" t="inlineStr">
         <is>
-          <t>재산분할은 가사비송사건으로 법원이 후견적 입장에서 직권으로 대상과 가액을 조사·판단한다.</t>
+          <t>협의나 심판으로 구체적 내용이 형성되기 전의 재산분할청구권은 범위와 내용이 불명확하여 양도의 대상이 될 수 없다.</t>
         </is>
       </c>
       <c r="G1429" t="inlineStr">
         <is>
-          <t>대판 2022.1.27. 2018므11273 · 판례</t>
+          <t>대판 1999.4.9. 98다58016</t>
         </is>
       </c>
       <c r="H1429" t="inlineStr">
@@ -57626,7 +57626,7 @@
     </row>
     <row r="1430">
       <c r="A1430" t="n">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
@@ -57635,32 +57635,232 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>재산분할청구권은 이혼이 성립한 때 법적 효과로서 발생하므로, 협의나 심판에 의하여 그 구체적 내용이 형성되기 전이라도 이혼 성립 후에는 곧바로 채권양도의 대상이 된다.</t>
+          <t>손해배상 예정액이 부당히 과다한지 여부는 계약 당시가 아니라 사실심 변론종결 당시를 기준으로 판단하여야 한다.</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>문21·감액기준시</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>판례는 손해배상 예정액의 과다 여부를 사실심 변론종결 시를 기준으로 판단한다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>대판 2017.8.18. 2017다228762 · 판례</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>위약벌의 약정은 손해배상액의 예정과 그 내용이 다르므로, 민법 제398조 제2항을 유추적용하여 그 액을 감액할 수 없다.</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>문21·위약벌감액</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>판례는 위약벌은 손해배상액의 예정과 달라 제398조 제2항에 의한 직권 감액의 대상이 아니라고 한다(공서양속 위반 시 일부 무효만 가능).</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>대판 2016.1.28. 2015다239324</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정된 경우, 채무불이행으로 인한 손해의 발생·확대에 채권자의 과실이 있더라도 제398조 제2항에 따른 감액과는 별도로 과실상계를 적용하여 직권으로 감경하여야 한다.</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E1430" t="inlineStr">
-        <is>
-          <t>문35·분할청구권양도</t>
-        </is>
-      </c>
-      <c r="F1430" t="inlineStr">
-        <is>
-          <t>협의나 심판으로 구체적 내용이 형성되기 전의 재산분할청구권은 범위와 내용이 불명확하여 양도의 대상이 될 수 없다.</t>
-        </is>
-      </c>
-      <c r="G1430" t="inlineStr">
-        <is>
-          <t>대판 1999.4.9. 98다58016</t>
-        </is>
-      </c>
-      <c r="H1430" t="inlineStr">
-        <is>
-          <t>제839조의2</t>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>문21·예정액과실상계</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>손해배상액이 예정된 경우에는 과실상계를 따로 적용할 수 없고, 예정액이 부당히 과다하면 제398조 제2항에 의한 직권 감액만 할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>대판 2016.6.10. 2014다200763</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>제398조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>전세권이 존속하는 동안은 전세권을 존속시키기로 하면서 전세금반환채권만을 전세권과 분리하여 확정적으로 양도하는 것은 허용되지 않으며, 이는 임대차보증금반환채권을 담보하기 위하여 설정된 전세권에 관하여도 동일하게 적용된다.</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>문22·전세금채권분리양도</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>판례는 전세권 존속 중 전세금반환채권만의 확정적 분리양도를 허용하지 않으며 담보 목적 전세권에도 동일하게 본다.</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>대판 2002.8.23. 2001다69122 · 판례</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>제303조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>전세권설정자가 전세권 소멸 후 전세권자로부터 목적물을 인도받았더라도, 전세권설정등기의 말소에 필요한 서류를 교부받기 전까지는 전세금 반환을 거부하더라도 특별한 사정이 없는 한 전세금에 대한 이자 상당액을 부당이득으로 반환할 의무가 없다.</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>문22·전세금동시이행</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>전세금 반환의무와 전세권설정등기 말소서류 교부의무는 동시이행관계이므로, 목적물을 인도받았더라도 말소서류를 받기 전에는 이자 상당 부당이득 반환의무가 없다.</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>대판 2002.2.5. 2001다62091</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>제317조</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>변시15</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>전세권이 존속기간의 만료로 소멸한 경우, 전세금반환채권 양도계약 당사자 간의 특약에 따라 채권양수인은 담보물권이 없는 무담보의 전세금반환채권을 유효하게 취득할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>문22·무담보채권양수</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>판례는 존속기간 만료로 전세권이 소멸한 경우 특약에 의하여 전세권과 분리된 무담보의 전세금반환채권을 양수할 수 있다고 한다.</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>대판 1997.11.25. 97다29790 · 판례</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>제303조</t>
         </is>
       </c>
     </row>
